--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AF4" headerRowCount="1">
-  <autoFilter ref="A1:AF4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AF9" headerRowCount="1">
+  <autoFilter ref="A1:AF9"/>
   <tableColumns count="32">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="game_week"/>
@@ -466,13 +466,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF4"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="13.2" customWidth="1" min="2" max="2"/>
-    <col width="21.6" customWidth="1" min="3" max="3"/>
-    <col width="22.8" customWidth="1" min="4" max="4"/>
+    <col width="28.8" customWidth="1" min="3" max="3"/>
+    <col width="26.4" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
@@ -668,7 +668,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-12 21:00:00</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -676,207 +676,207 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>La Equidad</t>
+          <t>Llaneros</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.53</v>
+        <v>1.15</v>
       </c>
       <c r="F2" t="n">
-        <v>1.18</v>
+        <v>0.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="J2" t="n">
         <v>44</v>
       </c>
       <c r="K2" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M2" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="N2" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="O2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB2" t="n">
         <v>1.9</v>
       </c>
-      <c r="R2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
       <c r="AC2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-12 23:30:00</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6</v>
+        <v>1.34</v>
       </c>
       <c r="G3" t="n">
-        <v>1.81</v>
+        <v>1.23</v>
       </c>
       <c r="H3" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="I3" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="J3" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="K3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L3" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="M3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="O3" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="P3" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="R3" t="n">
-        <v>3.23</v>
+        <v>3.08</v>
       </c>
       <c r="S3" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="U3" t="n">
         <v>2.15</v>
       </c>
       <c r="V3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="W3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.93</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.03</v>
       </c>
       <c r="AC3" t="n">
         <v>1.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-13 01:20:00</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -884,97 +884,617 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boyacá Chicó</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Alianza Petrolera</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.92</v>
+        <v>1.64</v>
       </c>
       <c r="F4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>2.61</v>
+        <v>2.71</v>
       </c>
       <c r="J4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N4" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O4" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="P4" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.84</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="U4" t="n">
         <v>1.96</v>
       </c>
       <c r="V4" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="J5" t="n">
+        <v>46</v>
+      </c>
+      <c r="K5" t="n">
+        <v>63</v>
+      </c>
+      <c r="L5" t="n">
+        <v>23</v>
+      </c>
+      <c r="M5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N5" t="n">
+        <v>71</v>
+      </c>
+      <c r="O5" t="n">
+        <v>37</v>
+      </c>
+      <c r="P5" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.88</v>
       </c>
-      <c r="Y4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AC5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J6" t="n">
+        <v>48</v>
+      </c>
+      <c r="K6" t="n">
+        <v>80</v>
+      </c>
+      <c r="L6" t="n">
+        <v>31</v>
+      </c>
+      <c r="M6" t="n">
+        <v>31</v>
+      </c>
+      <c r="N6" t="n">
+        <v>70</v>
+      </c>
+      <c r="O6" t="n">
+        <v>44</v>
+      </c>
+      <c r="P6" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>20</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J7" t="n">
+        <v>55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>75</v>
+      </c>
+      <c r="L7" t="n">
+        <v>33</v>
+      </c>
+      <c r="M7" t="n">
+        <v>28</v>
+      </c>
+      <c r="N7" t="n">
+        <v>72</v>
+      </c>
+      <c r="O7" t="n">
+        <v>51</v>
+      </c>
+      <c r="P7" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA7" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AB7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J8" t="n">
+        <v>53</v>
+      </c>
+      <c r="K8" t="n">
+        <v>66</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32</v>
+      </c>
+      <c r="M8" t="n">
+        <v>35</v>
+      </c>
+      <c r="N8" t="n">
+        <v>66</v>
+      </c>
+      <c r="O8" t="n">
+        <v>43</v>
+      </c>
+      <c r="P8" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.36</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Unión Magdalena</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J9" t="n">
+        <v>48</v>
+      </c>
+      <c r="K9" t="n">
+        <v>56</v>
+      </c>
+      <c r="L9" t="n">
+        <v>26</v>
+      </c>
+      <c r="M9" t="n">
+        <v>34</v>
+      </c>
+      <c r="N9" t="n">
+        <v>67</v>
+      </c>
+      <c r="O9" t="n">
+        <v>39</v>
+      </c>
+      <c r="P9" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -721,19 +721,19 @@
         <v>60</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="R2" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>1.33</v>
       </c>
       <c r="U2" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
         <v>3.9</v>
@@ -742,28 +742,28 @@
         <v>2.17</v>
       </c>
       <c r="X2" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AA2" t="n">
         <v>1.53</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AD2" t="n">
         <v>3.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AF2" t="n">
         <v>1.3</v>
@@ -825,46 +825,46 @@
         <v>60</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="R3" t="n">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
         <v>1.36</v>
       </c>
       <c r="U3" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
         <v>4.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC3" t="n">
         <v>1.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>2.7</v>
@@ -929,28 +929,28 @@
         <v>58</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="U4" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="V4" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="W4" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="X4" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Y4" t="n">
         <v>2.36</v>
@@ -959,7 +959,7 @@
         <v>1.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
         <v>1.89</v>
@@ -971,10 +971,10 @@
         <v>2.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="5">
@@ -1033,52 +1033,52 @@
         <v>64</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="S5" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="U5" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
         <v>3.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="X5" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="Z5" t="n">
         <v>1.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AC5" t="n">
         <v>1.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AE5" t="n">
         <v>2.69</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="6">
@@ -1137,22 +1137,22 @@
         <v>57</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="R6" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="S6" t="n">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="T6" t="n">
         <v>1.4</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="V6" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="W6" t="n">
         <v>1.93</v>
@@ -1173,7 +1173,7 @@
         <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AD6" t="n">
         <v>3</v>
@@ -1182,7 +1182,7 @@
         <v>2.65</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7">
@@ -1241,31 +1241,31 @@
         <v>49</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="S7" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="V7" t="n">
         <v>2.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="Z7" t="n">
         <v>1.72</v>
@@ -1277,7 +1277,7 @@
         <v>2.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AD7" t="n">
         <v>2.38</v>
@@ -1357,40 +1357,40 @@
         <v>1.36</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V8" t="n">
-        <v>4.08</v>
+        <v>4.03</v>
       </c>
       <c r="W8" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="X8" t="n">
         <v>1.83</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Z8" t="n">
         <v>1.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB8" t="n">
         <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AE8" t="n">
         <v>2.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="9">
@@ -1449,34 +1449,34 @@
         <v>61</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="U9" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="V9" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.75</v>
       </c>
       <c r="X9" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AA9" t="n">
         <v>1.67</v>
@@ -1485,16 +1485,16 @@
         <v>2.46</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,41 +137,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AF9" headerRowCount="1">
-  <autoFilter ref="A1:AF9"/>
-  <tableColumns count="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG9" headerRowCount="1">
+  <autoFilter ref="A1:AG9"/>
+  <tableColumns count="33">
     <tableColumn id="1" name="date"/>
-    <tableColumn id="2" name="game_week"/>
-    <tableColumn id="3" name="home_name"/>
-    <tableColumn id="4" name="away_name"/>
-    <tableColumn id="5" name="pre_match_home_ppg"/>
-    <tableColumn id="6" name="pre_match_away_ppg"/>
-    <tableColumn id="7" name="team_a_xg_prematch"/>
-    <tableColumn id="8" name="team_b_xg_prematch"/>
-    <tableColumn id="9" name="total_xg_prematch"/>
-    <tableColumn id="10" name="btts_potential"/>
-    <tableColumn id="11" name="o05HT_potential"/>
-    <tableColumn id="12" name="o15HT_potential"/>
-    <tableColumn id="13" name="u15_potential"/>
-    <tableColumn id="14" name="o15_potential"/>
-    <tableColumn id="15" name="o25_potential"/>
-    <tableColumn id="16" name="u25_potential"/>
-    <tableColumn id="17" name="odds_ft_1"/>
-    <tableColumn id="18" name="odds_ft_x"/>
-    <tableColumn id="19" name="odds_ft_2"/>
-    <tableColumn id="20" name="odds_ft_over15"/>
-    <tableColumn id="21" name="odds_ft_over25"/>
-    <tableColumn id="22" name="odds_ft_over35"/>
-    <tableColumn id="23" name="odds_btts_yes"/>
-    <tableColumn id="24" name="odds_btts_no"/>
-    <tableColumn id="25" name="odds_corners_under_85"/>
-    <tableColumn id="26" name="odds_corners_under_95"/>
-    <tableColumn id="27" name="odds_corners_over_85"/>
-    <tableColumn id="28" name="odds_corners_over_95"/>
-    <tableColumn id="29" name="odds_1st_half_over05"/>
-    <tableColumn id="30" name="odds_1st_half_over15"/>
-    <tableColumn id="31" name="odds_1st_half_under05"/>
-    <tableColumn id="32" name="odds_1st_half_under15"/>
+    <tableColumn id="2" name="league"/>
+    <tableColumn id="3" name="game_week"/>
+    <tableColumn id="4" name="home_name"/>
+    <tableColumn id="5" name="away_name"/>
+    <tableColumn id="6" name="pre_match_home_ppg"/>
+    <tableColumn id="7" name="pre_match_away_ppg"/>
+    <tableColumn id="8" name="team_a_xg_prematch"/>
+    <tableColumn id="9" name="team_b_xg_prematch"/>
+    <tableColumn id="10" name="total_xg_prematch"/>
+    <tableColumn id="11" name="btts_potential"/>
+    <tableColumn id="12" name="o05HT_potential"/>
+    <tableColumn id="13" name="o15HT_potential"/>
+    <tableColumn id="14" name="u15_potential"/>
+    <tableColumn id="15" name="o15_potential"/>
+    <tableColumn id="16" name="o25_potential"/>
+    <tableColumn id="17" name="u25_potential"/>
+    <tableColumn id="18" name="odds_ft_1"/>
+    <tableColumn id="19" name="odds_ft_x"/>
+    <tableColumn id="20" name="odds_ft_2"/>
+    <tableColumn id="21" name="odds_ft_over15"/>
+    <tableColumn id="22" name="odds_ft_over25"/>
+    <tableColumn id="23" name="odds_ft_over35"/>
+    <tableColumn id="24" name="odds_btts_yes"/>
+    <tableColumn id="25" name="odds_btts_no"/>
+    <tableColumn id="26" name="odds_corners_under_85"/>
+    <tableColumn id="27" name="odds_corners_under_95"/>
+    <tableColumn id="28" name="odds_corners_over_85"/>
+    <tableColumn id="29" name="odds_corners_over_95"/>
+    <tableColumn id="30" name="odds_1st_half_over05"/>
+    <tableColumn id="31" name="odds_1st_half_over15"/>
+    <tableColumn id="32" name="odds_1st_half_under05"/>
+    <tableColumn id="33" name="odds_1st_half_under15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -466,41 +467,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AG9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="13.2" customWidth="1" min="2" max="2"/>
-    <col width="28.8" customWidth="1" min="3" max="3"/>
-    <col width="26.4" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="13.2" customWidth="1" min="3" max="3"/>
+    <col width="28.8" customWidth="1" min="4" max="4"/>
+    <col width="26.4" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="22.8" customWidth="1" min="9" max="9"/>
-    <col width="19.2" customWidth="1" min="10" max="10"/>
-    <col width="20.4" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="22.8" customWidth="1" min="10" max="10"/>
+    <col width="19.2" customWidth="1" min="11" max="11"/>
     <col width="20.4" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="20.4" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="13.2" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
     <col width="13.2" customWidth="1" min="18" max="18"/>
     <col width="13.2" customWidth="1" min="19" max="19"/>
-    <col width="19.2" customWidth="1" min="20" max="20"/>
+    <col width="13.2" customWidth="1" min="20" max="20"/>
     <col width="19.2" customWidth="1" min="21" max="21"/>
     <col width="19.2" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="16.8" customWidth="1" min="24" max="24"/>
-    <col width="27.6" customWidth="1" min="25" max="25"/>
+    <col width="19.2" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="16.8" customWidth="1" min="25" max="25"/>
     <col width="27.6" customWidth="1" min="26" max="26"/>
-    <col width="26.4" customWidth="1" min="27" max="27"/>
+    <col width="27.6" customWidth="1" min="27" max="27"/>
     <col width="26.4" customWidth="1" min="28" max="28"/>
     <col width="26.4" customWidth="1" min="29" max="29"/>
     <col width="26.4" customWidth="1" min="30" max="30"/>
-    <col width="27.6" customWidth="1" min="31" max="31"/>
+    <col width="26.4" customWidth="1" min="31" max="31"/>
     <col width="27.6" customWidth="1" min="32" max="32"/>
+    <col width="27.6" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,155 +513,160 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>game_week</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>home_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>away_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pre_match_home_ppg</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pre_match_away_ppg</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>team_a_xg_prematch</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>team_b_xg_prematch</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total_xg_prematch</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>btts_potential</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>o05HT_potential</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>o15HT_potential</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>u15_potential</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>o15_potential</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>o25_potential</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>u25_potential</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>odds_ft_1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>odds_ft_x</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>odds_ft_2</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>odds_ft_over15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>odds_ft_over25</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>odds_ft_over35</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>odds_btts_yes</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>odds_btts_no</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>odds_corners_under_85</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>odds_corners_under_95</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>odds_corners_over_85</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>odds_corners_over_95</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>odds_1st_half_under15</t>
         </is>
@@ -671,101 +678,106 @@
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Colombia Categoria Primera A</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>20</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Llaneros</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Envigado</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>1.15</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.9</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1.06</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1.1</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2.16</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>44</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>63</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>30</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>44</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>40</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>60</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.62</v>
-      </c>
       <c r="R2" t="n">
-        <v>3.7</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.33</v>
       </c>
-      <c r="U2" t="n">
-        <v>2.12</v>
-      </c>
       <c r="V2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="W2" t="n">
         <v>3.9</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>2.17</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>1.68</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>2.31</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>1.78</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>1.53</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>1.89</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>1.38</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>3.1</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>2.75</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -775,101 +787,106 @@
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Colombia Categoria Primera A</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>20</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Deportivo Cali</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Once Caldas</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>1.13</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>1.34</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1.23</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1.39</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2.62</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>42</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>67</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>28</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>40</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>60</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>41</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>60</v>
       </c>
-      <c r="Q3" t="n">
-        <v>2.13</v>
-      </c>
       <c r="R3" t="n">
-        <v>2.87</v>
+        <v>1.83</v>
       </c>
       <c r="S3" t="n">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.36</v>
       </c>
-      <c r="U3" t="n">
-        <v>2.2</v>
-      </c>
       <c r="V3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W3" t="n">
         <v>4.2</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>1.86</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>1.82</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>2.24</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>1.77</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>1.94</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>3</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>2.7</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
         <v>1.35</v>
       </c>
     </row>
@@ -879,101 +896,106 @@
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Colombia Categoria Primera A</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>20</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Santa Fe</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Alianza Petrolera</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>1.64</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1.49</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1.32</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>1.39</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2.71</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>45</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>61</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>29</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>36</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>64</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>42</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>58</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.9</v>
       </c>
-      <c r="R4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="V4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>2.36</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>1.78</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>1.89</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>2.9</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>2.8</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -983,101 +1005,106 @@
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Colombia Categoria Primera A</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>20</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Independiente Medellín</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>América de Cali</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1.79</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1.71</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1.66</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1.53</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>3.19</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>46</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>63</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>23</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>30</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>71</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>37</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>64</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.63</v>
-      </c>
       <c r="R5" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.29</v>
       </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
       <c r="V5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="W5" t="n">
         <v>3.28</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>1.88</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>1.82</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>2.22</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>1.75</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>1.58</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>1.92</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>2.65</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>2.69</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>1.41</v>
       </c>
     </row>
@@ -1087,101 +1114,106 @@
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Colombia Categoria Primera A</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>20</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Deportivo Pasto</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Atlético Bucaramanga</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1.15</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1.69</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1.21</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>1.44</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>2.65</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>48</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>80</v>
-      </c>
-      <c r="L6" t="n">
-        <v>31</v>
       </c>
       <c r="M6" t="n">
         <v>31</v>
       </c>
       <c r="N6" t="n">
+        <v>31</v>
+      </c>
+      <c r="O6" t="n">
         <v>70</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>44</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>57</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.75</v>
-      </c>
       <c r="R6" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.03</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.4</v>
       </c>
-      <c r="U6" t="n">
-        <v>2.21</v>
-      </c>
       <c r="V6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W6" t="n">
         <v>3.82</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>1.93</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>1.79</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>1.98</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>1.65</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>2.15</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>1.38</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>3</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
         <v>2.65</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AG6" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -1191,101 +1223,106 @@
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Colombia Categoria Primera A</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>20</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Junior</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Atlético Nacional</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>1.56</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1.29</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>1.7</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>2.99</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>55</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>75</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>33</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>28</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>72</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>51</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>49</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.32</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>1.26</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>2.38</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
         <v>3.3</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1295,101 +1332,106 @@
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Colombia Categoria Primera A</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>20</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Rionegro Águilas</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Deportes Tolima</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1.23</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>1.76</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1.32</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>1.33</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>2.65</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>53</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>66</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>32</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>35</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>66</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>43</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>57</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3.1</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>2.82</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>2.26</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>1.36</v>
       </c>
-      <c r="U8" t="n">
-        <v>2.14</v>
-      </c>
       <c r="V8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W8" t="n">
         <v>4.03</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>1.95</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>1.83</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>2.23</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>1.83</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>1.58</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>1.49</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>2.9</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
         <v>2.7</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
         <v>1.35</v>
       </c>
     </row>
@@ -1399,101 +1441,106 @@
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Colombia Categoria Primera A</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>20</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Unión Magdalena</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0.76</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>1.41</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1.23</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>1.31</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>2.54</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>48</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>56</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>26</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>34</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>67</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>39</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>61</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2.7</v>
-      </c>
       <c r="R9" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="S9" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="T9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.31</v>
       </c>
-      <c r="U9" t="n">
-        <v>2.11</v>
-      </c>
       <c r="V9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W9" t="n">
         <v>3.5</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>1.75</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>1.89</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>2.08</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>1.66</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>2.46</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>1.42</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>2.9</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
         <v>2.62</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
         <v>1.35</v>
       </c>
     </row>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG9" headerRowCount="1">
-  <autoFilter ref="A1:AG9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG4" headerRowCount="1">
+  <autoFilter ref="A1:AG4"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG9"/>
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="33.6" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="28.8" customWidth="1" min="4" max="4"/>
-    <col width="26.4" customWidth="1" min="5" max="5"/>
+    <col width="20.4" customWidth="1" min="4" max="4"/>
+    <col width="21.6" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,107 +675,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>2025-11-14 19:30:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Colombia Categoria Primera A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Llaneros</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9</v>
+        <v>1.67</v>
       </c>
       <c r="H2" t="n">
-        <v>1.06</v>
+        <v>1.93</v>
       </c>
       <c r="I2" t="n">
         <v>1.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2.16</v>
+        <v>3.03</v>
       </c>
       <c r="K2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L2" t="n">
+        <v>60</v>
+      </c>
+      <c r="M2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O2" t="n">
+        <v>52</v>
+      </c>
+      <c r="P2" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q2" t="n">
         <v>63</v>
       </c>
-      <c r="M2" t="n">
-        <v>30</v>
-      </c>
-      <c r="N2" t="n">
-        <v>44</v>
-      </c>
-      <c r="O2" t="n">
-        <v>56</v>
-      </c>
-      <c r="P2" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>60</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>3.07</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>3.32</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="V2" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="W2" t="n">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="X2" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AG2" t="n">
         <v>1.3</v>
@@ -784,764 +784,219 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>2025-11-14 23:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Colombia Categoria Primera A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.13</v>
+        <v>0.67</v>
       </c>
       <c r="G3" t="n">
-        <v>1.34</v>
+        <v>0.39</v>
       </c>
       <c r="H3" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="I3" t="n">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="J3" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M3" t="n">
         <v>42</v>
       </c>
-      <c r="L3" t="n">
-        <v>67</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>28</v>
       </c>
-      <c r="N3" t="n">
-        <v>40</v>
-      </c>
       <c r="O3" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="P3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q3" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="S3" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="W3" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="X3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.86</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.82</v>
-      </c>
       <c r="Z3" t="n">
-        <v>2.24</v>
+        <v>2.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>2025-11-14 23:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Colombia Categoria Primera A</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alianza Petrolera</t>
+          <t>Atlético Tucumán</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="G4" t="n">
-        <v>1.49</v>
+        <v>0.33</v>
       </c>
       <c r="H4" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="I4" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="J4" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="K4" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L4" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="N4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O4" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="P4" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="Q4" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="S4" t="n">
         <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="U4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="W4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.28</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Colombia Categoria Primera A</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Independiente Medellín</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>América de Cali</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="K5" t="n">
-        <v>46</v>
-      </c>
-      <c r="L5" t="n">
-        <v>63</v>
-      </c>
-      <c r="M5" t="n">
-        <v>23</v>
-      </c>
-      <c r="N5" t="n">
-        <v>30</v>
-      </c>
-      <c r="O5" t="n">
-        <v>71</v>
-      </c>
-      <c r="P5" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>64</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Colombia Categoria Primera A</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Deportivo Pasto</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="K6" t="n">
-        <v>48</v>
-      </c>
-      <c r="L6" t="n">
-        <v>80</v>
-      </c>
-      <c r="M6" t="n">
-        <v>31</v>
-      </c>
-      <c r="N6" t="n">
-        <v>31</v>
-      </c>
-      <c r="O6" t="n">
-        <v>70</v>
-      </c>
-      <c r="P6" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>57</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W6" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Colombia Categoria Primera A</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>20</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Atlético Nacional</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="K7" t="n">
-        <v>55</v>
-      </c>
-      <c r="L7" t="n">
-        <v>75</v>
-      </c>
-      <c r="M7" t="n">
-        <v>33</v>
-      </c>
-      <c r="N7" t="n">
-        <v>28</v>
-      </c>
-      <c r="O7" t="n">
-        <v>72</v>
-      </c>
-      <c r="P7" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>49</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Colombia Categoria Primera A</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>20</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Rionegro Águilas</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Deportes Tolima</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="K8" t="n">
-        <v>53</v>
-      </c>
-      <c r="L8" t="n">
-        <v>66</v>
-      </c>
-      <c r="M8" t="n">
-        <v>32</v>
-      </c>
-      <c r="N8" t="n">
-        <v>35</v>
-      </c>
-      <c r="O8" t="n">
-        <v>66</v>
-      </c>
-      <c r="P8" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>57</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="W8" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Colombia Categoria Primera A</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>20</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Unión Magdalena</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Fortaleza CEIF</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K9" t="n">
-        <v>48</v>
-      </c>
-      <c r="L9" t="n">
-        <v>56</v>
-      </c>
-      <c r="M9" t="n">
-        <v>26</v>
-      </c>
-      <c r="N9" t="n">
-        <v>34</v>
-      </c>
-      <c r="O9" t="n">
-        <v>67</v>
-      </c>
-      <c r="P9" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>61</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG4" headerRowCount="1">
-  <autoFilter ref="A1:AG4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG17" headerRowCount="1">
+  <autoFilter ref="A1:AG17"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AG17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="33.6" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="20.4" customWidth="1" min="4" max="4"/>
-    <col width="21.6" customWidth="1" min="5" max="5"/>
+    <col width="22.8" customWidth="1" min="4" max="4"/>
+    <col width="25.2" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,7 +675,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-14 19:30:00</t>
+          <t>2025-11-15 15:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -688,315 +688,1732 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="G2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.67</v>
       </c>
-      <c r="H2" t="n">
-        <v>1.93</v>
-      </c>
       <c r="I2" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="J2" t="n">
-        <v>3.03</v>
+        <v>3.21</v>
       </c>
       <c r="K2" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="L2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="P2" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="Q2" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="S2" t="n">
-        <v>3.07</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.45</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="W2" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-14 23:00:00</t>
+          <t>2025-11-15 15:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="G3" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="I3" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="J3" t="n">
-        <v>2.58</v>
+        <v>2.95</v>
       </c>
       <c r="K3" t="n">
         <v>59</v>
       </c>
       <c r="L3" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="M3" t="n">
+        <v>25</v>
+      </c>
+      <c r="N3" t="n">
         <v>42</v>
       </c>
-      <c r="N3" t="n">
-        <v>28</v>
-      </c>
       <c r="O3" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="P3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Q3" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="R3" t="n">
-        <v>2.18</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.07</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.98</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="V3" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="W3" t="n">
-        <v>3.84</v>
+        <v>2.51</v>
       </c>
       <c r="X3" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.83</v>
+        <v>2.31</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.71</v>
+        <v>3.22</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-14 23:00:00</t>
+          <t>2025-11-15 17:45:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K4" t="n">
+        <v>44</v>
+      </c>
+      <c r="L4" t="n">
+        <v>69</v>
+      </c>
+      <c r="M4" t="n">
+        <v>44</v>
+      </c>
+      <c r="N4" t="n">
+        <v>44</v>
+      </c>
+      <c r="O4" t="n">
+        <v>57</v>
+      </c>
+      <c r="P4" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>57</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-11-15 19:30:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>37</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K5" t="n">
+        <v>36</v>
+      </c>
+      <c r="L5" t="n">
+        <v>56</v>
+      </c>
+      <c r="M5" t="n">
+        <v>36</v>
+      </c>
+      <c r="N5" t="n">
+        <v>39</v>
+      </c>
+      <c r="O5" t="n">
+        <v>62</v>
+      </c>
+      <c r="P5" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>64</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-11-15 19:30:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>37</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K6" t="n">
+        <v>47</v>
+      </c>
+      <c r="L6" t="n">
+        <v>62</v>
+      </c>
+      <c r="M6" t="n">
+        <v>39</v>
+      </c>
+      <c r="N6" t="n">
+        <v>31</v>
+      </c>
+      <c r="O6" t="n">
+        <v>70</v>
+      </c>
+      <c r="P6" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>59</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-11-15 19:30:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>37</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K7" t="n">
+        <v>64</v>
+      </c>
+      <c r="L7" t="n">
+        <v>61</v>
+      </c>
+      <c r="M7" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20</v>
+      </c>
+      <c r="O7" t="n">
+        <v>81</v>
+      </c>
+      <c r="P7" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>56</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-11-15 19:30:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>37</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K8" t="n">
+        <v>42</v>
+      </c>
+      <c r="L8" t="n">
+        <v>67</v>
+      </c>
+      <c r="M8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N8" t="n">
+        <v>36</v>
+      </c>
+      <c r="O8" t="n">
+        <v>64</v>
+      </c>
+      <c r="P8" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>67</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-11-15 19:30:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>37</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K9" t="n">
+        <v>31</v>
+      </c>
+      <c r="L9" t="n">
+        <v>44</v>
+      </c>
+      <c r="M9" t="n">
+        <v>12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>56</v>
+      </c>
+      <c r="O9" t="n">
+        <v>45</v>
+      </c>
+      <c r="P9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>75</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-11-15 20:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Willem II</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Emmen</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K10" t="n">
+        <v>54</v>
+      </c>
+      <c r="L10" t="n">
+        <v>60</v>
+      </c>
+      <c r="M10" t="n">
+        <v>27</v>
+      </c>
+      <c r="N10" t="n">
+        <v>34</v>
+      </c>
+      <c r="O10" t="n">
+        <v>66</v>
+      </c>
+      <c r="P10" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>48</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-11-15 20:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Argentina Primera División</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C11" t="n">
         <v>16</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Lanús</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Atlético Tucumán</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K11" t="n">
+        <v>39</v>
+      </c>
+      <c r="L11" t="n">
+        <v>55</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20</v>
+      </c>
+      <c r="N11" t="n">
+        <v>46</v>
+      </c>
+      <c r="O11" t="n">
+        <v>55</v>
+      </c>
+      <c r="P11" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="W11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11-15 20:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Argentina Primera División</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>San Martín San Juan</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L12" t="n">
+        <v>53</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20</v>
+      </c>
+      <c r="N12" t="n">
+        <v>44</v>
+      </c>
+      <c r="O12" t="n">
+        <v>57</v>
+      </c>
+      <c r="P12" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>70</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-15 20:00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>14</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="K13" t="n">
+        <v>61</v>
+      </c>
+      <c r="L13" t="n">
+        <v>69</v>
+      </c>
+      <c r="M13" t="n">
+        <v>37</v>
+      </c>
+      <c r="N13" t="n">
+        <v>24</v>
+      </c>
+      <c r="O13" t="n">
+        <v>77</v>
+      </c>
+      <c r="P13" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>32</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K14" t="n">
+        <v>52</v>
+      </c>
+      <c r="L14" t="n">
+        <v>62</v>
+      </c>
+      <c r="M14" t="n">
+        <v>23</v>
+      </c>
+      <c r="N14" t="n">
+        <v>29</v>
+      </c>
+      <c r="O14" t="n">
+        <v>71</v>
+      </c>
+      <c r="P14" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>52</v>
+      </c>
+      <c r="R14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:15:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Argentina Primera División</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sarmiento</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="K15" t="n">
+        <v>28</v>
+      </c>
+      <c r="L15" t="n">
+        <v>44</v>
+      </c>
+      <c r="M15" t="n">
+        <v>19</v>
+      </c>
+      <c r="N15" t="n">
+        <v>59</v>
+      </c>
+      <c r="O15" t="n">
+        <v>41</v>
+      </c>
+      <c r="P15" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-11-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G16" t="n">
         <v>1.93</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="H16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>57</v>
+      </c>
+      <c r="L16" t="n">
+        <v>67</v>
+      </c>
+      <c r="M16" t="n">
+        <v>34</v>
+      </c>
+      <c r="N16" t="n">
+        <v>34</v>
+      </c>
+      <c r="O16" t="n">
+        <v>67</v>
+      </c>
+      <c r="P16" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>50</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z16" t="n">
         <v>2.67</v>
       </c>
-      <c r="K4" t="n">
-        <v>37</v>
-      </c>
-      <c r="L4" t="n">
-        <v>57</v>
-      </c>
-      <c r="M4" t="n">
-        <v>24</v>
-      </c>
-      <c r="N4" t="n">
-        <v>40</v>
-      </c>
-      <c r="O4" t="n">
-        <v>60</v>
-      </c>
-      <c r="P4" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>74</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="AA16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-11-16 00:30:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Argentina Primera División</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K17" t="n">
+        <v>26</v>
+      </c>
+      <c r="L17" t="n">
+        <v>56</v>
+      </c>
+      <c r="M17" t="n">
+        <v>19</v>
+      </c>
+      <c r="N17" t="n">
+        <v>45</v>
+      </c>
+      <c r="O17" t="n">
+        <v>56</v>
+      </c>
+      <c r="P17" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>63</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.55</v>
       </c>
-      <c r="V4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="W4" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.28</v>
+      <c r="AE17" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG17" headerRowCount="1">
-  <autoFilter ref="A1:AG17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG20" headerRowCount="1">
+  <autoFilter ref="A1:AG20"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,13 +467,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG17"/>
+  <dimension ref="A1:AG20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="33.6" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="22.8" customWidth="1" min="4" max="4"/>
+    <col width="25.2" customWidth="1" min="4" max="4"/>
     <col width="25.2" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
@@ -675,116 +675,116 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-15 15:00:00</t>
+          <t>2025-11-16 11:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1.14</v>
+        <v>2.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="I2" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="J2" t="n">
-        <v>3.21</v>
+        <v>3.11</v>
       </c>
       <c r="K2" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="L2" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="P2" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="Q2" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="R2" t="n">
-        <v>1.99</v>
+        <v>2.55</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="X2" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.21</v>
+        <v>2.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.94</v>
+        <v>2.63</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-15 15:00:00</t>
+          <t>2025-11-16 13:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -797,648 +797,648 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="J3" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="K3" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="L3" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="M3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N3" t="n">
+        <v>52</v>
+      </c>
+      <c r="O3" t="n">
+        <v>49</v>
+      </c>
+      <c r="P3" t="n">
         <v>25</v>
       </c>
-      <c r="N3" t="n">
-        <v>42</v>
-      </c>
-      <c r="O3" t="n">
-        <v>59</v>
-      </c>
-      <c r="P3" t="n">
-        <v>50</v>
-      </c>
       <c r="Q3" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4</v>
+        <v>3.08</v>
       </c>
       <c r="T3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="V3" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="W3" t="n">
-        <v>2.51</v>
+        <v>4.2</v>
       </c>
       <c r="X3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.78</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.9</v>
-      </c>
       <c r="Z3" t="n">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.41</v>
+        <v>3.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.22</v>
+        <v>2.34</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-15 17:45:00</t>
+          <t>2025-11-16 15:15:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.88</v>
+        <v>1.86</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>0.17</v>
       </c>
       <c r="H4" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="I4" t="n">
-        <v>1.59</v>
+        <v>1.18</v>
       </c>
       <c r="J4" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="K4" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="L4" t="n">
         <v>69</v>
       </c>
       <c r="M4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="N4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="O4" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="P4" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="Q4" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="R4" t="n">
-        <v>4.5</v>
+        <v>2.22</v>
       </c>
       <c r="S4" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="T4" t="n">
-        <v>1.65</v>
+        <v>3.56</v>
       </c>
       <c r="U4" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="W4" t="n">
-        <v>2.33</v>
+        <v>4.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.78</v>
+        <v>2.09</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.14</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.86</v>
+        <v>2.49</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.31</v>
+        <v>3.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.44</v>
+        <v>2.34</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-15 19:30:00</t>
+          <t>2025-11-16 15:15:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.89</v>
+        <v>2.17</v>
       </c>
       <c r="G5" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="H5" t="n">
-        <v>1.52</v>
+        <v>2.17</v>
       </c>
       <c r="I5" t="n">
-        <v>1.12</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2.64</v>
+        <v>3.07</v>
       </c>
       <c r="K5" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="L5" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O5" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="P5" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="Q5" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>3.61</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="W5" t="n">
-        <v>4.5</v>
+        <v>2.99</v>
       </c>
       <c r="X5" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-15 19:30:00</t>
+          <t>2025-11-16 17:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="G6" t="n">
-        <v>0.78</v>
+        <v>1.57</v>
       </c>
       <c r="H6" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="I6" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="J6" t="n">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="K6" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="L6" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="M6" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="P6" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="Q6" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="R6" t="n">
-        <v>1.76</v>
+        <v>2.39</v>
       </c>
       <c r="S6" t="n">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>4.1</v>
+        <v>3.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="W6" t="n">
-        <v>4.5</v>
+        <v>3.03</v>
       </c>
       <c r="X6" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.35</v>
+        <v>2.59</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-15 19:30:00</t>
+          <t>2025-11-16 17:30:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="K7" t="n">
+        <v>67</v>
+      </c>
+      <c r="L7" t="n">
+        <v>83</v>
+      </c>
+      <c r="M7" t="n">
+        <v>42</v>
+      </c>
+      <c r="N7" t="n">
+        <v>34</v>
+      </c>
+      <c r="O7" t="n">
+        <v>67</v>
+      </c>
+      <c r="P7" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>34</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z7" t="n">
         <v>1.83</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K7" t="n">
-        <v>64</v>
-      </c>
-      <c r="L7" t="n">
-        <v>61</v>
-      </c>
-      <c r="M7" t="n">
-        <v>17</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20</v>
-      </c>
-      <c r="O7" t="n">
-        <v>81</v>
-      </c>
-      <c r="P7" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>56</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.06</v>
-      </c>
       <c r="AA7" t="n">
-        <v>2.26</v>
+        <v>1.49</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.26</v>
+        <v>1.91</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.7</v>
+        <v>2.48</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.77</v>
+        <v>3.58</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.81</v>
+        <v>2.43</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-15 19:30:00</t>
+          <t>2025-11-16 18:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Leixões</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GD Chaves</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K8" t="n">
         <v>37</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="K8" t="n">
-        <v>42</v>
-      </c>
       <c r="L8" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M8" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="N8" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="O8" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="P8" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="Q8" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>3.15</v>
       </c>
       <c r="S8" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>5.2</v>
+        <v>2.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="W8" t="n">
-        <v>3.42</v>
+        <v>3.76</v>
       </c>
       <c r="X8" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-15 19:30:00</t>
+          <t>2025-11-16 19:30:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1451,757 +1451,757 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="G9" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="H9" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="I9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K9" t="n">
+        <v>42</v>
+      </c>
+      <c r="L9" t="n">
+        <v>61</v>
+      </c>
+      <c r="M9" t="n">
+        <v>28</v>
+      </c>
+      <c r="N9" t="n">
+        <v>42</v>
+      </c>
+      <c r="O9" t="n">
+        <v>59</v>
+      </c>
+      <c r="P9" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>67</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.32</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="K9" t="n">
-        <v>31</v>
-      </c>
-      <c r="L9" t="n">
-        <v>44</v>
-      </c>
-      <c r="M9" t="n">
-        <v>12</v>
-      </c>
-      <c r="N9" t="n">
-        <v>56</v>
-      </c>
-      <c r="O9" t="n">
-        <v>45</v>
-      </c>
-      <c r="P9" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>75</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AC9" t="n">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-15 20:00:00</t>
+          <t>2025-11-16 19:30:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="G10" t="n">
-        <v>1.13</v>
+        <v>0.89</v>
       </c>
       <c r="H10" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="I10" t="n">
-        <v>1.55</v>
+        <v>1.07</v>
       </c>
       <c r="J10" t="n">
-        <v>3.49</v>
+        <v>2.88</v>
       </c>
       <c r="K10" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="L10" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M10" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="N10" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O10" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="P10" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="T10" t="n">
-        <v>3.35</v>
+        <v>6.7</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>2.1</v>
       </c>
       <c r="W10" t="n">
-        <v>2.25</v>
+        <v>3.68</v>
       </c>
       <c r="X10" t="n">
-        <v>1.46</v>
+        <v>2.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.53</v>
+        <v>1.63</v>
       </c>
       <c r="Z10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.78</v>
       </c>
-      <c r="AA10" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-15 20:00:00</t>
+          <t>2025-11-16 19:30:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.93</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="H11" t="n">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="I11" t="n">
-        <v>0.91</v>
+        <v>1.36</v>
       </c>
       <c r="J11" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L11" t="n">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="M11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="O11" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="Q11" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="R11" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="T11" t="n">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="U11" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>3.27</v>
+        <v>2.25</v>
       </c>
       <c r="W11" t="n">
-        <v>7.5</v>
+        <v>4.35</v>
       </c>
       <c r="X11" t="n">
-        <v>2.72</v>
+        <v>2.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.03</v>
+        <v>2.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.62</v>
+        <v>1.99</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-15 20:00:00</t>
+          <t>2025-11-16 19:30:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="G12" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="H12" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="I12" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="J12" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="L12" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="N12" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="O12" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="P12" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="Q12" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="R12" t="n">
-        <v>2.8</v>
+        <v>3.71</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="T12" t="n">
-        <v>3.15</v>
+        <v>1.88</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="W12" t="n">
-        <v>5.75</v>
+        <v>3.99</v>
       </c>
       <c r="X12" t="n">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.01</v>
+        <v>1.69</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-15 20:00:00</t>
+          <t>2025-11-16 20:00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="H13" t="n">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="I13" t="n">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="J13" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K13" t="n">
+        <v>34</v>
+      </c>
+      <c r="L13" t="n">
+        <v>57</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20</v>
+      </c>
+      <c r="N13" t="n">
+        <v>40</v>
+      </c>
+      <c r="O13" t="n">
+        <v>60</v>
+      </c>
+      <c r="P13" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>70</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.95</v>
       </c>
-      <c r="K13" t="n">
-        <v>61</v>
-      </c>
-      <c r="L13" t="n">
-        <v>69</v>
-      </c>
-      <c r="M13" t="n">
-        <v>37</v>
-      </c>
-      <c r="N13" t="n">
-        <v>24</v>
-      </c>
-      <c r="O13" t="n">
-        <v>77</v>
-      </c>
-      <c r="P13" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>32</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.67</v>
-      </c>
       <c r="T13" t="n">
-        <v>3.98</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6</v>
+        <v>5.61</v>
       </c>
       <c r="X13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.61</v>
       </c>
-      <c r="Y13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.44</v>
+        <v>3.66</v>
       </c>
       <c r="AF13" t="n">
-        <v>3.15</v>
+        <v>2.23</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-15 21:30:00</t>
+          <t>2025-11-16 20:00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.63</v>
+        <v>1.33</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="H14" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="I14" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="J14" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="K14" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="L14" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N14" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="O14" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="P14" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="R14" t="n">
-        <v>10</v>
+        <v>3.05</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>1.28</v>
+        <v>2.45</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="V14" t="n">
-        <v>1.96</v>
+        <v>2.45</v>
       </c>
       <c r="W14" t="n">
-        <v>2.94</v>
+        <v>5.05</v>
       </c>
       <c r="X14" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.73</v>
+        <v>2.09</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>2.48</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.65</v>
+        <v>3.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.99</v>
+        <v>2.29</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-15 22:15:00</t>
+          <t>2025-11-16 20:00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.82</v>
+        <v>0.33</v>
       </c>
       <c r="G15" t="n">
-        <v>1.13</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="J15" t="n">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="K15" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L15" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="M15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N15" t="n">
+        <v>33</v>
+      </c>
+      <c r="O15" t="n">
+        <v>67</v>
+      </c>
+      <c r="P15" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q15" t="n">
         <v>59</v>
       </c>
-      <c r="O15" t="n">
-        <v>41</v>
-      </c>
-      <c r="P15" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>75</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="V15" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="W15" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="X15" t="n">
-        <v>2.58</v>
+        <v>2.13</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.96</v>
+        <v>3.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-16 22:00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2210,107 +2210,107 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="G16" t="n">
-        <v>1.93</v>
+        <v>0.76</v>
       </c>
       <c r="H16" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="I16" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="K16" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L16" t="n">
         <v>67</v>
       </c>
       <c r="M16" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="N16" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="O16" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="P16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q16" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="W16" t="n">
         <v>3.96</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.4</v>
-      </c>
       <c r="X16" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.85</v>
+        <v>3.42</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-16 00:30:00</t>
+          <t>2025-11-16 23:15:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2323,97 +2323,424 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Independiente</t>
+          <t>Central Córdoba SdE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="G17" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K17" t="n">
+        <v>44</v>
+      </c>
+      <c r="L17" t="n">
+        <v>64</v>
+      </c>
+      <c r="M17" t="n">
+        <v>14</v>
+      </c>
+      <c r="N17" t="n">
+        <v>34</v>
+      </c>
+      <c r="O17" t="n">
+        <v>67</v>
+      </c>
+      <c r="P17" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>57</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="W17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-11-16 23:15:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Argentina Primera División</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K17" t="n">
-        <v>26</v>
-      </c>
-      <c r="L17" t="n">
-        <v>56</v>
-      </c>
-      <c r="M17" t="n">
-        <v>19</v>
-      </c>
-      <c r="N17" t="n">
-        <v>45</v>
-      </c>
-      <c r="O17" t="n">
-        <v>56</v>
-      </c>
-      <c r="P17" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>63</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="G18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K18" t="n">
+        <v>47</v>
+      </c>
+      <c r="L18" t="n">
+        <v>60</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20</v>
+      </c>
+      <c r="N18" t="n">
+        <v>37</v>
+      </c>
+      <c r="O18" t="n">
+        <v>64</v>
+      </c>
+      <c r="P18" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>67</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-11-16 23:15:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Argentina Primera División</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>16</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="K19" t="n">
+        <v>40</v>
+      </c>
+      <c r="L19" t="n">
+        <v>52</v>
+      </c>
+      <c r="M19" t="n">
+        <v>22</v>
+      </c>
+      <c r="N19" t="n">
+        <v>37</v>
+      </c>
+      <c r="O19" t="n">
+        <v>64</v>
+      </c>
+      <c r="P19" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>64</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V19" t="n">
         <v>2.35</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="W19" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.67</v>
       </c>
-      <c r="V17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="W17" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AB19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.55</v>
       </c>
-      <c r="AE17" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.25</v>
+      <c r="AE19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-11-16 23:15:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Argentina Primera División</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K20" t="n">
+        <v>47</v>
+      </c>
+      <c r="L20" t="n">
+        <v>64</v>
+      </c>
+      <c r="M20" t="n">
+        <v>24</v>
+      </c>
+      <c r="N20" t="n">
+        <v>34</v>
+      </c>
+      <c r="O20" t="n">
+        <v>67</v>
+      </c>
+      <c r="P20" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>70</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG6" headerRowCount="1">
-  <autoFilter ref="A1:AG6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG3" headerRowCount="1">
+  <autoFilter ref="A1:AG3"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG6"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="33.6" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="19.2" customWidth="1" min="4" max="4"/>
+    <col width="20.4" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,546 +675,219 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-17 19:30:00</t>
+          <t>2025-11-18 23:30:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.83</v>
+        <v>1.81</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="H2" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="I2" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3</v>
+        <v>3.09</v>
       </c>
       <c r="K2" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L2" t="n">
+        <v>79</v>
+      </c>
+      <c r="M2" t="n">
+        <v>26</v>
+      </c>
+      <c r="N2" t="n">
+        <v>22</v>
+      </c>
+      <c r="O2" t="n">
+        <v>78</v>
+      </c>
+      <c r="P2" t="n">
         <v>50</v>
       </c>
-      <c r="M2" t="n">
-        <v>25</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>50</v>
       </c>
-      <c r="O2" t="n">
-        <v>50</v>
-      </c>
-      <c r="P2" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>59</v>
-      </c>
       <c r="R2" t="n">
-        <v>2.22</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.28</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>3.17</v>
+        <v>12.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="V2" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>4.35</v>
+        <v>2.6</v>
       </c>
       <c r="X2" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.03</v>
+        <v>2.43</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.58</v>
+        <v>1.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.95</v>
+        <v>2.46</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-17 20:00:00</t>
+          <t>2025-11-18 23:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Colombia Categoria Primera A</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="G3" t="n">
-        <v>1.13</v>
+        <v>1.65</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="I3" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="J3" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="K3" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="L3" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="O3" t="n">
+        <v>60</v>
+      </c>
+      <c r="P3" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q3" t="n">
         <v>68</v>
       </c>
-      <c r="P3" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>58</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="S3" t="n">
-        <v>3.35</v>
+        <v>2.93</v>
       </c>
       <c r="T3" t="n">
-        <v>4.5</v>
+        <v>3.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="W3" t="n">
-        <v>4.55</v>
+        <v>4.11</v>
       </c>
       <c r="X3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB3" t="n">
         <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AG3" t="n">
         <v>1.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-11-17 20:00:00</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Argentina Primera División</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Belgrano</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Unión Santa Fe</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K4" t="n">
-        <v>47</v>
-      </c>
-      <c r="L4" t="n">
-        <v>70</v>
-      </c>
-      <c r="M4" t="n">
-        <v>24</v>
-      </c>
-      <c r="N4" t="n">
-        <v>30</v>
-      </c>
-      <c r="O4" t="n">
-        <v>70</v>
-      </c>
-      <c r="P4" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>60</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-11-17 20:00:00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Argentina Primera División</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>16</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Barracas Central</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Huracán</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="K5" t="n">
-        <v>51</v>
-      </c>
-      <c r="L5" t="n">
-        <v>76</v>
-      </c>
-      <c r="M5" t="n">
-        <v>16</v>
-      </c>
-      <c r="N5" t="n">
-        <v>31</v>
-      </c>
-      <c r="O5" t="n">
-        <v>70</v>
-      </c>
-      <c r="P5" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>62</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V5" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="W5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-11-17 22:30:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Argentina Primera División</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>16</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Platense</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Gimnasia La Plata</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="K6" t="n">
-        <v>37</v>
-      </c>
-      <c r="L6" t="n">
-        <v>53</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20</v>
-      </c>
-      <c r="N6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O6" t="n">
-        <v>50</v>
-      </c>
-      <c r="P6" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>74</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W6" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG3" headerRowCount="1">
-  <autoFilter ref="A1:AG3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG10" headerRowCount="1">
+  <autoFilter ref="A1:AG10"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="19.2" customWidth="1" min="4" max="4"/>
-    <col width="20.4" customWidth="1" min="5" max="5"/>
+    <col width="26.4" customWidth="1" min="4" max="4"/>
+    <col width="28.8" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,7 +675,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-18 23:30:00</t>
+          <t>2025-11-19 18:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -688,206 +688,969 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="G2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="I2" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.09</v>
+        <v>2.69</v>
       </c>
       <c r="K2" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L2" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="M2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="O2" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="P2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-18 23:30:00</t>
+          <t>2025-11-19 18:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="K3" t="n">
+        <v>57</v>
+      </c>
+      <c r="L3" t="n">
+        <v>60</v>
+      </c>
+      <c r="M3" t="n">
+        <v>32</v>
+      </c>
+      <c r="N3" t="n">
+        <v>35</v>
+      </c>
+      <c r="O3" t="n">
+        <v>66</v>
+      </c>
+      <c r="P3" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>50</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-11-19 22:30:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K4" t="n">
+        <v>43</v>
+      </c>
+      <c r="L4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M4" t="n">
+        <v>33</v>
+      </c>
+      <c r="N4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O4" t="n">
+        <v>70</v>
+      </c>
+      <c r="P4" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>58</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-11-19 22:30:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>38</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K5" t="n">
+        <v>39</v>
+      </c>
+      <c r="L5" t="n">
+        <v>67</v>
+      </c>
+      <c r="M5" t="n">
+        <v>22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>33</v>
+      </c>
+      <c r="O5" t="n">
+        <v>67</v>
+      </c>
+      <c r="P5" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>67</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-11-19 23:30:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Colombia Categoria Primera A</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Fortaleza CEIF</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Deportes Tolima</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K6" t="n">
+        <v>45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>65</v>
+      </c>
+      <c r="M6" t="n">
+        <v>35</v>
+      </c>
+      <c r="N6" t="n">
+        <v>27</v>
+      </c>
+      <c r="O6" t="n">
+        <v>73</v>
+      </c>
+      <c r="P6" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>59</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:30:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>34</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="K7" t="n">
+        <v>44</v>
+      </c>
+      <c r="L7" t="n">
+        <v>69</v>
+      </c>
+      <c r="M7" t="n">
+        <v>22</v>
+      </c>
+      <c r="N7" t="n">
+        <v>35</v>
+      </c>
+      <c r="O7" t="n">
+        <v>66</v>
+      </c>
+      <c r="P7" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>57</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W7" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:30:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>34</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="K8" t="n">
+        <v>47</v>
+      </c>
+      <c r="L8" t="n">
+        <v>66</v>
+      </c>
+      <c r="M8" t="n">
+        <v>29</v>
+      </c>
+      <c r="N8" t="n">
+        <v>38</v>
+      </c>
+      <c r="O8" t="n">
+        <v>63</v>
+      </c>
+      <c r="P8" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>63</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:30:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>34</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K9" t="n">
+        <v>50</v>
+      </c>
+      <c r="L9" t="n">
+        <v>76</v>
+      </c>
+      <c r="M9" t="n">
+        <v>32</v>
+      </c>
+      <c r="N9" t="n">
+        <v>22</v>
+      </c>
+      <c r="O9" t="n">
+        <v>79</v>
+      </c>
+      <c r="P9" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>53</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.95</v>
       </c>
-      <c r="G3" t="n">
+      <c r="Z9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-11-20 01:30:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Colombia Categoria Primera A</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="K10" t="n">
+        <v>51</v>
+      </c>
+      <c r="L10" t="n">
+        <v>69</v>
+      </c>
+      <c r="M10" t="n">
+        <v>22</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" t="n">
+        <v>71</v>
+      </c>
+      <c r="P10" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>58</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.65</v>
       </c>
-      <c r="H3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="K3" t="n">
-        <v>42</v>
-      </c>
-      <c r="L3" t="n">
-        <v>64</v>
-      </c>
-      <c r="M3" t="n">
-        <v>26</v>
-      </c>
-      <c r="N3" t="n">
-        <v>40</v>
-      </c>
-      <c r="O3" t="n">
-        <v>60</v>
-      </c>
-      <c r="P3" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>68</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W3" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.3</v>
+      <c r="Y10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG10" headerRowCount="1">
-  <autoFilter ref="A1:AG10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG9" headerRowCount="1">
+  <autoFilter ref="A1:AG9"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG10"/>
+  <dimension ref="A1:AG9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="40.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="26.4" customWidth="1" min="4" max="4"/>
-    <col width="28.8" customWidth="1" min="5" max="5"/>
+    <col width="22.8" customWidth="1" min="4" max="4"/>
+    <col width="20.4" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,7 +675,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-19 18:00:00</t>
+          <t>2025-11-20 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -688,103 +688,103 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>1.56</v>
       </c>
       <c r="H2" t="n">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="J2" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="K2" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="L2" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M2" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O2" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P2" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-19 18:00:00</t>
+          <t>2025-11-20 21:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -797,103 +797,103 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.94</v>
+        <v>2.44</v>
       </c>
       <c r="G3" t="n">
-        <v>1.81</v>
+        <v>0.63</v>
       </c>
       <c r="H3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>60</v>
+      </c>
+      <c r="L3" t="n">
+        <v>79</v>
+      </c>
+      <c r="M3" t="n">
+        <v>22</v>
+      </c>
+      <c r="N3" t="n">
+        <v>25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>75</v>
+      </c>
+      <c r="P3" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>47</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC3" t="n">
         <v>1.83</v>
       </c>
-      <c r="I3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="K3" t="n">
-        <v>57</v>
-      </c>
-      <c r="L3" t="n">
-        <v>60</v>
-      </c>
-      <c r="M3" t="n">
-        <v>32</v>
-      </c>
-      <c r="N3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O3" t="n">
-        <v>66</v>
-      </c>
-      <c r="P3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>50</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-19 22:30:00</t>
+          <t>2025-11-20 22:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -902,207 +902,207 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.29</v>
+        <v>1.56</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>1.06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="J4" t="n">
-        <v>2.98</v>
+        <v>2.73</v>
       </c>
       <c r="K4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="N4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>2.09</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2.72</v>
       </c>
       <c r="T4" t="n">
-        <v>9.5</v>
+        <v>3.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="V4" t="n">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>4.55</v>
       </c>
       <c r="X4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.71</v>
+        <v>3.42</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.33</v>
+        <v>2.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-19 22:30:00</t>
+          <t>2025-11-21 00:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="G5" t="n">
-        <v>0.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="I5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K5" t="n">
+        <v>47</v>
+      </c>
+      <c r="L5" t="n">
+        <v>78</v>
+      </c>
+      <c r="M5" t="n">
+        <v>26</v>
+      </c>
+      <c r="N5" t="n">
+        <v>28</v>
+      </c>
+      <c r="O5" t="n">
+        <v>72</v>
+      </c>
+      <c r="P5" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>72</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.48</v>
       </c>
-      <c r="J5" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="K5" t="n">
-        <v>39</v>
-      </c>
-      <c r="L5" t="n">
-        <v>67</v>
-      </c>
-      <c r="M5" t="n">
-        <v>22</v>
-      </c>
-      <c r="N5" t="n">
-        <v>33</v>
-      </c>
-      <c r="O5" t="n">
-        <v>67</v>
-      </c>
-      <c r="P5" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>67</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.5</v>
       </c>
-      <c r="V5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="W5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AE5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AG5" t="n">
         <v>1.27</v>
@@ -1111,7 +1111,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-19 23:30:00</t>
+          <t>2025-11-21 00:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1124,533 +1124,424 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>América de Cali</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="G6" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="H6" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="I6" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="J6" t="n">
-        <v>2.71</v>
+        <v>3.17</v>
       </c>
       <c r="K6" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M6" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="N6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="O6" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="R6" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>3.41</v>
       </c>
       <c r="T6" t="n">
         <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="W6" t="n">
-        <v>4.75</v>
+        <v>3.08</v>
       </c>
       <c r="X6" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.36</v>
+        <v>2.84</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-20 00:30:00</t>
+          <t>2025-11-21 01:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Mexico Liga MX</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.31</v>
+        <v>1.29</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88</v>
+        <v>1.24</v>
       </c>
       <c r="H7" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="I7" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="J7" t="n">
-        <v>3.26</v>
+        <v>2.87</v>
       </c>
       <c r="K7" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="L7" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M7" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="N7" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="O7" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="P7" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q7" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="R7" t="n">
-        <v>3.63</v>
+        <v>1.8</v>
       </c>
       <c r="S7" t="n">
-        <v>2.94</v>
+        <v>3.51</v>
       </c>
       <c r="T7" t="n">
-        <v>1.98</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="V7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.4</v>
       </c>
-      <c r="W7" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.39</v>
+        <v>3.28</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-20 00:30:00</t>
+          <t>2025-11-21 03:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Mexico Liga MX</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Juárez</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K8" t="n">
+        <v>62</v>
+      </c>
+      <c r="L8" t="n">
+        <v>74</v>
+      </c>
+      <c r="M8" t="n">
+        <v>30</v>
+      </c>
+      <c r="N8" t="n">
+        <v>15</v>
+      </c>
+      <c r="O8" t="n">
+        <v>85</v>
+      </c>
+      <c r="P8" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>47</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.44</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="K8" t="n">
-        <v>47</v>
-      </c>
-      <c r="L8" t="n">
-        <v>66</v>
-      </c>
-      <c r="M8" t="n">
-        <v>29</v>
-      </c>
-      <c r="N8" t="n">
-        <v>38</v>
-      </c>
-      <c r="O8" t="n">
-        <v>63</v>
-      </c>
-      <c r="P8" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>63</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-20 00:30:00</t>
+          <t>2025-11-21 13:45:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.63</v>
+        <v>0.75</v>
       </c>
       <c r="G9" t="n">
-        <v>1.06</v>
+        <v>0.25</v>
       </c>
       <c r="H9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I9" t="n">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="J9" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="K9" t="n">
         <v>50</v>
       </c>
       <c r="L9" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="N9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="P9" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="Q9" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="R9" t="n">
-        <v>2.12</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>3.23</v>
+        <v>5.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.94</v>
+        <v>7.6</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="V9" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>3.84</v>
+        <v>2.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.09</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.69</v>
+        <v>3.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2025-11-20 01:30:00</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Colombia Categoria Primera A</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Independiente Medellín</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="K10" t="n">
-        <v>51</v>
-      </c>
-      <c r="L10" t="n">
-        <v>69</v>
-      </c>
-      <c r="M10" t="n">
-        <v>22</v>
-      </c>
-      <c r="N10" t="n">
-        <v>30</v>
-      </c>
-      <c r="O10" t="n">
-        <v>71</v>
-      </c>
-      <c r="P10" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>58</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG9" headerRowCount="1">
-  <autoFilter ref="A1:AG9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG43" headerRowCount="1">
+  <autoFilter ref="A1:AG43"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG9"/>
+  <dimension ref="A1:AG43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="40.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="22.8" customWidth="1" min="4" max="4"/>
-    <col width="20.4" customWidth="1" min="5" max="5"/>
+    <col width="26.4" customWidth="1" min="4" max="4"/>
+    <col width="28.8" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,873 +675,4579 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-20 19:00:00</t>
+          <t>2025-11-21 14:50:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="H2" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="I2" t="n">
-        <v>1.26</v>
+        <v>0.88</v>
       </c>
       <c r="J2" t="n">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="K2" t="n">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="L2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M2" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="P2" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q2" t="n">
         <v>25</v>
       </c>
-      <c r="Q2" t="n">
-        <v>75</v>
-      </c>
       <c r="R2" t="n">
-        <v>3.75</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="V2" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="W2" t="n">
-        <v>3.44</v>
+        <v>2.74</v>
       </c>
       <c r="X2" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.86</v>
+        <v>2.29</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.9</v>
+        <v>2.61</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-20 21:00:00</t>
+          <t>2025-11-21 15:15:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.44</v>
+        <v>0.75</v>
       </c>
       <c r="G3" t="n">
-        <v>0.63</v>
+        <v>0.25</v>
       </c>
       <c r="H3" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="K3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L3" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M3" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="P3" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="Q3" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>3.82</v>
+        <v>5.5</v>
       </c>
       <c r="T3" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="V3" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2</v>
       </c>
-      <c r="Z3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AB3" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-20 22:30:00</t>
+          <t>2025-11-21 15:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="I4" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="J4" t="n">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="K4" t="n">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="L4" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="M4" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N4" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="P4" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="Q4" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="R4" t="n">
-        <v>2.09</v>
+        <v>2.46</v>
       </c>
       <c r="S4" t="n">
-        <v>2.72</v>
+        <v>2.97</v>
       </c>
       <c r="T4" t="n">
-        <v>3.66</v>
+        <v>2.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="W4" t="n">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="X4" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-21 00:30:00</t>
+          <t>2025-11-21 15:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FK Sochi</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>75</v>
+      </c>
+      <c r="L5" t="n">
+        <v>68</v>
+      </c>
+      <c r="M5" t="n">
         <v>34</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ceará</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="K5" t="n">
-        <v>47</v>
-      </c>
-      <c r="L5" t="n">
-        <v>78</v>
-      </c>
-      <c r="M5" t="n">
-        <v>26</v>
-      </c>
       <c r="N5" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="P5" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="Q5" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="S5" t="n">
-        <v>2.93</v>
+        <v>3.47</v>
       </c>
       <c r="T5" t="n">
-        <v>3.39</v>
+        <v>3.65</v>
       </c>
       <c r="U5" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="V5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="W5" t="n">
-        <v>5.11</v>
+        <v>2.94</v>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-21 00:30:00</t>
+          <t>2025-11-21 17:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Colombia Categoria Primera A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>América de Cali</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="G6" t="n">
-        <v>1.22</v>
+        <v>0.33</v>
       </c>
       <c r="H6" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="I6" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="J6" t="n">
-        <v>3.17</v>
+        <v>3.01</v>
       </c>
       <c r="K6" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="L6" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="M6" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="N6" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="O6" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="P6" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="Q6" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="R6" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="S6" t="n">
-        <v>3.41</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="W6" t="n">
         <v>3.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AD6" t="n">
         <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-21 01:00:00</t>
+          <t>2025-11-21 17:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mexico Liga MX</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.29</v>
+        <v>0.87</v>
       </c>
       <c r="G7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K7" t="n">
+        <v>57</v>
+      </c>
+      <c r="L7" t="n">
+        <v>80</v>
+      </c>
+      <c r="M7" t="n">
+        <v>34</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20</v>
+      </c>
+      <c r="O7" t="n">
+        <v>80</v>
+      </c>
+      <c r="P7" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>47</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.24</v>
       </c>
-      <c r="H7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="K7" t="n">
-        <v>56</v>
-      </c>
-      <c r="L7" t="n">
-        <v>62</v>
-      </c>
-      <c r="M7" t="n">
-        <v>38</v>
-      </c>
-      <c r="N7" t="n">
-        <v>24</v>
-      </c>
-      <c r="O7" t="n">
-        <v>77</v>
-      </c>
-      <c r="P7" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>53</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.18</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="W7" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="X7" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AA7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1.86</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-21 03:00:00</t>
+          <t>2025-11-21 17:30:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mexico Liga MX</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Juárez</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="H8" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="I8" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="J8" t="n">
-        <v>2.69</v>
+        <v>3.13</v>
       </c>
       <c r="K8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="M8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O8" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="P8" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="R8" t="n">
         <v>2.02</v>
       </c>
       <c r="S8" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>3.13</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="W8" t="n">
         <v>2.9</v>
       </c>
       <c r="X8" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="Z8" t="n">
         <v>2.34</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-21 13:45:00</t>
+          <t>2025-11-21 17:30:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.75</v>
+        <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="I9" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="J9" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L9" t="n">
         <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="O9" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="P9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="T9" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="X9" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.43</v>
+        <v>2.69</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AB9" t="n">
         <v>1.44</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-11-21 17:30:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>13</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Dynamo Dresden</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>54</v>
+      </c>
+      <c r="L10" t="n">
+        <v>90</v>
+      </c>
+      <c r="M10" t="n">
+        <v>45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" t="n">
+        <v>90</v>
+      </c>
+      <c r="P10" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>47</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-11-21 18:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Denmark Superliga</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Silkeborg</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K11" t="n">
+        <v>79</v>
+      </c>
+      <c r="L11" t="n">
+        <v>86</v>
+      </c>
+      <c r="M11" t="n">
+        <v>50</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>100</v>
+      </c>
+      <c r="P11" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>43</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11-21 18:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>29</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K12" t="n">
+        <v>71</v>
+      </c>
+      <c r="L12" t="n">
+        <v>79</v>
+      </c>
+      <c r="M12" t="n">
+        <v>47</v>
+      </c>
+      <c r="N12" t="n">
+        <v>14</v>
+      </c>
+      <c r="O12" t="n">
+        <v>86</v>
+      </c>
+      <c r="P12" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>33</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-21 18:30:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Argeș</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CS U Craiova</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K13" t="n">
+        <v>50</v>
+      </c>
+      <c r="L13" t="n">
+        <v>64</v>
+      </c>
+      <c r="M13" t="n">
+        <v>50</v>
+      </c>
+      <c r="N13" t="n">
+        <v>36</v>
+      </c>
+      <c r="O13" t="n">
+        <v>64</v>
+      </c>
+      <c r="P13" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>64</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>16</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Den Bosch</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Almere City</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K14" t="n">
+        <v>64</v>
+      </c>
+      <c r="L14" t="n">
+        <v>79</v>
+      </c>
+      <c r="M14" t="n">
+        <v>50</v>
+      </c>
+      <c r="N14" t="n">
+        <v>14</v>
+      </c>
+      <c r="O14" t="n">
+        <v>86</v>
+      </c>
+      <c r="P14" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>36</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ajax II</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K15" t="n">
+        <v>39</v>
+      </c>
+      <c r="L15" t="n">
+        <v>60</v>
+      </c>
+      <c r="M15" t="n">
+        <v>40</v>
+      </c>
+      <c r="N15" t="n">
+        <v>41</v>
+      </c>
+      <c r="O15" t="n">
+        <v>60</v>
+      </c>
+      <c r="P15" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>48</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Helmond Sport</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K16" t="n">
+        <v>65</v>
+      </c>
+      <c r="L16" t="n">
+        <v>71</v>
+      </c>
+      <c r="M16" t="n">
+        <v>43</v>
+      </c>
+      <c r="N16" t="n">
+        <v>22</v>
+      </c>
+      <c r="O16" t="n">
+        <v>79</v>
+      </c>
+      <c r="P16" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>50</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MVV</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AZ II</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K17" t="n">
+        <v>64</v>
+      </c>
+      <c r="L17" t="n">
+        <v>79</v>
+      </c>
+      <c r="M17" t="n">
+        <v>57</v>
+      </c>
+      <c r="N17" t="n">
+        <v>36</v>
+      </c>
+      <c r="O17" t="n">
+        <v>64</v>
+      </c>
+      <c r="P17" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>43</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:00:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PSV II</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Utrecht II</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K18" t="n">
+        <v>43</v>
+      </c>
+      <c r="L18" t="n">
+        <v>79</v>
+      </c>
+      <c r="M18" t="n">
+        <v>22</v>
+      </c>
+      <c r="N18" t="n">
+        <v>29</v>
+      </c>
+      <c r="O18" t="n">
+        <v>71</v>
+      </c>
+      <c r="P18" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>43</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:00:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>16</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VVV</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Willem II</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K19" t="n">
+        <v>57</v>
+      </c>
+      <c r="L19" t="n">
+        <v>76</v>
+      </c>
+      <c r="M19" t="n">
+        <v>25</v>
+      </c>
+      <c r="N19" t="n">
+        <v>26</v>
+      </c>
+      <c r="O19" t="n">
+        <v>76</v>
+      </c>
+      <c r="P19" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>38</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:00:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ADO Den Haag</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="K20" t="n">
+        <v>64</v>
+      </c>
+      <c r="L20" t="n">
+        <v>86</v>
+      </c>
+      <c r="M20" t="n">
+        <v>50</v>
+      </c>
+      <c r="N20" t="n">
+        <v>14</v>
+      </c>
+      <c r="O20" t="n">
+        <v>86</v>
+      </c>
+      <c r="P20" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>22</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:00:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>16</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Oss</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="K21" t="n">
+        <v>64</v>
+      </c>
+      <c r="L21" t="n">
+        <v>93</v>
+      </c>
+      <c r="M21" t="n">
+        <v>22</v>
+      </c>
+      <c r="N21" t="n">
+        <v>7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>93</v>
+      </c>
+      <c r="P21" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>29</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>16</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Dordrecht</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K22" t="n">
+        <v>64</v>
+      </c>
+      <c r="L22" t="n">
+        <v>79</v>
+      </c>
+      <c r="M22" t="n">
+        <v>14</v>
+      </c>
+      <c r="N22" t="n">
+        <v>15</v>
+      </c>
+      <c r="O22" t="n">
+        <v>86</v>
+      </c>
+      <c r="P22" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>43</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:30:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>13</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Pescara</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="K23" t="n">
+        <v>74</v>
+      </c>
+      <c r="L23" t="n">
+        <v>74</v>
+      </c>
+      <c r="M23" t="n">
+        <v>9</v>
+      </c>
+      <c r="N23" t="n">
+        <v>17</v>
+      </c>
+      <c r="O23" t="n">
+        <v>84</v>
+      </c>
+      <c r="P23" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>44</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:30:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>11</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mainz 05</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K24" t="n">
+        <v>60</v>
+      </c>
+      <c r="L24" t="n">
+        <v>80</v>
+      </c>
+      <c r="M24" t="n">
+        <v>60</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20</v>
+      </c>
+      <c r="O24" t="n">
+        <v>80</v>
+      </c>
+      <c r="P24" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>50</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:30:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Górnik Zabrze</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Wisła Płock</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="K25" t="n">
+        <v>55</v>
+      </c>
+      <c r="L25" t="n">
+        <v>77</v>
+      </c>
+      <c r="M25" t="n">
+        <v>25</v>
+      </c>
+      <c r="N25" t="n">
+        <v>24</v>
+      </c>
+      <c r="O25" t="n">
+        <v>76</v>
+      </c>
+      <c r="P25" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>63</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:30:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>15</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>UD Las Palmas</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Albacete Balompié</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K26" t="n">
+        <v>57</v>
+      </c>
+      <c r="L26" t="n">
+        <v>79</v>
+      </c>
+      <c r="M26" t="n">
+        <v>22</v>
+      </c>
+      <c r="N26" t="n">
+        <v>43</v>
+      </c>
+      <c r="O26" t="n">
+        <v>57</v>
+      </c>
+      <c r="P26" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>50</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:45:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>13</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Olympique Marseille</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K27" t="n">
+        <v>42</v>
+      </c>
+      <c r="L27" t="n">
+        <v>50</v>
+      </c>
+      <c r="M27" t="n">
+        <v>25</v>
+      </c>
+      <c r="N27" t="n">
+        <v>42</v>
+      </c>
+      <c r="O27" t="n">
+        <v>59</v>
+      </c>
+      <c r="P27" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>59</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-11-21 19:45:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>15</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K28" t="n">
+        <v>79</v>
+      </c>
+      <c r="L28" t="n">
+        <v>79</v>
+      </c>
+      <c r="M28" t="n">
+        <v>36</v>
+      </c>
+      <c r="N28" t="n">
+        <v>14</v>
+      </c>
+      <c r="O28" t="n">
+        <v>86</v>
+      </c>
+      <c r="P28" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>36</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-11-21 20:00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>13</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Valencia CF</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K29" t="n">
+        <v>54</v>
+      </c>
+      <c r="L29" t="n">
+        <v>68</v>
+      </c>
+      <c r="M29" t="n">
+        <v>7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>100</v>
+      </c>
+      <c r="P29" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>62</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-11-21 20:00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>25</v>
+      </c>
+      <c r="L30" t="n">
+        <v>73</v>
+      </c>
+      <c r="M30" t="n">
+        <v>7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>41</v>
+      </c>
+      <c r="O30" t="n">
+        <v>60</v>
+      </c>
+      <c r="P30" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>61</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-11-22 05:00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>37</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K31" t="n">
+        <v>50</v>
+      </c>
+      <c r="L31" t="n">
+        <v>56</v>
+      </c>
+      <c r="M31" t="n">
+        <v>25</v>
+      </c>
+      <c r="N31" t="n">
+        <v>32</v>
+      </c>
+      <c r="O31" t="n">
+        <v>69</v>
+      </c>
+      <c r="P31" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>51</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-11-22 05:00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>37</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Suwon</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="K32" t="n">
+        <v>65</v>
+      </c>
+      <c r="L32" t="n">
+        <v>67</v>
+      </c>
+      <c r="M32" t="n">
+        <v>32</v>
+      </c>
+      <c r="N32" t="n">
+        <v>24</v>
+      </c>
+      <c r="O32" t="n">
+        <v>77</v>
+      </c>
+      <c r="P32" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>44</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-11-22 05:00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>37</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FC Seoul</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sangju Sangmu</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="K33" t="n">
+        <v>57</v>
+      </c>
+      <c r="L33" t="n">
+        <v>61</v>
+      </c>
+      <c r="M33" t="n">
+        <v>27</v>
+      </c>
+      <c r="N33" t="n">
+        <v>32</v>
+      </c>
+      <c r="O33" t="n">
+        <v>68</v>
+      </c>
+      <c r="P33" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>52</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-11-22 07:30:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>China Chinese Super League</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>30</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Henan Jianye</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Yunnan Yukun</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K34" t="n">
+        <v>79</v>
+      </c>
+      <c r="L34" t="n">
+        <v>79</v>
+      </c>
+      <c r="M34" t="n">
+        <v>36</v>
+      </c>
+      <c r="N34" t="n">
+        <v>11</v>
+      </c>
+      <c r="O34" t="n">
+        <v>90</v>
+      </c>
+      <c r="P34" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>29</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-11-22 07:30:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>China Chinese Super League</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>30</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sichuan Jiuniu</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Chengdu Better City FC</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K35" t="n">
+        <v>75</v>
+      </c>
+      <c r="L35" t="n">
+        <v>86</v>
+      </c>
+      <c r="M35" t="n">
+        <v>50</v>
+      </c>
+      <c r="N35" t="n">
+        <v>7</v>
+      </c>
+      <c r="O35" t="n">
+        <v>93</v>
+      </c>
+      <c r="P35" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>25</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X35" t="n">
         <v>1.79</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="Y35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-11-22 07:30:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>China Chinese Super League</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>30</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Tianjin Teda</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Shanghai Shenhua</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K36" t="n">
+        <v>47</v>
+      </c>
+      <c r="L36" t="n">
+        <v>68</v>
+      </c>
+      <c r="M36" t="n">
+        <v>32</v>
+      </c>
+      <c r="N36" t="n">
+        <v>36</v>
+      </c>
+      <c r="O36" t="n">
+        <v>64</v>
+      </c>
+      <c r="P36" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>50</v>
+      </c>
+      <c r="R36" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-11-22 07:30:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>China Chinese Super League</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>30</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Wuhan Three Towns</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Shandong Luneng</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K37" t="n">
+        <v>75</v>
+      </c>
+      <c r="L37" t="n">
+        <v>90</v>
+      </c>
+      <c r="M37" t="n">
+        <v>61</v>
+      </c>
+      <c r="N37" t="n">
+        <v>11</v>
+      </c>
+      <c r="O37" t="n">
+        <v>90</v>
+      </c>
+      <c r="P37" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>29</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-11-22 07:30:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>China Chinese Super League</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>30</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Qingdao Youth Island</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Changchun Yatai</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K38" t="n">
+        <v>57</v>
+      </c>
+      <c r="L38" t="n">
+        <v>71</v>
+      </c>
+      <c r="M38" t="n">
+        <v>36</v>
+      </c>
+      <c r="N38" t="n">
+        <v>18</v>
+      </c>
+      <c r="O38" t="n">
+        <v>83</v>
+      </c>
+      <c r="P38" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>43</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-11-22 07:30:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>China Chinese Super League</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>30</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Zhejiang FC</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Qingdao Jonoon</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K39" t="n">
+        <v>61</v>
+      </c>
+      <c r="L39" t="n">
+        <v>83</v>
+      </c>
+      <c r="M39" t="n">
+        <v>36</v>
+      </c>
+      <c r="N39" t="n">
+        <v>22</v>
+      </c>
+      <c r="O39" t="n">
+        <v>79</v>
+      </c>
+      <c r="P39" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>39</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-11-22 07:30:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>China Chinese Super League</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>30</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Beijing Guoan</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Meizhou Hakka</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="K40" t="n">
+        <v>68</v>
+      </c>
+      <c r="L40" t="n">
+        <v>90</v>
+      </c>
+      <c r="M40" t="n">
+        <v>43</v>
+      </c>
+      <c r="N40" t="n">
+        <v>14</v>
+      </c>
+      <c r="O40" t="n">
+        <v>86</v>
+      </c>
+      <c r="P40" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>36</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V40" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="W40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-11-22 07:30:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>China Chinese Super League</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>30</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Dalian Zhixing</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Shanghai SIPG</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="K41" t="n">
+        <v>57</v>
+      </c>
+      <c r="L41" t="n">
+        <v>86</v>
+      </c>
+      <c r="M41" t="n">
+        <v>43</v>
+      </c>
+      <c r="N41" t="n">
+        <v>15</v>
+      </c>
+      <c r="O41" t="n">
+        <v>86</v>
+      </c>
+      <c r="P41" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>43</v>
+      </c>
+      <c r="R41" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W41" t="n">
         <v>2.1</v>
       </c>
-      <c r="AF9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.7</v>
+      <c r="X41" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-11-22 07:30:00</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>37</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>53</v>
+      </c>
+      <c r="L42" t="n">
+        <v>68</v>
+      </c>
+      <c r="M42" t="n">
+        <v>38</v>
+      </c>
+      <c r="N42" t="n">
+        <v>28</v>
+      </c>
+      <c r="O42" t="n">
+        <v>73</v>
+      </c>
+      <c r="P42" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>54</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-11-22 07:30:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>37</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ulsan</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K43" t="n">
+        <v>49</v>
+      </c>
+      <c r="L43" t="n">
+        <v>66</v>
+      </c>
+      <c r="M43" t="n">
+        <v>21</v>
+      </c>
+      <c r="N43" t="n">
+        <v>35</v>
+      </c>
+      <c r="O43" t="n">
+        <v>65</v>
+      </c>
+      <c r="P43" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>61</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W43" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG32" headerRowCount="1">
-  <autoFilter ref="A1:AG32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG31" headerRowCount="1">
+  <autoFilter ref="A1:AG31"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG32"/>
+  <dimension ref="A1:AG31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="33.6" customWidth="1" min="2" max="2"/>
+    <col width="37.2" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="26.4" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="28.8" customWidth="1" min="4" max="4"/>
+    <col width="26.4" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,7 +675,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-24 13:45:00</t>
+          <t>2025-11-25 12:15:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -688,212 +688,212 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L2" t="n">
+        <v>55</v>
+      </c>
+      <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="K2" t="n">
-        <v>63</v>
-      </c>
-      <c r="L2" t="n">
-        <v>88</v>
-      </c>
-      <c r="M2" t="n">
-        <v>50</v>
-      </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="P2" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="R2" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="V2" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="X2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.7</v>
+        <v>2.21</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AD2" t="n">
         <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-24 15:30:00</t>
+          <t>2025-11-25 15:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.63</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1.22</v>
+        <v>1.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="J3" t="n">
-        <v>2.36</v>
+        <v>3.07</v>
       </c>
       <c r="K3" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L3" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="O3" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="P3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q3" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="R3" t="n">
-        <v>3.17</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>3.08</v>
+        <v>3.99</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>7.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="W3" t="n">
-        <v>3.72</v>
+        <v>3.28</v>
       </c>
       <c r="X3" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-24 16:00:00</t>
+          <t>2025-11-25 16:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -906,37 +906,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.41</v>
+        <v>1.82</v>
       </c>
       <c r="I4" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M4" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N4" t="n">
         <v>13</v>
@@ -945,69 +945,69 @@
         <v>88</v>
       </c>
       <c r="P4" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="R4" t="n">
-        <v>3.04</v>
+        <v>1.97</v>
       </c>
       <c r="S4" t="n">
-        <v>3.76</v>
+        <v>3.95</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="X4" t="n">
         <v>1.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-24 16:00:00</t>
+          <t>2025-11-25 17:45:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Asia AFC Champions League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1015,146 +1015,146 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="H5" t="n">
-        <v>2.07</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.89</v>
+        <v>1.46</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>2.26</v>
       </c>
       <c r="K5" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="M5" t="n">
+        <v>38</v>
+      </c>
+      <c r="N5" t="n">
+        <v>25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>75</v>
+      </c>
+      <c r="P5" t="n">
         <v>50</v>
       </c>
-      <c r="N5" t="n">
-        <v>13</v>
-      </c>
-      <c r="O5" t="n">
-        <v>88</v>
-      </c>
-      <c r="P5" t="n">
-        <v>63</v>
-      </c>
       <c r="Q5" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>3.81</v>
       </c>
       <c r="S5" t="n">
-        <v>4.85</v>
+        <v>3.57</v>
       </c>
       <c r="T5" t="n">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
         <v>2.3</v>
       </c>
       <c r="X5" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-24 16:00:00</t>
+          <t>2025-11-25 17:45:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>2.25</v>
       </c>
       <c r="G6" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="I6" t="n">
-        <v>1.02</v>
+        <v>1.59</v>
       </c>
       <c r="J6" t="n">
-        <v>2.12</v>
+        <v>3.29</v>
       </c>
       <c r="K6" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="L6" t="n">
         <v>88</v>
       </c>
       <c r="M6" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="N6" t="n">
         <v>13</v>
@@ -1163,832 +1163,832 @@
         <v>88</v>
       </c>
       <c r="P6" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="Q6" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>3.05</v>
+        <v>1.57</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>4.33</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="V6" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>4.07</v>
+        <v>2.15</v>
       </c>
       <c r="X6" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.98</v>
+        <v>2.42</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-24 17:00:00</t>
+          <t>2025-11-25 18:15:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Asia AFC Champions League</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Al Shorta</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="K7" t="n">
+        <v>75</v>
+      </c>
+      <c r="L7" t="n">
+        <v>88</v>
+      </c>
+      <c r="M7" t="n">
+        <v>38</v>
+      </c>
+      <c r="N7" t="n">
         <v>13</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>İstanbul Başakşehir</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Trabzonspor</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="K7" t="n">
-        <v>50</v>
-      </c>
-      <c r="L7" t="n">
-        <v>60</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20</v>
-      </c>
-      <c r="N7" t="n">
-        <v>50</v>
-      </c>
       <c r="O7" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="P7" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="Q7" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="R7" t="n">
-        <v>2.44</v>
+        <v>1.14</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.82</v>
+        <v>16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.88</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>3.01</v>
+        <v>1.65</v>
       </c>
       <c r="X7" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.71</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.85</v>
+        <v>4.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-24 17:00:00</t>
+          <t>2025-11-25 19:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="H8" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="I8" t="n">
-        <v>0.82</v>
+        <v>1.45</v>
       </c>
       <c r="J8" t="n">
-        <v>2.57</v>
+        <v>3.27</v>
       </c>
       <c r="K8" t="n">
+        <v>63</v>
+      </c>
+      <c r="L8" t="n">
+        <v>82</v>
+      </c>
+      <c r="M8" t="n">
         <v>50</v>
       </c>
-      <c r="L8" t="n">
-        <v>75</v>
-      </c>
-      <c r="M8" t="n">
-        <v>25</v>
-      </c>
       <c r="N8" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O8" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="P8" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="Q8" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R8" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="T8" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="U8" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="V8" t="n">
-        <v>1.88</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>3.26</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.41</v>
+        <v>3.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.14</v>
+        <v>1.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.81</v>
+        <v>3.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-24 17:30:00</t>
+          <t>2025-11-25 19:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="I9" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="J9" t="n">
-        <v>2.69</v>
+        <v>3.38</v>
       </c>
       <c r="K9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="M9" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="O9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="P9" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="Q9" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="R9" t="n">
-        <v>3.37</v>
+        <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>3.17</v>
+        <v>3.89</v>
       </c>
       <c r="T9" t="n">
-        <v>2.19</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="V9" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="W9" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="X9" t="n">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.88</v>
+        <v>2.51</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.01</v>
+        <v>3.07</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.63</v>
+        <v>2.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>1.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.59</v>
+        <v>1.48</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.05</v>
+        <v>2.31</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.61</v>
+        <v>3.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24 18:00:00</t>
+          <t>2025-11-25 19:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.43</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="H10" t="n">
-        <v>1.32</v>
+        <v>2.47</v>
       </c>
       <c r="I10" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="J10" t="n">
-        <v>2.56</v>
+        <v>4.23</v>
       </c>
       <c r="K10" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="L10" t="n">
         <v>79</v>
       </c>
       <c r="M10" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="N10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="P10" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="Q10" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="R10" t="n">
-        <v>2.13</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.37</v>
+        <v>5.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.83</v>
+        <v>6.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="V10" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>2.29</v>
+        <v>1.79</v>
       </c>
       <c r="X10" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.43</v>
+        <v>2.98</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24 18:00:00</t>
+          <t>2025-11-25 19:00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="H11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.8</v>
       </c>
-      <c r="I11" t="n">
-        <v>1.41</v>
-      </c>
       <c r="J11" t="n">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L11" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="N11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="Q11" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="R11" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="S11" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>3.78</v>
+        <v>3.32</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24 18:00:00</t>
+          <t>2025-11-25 19:45:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.4</v>
+        <v>2.13</v>
       </c>
       <c r="G12" t="n">
-        <v>0.75</v>
+        <v>1.33</v>
       </c>
       <c r="H12" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="I12" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="J12" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="K12" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="L12" t="n">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O12" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="P12" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="Q12" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="R12" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.25</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.83</v>
+        <v>3.31</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24 18:15:00</t>
+          <t>2025-11-25 19:45:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Asia AFC Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="K13" t="n">
+        <v>54</v>
+      </c>
+      <c r="L13" t="n">
+        <v>66</v>
+      </c>
+      <c r="M13" t="n">
+        <v>26</v>
+      </c>
+      <c r="N13" t="n">
+        <v>34</v>
+      </c>
+      <c r="O13" t="n">
+        <v>66</v>
+      </c>
+      <c r="P13" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>41</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE13" t="n">
         <v>2.5</v>
       </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="K13" t="n">
-        <v>63</v>
-      </c>
-      <c r="L13" t="n">
-        <v>100</v>
-      </c>
-      <c r="M13" t="n">
-        <v>63</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>100</v>
-      </c>
-      <c r="P13" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>13</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>9</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AF13" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24 18:30:00</t>
+          <t>2025-11-25 19:45:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1996,108 +1996,108 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="G14" t="n">
-        <v>1.88</v>
+        <v>1.13</v>
       </c>
       <c r="H14" t="n">
         <v>1.46</v>
       </c>
       <c r="I14" t="n">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="J14" t="n">
-        <v>3.08</v>
+        <v>2.73</v>
       </c>
       <c r="K14" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="L14" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="M14" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="O14" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="P14" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="Q14" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="R14" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="S14" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="W14" t="n">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="X14" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.18</v>
+        <v>1.76</v>
       </c>
       <c r="AD14" t="n">
         <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>2.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24 19:00:00</t>
+          <t>2025-11-25 19:45:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2105,108 +2105,108 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="G15" t="n">
-        <v>0.88</v>
+        <v>1.57</v>
       </c>
       <c r="H15" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="I15" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K15" t="n">
+        <v>73</v>
+      </c>
+      <c r="L15" t="n">
+        <v>73</v>
+      </c>
+      <c r="M15" t="n">
+        <v>26</v>
+      </c>
+      <c r="N15" t="n">
+        <v>27</v>
+      </c>
+      <c r="O15" t="n">
+        <v>73</v>
+      </c>
+      <c r="P15" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>47</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.39</v>
       </c>
-      <c r="J15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="K15" t="n">
-        <v>50</v>
-      </c>
-      <c r="L15" t="n">
-        <v>82</v>
-      </c>
-      <c r="M15" t="n">
-        <v>32</v>
-      </c>
-      <c r="N15" t="n">
-        <v>19</v>
-      </c>
-      <c r="O15" t="n">
-        <v>82</v>
-      </c>
-      <c r="P15" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>51</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="AC15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE15" t="n">
         <v>3.4</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AF15" t="n">
-        <v>3.2</v>
+        <v>2.39</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24 19:00:00</t>
+          <t>2025-11-25 19:45:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2214,108 +2214,108 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="G16" t="n">
-        <v>0.29</v>
+        <v>1.29</v>
       </c>
       <c r="H16" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="I16" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="J16" t="n">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
       <c r="K16" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L16" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M16" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N16" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O16" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="P16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="Q16" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="R16" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="W16" t="n">
-        <v>2.38</v>
+        <v>3.94</v>
       </c>
       <c r="X16" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.36</v>
+        <v>2.79</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-24 19:00:00</t>
+          <t>2025-11-25 19:45:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2323,697 +2323,697 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K17" t="n">
+        <v>60</v>
+      </c>
+      <c r="L17" t="n">
+        <v>59</v>
+      </c>
+      <c r="M17" t="n">
+        <v>32</v>
+      </c>
+      <c r="N17" t="n">
+        <v>34</v>
+      </c>
+      <c r="O17" t="n">
+        <v>67</v>
+      </c>
+      <c r="P17" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>41</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.5</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K17" t="n">
-        <v>63</v>
-      </c>
-      <c r="L17" t="n">
-        <v>76</v>
-      </c>
-      <c r="M17" t="n">
-        <v>57</v>
-      </c>
-      <c r="N17" t="n">
-        <v>19</v>
-      </c>
-      <c r="O17" t="n">
-        <v>82</v>
-      </c>
-      <c r="P17" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>26</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.35</v>
+        <v>3.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-24 19:00:00</t>
+          <t>2025-11-25 19:45:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="G18" t="n">
-        <v>1.29</v>
+        <v>1.71</v>
       </c>
       <c r="H18" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="I18" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="J18" t="n">
-        <v>3.57</v>
+        <v>2.91</v>
       </c>
       <c r="K18" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L18" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="M18" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="N18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O18" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P18" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="Q18" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R18" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.41</v>
       </c>
       <c r="T18" t="n">
-        <v>3.7</v>
+        <v>2.46</v>
       </c>
       <c r="U18" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.51</v>
+        <v>1.78</v>
       </c>
       <c r="W18" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="X18" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.39</v>
+        <v>2.16</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-24 19:30:00</t>
+          <t>2025-11-25 20:00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="H19" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="I19" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="J19" t="n">
-        <v>2.73</v>
+        <v>3.14</v>
       </c>
       <c r="K19" t="n">
+        <v>66</v>
+      </c>
+      <c r="L19" t="n">
         <v>59</v>
       </c>
-      <c r="L19" t="n">
-        <v>67</v>
-      </c>
       <c r="M19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N19" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="O19" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="P19" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="Q19" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R19" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="S19" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="T19" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="V19" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="W19" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="X19" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.42</v>
+        <v>2.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-24 19:30:00</t>
+          <t>2025-11-25 20:00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="H20" t="n">
-        <v>1.15</v>
+        <v>1.39</v>
       </c>
       <c r="I20" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="J20" t="n">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="K20" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="L20" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="M20" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="N20" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O20" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P20" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="Q20" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="R20" t="n">
-        <v>3.45</v>
+        <v>1.72</v>
       </c>
       <c r="S20" t="n">
-        <v>3.19</v>
+        <v>3.88</v>
       </c>
       <c r="T20" t="n">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="V20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.2</v>
       </c>
-      <c r="W20" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-24 19:45:00</t>
+          <t>2025-11-25 20:00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88</v>
+      </c>
+      <c r="L21" t="n">
+        <v>88</v>
+      </c>
+      <c r="M21" t="n">
+        <v>75</v>
+      </c>
+      <c r="N21" t="n">
+        <v>13</v>
+      </c>
+      <c r="O21" t="n">
+        <v>88</v>
+      </c>
+      <c r="P21" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>13</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.2</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="K21" t="n">
-        <v>60</v>
-      </c>
-      <c r="L21" t="n">
-        <v>90</v>
-      </c>
-      <c r="M21" t="n">
-        <v>30</v>
-      </c>
-      <c r="N21" t="n">
-        <v>20</v>
-      </c>
-      <c r="O21" t="n">
-        <v>80</v>
-      </c>
-      <c r="P21" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>40</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="AE21" t="n">
         <v>2.07</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>3.42</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.58</v>
+        <v>4.05</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11-24 20:00:00</t>
+          <t>2025-11-25 20:00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.86</v>
+        <v>0.83</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.78</v>
       </c>
       <c r="J22" t="n">
-        <v>2.6</v>
+        <v>3.44</v>
       </c>
       <c r="K22" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="L22" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M22" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="N22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O22" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P22" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="Q22" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="R22" t="n">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.93</v>
       </c>
       <c r="T22" t="n">
-        <v>3.94</v>
+        <v>1.99</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="V22" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="W22" t="n">
-        <v>3.88</v>
+        <v>2.45</v>
       </c>
       <c r="X22" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.56</v>
+        <v>3.18</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-11-24 20:00:00</t>
+          <t>2025-11-25 20:00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8</v>
+        <v>1.25</v>
       </c>
       <c r="H23" t="n">
-        <v>1.92</v>
+        <v>2.21</v>
       </c>
       <c r="I23" t="n">
-        <v>0.92</v>
+        <v>1.15</v>
       </c>
       <c r="J23" t="n">
-        <v>2.84</v>
+        <v>3.36</v>
       </c>
       <c r="K23" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L23" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="M23" t="n">
         <v>50</v>
       </c>
       <c r="N23" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="O23" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="P23" t="n">
         <v>50</v>
@@ -3022,821 +3022,821 @@
         <v>50</v>
       </c>
       <c r="R23" t="n">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>4.05</v>
+        <v>6.2</v>
       </c>
       <c r="T23" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="V23" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="W23" t="n">
-        <v>2.72</v>
+        <v>1.86</v>
       </c>
       <c r="X23" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.35</v>
+        <v>4.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-11-24 20:00:00</t>
+          <t>2025-11-25 20:00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.58</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>1.12</v>
+        <v>1.49</v>
       </c>
       <c r="J24" t="n">
-        <v>2.13</v>
+        <v>2.64</v>
       </c>
       <c r="K24" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="L24" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="M24" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N24" t="n">
+        <v>23</v>
+      </c>
+      <c r="O24" t="n">
+        <v>78</v>
+      </c>
+      <c r="P24" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q24" t="n">
         <v>40</v>
       </c>
-      <c r="O24" t="n">
-        <v>61</v>
-      </c>
-      <c r="P24" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>66</v>
-      </c>
       <c r="R24" t="n">
-        <v>2.3</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>2.85</v>
+        <v>5.6</v>
       </c>
       <c r="T24" t="n">
-        <v>3.85</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="V24" t="n">
-        <v>3.15</v>
+        <v>1.54</v>
       </c>
       <c r="W24" t="n">
-        <v>6.25</v>
+        <v>2.2</v>
       </c>
       <c r="X24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE24" t="n">
         <v>2.4</v>
       </c>
-      <c r="Y24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AF24" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.23</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-11-24 22:00:00</t>
+          <t>2025-11-25 20:00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.29</v>
+        <v>0.75</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="H25" t="n">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="I25" t="n">
-        <v>1.14</v>
+        <v>1.54</v>
       </c>
       <c r="J25" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K25" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L25" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M25" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N25" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="O25" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="P25" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="Q25" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.69</v>
+        <v>2.94</v>
       </c>
       <c r="S25" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AF25" t="n">
         <v>3.2</v>
       </c>
-      <c r="T25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="W25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.59</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-11-24 22:15:00</t>
+          <t>2025-11-25 20:00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.61</v>
+        <v>0.5</v>
       </c>
       <c r="G26" t="n">
-        <v>1.68</v>
+        <v>0.75</v>
       </c>
       <c r="H26" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="I26" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="K26" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L26" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="M26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N26" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O26" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="P26" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="Q26" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="R26" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="T26" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="U26" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="V26" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="W26" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="X26" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.53</v>
+        <v>1.99</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AE26" t="n">
-        <v>3.34</v>
+        <v>2.89</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.39</v>
+        <v>2.89</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-25 23:30:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Colombia Categoria Primera A</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="G27" t="n">
         <v>0.76</v>
       </c>
       <c r="H27" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="I27" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="J27" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="K27" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="L27" t="n">
         <v>74</v>
       </c>
       <c r="M27" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="N27" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="O27" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="P27" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Q27" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="R27" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-11-25 01:00:00</t>
+          <t>2025-11-26 00:30:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.22</v>
+        <v>1.94</v>
       </c>
       <c r="G28" t="n">
-        <v>1.19</v>
+        <v>1.76</v>
       </c>
       <c r="H28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K28" t="n">
+        <v>52</v>
+      </c>
+      <c r="L28" t="n">
+        <v>55</v>
+      </c>
+      <c r="M28" t="n">
+        <v>24</v>
+      </c>
+      <c r="N28" t="n">
+        <v>31</v>
+      </c>
+      <c r="O28" t="n">
+        <v>70</v>
+      </c>
+      <c r="P28" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>52</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.45</v>
       </c>
-      <c r="I28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K28" t="n">
-        <v>32</v>
-      </c>
-      <c r="L28" t="n">
-        <v>63</v>
-      </c>
-      <c r="M28" t="n">
-        <v>18</v>
-      </c>
-      <c r="N28" t="n">
-        <v>47</v>
-      </c>
-      <c r="O28" t="n">
-        <v>53</v>
-      </c>
-      <c r="P28" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>69</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V28" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC28" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-11-25 03:00:00</t>
+          <t>2025-11-26 00:30:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>227</v>
+        <v>36</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="G29" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="H29" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="I29" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="J29" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="K29" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L29" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M29" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="N29" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="O29" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="P29" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="Q29" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="R29" t="n">
-        <v>1.68</v>
+        <v>3.92</v>
       </c>
       <c r="S29" t="n">
-        <v>4.31</v>
+        <v>3.32</v>
       </c>
       <c r="T29" t="n">
-        <v>5.4</v>
+        <v>1.78</v>
       </c>
       <c r="U29" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="W29" t="n">
-        <v>2.4</v>
+        <v>4.25</v>
       </c>
       <c r="X29" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AF29" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-11-25 07:45:00</t>
+          <t>2025-11-26 00:30:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Asia AFC Champions League</t>
+          <t>Colombia Categoria Primera A</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="G30" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9</v>
+        <v>1.53</v>
       </c>
       <c r="I30" t="n">
-        <v>1.77</v>
+        <v>1.23</v>
       </c>
       <c r="J30" t="n">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="K30" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L30" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="M30" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="N30" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="O30" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="P30" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="Q30" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="R30" t="n">
-        <v>2.82</v>
+        <v>2.16</v>
       </c>
       <c r="S30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE30" t="n">
         <v>3.25</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD30" t="n">
+      <c r="AF30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-11-25 10:00:00</t>
+          <t>2025-11-26 10:00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3849,28 +3849,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G31" t="n">
         <v>1.5</v>
       </c>
-      <c r="G31" t="n">
-        <v>1.25</v>
-      </c>
       <c r="H31" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="I31" t="n">
-        <v>1.93</v>
+        <v>0.89</v>
       </c>
       <c r="J31" t="n">
-        <v>3.13</v>
+        <v>2.36</v>
       </c>
       <c r="K31" t="n">
         <v>50</v>
@@ -3879,176 +3879,67 @@
         <v>63</v>
       </c>
       <c r="M31" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="N31" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="O31" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="P31" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="Q31" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="R31" t="n">
-        <v>3.24</v>
+        <v>2.8</v>
       </c>
       <c r="S31" t="n">
         <v>3.3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="U31" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="V31" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="W31" t="n">
-        <v>3.94</v>
+        <v>2.8</v>
       </c>
       <c r="X31" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AD31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2025-11-25 10:00:00</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Asia AFC Champions League</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>5</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Shanghai SIPG</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>FC Seoul</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>25</v>
-      </c>
-      <c r="L32" t="n">
-        <v>63</v>
-      </c>
-      <c r="M32" t="n">
-        <v>38</v>
-      </c>
-      <c r="N32" t="n">
-        <v>13</v>
-      </c>
-      <c r="O32" t="n">
-        <v>88</v>
-      </c>
-      <c r="P32" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>75</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG31" headerRowCount="1">
-  <autoFilter ref="A1:AG31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG24" headerRowCount="1">
+  <autoFilter ref="A1:AG24"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG31"/>
+  <dimension ref="A1:AG24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="37.2" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="28.8" customWidth="1" min="4" max="4"/>
-    <col width="26.4" customWidth="1" min="5" max="5"/>
+    <col width="26.4" customWidth="1" min="4" max="4"/>
+    <col width="25.2" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,7 +675,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-25 12:15:00</t>
+          <t>2025-11-26 12:15:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -688,217 +688,217 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="H2" t="n">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="J2" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="L2" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N2" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="O2" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="P2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="Q2" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R2" t="n">
-        <v>2.94</v>
+        <v>3.14</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="U2" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W2" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="X2" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-25 15:00:00</t>
+          <t>2025-11-26 17:45:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>København</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9</v>
+        <v>1.43</v>
       </c>
       <c r="I3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K3" t="n">
+        <v>28</v>
+      </c>
+      <c r="L3" t="n">
+        <v>60</v>
+      </c>
+      <c r="M3" t="n">
+        <v>24</v>
+      </c>
+      <c r="N3" t="n">
+        <v>31</v>
+      </c>
+      <c r="O3" t="n">
+        <v>69</v>
+      </c>
+      <c r="P3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>64</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>9</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.17</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="K3" t="n">
-        <v>42</v>
-      </c>
-      <c r="L3" t="n">
-        <v>42</v>
-      </c>
-      <c r="M3" t="n">
-        <v>9</v>
-      </c>
-      <c r="N3" t="n">
-        <v>42</v>
-      </c>
-      <c r="O3" t="n">
-        <v>59</v>
-      </c>
-      <c r="P3" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>59</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="T3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.27</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE3" t="n">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-25 16:00:00</t>
+          <t>2025-11-26 17:45:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Asia AFC Champions League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -906,435 +906,435 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="K4" t="n">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="L4" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="M4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="O4" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="P4" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="Q4" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="R4" t="n">
-        <v>1.97</v>
+        <v>5.1</v>
       </c>
       <c r="S4" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="V4" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="W4" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="X4" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
         <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
         <v>1.26</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.18</v>
+        <v>2.51</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-25 17:45:00</t>
+          <t>2025-11-26 18:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="G5" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="I5" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.26</v>
+        <v>2.83</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="L5" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="M5" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="N5" t="n">
+        <v>9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>92</v>
+      </c>
+      <c r="P5" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q5" t="n">
         <v>25</v>
       </c>
-      <c r="O5" t="n">
-        <v>75</v>
-      </c>
-      <c r="P5" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>50</v>
-      </c>
       <c r="R5" t="n">
-        <v>3.81</v>
+        <v>1.96</v>
       </c>
       <c r="S5" t="n">
-        <v>3.57</v>
+        <v>3.36</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE5" t="n">
         <v>2.3</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.47</v>
-      </c>
       <c r="AF5" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-25 17:45:00</t>
+          <t>2025-11-26 19:45:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="G6" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="I6" t="n">
-        <v>1.59</v>
+        <v>1.26</v>
       </c>
       <c r="J6" t="n">
-        <v>3.29</v>
+        <v>2.65</v>
       </c>
       <c r="K6" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L6" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="M6" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="N6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O6" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="P6" t="n">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="R6" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>4.33</v>
+        <v>3.63</v>
       </c>
       <c r="T6" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="W6" t="n">
-        <v>2.15</v>
+        <v>3.57</v>
       </c>
       <c r="X6" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.42</v>
+        <v>2.83</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.07</v>
+        <v>1.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>2.89</v>
       </c>
       <c r="AF6" t="n">
-        <v>3.8</v>
+        <v>2.99</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-25 18:15:00</t>
+          <t>2025-11-26 19:45:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Asia AFC Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shorta</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0.57</v>
       </c>
       <c r="G7" t="n">
-        <v>0.25</v>
+        <v>0.86</v>
       </c>
       <c r="H7" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="J7" t="n">
-        <v>3.98</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="L7" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="M7" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="N7" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="O7" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="P7" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="Q7" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R7" t="n">
-        <v>1.14</v>
+        <v>1.81</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>3.45</v>
       </c>
       <c r="T7" t="n">
-        <v>16</v>
+        <v>4.4</v>
       </c>
       <c r="U7" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.98</v>
       </c>
       <c r="W7" t="n">
-        <v>1.65</v>
+        <v>3.4</v>
       </c>
       <c r="X7" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.5</v>
+        <v>3.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.93</v>
+        <v>2.37</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.07</v>
+        <v>1.49</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>4.7</v>
+        <v>2.81</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-25 19:00:00</t>
+          <t>2025-11-26 19:45:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1342,37 +1342,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G8" t="n">
         <v>1.38</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.75</v>
-      </c>
       <c r="H8" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="J8" t="n">
-        <v>3.27</v>
+        <v>2.68</v>
       </c>
       <c r="K8" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="L8" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M8" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="N8" t="n">
         <v>19</v>
@@ -1381,69 +1381,69 @@
         <v>82</v>
       </c>
       <c r="P8" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>2.07</v>
       </c>
       <c r="S8" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="U8" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>3.38</v>
       </c>
       <c r="X8" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.35</v>
+        <v>2.01</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.9</v>
+        <v>2.89</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.71</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-25 19:00:00</t>
+          <t>2025-11-26 19:45:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1451,108 +1451,108 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="H9" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="I9" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="J9" t="n">
-        <v>3.38</v>
+        <v>3.13</v>
       </c>
       <c r="K9" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="L9" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="M9" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="N9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O9" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P9" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Q9" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="R9" t="n">
-        <v>1.96</v>
+        <v>2.44</v>
       </c>
       <c r="S9" t="n">
-        <v>3.89</v>
+        <v>3.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="W9" t="n">
-        <v>2.3</v>
+        <v>3.66</v>
       </c>
       <c r="X9" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.51</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.07</v>
+        <v>2.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.31</v>
+        <v>2.94</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.22</v>
+        <v>2.65</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-25 19:00:00</t>
+          <t>2025-11-26 20:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1560,2386 +1560,1623 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
-        <v>1.57</v>
+        <v>0.88</v>
       </c>
       <c r="H10" t="n">
-        <v>2.47</v>
+        <v>1.68</v>
       </c>
       <c r="I10" t="n">
-        <v>1.76</v>
+        <v>1.03</v>
       </c>
       <c r="J10" t="n">
-        <v>4.23</v>
+        <v>2.71</v>
       </c>
       <c r="K10" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="L10" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M10" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="O10" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="P10" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="Q10" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>2.52</v>
       </c>
       <c r="S10" t="n">
-        <v>5.4</v>
+        <v>3.13</v>
       </c>
       <c r="T10" t="n">
-        <v>6.6</v>
+        <v>2.83</v>
       </c>
       <c r="U10" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>2.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.79</v>
+        <v>4.33</v>
       </c>
       <c r="X10" t="n">
-        <v>1.45</v>
+        <v>2.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.75</v>
+        <v>1.89</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.98</v>
+        <v>2.43</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.89</v>
+        <v>3.28</v>
       </c>
       <c r="AF10" t="n">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.84</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-25 19:00:00</t>
+          <t>2025-11-26 20:00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.17</v>
+        <v>2.25</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="H11" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.51</v>
       </c>
       <c r="K11" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L11" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="M11" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O11" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="P11" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="R11" t="n">
-        <v>1.81</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="T11" t="n">
-        <v>3.32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U11" t="n">
         <v>1.08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>2.16</v>
+        <v>1.76</v>
       </c>
       <c r="X11" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="Y11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.87</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.42</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.42</v>
+        <v>1.76</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="AF11" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-25 19:45:00</t>
+          <t>2025-11-26 20:00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.13</v>
+        <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="H12" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.37</v>
+        <v>2.46</v>
       </c>
       <c r="J12" t="n">
-        <v>2.64</v>
+        <v>3.86</v>
       </c>
       <c r="K12" t="n">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="M12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="N12" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="O12" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="P12" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q12" t="n">
         <v>63</v>
       </c>
-      <c r="Q12" t="n">
-        <v>38</v>
-      </c>
       <c r="R12" t="n">
-        <v>3.57</v>
+        <v>6.9</v>
       </c>
       <c r="S12" t="n">
-        <v>3.37</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.03</v>
+        <v>1.38</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="W12" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="X12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.7</v>
       </c>
-      <c r="Y12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="AF12" t="n">
-        <v>3.31</v>
+        <v>3.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-25 19:45:00</t>
+          <t>2025-11-26 20:00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.43</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="I13" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="J13" t="n">
-        <v>3.19</v>
+        <v>3.71</v>
       </c>
       <c r="K13" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L13" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="N13" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="P13" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="Q13" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="R13" t="n">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="S13" t="n">
-        <v>3.45</v>
+        <v>3.39</v>
       </c>
       <c r="T13" t="n">
-        <v>2.52</v>
+        <v>2.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W13" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AF13" t="n">
         <v>3.14</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-25 19:45:00</t>
+          <t>2025-11-26 20:00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>1.13</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="I14" t="n">
-        <v>1.27</v>
+        <v>2.28</v>
       </c>
       <c r="J14" t="n">
-        <v>2.73</v>
+        <v>4.05</v>
       </c>
       <c r="K14" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L14" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="M14" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="Q14" t="n">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="R14" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="T14" t="n">
-        <v>3.75</v>
+        <v>3.27</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="V14" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="W14" t="n">
-        <v>3.44</v>
+        <v>2.3</v>
       </c>
       <c r="X14" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.78</v>
+        <v>2.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.88</v>
+        <v>3.33</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-25 19:45:00</t>
+          <t>2025-11-26 20:00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.13</v>
+        <v>2.25</v>
       </c>
       <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="K15" t="n">
+        <v>50</v>
+      </c>
+      <c r="L15" t="n">
+        <v>75</v>
+      </c>
+      <c r="M15" t="n">
+        <v>50</v>
+      </c>
+      <c r="N15" t="n">
+        <v>25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>75</v>
+      </c>
+      <c r="P15" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.57</v>
       </c>
-      <c r="H15" t="n">
+      <c r="AD15" t="n">
         <v>1.25</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="K15" t="n">
-        <v>73</v>
-      </c>
-      <c r="L15" t="n">
-        <v>73</v>
-      </c>
-      <c r="M15" t="n">
-        <v>26</v>
-      </c>
-      <c r="N15" t="n">
-        <v>27</v>
-      </c>
-      <c r="O15" t="n">
-        <v>73</v>
-      </c>
-      <c r="P15" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>47</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="W15" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AE15" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.39</v>
+        <v>3.54</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-25 19:45:00</t>
+          <t>2025-11-26 20:00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.13</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="H16" t="n">
-        <v>1.74</v>
+        <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="J16" t="n">
-        <v>3.12</v>
+        <v>2.32</v>
       </c>
       <c r="K16" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="L16" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="M16" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N16" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="O16" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="P16" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="Q16" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>3.51</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="V16" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="W16" t="n">
-        <v>3.94</v>
+        <v>2.7</v>
       </c>
       <c r="X16" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.79</v>
+        <v>3.36</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-25 19:45:00</t>
+          <t>2025-11-26 20:00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="G17" t="n">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>2.62</v>
+        <v>3.24</v>
       </c>
       <c r="K17" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="L17" t="n">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="M17" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="N17" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="P17" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="Q17" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="R17" t="n">
-        <v>2.01</v>
+        <v>1.71</v>
       </c>
       <c r="S17" t="n">
-        <v>3.45</v>
+        <v>3.92</v>
       </c>
       <c r="T17" t="n">
-        <v>3.53</v>
+        <v>4.33</v>
       </c>
       <c r="U17" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="V17" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="W17" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="X17" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="Y17" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.14</v>
+        <v>2.37</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-25 19:45:00</t>
+          <t>2025-11-26 22:00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="G18" t="n">
-        <v>1.71</v>
+        <v>0.76</v>
       </c>
       <c r="H18" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="I18" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="J18" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="K18" t="n">
+        <v>62</v>
+      </c>
+      <c r="L18" t="n">
+        <v>80</v>
+      </c>
+      <c r="M18" t="n">
+        <v>29</v>
+      </c>
+      <c r="N18" t="n">
+        <v>24</v>
+      </c>
+      <c r="O18" t="n">
+        <v>77</v>
+      </c>
+      <c r="P18" t="n">
         <v>59</v>
       </c>
-      <c r="L18" t="n">
-        <v>76</v>
-      </c>
-      <c r="M18" t="n">
-        <v>32</v>
-      </c>
-      <c r="N18" t="n">
-        <v>15</v>
-      </c>
-      <c r="O18" t="n">
-        <v>86</v>
-      </c>
-      <c r="P18" t="n">
-        <v>56</v>
-      </c>
       <c r="Q18" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="R18" t="n">
-        <v>2.38</v>
+        <v>1.96</v>
       </c>
       <c r="S18" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.46</v>
+        <v>3.31</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V18" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="W18" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="X18" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-25 20:00:00</t>
+          <t>2025-11-26 23:30:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Colombia Categoria Primera A</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.29</v>
+        <v>2.05</v>
       </c>
       <c r="G19" t="n">
-        <v>1.38</v>
+        <v>0.76</v>
       </c>
       <c r="H19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K19" t="n">
+        <v>38</v>
+      </c>
+      <c r="L19" t="n">
+        <v>74</v>
+      </c>
+      <c r="M19" t="n">
+        <v>31</v>
+      </c>
+      <c r="N19" t="n">
+        <v>29</v>
+      </c>
+      <c r="O19" t="n">
+        <v>71</v>
+      </c>
+      <c r="P19" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>62</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.72</v>
       </c>
-      <c r="I19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="K19" t="n">
-        <v>66</v>
-      </c>
-      <c r="L19" t="n">
-        <v>59</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20</v>
-      </c>
-      <c r="N19" t="n">
-        <v>27</v>
-      </c>
-      <c r="O19" t="n">
-        <v>73</v>
-      </c>
-      <c r="P19" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>48</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.38</v>
-      </c>
       <c r="S19" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
-        <v>2.84</v>
+        <v>4.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="V19" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="W19" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="X19" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.08</v>
+        <v>1.51</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.93</v>
+        <v>2.87</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.62</v>
+        <v>2.99</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-25 20:00:00</t>
+          <t>2025-11-27 00:30:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="G20" t="n">
-        <v>0.25</v>
+        <v>1.48</v>
       </c>
       <c r="H20" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="I20" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="J20" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="K20" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L20" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="M20" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="N20" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="O20" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="P20" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="Q20" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="R20" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="S20" t="n">
-        <v>3.88</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="V20" t="n">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="W20" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="X20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.65</v>
       </c>
-      <c r="Y20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE20" t="n">
-        <v>2.48</v>
+        <v>3.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.1</v>
+        <v>2.16</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-25 20:00:00</t>
+          <t>2025-11-27 01:00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Mexico Liga MX</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Juárez</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="G21" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="H21" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="I21" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="J21" t="n">
-        <v>3.48</v>
+        <v>3.07</v>
       </c>
       <c r="K21" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="L21" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="M21" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="N21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O21" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="P21" t="n">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="R21" t="n">
-        <v>2.23</v>
+        <v>3.08</v>
       </c>
       <c r="S21" t="n">
-        <v>3.84</v>
+        <v>3.21</v>
       </c>
       <c r="T21" t="n">
-        <v>2.78</v>
+        <v>2.07</v>
       </c>
       <c r="U21" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="W21" t="n">
-        <v>1.98</v>
+        <v>3.2</v>
       </c>
       <c r="X21" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.07</v>
+        <v>2.82</v>
       </c>
       <c r="AF21" t="n">
-        <v>4.05</v>
+        <v>3.17</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11-25 20:00:00</t>
+          <t>2025-11-27 01:30:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Colombia Categoria Primera A</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Junior</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.83</v>
+        <v>2.17</v>
       </c>
       <c r="G22" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="H22" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="I22" t="n">
-        <v>1.78</v>
+        <v>1.13</v>
       </c>
       <c r="J22" t="n">
-        <v>3.44</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
+        <v>52</v>
+      </c>
+      <c r="L22" t="n">
+        <v>73</v>
+      </c>
+      <c r="M22" t="n">
+        <v>33</v>
+      </c>
+      <c r="N22" t="n">
+        <v>29</v>
+      </c>
+      <c r="O22" t="n">
         <v>71</v>
       </c>
-      <c r="L22" t="n">
-        <v>67</v>
-      </c>
-      <c r="M22" t="n">
-        <v>38</v>
-      </c>
-      <c r="N22" t="n">
-        <v>21</v>
-      </c>
-      <c r="O22" t="n">
-        <v>79</v>
-      </c>
       <c r="P22" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="Q22" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="R22" t="n">
-        <v>3.2</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="T22" t="n">
-        <v>1.99</v>
+        <v>5.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="X22" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-11-25 20:00:00</t>
+          <t>2025-11-27 03:05:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Mexico Liga MX</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>América</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="G23" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>2.21</v>
+        <v>1.59</v>
       </c>
       <c r="I23" t="n">
-        <v>1.15</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="K23" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L23" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="M23" t="n">
         <v>50</v>
       </c>
       <c r="N23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O23" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P23" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="Q23" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>2.85</v>
       </c>
       <c r="S23" t="n">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
-        <v>11</v>
+        <v>2.29</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="V23" t="n">
-        <v>1.35</v>
+        <v>1.86</v>
       </c>
       <c r="W23" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="X23" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.03</v>
+        <v>2.56</v>
       </c>
       <c r="AF23" t="n">
-        <v>4.15</v>
+        <v>2.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-11-25 20:00:00</t>
+          <t>2025-11-27 05:00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Mexico Liga MX</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G24" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="H24" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="I24" t="n">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="J24" t="n">
-        <v>2.64</v>
+        <v>3.26</v>
       </c>
       <c r="K24" t="n">
+        <v>52</v>
+      </c>
+      <c r="L24" t="n">
+        <v>60</v>
+      </c>
+      <c r="M24" t="n">
+        <v>32</v>
+      </c>
+      <c r="N24" t="n">
+        <v>21</v>
+      </c>
+      <c r="O24" t="n">
+        <v>80</v>
+      </c>
+      <c r="P24" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q24" t="n">
         <v>55</v>
       </c>
-      <c r="L24" t="n">
-        <v>75</v>
-      </c>
-      <c r="M24" t="n">
-        <v>38</v>
-      </c>
-      <c r="N24" t="n">
-        <v>23</v>
-      </c>
-      <c r="O24" t="n">
-        <v>78</v>
-      </c>
-      <c r="P24" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>40</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>3.55</v>
       </c>
       <c r="S24" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>9.300000000000001</v>
+        <v>1.98</v>
       </c>
       <c r="U24" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="W24" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="X24" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2025-11-25 20:00:00</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Olympique Marseille</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Newcastle United</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K25" t="n">
-        <v>38</v>
-      </c>
-      <c r="L25" t="n">
-        <v>75</v>
-      </c>
-      <c r="M25" t="n">
-        <v>38</v>
-      </c>
-      <c r="N25" t="n">
-        <v>13</v>
-      </c>
-      <c r="O25" t="n">
-        <v>88</v>
-      </c>
-      <c r="P25" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>25</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2025-11-25 20:00:00</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>5</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Slavia Praha</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Athletic Club Bilbao</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K26" t="n">
-        <v>38</v>
-      </c>
-      <c r="L26" t="n">
-        <v>75</v>
-      </c>
-      <c r="M26" t="n">
-        <v>25</v>
-      </c>
-      <c r="N26" t="n">
-        <v>13</v>
-      </c>
-      <c r="O26" t="n">
-        <v>88</v>
-      </c>
-      <c r="P26" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>38</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2025-11-25 23:30:00</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Colombia Categoria Primera A</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Fortaleza CEIF</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K27" t="n">
-        <v>38</v>
-      </c>
-      <c r="L27" t="n">
-        <v>74</v>
-      </c>
-      <c r="M27" t="n">
-        <v>31</v>
-      </c>
-      <c r="N27" t="n">
-        <v>29</v>
-      </c>
-      <c r="O27" t="n">
-        <v>71</v>
-      </c>
-      <c r="P27" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>62</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:30:00</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>36</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Atlético Mineiro</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="K28" t="n">
-        <v>52</v>
-      </c>
-      <c r="L28" t="n">
-        <v>55</v>
-      </c>
-      <c r="M28" t="n">
-        <v>24</v>
-      </c>
-      <c r="N28" t="n">
-        <v>31</v>
-      </c>
-      <c r="O28" t="n">
-        <v>70</v>
-      </c>
-      <c r="P28" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>52</v>
-      </c>
-      <c r="R28" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:30:00</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>36</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Grêmio</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="K29" t="n">
-        <v>55</v>
-      </c>
-      <c r="L29" t="n">
-        <v>67</v>
-      </c>
-      <c r="M29" t="n">
-        <v>31</v>
-      </c>
-      <c r="N29" t="n">
-        <v>33</v>
-      </c>
-      <c r="O29" t="n">
-        <v>67</v>
-      </c>
-      <c r="P29" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>60</v>
-      </c>
-      <c r="R29" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W29" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:30:00</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Colombia Categoria Primera A</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>3</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Deportes Tolima</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="H30" t="n">
         <v>1.53</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K30" t="n">
-        <v>45</v>
-      </c>
-      <c r="L30" t="n">
-        <v>70</v>
-      </c>
-      <c r="M30" t="n">
-        <v>27</v>
-      </c>
-      <c r="N30" t="n">
-        <v>39</v>
-      </c>
-      <c r="O30" t="n">
-        <v>62</v>
-      </c>
-      <c r="P30" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>62</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2025-11-26 10:00:00</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Asia AFC Champions League</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>5</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Ulsan</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Buriram United</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="K31" t="n">
-        <v>50</v>
-      </c>
-      <c r="L31" t="n">
-        <v>63</v>
-      </c>
-      <c r="M31" t="n">
-        <v>13</v>
-      </c>
-      <c r="N31" t="n">
-        <v>25</v>
-      </c>
-      <c r="O31" t="n">
-        <v>75</v>
-      </c>
-      <c r="P31" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>50</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG24" headerRowCount="1">
-  <autoFilter ref="A1:AG24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG40" headerRowCount="1">
+  <autoFilter ref="A1:AG40"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG24"/>
+  <dimension ref="A1:AG40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="45.6" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="26.4" customWidth="1" min="4" max="4"/>
-    <col width="25.2" customWidth="1" min="5" max="5"/>
+    <col width="27.6" customWidth="1" min="4" max="4"/>
+    <col width="28.8" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,12 +675,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-26 12:15:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Asia AFC Champions League</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -688,43 +688,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="I2" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="J2" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="K2" t="n">
+        <v>63</v>
+      </c>
+      <c r="L2" t="n">
+        <v>88</v>
+      </c>
+      <c r="M2" t="n">
         <v>50</v>
       </c>
-      <c r="L2" t="n">
-        <v>38</v>
-      </c>
-      <c r="M2" t="n">
-        <v>25</v>
-      </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="P2" t="n">
         <v>50</v>
@@ -733,63 +733,63 @@
         <v>50</v>
       </c>
       <c r="R2" t="n">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="W2" t="n">
-        <v>2.61</v>
+        <v>3.4</v>
       </c>
       <c r="X2" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.51</v>
+        <v>2.93</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-26 17:45:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -797,108 +797,108 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.08</v>
+        <v>2.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.43</v>
+        <v>1.86</v>
       </c>
       <c r="I3" t="n">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="J3" t="n">
-        <v>2.75</v>
+        <v>3.82</v>
       </c>
       <c r="K3" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="L3" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="M3" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="N3" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="P3" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="Q3" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T3" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="X3" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-26 17:45:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -906,2005 +906,2005 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="G4" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="I4" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="J4" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="K4" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="L4" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="M4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N4" t="n">
+        <v>38</v>
+      </c>
+      <c r="O4" t="n">
+        <v>63</v>
+      </c>
+      <c r="P4" t="n">
         <v>50</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>50</v>
       </c>
-      <c r="P4" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>65</v>
-      </c>
       <c r="R4" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6</v>
+        <v>7.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="W4" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="X4" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.36</v>
+        <v>3.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-26 18:00:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="J5" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="K5" t="n">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="M5" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="O5" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="P5" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.96</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.36</v>
+        <v>5.4</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>11.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-26 19:45:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="G6" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="J6" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="K6" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="M6" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="N6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="O6" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="P6" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="Q6" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="R6" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>3.63</v>
+        <v>4.3</v>
       </c>
       <c r="T6" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="W6" t="n">
-        <v>3.57</v>
+        <v>2.88</v>
       </c>
       <c r="X6" t="n">
         <v>2</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.83</v>
+        <v>2.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.89</v>
+        <v>2.64</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-26 19:45:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.57</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.86</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="I7" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7</v>
+        <v>3.23</v>
       </c>
       <c r="K7" t="n">
+        <v>63</v>
+      </c>
+      <c r="L7" t="n">
+        <v>75</v>
+      </c>
+      <c r="M7" t="n">
         <v>50</v>
       </c>
-      <c r="L7" t="n">
-        <v>72</v>
-      </c>
-      <c r="M7" t="n">
-        <v>22</v>
-      </c>
       <c r="N7" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="O7" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="P7" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="Q7" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R7" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="W7" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="X7" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.24</v>
+        <v>2.37</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.49</v>
+        <v>2.11</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF7" t="n">
         <v>3.1</v>
       </c>
-      <c r="AF7" t="n">
-        <v>2.81</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-26 19:45:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="G8" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="I8" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="J8" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="M8" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O8" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="P8" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="R8" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="T8" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="V8" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="W8" t="n">
-        <v>3.38</v>
+        <v>2.4</v>
       </c>
       <c r="X8" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AB8" t="n">
         <v>1.31</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-26 19:45:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="H9" t="n">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="I9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="J9" t="n">
-        <v>3.13</v>
+        <v>3.39</v>
       </c>
       <c r="K9" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="L9" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="M9" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="N9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="R9" t="n">
-        <v>2.44</v>
+        <v>4.5</v>
       </c>
       <c r="S9" t="n">
-        <v>3.31</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="W9" t="n">
-        <v>3.66</v>
+        <v>3.36</v>
       </c>
       <c r="X9" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-26 20:00:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G10" t="n">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="I10" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="J10" t="n">
-        <v>2.71</v>
+        <v>2.95</v>
       </c>
       <c r="K10" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="N10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O10" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="P10" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="Q10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="R10" t="n">
-        <v>2.52</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>3.13</v>
+        <v>4.15</v>
       </c>
       <c r="T10" t="n">
-        <v>2.83</v>
+        <v>5.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2.28</v>
       </c>
-      <c r="W10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC10" t="n">
         <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.28</v>
+        <v>2.61</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.42</v>
+        <v>3.34</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-26 20:00:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="I11" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="J11" t="n">
-        <v>3.51</v>
+        <v>2.97</v>
       </c>
       <c r="K11" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="L11" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="M11" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="N11" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="O11" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="P11" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>6.89</v>
       </c>
       <c r="T11" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.87</v>
+        <v>2.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>4.6</v>
+        <v>3.66</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-26 20:00:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>44</v>
+      </c>
+      <c r="L12" t="n">
+        <v>80</v>
+      </c>
+      <c r="M12" t="n">
+        <v>27</v>
+      </c>
+      <c r="N12" t="n">
+        <v>30</v>
+      </c>
+      <c r="O12" t="n">
+        <v>70</v>
+      </c>
+      <c r="P12" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>47</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z12" t="n">
         <v>2.25</v>
       </c>
-      <c r="H12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="K12" t="n">
-        <v>38</v>
-      </c>
-      <c r="L12" t="n">
-        <v>63</v>
-      </c>
-      <c r="M12" t="n">
-        <v>25</v>
-      </c>
-      <c r="N12" t="n">
-        <v>38</v>
-      </c>
-      <c r="O12" t="n">
-        <v>63</v>
-      </c>
-      <c r="P12" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>63</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="AA12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.63</v>
       </c>
-      <c r="W12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z12" t="n">
+      <c r="AC12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE12" t="n">
         <v>2.7</v>
       </c>
-      <c r="AA12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AF12" t="n">
-        <v>3.75</v>
+        <v>3.02</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-26 20:00:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="H13" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="I13" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="J13" t="n">
-        <v>3.71</v>
+        <v>3.59</v>
       </c>
       <c r="K13" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="L13" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M13" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O13" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="P13" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="R13" t="n">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="S13" t="n">
-        <v>3.39</v>
+        <v>4.21</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>3.77</v>
       </c>
       <c r="U13" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="V13" t="n">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>3.13</v>
+        <v>2.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.2</v>
+        <v>2.71</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.64</v>
+        <v>2.13</v>
       </c>
       <c r="AF13" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-26 20:00:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1.77</v>
+        <v>1.31</v>
       </c>
       <c r="I14" t="n">
-        <v>2.28</v>
+        <v>1.45</v>
       </c>
       <c r="J14" t="n">
-        <v>4.05</v>
+        <v>2.76</v>
       </c>
       <c r="K14" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M14" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="O14" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="P14" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="R14" t="n">
-        <v>2.07</v>
+        <v>2.66</v>
       </c>
       <c r="S14" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
-        <v>3.27</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.33</v>
+        <v>2.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-26 20:00:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="H15" t="n">
-        <v>2.46</v>
+        <v>1.65</v>
       </c>
       <c r="I15" t="n">
-        <v>1.22</v>
+        <v>1.86</v>
       </c>
       <c r="J15" t="n">
-        <v>3.68</v>
+        <v>3.51</v>
       </c>
       <c r="K15" t="n">
+        <v>45</v>
+      </c>
+      <c r="L15" t="n">
+        <v>67</v>
+      </c>
+      <c r="M15" t="n">
+        <v>34</v>
+      </c>
+      <c r="N15" t="n">
+        <v>22</v>
+      </c>
+      <c r="O15" t="n">
+        <v>78</v>
+      </c>
+      <c r="P15" t="n">
         <v>50</v>
       </c>
-      <c r="L15" t="n">
-        <v>75</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="Q15" t="n">
         <v>50</v>
       </c>
-      <c r="N15" t="n">
-        <v>25</v>
-      </c>
-      <c r="O15" t="n">
-        <v>75</v>
-      </c>
-      <c r="P15" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>25</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.86</v>
       </c>
       <c r="S15" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="T15" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3</v>
+        <v>3.24</v>
       </c>
       <c r="X15" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.87</v>
+        <v>2.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.23</v>
+        <v>1.71</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>2.89</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.54</v>
+        <v>2.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-26 20:00:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="G16" t="n">
-        <v>1.75</v>
-      </c>
       <c r="H16" t="n">
-        <v>0.88</v>
+        <v>1.48</v>
       </c>
       <c r="I16" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="J16" t="n">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="K16" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="L16" t="n">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="M16" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N16" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="O16" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="P16" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="Q16" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="R16" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>3.51</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="V16" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="X16" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.42</v>
+        <v>2.69</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.36</v>
+        <v>2.94</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-26 20:00:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="H17" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.24</v>
+        <v>2.97</v>
       </c>
       <c r="K17" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="L17" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N17" t="n">
         <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P17" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.71</v>
+        <v>2.35</v>
       </c>
       <c r="S17" t="n">
-        <v>3.92</v>
+        <v>3.45</v>
       </c>
       <c r="T17" t="n">
-        <v>4.33</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="V17" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="Y17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2.46</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AA17" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.36</v>
+        <v>2.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-26 22:00:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.76</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.59</v>
+        <v>1.19</v>
       </c>
       <c r="I18" t="n">
-        <v>1.17</v>
+        <v>2.06</v>
       </c>
       <c r="J18" t="n">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="L18" t="n">
         <v>80</v>
       </c>
       <c r="M18" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="N18" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O18" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P18" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="Q18" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="R18" t="n">
-        <v>1.96</v>
+        <v>4.6</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>3.31</v>
+        <v>1.67</v>
       </c>
       <c r="U18" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="V18" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="W18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AF18" t="n">
         <v>2.9</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.94</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-26 23:30:00</t>
+          <t>2025-11-27 17:45:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Colombia Categoria Primera A</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="G19" t="n">
-        <v>0.76</v>
+        <v>2.4</v>
       </c>
       <c r="H19" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="I19" t="n">
-        <v>1.27</v>
+        <v>1.79</v>
       </c>
       <c r="J19" t="n">
-        <v>2.86</v>
+        <v>3.17</v>
       </c>
       <c r="K19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="L19" t="n">
         <v>74</v>
       </c>
       <c r="M19" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="N19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="O19" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="P19" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="Q19" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="R19" t="n">
-        <v>1.72</v>
+        <v>4.2</v>
       </c>
       <c r="S19" t="n">
-        <v>3.18</v>
+        <v>3.7</v>
       </c>
       <c r="T19" t="n">
-        <v>4.5</v>
+        <v>1.81</v>
       </c>
       <c r="U19" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="W19" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="X19" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.88</v>
       </c>
-      <c r="AA19" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.87</v>
+        <v>1.84</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-27 00:30:00</t>
+          <t>2025-11-27 20:00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="H20" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="I20" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="K20" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L20" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="M20" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N20" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="O20" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="P20" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="Q20" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="R20" t="n">
-        <v>2.07</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="V20" t="n">
-        <v>2.62</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>5.5</v>
+        <v>2.55</v>
       </c>
       <c r="X20" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.88</v>
+        <v>2.27</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AC20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE20" t="n">
         <v>2.46</v>
       </c>
-      <c r="AD20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AF20" t="n">
-        <v>2.16</v>
+        <v>3.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-27 01:00:00</t>
+          <t>2025-11-27 20:00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mexico Liga MX</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Juárez</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="I21" t="n">
-        <v>1.77</v>
+        <v>1.12</v>
       </c>
       <c r="J21" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="K21" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="L21" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="M21" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="O21" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="P21" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="Q21" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="R21" t="n">
-        <v>3.08</v>
+        <v>1.78</v>
       </c>
       <c r="S21" t="n">
-        <v>3.21</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.07</v>
+        <v>4.7</v>
       </c>
       <c r="U21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="W21" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11-27 01:30:00</t>
+          <t>2025-11-27 20:00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Colombia Categoria Primera A</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.17</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="H22" t="n">
-        <v>1.92</v>
+        <v>1.14</v>
       </c>
       <c r="I22" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="K22" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L22" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M22" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N22" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="O22" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="P22" t="n">
         <v>50</v>
@@ -2913,270 +2913,2014 @@
         <v>50</v>
       </c>
       <c r="R22" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="S22" t="n">
-        <v>3.91</v>
+        <v>3.8</v>
       </c>
       <c r="T22" t="n">
         <v>5.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="W22" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="X22" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-11-27 03:05:00</t>
+          <t>2025-11-27 20:00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mexico Liga MX</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>América</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.82</v>
+        <v>1.25</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="H23" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="J23" t="n">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="L23" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="M23" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="N23" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="O23" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="P23" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="Q23" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="R23" t="n">
-        <v>2.85</v>
+        <v>1.55</v>
       </c>
       <c r="S23" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="T23" t="n">
-        <v>2.29</v>
+        <v>6.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="W23" t="n">
         <v>2.8</v>
       </c>
       <c r="X23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.62</v>
       </c>
-      <c r="Y23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AC23" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-11-27 05:00:00</t>
+          <t>2025-11-27 20:00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mexico Liga MX</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1.5</v>
       </c>
       <c r="G24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K24" t="n">
+        <v>38</v>
+      </c>
+      <c r="L24" t="n">
+        <v>50</v>
+      </c>
+      <c r="M24" t="n">
+        <v>13</v>
+      </c>
+      <c r="N24" t="n">
+        <v>25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>75</v>
+      </c>
+      <c r="P24" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>63</v>
+      </c>
+      <c r="R24" t="n">
+        <v>5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-11-27 20:00:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>50</v>
+      </c>
+      <c r="L25" t="n">
+        <v>84</v>
+      </c>
+      <c r="M25" t="n">
+        <v>25</v>
+      </c>
+      <c r="N25" t="n">
+        <v>25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>75</v>
+      </c>
+      <c r="P25" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>50</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-11-27 20:00:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Olympique Lyonnais</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K26" t="n">
+        <v>25</v>
+      </c>
+      <c r="L26" t="n">
+        <v>75</v>
+      </c>
+      <c r="M26" t="n">
+        <v>32</v>
+      </c>
+      <c r="N26" t="n">
+        <v>25</v>
+      </c>
+      <c r="O26" t="n">
+        <v>75</v>
+      </c>
+      <c r="P26" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>69</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-11-27 20:00:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Malmö FF</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K27" t="n">
+        <v>42</v>
+      </c>
+      <c r="L27" t="n">
+        <v>71</v>
+      </c>
+      <c r="M27" t="n">
+        <v>50</v>
+      </c>
+      <c r="N27" t="n">
+        <v>21</v>
+      </c>
+      <c r="O27" t="n">
+        <v>79</v>
+      </c>
+      <c r="P27" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>50</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-11-27 20:00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sporting Braga</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K28" t="n">
+        <v>28</v>
+      </c>
+      <c r="L28" t="n">
+        <v>73</v>
+      </c>
+      <c r="M28" t="n">
+        <v>50</v>
+      </c>
+      <c r="N28" t="n">
+        <v>28</v>
+      </c>
+      <c r="O28" t="n">
+        <v>73</v>
+      </c>
+      <c r="P28" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>55</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-11-27 20:00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Artsakh</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K29" t="n">
+        <v>57</v>
+      </c>
+      <c r="L29" t="n">
+        <v>84</v>
+      </c>
+      <c r="M29" t="n">
+        <v>64</v>
+      </c>
+      <c r="N29" t="n">
+        <v>27</v>
+      </c>
+      <c r="O29" t="n">
+        <v>74</v>
+      </c>
+      <c r="P29" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>37</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-11-27 20:00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Samsunspor</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K30" t="n">
+        <v>20</v>
+      </c>
+      <c r="L30" t="n">
+        <v>90</v>
+      </c>
+      <c r="M30" t="n">
+        <v>47</v>
+      </c>
+      <c r="N30" t="n">
+        <v>27</v>
+      </c>
+      <c r="O30" t="n">
+        <v>74</v>
+      </c>
+      <c r="P30" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>37</v>
+      </c>
+      <c r="R30" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Y30" t="n">
         <v>2.12</v>
       </c>
-      <c r="H24" t="n">
+      <c r="Z30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-11-27 20:00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Drita</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Shkendija</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="K31" t="n">
+        <v>47</v>
+      </c>
+      <c r="L31" t="n">
+        <v>37</v>
+      </c>
+      <c r="M31" t="n">
+        <v>27</v>
+      </c>
+      <c r="N31" t="n">
+        <v>37</v>
+      </c>
+      <c r="O31" t="n">
+        <v>64</v>
+      </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>90</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.37</v>
       </c>
-      <c r="I24" t="n">
+      <c r="V31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-11-27 20:00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I32" t="n">
         <v>1.89</v>
       </c>
-      <c r="J24" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="J32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>48</v>
+      </c>
+      <c r="L32" t="n">
+        <v>84</v>
+      </c>
+      <c r="M32" t="n">
+        <v>37</v>
+      </c>
+      <c r="N32" t="n">
+        <v>11</v>
+      </c>
+      <c r="O32" t="n">
+        <v>89</v>
+      </c>
+      <c r="P32" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>38</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-11-27 20:00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AEK Larnaca</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="K33" t="n">
+        <v>17</v>
+      </c>
+      <c r="L33" t="n">
+        <v>50</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>67</v>
+      </c>
+      <c r="O33" t="n">
+        <v>33</v>
+      </c>
+      <c r="P33" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>84</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-11-27 20:00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jagiellonia Białystok</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K34" t="n">
+        <v>67</v>
+      </c>
+      <c r="L34" t="n">
+        <v>39</v>
+      </c>
+      <c r="M34" t="n">
+        <v>33</v>
+      </c>
+      <c r="N34" t="n">
+        <v>28</v>
+      </c>
+      <c r="O34" t="n">
+        <v>73</v>
+      </c>
+      <c r="P34" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>62</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T34" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-11-27 20:00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Legia Warszawa</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sparta Praha</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K35" t="n">
+        <v>62</v>
+      </c>
+      <c r="L35" t="n">
+        <v>78</v>
+      </c>
+      <c r="M35" t="n">
+        <v>27</v>
+      </c>
+      <c r="N35" t="n">
+        <v>27</v>
+      </c>
+      <c r="O35" t="n">
+        <v>74</v>
+      </c>
+      <c r="P35" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>32</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-11-27 20:00:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K36" t="n">
+        <v>57</v>
+      </c>
+      <c r="L36" t="n">
+        <v>74</v>
+      </c>
+      <c r="M36" t="n">
+        <v>27</v>
+      </c>
+      <c r="N36" t="n">
+        <v>17</v>
+      </c>
+      <c r="O36" t="n">
+        <v>84</v>
+      </c>
+      <c r="P36" t="n">
         <v>52</v>
       </c>
-      <c r="L24" t="n">
+      <c r="Q36" t="n">
+        <v>48</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-11-27 20:00:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K37" t="n">
+        <v>50</v>
+      </c>
+      <c r="L37" t="n">
+        <v>50</v>
+      </c>
+      <c r="M37" t="n">
+        <v>30</v>
+      </c>
+      <c r="N37" t="n">
+        <v>40</v>
+      </c>
+      <c r="O37" t="n">
         <v>60</v>
       </c>
-      <c r="M24" t="n">
-        <v>32</v>
-      </c>
-      <c r="N24" t="n">
-        <v>21</v>
-      </c>
-      <c r="O24" t="n">
-        <v>80</v>
-      </c>
-      <c r="P24" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>55</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="P37" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>60</v>
+      </c>
+      <c r="R37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-11-27 23:30:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>36</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K38" t="n">
+        <v>41</v>
+      </c>
+      <c r="L38" t="n">
+        <v>68</v>
+      </c>
+      <c r="M38" t="n">
+        <v>24</v>
+      </c>
+      <c r="N38" t="n">
+        <v>35</v>
+      </c>
+      <c r="O38" t="n">
+        <v>65</v>
+      </c>
+      <c r="P38" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>59</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.63</v>
       </c>
-      <c r="W24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="Z38" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-11-27 23:30:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Colombia Categoria Primera A</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K39" t="n">
+        <v>49</v>
+      </c>
+      <c r="L39" t="n">
+        <v>64</v>
+      </c>
+      <c r="M39" t="n">
+        <v>27</v>
+      </c>
+      <c r="N39" t="n">
+        <v>29</v>
+      </c>
+      <c r="O39" t="n">
+        <v>72</v>
+      </c>
+      <c r="P39" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>61</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-11-28 02:07:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Mexico Liga MX</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>27</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Cruz Azul</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H40" t="n">
         <v>1.53</v>
       </c>
-      <c r="Y24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.53</v>
+      <c r="I40" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="K40" t="n">
+        <v>59</v>
+      </c>
+      <c r="L40" t="n">
+        <v>65</v>
+      </c>
+      <c r="M40" t="n">
+        <v>44</v>
+      </c>
+      <c r="N40" t="n">
+        <v>24</v>
+      </c>
+      <c r="O40" t="n">
+        <v>77</v>
+      </c>
+      <c r="P40" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>41</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W40" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG10" headerRowCount="1">
-  <autoFilter ref="A1:AG10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG26" headerRowCount="1">
+  <autoFilter ref="A1:AG26"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,13 +467,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG10"/>
+  <dimension ref="A1:AG26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="28.8" customWidth="1" min="2" max="2"/>
+    <col width="37.2" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="21.6" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="22.8" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
@@ -675,552 +675,552 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-02 13:30:00</t>
+          <t>2025-12-03 18:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.63</v>
+        <v>1.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.48</v>
+        <v>2.3</v>
       </c>
       <c r="K2" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="L2" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="M2" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="O2" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="P2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Q2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="R2" t="n">
-        <v>2.02</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>3.65</v>
+        <v>1.25</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="W2" t="n">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.6</v>
+        <v>2.42</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.2</v>
+        <v>1.49</v>
       </c>
       <c r="Z2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2.38</v>
       </c>
-      <c r="AA2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.24</v>
-      </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.58</v>
+        <v>2.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-02 19:30:00</t>
+          <t>2025-12-03 18:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="G3" t="n">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="I3" t="n">
-        <v>1.46</v>
+        <v>2.21</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>3.83</v>
       </c>
       <c r="K3" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O3" t="n">
         <v>59</v>
       </c>
       <c r="P3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q3" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="R3" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
         <v>1.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W3" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="X3" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
         <v>2.53</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.24</v>
+        <v>3.33</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-02 19:30:00</t>
+          <t>2025-12-03 19:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.33</v>
+        <v>0.67</v>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K4" t="n">
+        <v>62</v>
+      </c>
+      <c r="L4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N4" t="n">
+        <v>31</v>
+      </c>
+      <c r="O4" t="n">
+        <v>69</v>
+      </c>
+      <c r="P4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>61</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="T4" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.17</v>
       </c>
-      <c r="H4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="K4" t="n">
-        <v>50</v>
-      </c>
-      <c r="L4" t="n">
-        <v>67</v>
-      </c>
-      <c r="M4" t="n">
-        <v>33</v>
-      </c>
-      <c r="N4" t="n">
-        <v>33</v>
-      </c>
-      <c r="O4" t="n">
-        <v>67</v>
-      </c>
-      <c r="P4" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>59</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.3</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="X4" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-02 19:45:00</t>
+          <t>2025-12-03 19:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.38</v>
-      </c>
       <c r="H5" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="I5" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="J5" t="n">
-        <v>2.84</v>
+        <v>3.04</v>
       </c>
       <c r="K5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="L5" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="M5" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O5" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P5" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="R5" t="n">
-        <v>3.87</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.34</v>
+        <v>5.7</v>
       </c>
       <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.95</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.76</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.69</v>
+        <v>2.82</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AB5" t="n">
         <v>1.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.95</v>
+        <v>2.53</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.77</v>
+        <v>3.36</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-02 20:00:00</t>
+          <t>2025-12-03 19:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="H6" t="n">
-        <v>2.27</v>
+        <v>1.54</v>
       </c>
       <c r="I6" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="J6" t="n">
-        <v>3.68</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="L6" t="n">
+        <v>75</v>
+      </c>
+      <c r="M6" t="n">
+        <v>17</v>
+      </c>
+      <c r="N6" t="n">
+        <v>17</v>
+      </c>
+      <c r="O6" t="n">
         <v>84</v>
       </c>
-      <c r="M6" t="n">
-        <v>60</v>
-      </c>
-      <c r="N6" t="n">
-        <v>9</v>
-      </c>
-      <c r="O6" t="n">
-        <v>92</v>
-      </c>
       <c r="P6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q6" t="n">
         <v>42</v>
       </c>
       <c r="R6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.7</v>
       </c>
-      <c r="S6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Y6" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.06</v>
+        <v>2.81</v>
       </c>
       <c r="AF6" t="n">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-12-02 20:15:00</t>
+          <t>2025-12-03 19:30:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1233,424 +1233,2168 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0.17</v>
       </c>
       <c r="G7" t="n">
-        <v>2.17</v>
+        <v>0.83</v>
       </c>
       <c r="H7" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="J7" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="K7" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="L7" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="M7" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="R7" t="n">
-        <v>1.73</v>
+        <v>3.15</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>4.4</v>
+        <v>2.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="W7" t="n">
-        <v>2.5</v>
+        <v>3.54</v>
       </c>
       <c r="X7" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.2</v>
+        <v>2.47</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.44</v>
+        <v>3.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-12-02 22:00:00</t>
+          <t>2025-12-03 19:30:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.56</v>
+        <v>1.17</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="H8" t="n">
-        <v>1.61</v>
+        <v>0.77</v>
       </c>
       <c r="I8" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="J8" t="n">
-        <v>3.02</v>
+        <v>2.03</v>
       </c>
       <c r="K8" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="M8" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="N8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="O8" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="P8" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="Q8" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="R8" t="n">
-        <v>2.13</v>
+        <v>4.6</v>
       </c>
       <c r="S8" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA8" t="n">
         <v>1.9</v>
       </c>
-      <c r="W8" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.69</v>
+        <v>2.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-12-02 23:00:00</t>
+          <t>2025-12-03 19:45:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.33</v>
+        <v>1.17</v>
       </c>
       <c r="G9" t="n">
-        <v>0.39</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="I9" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="J9" t="n">
-        <v>3.01</v>
+        <v>3.21</v>
       </c>
       <c r="K9" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="L9" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="N9" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="P9" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>4.6</v>
       </c>
       <c r="S9" t="n">
-        <v>5.1</v>
+        <v>3.72</v>
       </c>
       <c r="T9" t="n">
-        <v>9</v>
+        <v>1.57</v>
       </c>
       <c r="U9" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
         <v>1.6</v>
       </c>
       <c r="W9" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="X9" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.78</v>
+        <v>3.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.09</v>
+        <v>2.29</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-12-03 00:30:00</t>
+          <t>2025-12-03 19:45:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="G10" t="n">
-        <v>0.83</v>
+        <v>0.29</v>
       </c>
       <c r="H10" t="n">
-        <v>1.52</v>
+        <v>2.43</v>
       </c>
       <c r="I10" t="n">
-        <v>1.13</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
-        <v>2.65</v>
+        <v>3.33</v>
       </c>
       <c r="K10" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M10" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="N10" t="n">
         <v>31</v>
       </c>
       <c r="O10" t="n">
+        <v>69</v>
+      </c>
+      <c r="P10" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>45</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>17</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-12-03 19:45:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>St. Mirren</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K11" t="n">
+        <v>48</v>
+      </c>
+      <c r="L11" t="n">
+        <v>54</v>
+      </c>
+      <c r="M11" t="n">
+        <v>32</v>
+      </c>
+      <c r="N11" t="n">
+        <v>30</v>
+      </c>
+      <c r="O11" t="n">
         <v>70</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P11" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>61</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-12-03 19:45:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>15</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Hearts</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Kilmarnock</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>93</v>
+      </c>
+      <c r="M12" t="n">
+        <v>62</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>93</v>
+      </c>
+      <c r="P12" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>30</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T12" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-12-03 19:45:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Falkirk</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>93</v>
+      </c>
+      <c r="L13" t="n">
+        <v>79</v>
+      </c>
+      <c r="M13" t="n">
+        <v>29</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>93</v>
+      </c>
+      <c r="P13" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>36</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-12-03 20:15:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>14</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>34</v>
+      </c>
+      <c r="L14" t="n">
+        <v>67</v>
+      </c>
+      <c r="M14" t="n">
+        <v>25</v>
+      </c>
+      <c r="N14" t="n">
+        <v>34</v>
+      </c>
+      <c r="O14" t="n">
+        <v>67</v>
+      </c>
+      <c r="P14" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>58</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-12-03 20:15:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>75</v>
+      </c>
+      <c r="M15" t="n">
+        <v>42</v>
+      </c>
+      <c r="N15" t="n">
+        <v>25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>75</v>
+      </c>
+      <c r="P15" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>33</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-12-03 22:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>47</v>
+      </c>
+      <c r="L16" t="n">
+        <v>67</v>
+      </c>
+      <c r="M16" t="n">
+        <v>28</v>
+      </c>
+      <c r="N16" t="n">
+        <v>33</v>
+      </c>
+      <c r="O16" t="n">
+        <v>67</v>
+      </c>
+      <c r="P16" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>53</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-12-03 22:00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>37</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="K17" t="n">
+        <v>39</v>
+      </c>
+      <c r="L17" t="n">
+        <v>81</v>
+      </c>
+      <c r="M17" t="n">
         <v>31</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="N17" t="n">
+        <v>31</v>
+      </c>
+      <c r="O17" t="n">
         <v>70</v>
       </c>
-      <c r="R10" t="n">
+      <c r="P17" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>64</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-12-03 22:30:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>37</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>53</v>
+      </c>
+      <c r="L18" t="n">
+        <v>78</v>
+      </c>
+      <c r="M18" t="n">
+        <v>28</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20</v>
+      </c>
+      <c r="O18" t="n">
+        <v>81</v>
+      </c>
+      <c r="P18" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>56</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-12-03 23:00:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>37</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K19" t="n">
+        <v>56</v>
+      </c>
+      <c r="L19" t="n">
+        <v>73</v>
+      </c>
+      <c r="M19" t="n">
+        <v>36</v>
+      </c>
+      <c r="N19" t="n">
+        <v>25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>75</v>
+      </c>
+      <c r="P19" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>56</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-12-03 23:00:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>37</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="K20" t="n">
+        <v>47</v>
+      </c>
+      <c r="L20" t="n">
+        <v>70</v>
+      </c>
+      <c r="M20" t="n">
+        <v>22</v>
+      </c>
+      <c r="N20" t="n">
+        <v>28</v>
+      </c>
+      <c r="O20" t="n">
+        <v>73</v>
+      </c>
+      <c r="P20" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>50</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-12-03 23:20:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Colombia Categoria Primera A</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K21" t="n">
+        <v>41</v>
+      </c>
+      <c r="L21" t="n">
+        <v>53</v>
+      </c>
+      <c r="M21" t="n">
+        <v>25</v>
+      </c>
+      <c r="N21" t="n">
+        <v>40</v>
+      </c>
+      <c r="O21" t="n">
+        <v>60</v>
+      </c>
+      <c r="P21" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>68</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:30:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>34</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="K22" t="n">
+        <v>59</v>
+      </c>
+      <c r="L22" t="n">
+        <v>62</v>
+      </c>
+      <c r="M22" t="n">
+        <v>33</v>
+      </c>
+      <c r="N22" t="n">
+        <v>32</v>
+      </c>
+      <c r="O22" t="n">
+        <v>68</v>
+      </c>
+      <c r="P22" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>50</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:30:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>37</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K23" t="n">
+        <v>36</v>
+      </c>
+      <c r="L23" t="n">
+        <v>59</v>
+      </c>
+      <c r="M23" t="n">
+        <v>28</v>
+      </c>
+      <c r="N23" t="n">
+        <v>42</v>
+      </c>
+      <c r="O23" t="n">
+        <v>58</v>
+      </c>
+      <c r="P23" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>56</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>11</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-12-04 01:00:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mexico Liga MX</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>28</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cruz Azul</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="K24" t="n">
+        <v>55</v>
+      </c>
+      <c r="L24" t="n">
+        <v>58</v>
+      </c>
+      <c r="M24" t="n">
+        <v>40</v>
+      </c>
+      <c r="N24" t="n">
+        <v>21</v>
+      </c>
+      <c r="O24" t="n">
+        <v>79</v>
+      </c>
+      <c r="P24" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>48</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-12-04 01:30:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Colombia Categoria Primera A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K25" t="n">
+        <v>42</v>
+      </c>
+      <c r="L25" t="n">
+        <v>81</v>
+      </c>
+      <c r="M25" t="n">
+        <v>32</v>
+      </c>
+      <c r="N25" t="n">
+        <v>32</v>
+      </c>
+      <c r="O25" t="n">
+        <v>69</v>
+      </c>
+      <c r="P25" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>62</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-12-04 03:10:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mexico Liga MX</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>28</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K26" t="n">
+        <v>61</v>
+      </c>
+      <c r="L26" t="n">
+        <v>87</v>
+      </c>
+      <c r="M26" t="n">
+        <v>53</v>
+      </c>
+      <c r="N26" t="n">
+        <v>19</v>
+      </c>
+      <c r="O26" t="n">
+        <v>82</v>
+      </c>
+      <c r="P26" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>37</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.6</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="U26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.33</v>
+      <c r="Y26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG8" headerRowCount="1">
-  <autoFilter ref="A1:AG8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG35" headerRowCount="1">
+  <autoFilter ref="A1:AG35"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG8"/>
+  <dimension ref="A1:AG35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="37.2" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="22.8" customWidth="1" min="4" max="4"/>
-    <col width="28.8" customWidth="1" min="5" max="5"/>
+    <col width="25.2" customWidth="1" min="4" max="4"/>
+    <col width="25.2" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,764 +675,3707 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-04 16:00:00</t>
+          <t>2025-12-05 16:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="G2" t="n">
-        <v>1.56</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K2" t="n">
+        <v>63</v>
+      </c>
+      <c r="L2" t="n">
+        <v>76</v>
+      </c>
+      <c r="M2" t="n">
+        <v>19</v>
+      </c>
+      <c r="N2" t="n">
+        <v>19</v>
+      </c>
+      <c r="O2" t="n">
+        <v>82</v>
+      </c>
+      <c r="P2" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>44</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE2" t="n">
         <v>2.77</v>
       </c>
-      <c r="K2" t="n">
-        <v>53</v>
-      </c>
-      <c r="L2" t="n">
-        <v>66</v>
-      </c>
-      <c r="M2" t="n">
-        <v>25</v>
-      </c>
-      <c r="N2" t="n">
-        <v>25</v>
-      </c>
-      <c r="O2" t="n">
-        <v>75</v>
-      </c>
-      <c r="P2" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>63</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="AF2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.42</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-04 18:30:00</t>
+          <t>2025-12-05 17:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.29</v>
+        <v>1.33</v>
       </c>
       <c r="H3" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="I3" t="n">
-        <v>0.99</v>
+        <v>1.59</v>
       </c>
       <c r="J3" t="n">
-        <v>2.41</v>
+        <v>3.23</v>
       </c>
       <c r="K3" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="L3" t="n">
         <v>77</v>
       </c>
       <c r="M3" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="O3" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="P3" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="Q3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="R3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S3" t="n">
-        <v>3.19</v>
+        <v>3.26</v>
       </c>
       <c r="T3" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.4</v>
       </c>
-      <c r="V3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="W3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AE3" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-04 19:00:00</t>
+          <t>2025-12-05 17:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.43</v>
+        <v>2.43</v>
       </c>
       <c r="G4" t="n">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.73</v>
+        <v>2.27</v>
       </c>
       <c r="I4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K4" t="n">
+        <v>77</v>
+      </c>
+      <c r="L4" t="n">
+        <v>77</v>
+      </c>
+      <c r="M4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O4" t="n">
+        <v>85</v>
+      </c>
+      <c r="P4" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC4" t="n">
         <v>1.74</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="K4" t="n">
-        <v>73</v>
-      </c>
-      <c r="L4" t="n">
-        <v>94</v>
-      </c>
-      <c r="M4" t="n">
-        <v>61</v>
-      </c>
-      <c r="N4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O4" t="n">
-        <v>94</v>
-      </c>
-      <c r="P4" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>26</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-04 20:00:00</t>
+          <t>2025-12-05 17:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="G5" t="n">
-        <v>0.83</v>
+        <v>2.14</v>
       </c>
       <c r="H5" t="n">
-        <v>2.04</v>
+        <v>1.31</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>1.67</v>
       </c>
       <c r="J5" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="K5" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="L5" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="P5" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="R5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.47</v>
       </c>
-      <c r="S5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC5" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.24</v>
+        <v>2.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-04 22:30:00</t>
+          <t>2025-12-05 17:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.33</v>
+        <v>0.71</v>
       </c>
       <c r="G6" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="H6" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="I6" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="J6" t="n">
-        <v>2.99</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L6" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="M6" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N6" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="O6" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="P6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="Q6" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="R6" t="n">
-        <v>2.09</v>
+        <v>2.68</v>
       </c>
       <c r="S6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE6" t="n">
         <v>2.9</v>
       </c>
-      <c r="T6" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W6" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF6" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-12-04 23:30:00</t>
+          <t>2025-12-05 18:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Colombia Categoria Primera A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independiente Medellín</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.12</v>
+        <v>0.88</v>
       </c>
       <c r="G7" t="n">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="H7" t="n">
-        <v>1.96</v>
+        <v>1.29</v>
       </c>
       <c r="I7" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="J7" t="n">
-        <v>3.53</v>
+        <v>2.57</v>
       </c>
       <c r="K7" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L7" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M7" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="N7" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="O7" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="P7" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="Q7" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="S7" t="n">
-        <v>3.16</v>
+        <v>3.31</v>
       </c>
       <c r="T7" t="n">
-        <v>3.63</v>
+        <v>2.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="V7" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF7" t="n">
         <v>3.34</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.69</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-12-05 01:35:00</t>
+          <t>2025-12-05 18:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Colombia Categoria Primera A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FC Penafiel</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>União de Leiria</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>44</v>
+      </c>
+      <c r="L8" t="n">
+        <v>62</v>
+      </c>
+      <c r="M8" t="n">
+        <v>17</v>
+      </c>
+      <c r="N8" t="n">
+        <v>37</v>
+      </c>
+      <c r="O8" t="n">
+        <v>64</v>
+      </c>
+      <c r="P8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>84</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-12-05 18:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K9" t="n">
+        <v>70</v>
+      </c>
+      <c r="L9" t="n">
+        <v>69</v>
+      </c>
+      <c r="M9" t="n">
+        <v>44</v>
+      </c>
+      <c r="N9" t="n">
+        <v>23</v>
+      </c>
+      <c r="O9" t="n">
+        <v>77</v>
+      </c>
+      <c r="P9" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>31</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-12-05 18:30:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>19</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Oţelul Galaţi</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Unirea Slobozia</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K10" t="n">
+        <v>62</v>
+      </c>
+      <c r="L10" t="n">
+        <v>84</v>
+      </c>
+      <c r="M10" t="n">
+        <v>33</v>
+      </c>
+      <c r="N10" t="n">
+        <v>22</v>
+      </c>
+      <c r="O10" t="n">
+        <v>78</v>
+      </c>
+      <c r="P10" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>44</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>América de Cali</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
+      <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-12-05 19:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Den Bosch</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K11" t="n">
+        <v>62</v>
+      </c>
+      <c r="L11" t="n">
+        <v>84</v>
+      </c>
+      <c r="M11" t="n">
+        <v>56</v>
+      </c>
+      <c r="N11" t="n">
+        <v>17</v>
+      </c>
+      <c r="O11" t="n">
+        <v>84</v>
+      </c>
+      <c r="P11" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>28</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-12-05 19:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ADO Den Haag</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Emmen</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="K12" t="n">
+        <v>60</v>
+      </c>
+      <c r="L12" t="n">
+        <v>66</v>
+      </c>
+      <c r="M12" t="n">
+        <v>49</v>
+      </c>
+      <c r="N12" t="n">
+        <v>11</v>
+      </c>
+      <c r="O12" t="n">
+        <v>89</v>
+      </c>
+      <c r="P12" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>29</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-12-05 19:00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>19</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Almere City</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ajax II</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="K13" t="n">
+        <v>60</v>
+      </c>
+      <c r="L13" t="n">
+        <v>78</v>
+      </c>
+      <c r="M13" t="n">
+        <v>47</v>
+      </c>
+      <c r="N13" t="n">
+        <v>12</v>
+      </c>
+      <c r="O13" t="n">
+        <v>89</v>
+      </c>
+      <c r="P13" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>30</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-12-05 19:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Helmond Sport</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MVV</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K14" t="n">
+        <v>56</v>
+      </c>
+      <c r="L14" t="n">
+        <v>84</v>
+      </c>
+      <c r="M14" t="n">
+        <v>39</v>
+      </c>
+      <c r="N14" t="n">
+        <v>28</v>
+      </c>
+      <c r="O14" t="n">
+        <v>73</v>
+      </c>
+      <c r="P14" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>33</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-12-05 19:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>19</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>VVV</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>64</v>
+      </c>
+      <c r="L15" t="n">
+        <v>88</v>
+      </c>
+      <c r="M15" t="n">
+        <v>47</v>
+      </c>
+      <c r="N15" t="n">
+        <v>12</v>
+      </c>
+      <c r="O15" t="n">
+        <v>89</v>
+      </c>
+      <c r="P15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>41</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.16</v>
       </c>
-      <c r="H8" t="n">
+      <c r="V15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-12-05 19:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Roda JC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AZ II</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K16" t="n">
+        <v>67</v>
+      </c>
+      <c r="L16" t="n">
+        <v>73</v>
+      </c>
+      <c r="M16" t="n">
+        <v>61</v>
+      </c>
+      <c r="N16" t="n">
+        <v>22</v>
+      </c>
+      <c r="O16" t="n">
+        <v>78</v>
+      </c>
+      <c r="P16" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>45</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.5</v>
       </c>
-      <c r="I8" t="n">
+      <c r="Y16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-12-05 19:00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PSV II</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K17" t="n">
+        <v>67</v>
+      </c>
+      <c r="L17" t="n">
+        <v>73</v>
+      </c>
+      <c r="M17" t="n">
+        <v>44</v>
+      </c>
+      <c r="N17" t="n">
+        <v>22</v>
+      </c>
+      <c r="O17" t="n">
+        <v>78</v>
+      </c>
+      <c r="P17" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>33</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.22</v>
       </c>
-      <c r="J8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="AE17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-12-05 19:00:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Excelsior</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K18" t="n">
+        <v>50</v>
+      </c>
+      <c r="L18" t="n">
+        <v>71</v>
+      </c>
+      <c r="M18" t="n">
+        <v>29</v>
+      </c>
+      <c r="N18" t="n">
+        <v>36</v>
+      </c>
+      <c r="O18" t="n">
+        <v>65</v>
+      </c>
+      <c r="P18" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>50</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-12-05 19:30:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>13</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mainz 05</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Borussia M'gladbach</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>45</v>
+      </c>
+      <c r="L19" t="n">
+        <v>72</v>
+      </c>
+      <c r="M19" t="n">
+        <v>37</v>
+      </c>
+      <c r="N19" t="n">
+        <v>27</v>
+      </c>
+      <c r="O19" t="n">
+        <v>74</v>
+      </c>
+      <c r="P19" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>62</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-12-05 19:30:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lechia Gdańsk</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Górnik Zabrze</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="K20" t="n">
+        <v>65</v>
+      </c>
+      <c r="L20" t="n">
+        <v>77</v>
+      </c>
+      <c r="M20" t="n">
+        <v>36</v>
+      </c>
+      <c r="N20" t="n">
+        <v>15</v>
+      </c>
+      <c r="O20" t="n">
+        <v>85</v>
+      </c>
+      <c r="P20" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>36</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-12-05 19:45:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K21" t="n">
+        <v>44</v>
+      </c>
+      <c r="L21" t="n">
+        <v>63</v>
+      </c>
+      <c r="M21" t="n">
+        <v>19</v>
+      </c>
+      <c r="N21" t="n">
+        <v>38</v>
+      </c>
+      <c r="O21" t="n">
+        <v>63</v>
+      </c>
+      <c r="P21" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>63</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-12-05 20:00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RCD Mallorca</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="K22" t="n">
+        <v>43</v>
+      </c>
+      <c r="L22" t="n">
+        <v>72</v>
+      </c>
+      <c r="M22" t="n">
+        <v>29</v>
+      </c>
+      <c r="N22" t="n">
+        <v>29</v>
+      </c>
+      <c r="O22" t="n">
+        <v>72</v>
+      </c>
+      <c r="P22" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>43</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-12-05 20:00:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>19</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K23" t="n">
+        <v>62</v>
+      </c>
+      <c r="L23" t="n">
+        <v>78</v>
+      </c>
+      <c r="M23" t="n">
+        <v>33</v>
+      </c>
+      <c r="N23" t="n">
+        <v>17</v>
+      </c>
+      <c r="O23" t="n">
+        <v>84</v>
+      </c>
+      <c r="P23" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>45</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-12-05 20:00:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Olympique Marseille</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K24" t="n">
+        <v>50</v>
+      </c>
+      <c r="L24" t="n">
+        <v>50</v>
+      </c>
+      <c r="M24" t="n">
+        <v>29</v>
+      </c>
+      <c r="N24" t="n">
+        <v>43</v>
+      </c>
+      <c r="O24" t="n">
+        <v>57</v>
+      </c>
+      <c r="P24" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>50</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-12-05 20:15:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>13</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="K25" t="n">
+        <v>59</v>
+      </c>
+      <c r="L25" t="n">
+        <v>84</v>
+      </c>
+      <c r="M25" t="n">
         <v>42</v>
       </c>
-      <c r="L8" t="n">
-        <v>66</v>
-      </c>
-      <c r="M8" t="n">
-        <v>16</v>
-      </c>
-      <c r="N8" t="n">
-        <v>32</v>
-      </c>
-      <c r="O8" t="n">
-        <v>68</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="N25" t="n">
+        <v>9</v>
+      </c>
+      <c r="O25" t="n">
+        <v>92</v>
+      </c>
+      <c r="P25" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>33</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-12-06 05:00:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>38</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Shonan Bellmare</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K26" t="n">
         <v>36</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="L26" t="n">
+        <v>45</v>
+      </c>
+      <c r="M26" t="n">
+        <v>20</v>
+      </c>
+      <c r="N26" t="n">
+        <v>39</v>
+      </c>
+      <c r="O26" t="n">
+        <v>61</v>
+      </c>
+      <c r="P26" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>59</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-12-06 05:00:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>38</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K27" t="n">
+        <v>48</v>
+      </c>
+      <c r="L27" t="n">
         <v>64</v>
       </c>
-      <c r="R8" t="n">
+      <c r="M27" t="n">
+        <v>34</v>
+      </c>
+      <c r="N27" t="n">
+        <v>33</v>
+      </c>
+      <c r="O27" t="n">
+        <v>67</v>
+      </c>
+      <c r="P27" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>47</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-12-06 05:00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>38</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Urawa Reds</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="K28" t="n">
+        <v>53</v>
+      </c>
+      <c r="L28" t="n">
+        <v>64</v>
+      </c>
+      <c r="M28" t="n">
+        <v>39</v>
+      </c>
+      <c r="N28" t="n">
+        <v>34</v>
+      </c>
+      <c r="O28" t="n">
+        <v>67</v>
+      </c>
+      <c r="P28" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>53</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-12-06 05:00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>38</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Kyoto Sanga</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K29" t="n">
+        <v>56</v>
+      </c>
+      <c r="L29" t="n">
+        <v>62</v>
+      </c>
+      <c r="M29" t="n">
+        <v>31</v>
+      </c>
+      <c r="N29" t="n">
+        <v>31</v>
+      </c>
+      <c r="O29" t="n">
+        <v>70</v>
+      </c>
+      <c r="P29" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>59</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-12-06 05:00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>38</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K30" t="n">
+        <v>47</v>
+      </c>
+      <c r="L30" t="n">
+        <v>53</v>
+      </c>
+      <c r="M30" t="n">
+        <v>23</v>
+      </c>
+      <c r="N30" t="n">
+        <v>39</v>
+      </c>
+      <c r="O30" t="n">
+        <v>61</v>
+      </c>
+      <c r="P30" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>59</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-12-06 05:00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>38</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Fagiano Okayama</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K31" t="n">
+        <v>50</v>
+      </c>
+      <c r="L31" t="n">
+        <v>64</v>
+      </c>
+      <c r="M31" t="n">
+        <v>28</v>
+      </c>
+      <c r="N31" t="n">
+        <v>25</v>
+      </c>
+      <c r="O31" t="n">
+        <v>75</v>
+      </c>
+      <c r="P31" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>62</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-12-06 05:00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>38</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Yokohama</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K32" t="n">
+        <v>58</v>
+      </c>
+      <c r="L32" t="n">
+        <v>61</v>
+      </c>
+      <c r="M32" t="n">
+        <v>25</v>
+      </c>
+      <c r="N32" t="n">
+        <v>28</v>
+      </c>
+      <c r="O32" t="n">
+        <v>72</v>
+      </c>
+      <c r="P32" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>61</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-12-06 05:00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>38</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K33" t="n">
+        <v>31</v>
+      </c>
+      <c r="L33" t="n">
+        <v>59</v>
+      </c>
+      <c r="M33" t="n">
+        <v>36</v>
+      </c>
+      <c r="N33" t="n">
+        <v>48</v>
+      </c>
+      <c r="O33" t="n">
+        <v>53</v>
+      </c>
+      <c r="P33" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>58</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-12-06 05:00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>38</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Nagoya Grampus</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K34" t="n">
+        <v>50</v>
+      </c>
+      <c r="L34" t="n">
+        <v>42</v>
+      </c>
+      <c r="M34" t="n">
+        <v>28</v>
+      </c>
+      <c r="N34" t="n">
+        <v>34</v>
+      </c>
+      <c r="O34" t="n">
+        <v>67</v>
+      </c>
+      <c r="P34" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>53</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="W34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.74</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AC34" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-12-06 05:00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>38</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K35" t="n">
+        <v>48</v>
+      </c>
+      <c r="L35" t="n">
+        <v>62</v>
+      </c>
+      <c r="M35" t="n">
+        <v>28</v>
+      </c>
+      <c r="N35" t="n">
+        <v>36</v>
+      </c>
+      <c r="O35" t="n">
+        <v>64</v>
+      </c>
+      <c r="P35" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>53</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X35" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.34</v>
+      <c r="Y35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG22" headerRowCount="1">
-  <autoFilter ref="A1:AG22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG15" headerRowCount="1">
+  <autoFilter ref="A1:AG15"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG22"/>
+  <dimension ref="A1:AG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
     <col width="26.4" customWidth="1" min="4" max="4"/>
-    <col width="26.4" customWidth="1" min="5" max="5"/>
+    <col width="21.6" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,12 +675,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-09 12:15:00</t>
+          <t>2025-12-10 17:45:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Asia AFC Champions League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -688,108 +688,108 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="H2" t="n">
-        <v>0.79</v>
+        <v>1.39</v>
       </c>
       <c r="I2" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="J2" t="n">
-        <v>2.01</v>
+        <v>2.9</v>
       </c>
       <c r="K2" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="L2" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="M2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P2" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="Q2" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="T2" t="n">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="U2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.27</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE2" t="n">
-        <v>2.85</v>
+        <v>2.32</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.81</v>
+        <v>3.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-09 12:15:00</t>
+          <t>2025-12-10 17:45:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Asia AFC Champions League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -797,321 +797,321 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.89</v>
+        <v>1.46</v>
       </c>
       <c r="I3" t="n">
         <v>0.85</v>
       </c>
       <c r="J3" t="n">
-        <v>2.74</v>
+        <v>2.31</v>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="Q3" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3.77</v>
       </c>
       <c r="T3" t="n">
-        <v>6.4</v>
+        <v>3.23</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="W3" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="X3" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.11</v>
+        <v>2.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="AF3" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-09 15:30:00</t>
+          <t>2025-12-10 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4</v>
+        <v>1.33</v>
       </c>
       <c r="H4" t="n">
-        <v>1.32</v>
+        <v>1.74</v>
       </c>
       <c r="I4" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="J4" t="n">
-        <v>2.83</v>
+        <v>3.39</v>
       </c>
       <c r="K4" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="L4" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="M4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O4" t="n">
+        <v>84</v>
+      </c>
+      <c r="P4" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q4" t="n">
         <v>28</v>
       </c>
-      <c r="N4" t="n">
-        <v>29</v>
-      </c>
-      <c r="O4" t="n">
-        <v>71</v>
-      </c>
-      <c r="P4" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>61</v>
-      </c>
       <c r="R4" t="n">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3</v>
+        <v>3.69</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.26</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AE4" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-09 17:45:00</t>
+          <t>2025-12-10 19:45:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K5" t="n">
+        <v>60</v>
+      </c>
+      <c r="L5" t="n">
+        <v>80</v>
+      </c>
+      <c r="M5" t="n">
+        <v>40</v>
+      </c>
+      <c r="N5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O5" t="n">
+        <v>70</v>
+      </c>
+      <c r="P5" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>40</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Y5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>80</v>
-      </c>
-      <c r="L5" t="n">
-        <v>100</v>
-      </c>
-      <c r="M5" t="n">
-        <v>70</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>100</v>
-      </c>
-      <c r="P5" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>10</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Z5" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.13</v>
+        <v>1.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>4.25</v>
+        <v>3.02</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.81</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-09 19:45:00</t>
+          <t>2025-12-10 19:45:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1124,103 +1124,103 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
         <v>1.67</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.9</v>
-      </c>
       <c r="H6" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="I6" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="J6" t="n">
-        <v>2.97</v>
+        <v>2.51</v>
       </c>
       <c r="K6" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="L6" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N6" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="O6" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="P6" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="Q6" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="R6" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="U6" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="W6" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="X6" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="Y6" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>3.05</v>
+        <v>2.39</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-12-09 19:45:00</t>
+          <t>2025-12-10 19:45:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1233,37 +1233,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.36</v>
+        <v>1.88</v>
       </c>
       <c r="I7" t="n">
-        <v>1.86</v>
+        <v>1.27</v>
       </c>
       <c r="J7" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M7" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N7" t="n">
         <v>25</v>
@@ -1272,64 +1272,64 @@
         <v>75</v>
       </c>
       <c r="P7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="R7" t="n">
-        <v>3.56</v>
+        <v>1.66</v>
       </c>
       <c r="S7" t="n">
-        <v>3.47</v>
+        <v>3.78</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W7" t="n">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="X7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.07</v>
+        <v>2.89</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-12-09 19:45:00</t>
+          <t>2025-12-10 20:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1342,648 +1342,648 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J8" t="n">
         <v>2.1</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.01</v>
-      </c>
       <c r="K8" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M8" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O8" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P8" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="Q8" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.52</v>
+        <v>2.35</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>6</v>
+        <v>2.92</v>
       </c>
       <c r="U8" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="X8" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.64</v>
+        <v>2.89</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.33</v>
+        <v>3.04</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-12-09 19:45:00</t>
+          <t>2025-12-10 20:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8</v>
+        <v>1.82</v>
       </c>
       <c r="H9" t="n">
-        <v>1.38</v>
+        <v>2.01</v>
       </c>
       <c r="I9" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="J9" t="n">
-        <v>2.59</v>
+        <v>3.17</v>
       </c>
       <c r="K9" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="L9" t="n">
+        <v>53</v>
+      </c>
+      <c r="M9" t="n">
+        <v>19</v>
+      </c>
+      <c r="N9" t="n">
+        <v>33</v>
+      </c>
+      <c r="O9" t="n">
         <v>68</v>
       </c>
-      <c r="M9" t="n">
-        <v>36</v>
-      </c>
-      <c r="N9" t="n">
-        <v>21</v>
-      </c>
-      <c r="O9" t="n">
-        <v>80</v>
-      </c>
       <c r="P9" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="Q9" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="R9" t="n">
-        <v>1.84</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>3.47</v>
+        <v>5.9</v>
       </c>
       <c r="T9" t="n">
-        <v>4.2</v>
+        <v>17</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF9" t="n">
         <v>3.75</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.87</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-12-09 19:45:00</t>
+          <t>2025-12-10 20:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.75</v>
       </c>
-      <c r="I10" t="n">
-        <v>1.23</v>
-      </c>
       <c r="J10" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L10" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M10" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="P10" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="Q10" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
-        <v>1.83</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>3.51</v>
+        <v>5.1</v>
       </c>
       <c r="T10" t="n">
-        <v>4.2</v>
+        <v>1.33</v>
       </c>
       <c r="U10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="X10" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.22</v>
+        <v>2.06</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.36</v>
+        <v>1.61</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.65</v>
+        <v>2.46</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-09 19:45:00</t>
+          <t>2025-12-10 20:00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="H11" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="I11" t="n">
-        <v>0.95</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2.24</v>
+        <v>3.17</v>
       </c>
       <c r="K11" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="L11" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M11" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="N11" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="P11" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>2.12</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.26</v>
+        <v>5.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.45</v>
+        <v>8.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.98</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
-        <v>3.62</v>
+        <v>1.87</v>
       </c>
       <c r="X11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.95</v>
       </c>
-      <c r="Y11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AF11" t="n">
-        <v>2.84</v>
+        <v>4.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-09 19:45:00</t>
+          <t>2025-12-10 20:00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>40</v>
+      </c>
+      <c r="L12" t="n">
+        <v>70</v>
+      </c>
+      <c r="M12" t="n">
+        <v>50</v>
+      </c>
+      <c r="N12" t="n">
         <v>20</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Charlton Athletic</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Middlesbrough</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>65</v>
-      </c>
-      <c r="M12" t="n">
-        <v>28</v>
-      </c>
-      <c r="N12" t="n">
-        <v>29</v>
-      </c>
       <c r="O12" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="P12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Q12" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="R12" t="n">
-        <v>2.86</v>
+        <v>2.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.19</v>
+        <v>3.78</v>
       </c>
       <c r="T12" t="n">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.05</v>
       </c>
-      <c r="W12" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-09 20:00:00</t>
+          <t>2025-12-10 20:00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.56</v>
+        <v>0.8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>2.32</v>
       </c>
       <c r="J13" t="n">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L13" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M13" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="P13" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="Q13" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="R13" t="n">
-        <v>2.73</v>
+        <v>5.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.19</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.56</v>
+        <v>1.57</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y13" t="n">
         <v>2</v>
       </c>
-      <c r="W13" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.04</v>
-      </c>
       <c r="Z13" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.73</v>
+        <v>3.12</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-09 20:00:00</t>
+          <t>2025-12-10 20:00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1996,103 +1996,103 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="I14" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="K14" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="L14" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="M14" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="N14" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="O14" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="P14" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="R14" t="n">
-        <v>2.82</v>
+        <v>2.31</v>
       </c>
       <c r="S14" t="n">
-        <v>3.53</v>
+        <v>3.31</v>
       </c>
       <c r="T14" t="n">
-        <v>2.32</v>
+        <v>2.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="W14" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="X14" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.24</v>
+        <v>2.59</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-09 20:00:00</t>
+          <t>2025-12-10 20:00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2105,37 +2105,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="H15" t="n">
-        <v>1.62</v>
+        <v>1.07</v>
       </c>
       <c r="I15" t="n">
-        <v>0.92</v>
+        <v>1.68</v>
       </c>
       <c r="J15" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="K15" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="L15" t="n">
         <v>70</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
         <v>10</v>
@@ -2144,821 +2144,58 @@
         <v>90</v>
       </c>
       <c r="P15" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="R15" t="n">
-        <v>1.16</v>
+        <v>2.69</v>
       </c>
       <c r="S15" t="n">
-        <v>7.9</v>
+        <v>3.47</v>
       </c>
       <c r="T15" t="n">
-        <v>12</v>
+        <v>2.44</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="X15" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AF15" t="n">
-        <v>5.2</v>
+        <v>3.18</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.07</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2025-12-09 20:00:00</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Inter Milan</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>50</v>
-      </c>
-      <c r="L16" t="n">
-        <v>90</v>
-      </c>
-      <c r="M16" t="n">
-        <v>50</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20</v>
-      </c>
-      <c r="O16" t="n">
-        <v>80</v>
-      </c>
-      <c r="P16" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>30</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2025-12-09 20:00:00</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>6</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Galatasaray</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H17" t="n">
         <v>1.51</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>50</v>
-      </c>
-      <c r="L17" t="n">
-        <v>70</v>
-      </c>
-      <c r="M17" t="n">
-        <v>50</v>
-      </c>
-      <c r="N17" t="n">
-        <v>40</v>
-      </c>
-      <c r="O17" t="n">
-        <v>60</v>
-      </c>
-      <c r="P17" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>40</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025-12-09 20:00:00</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>6</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="K18" t="n">
-        <v>40</v>
-      </c>
-      <c r="L18" t="n">
-        <v>70</v>
-      </c>
-      <c r="M18" t="n">
-        <v>40</v>
-      </c>
-      <c r="N18" t="n">
-        <v>30</v>
-      </c>
-      <c r="O18" t="n">
-        <v>70</v>
-      </c>
-      <c r="P18" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>30</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2025-12-09 20:00:00</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>6</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Tottenham Hotspur</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Slavia Praha</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="K19" t="n">
-        <v>30</v>
-      </c>
-      <c r="L19" t="n">
-        <v>60</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20</v>
-      </c>
-      <c r="N19" t="n">
-        <v>40</v>
-      </c>
-      <c r="O19" t="n">
-        <v>60</v>
-      </c>
-      <c r="P19" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>40</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2025-12-09 20:00:00</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>6</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>PSV</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Atlético Madrid</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="K20" t="n">
-        <v>90</v>
-      </c>
-      <c r="L20" t="n">
-        <v>80</v>
-      </c>
-      <c r="M20" t="n">
-        <v>50</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>100</v>
-      </c>
-      <c r="P20" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>20</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2025-12-10 10:00:00</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Asia AFC Champions League</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>6</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>FC Seoul</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Melbourne City FC</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="K21" t="n">
-        <v>40</v>
-      </c>
-      <c r="L21" t="n">
-        <v>30</v>
-      </c>
-      <c r="M21" t="n">
-        <v>20</v>
-      </c>
-      <c r="N21" t="n">
-        <v>20</v>
-      </c>
-      <c r="O21" t="n">
-        <v>80</v>
-      </c>
-      <c r="P21" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>60</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2025-12-10 10:00:00</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Asia AFC Champions League</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>6</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Sanfrecce Hiroshima</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Shanghai Shenhua</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K22" t="n">
-        <v>50</v>
-      </c>
-      <c r="L22" t="n">
-        <v>40</v>
-      </c>
-      <c r="M22" t="n">
-        <v>10</v>
-      </c>
-      <c r="N22" t="n">
-        <v>20</v>
-      </c>
-      <c r="O22" t="n">
-        <v>80</v>
-      </c>
-      <c r="P22" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>80</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>8</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.61</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG15" headerRowCount="1">
-  <autoFilter ref="A1:AG15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG38" headerRowCount="1">
+  <autoFilter ref="A1:AG38"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG15"/>
+  <dimension ref="A1:AG38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="45.6" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="26.4" customWidth="1" min="4" max="4"/>
-    <col width="21.6" customWidth="1" min="5" max="5"/>
+    <col width="27.6" customWidth="1" min="4" max="4"/>
+    <col width="22.8" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,12 +675,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-10 17:45:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -688,108 +688,108 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2</v>
+        <v>1.71</v>
       </c>
       <c r="G2" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="I2" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="K2" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="L2" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="M2" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P2" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="Q2" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51</v>
+        <v>4.4</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>5.7</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="V2" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X2" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.96</v>
+        <v>2.19</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.72</v>
+        <v>2.13</v>
       </c>
       <c r="AD2" t="n">
         <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-10 17:45:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -797,653 +797,653 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.85</v>
+        <v>1.23</v>
       </c>
       <c r="J3" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="L3" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="M3" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="P3" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="Q3" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="R3" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="S3" t="n">
-        <v>3.77</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>3.23</v>
+        <v>2.65</v>
       </c>
       <c r="U3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="V3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA3" t="n">
         <v>1.85</v>
       </c>
-      <c r="W3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AB3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.56</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-10 19:00:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K4" t="n">
+        <v>32</v>
+      </c>
+      <c r="L4" t="n">
+        <v>69</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32</v>
+      </c>
+      <c r="N4" t="n">
+        <v>21</v>
+      </c>
+      <c r="O4" t="n">
+        <v>79</v>
+      </c>
+      <c r="P4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>47</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.22</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="K4" t="n">
-        <v>67</v>
-      </c>
-      <c r="L4" t="n">
-        <v>84</v>
-      </c>
-      <c r="M4" t="n">
-        <v>50</v>
-      </c>
-      <c r="N4" t="n">
-        <v>17</v>
-      </c>
-      <c r="O4" t="n">
-        <v>84</v>
-      </c>
-      <c r="P4" t="n">
-        <v>73</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>28</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AE4" t="n">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-10 19:45:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>2.55</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="J5" t="n">
-        <v>2.68</v>
+        <v>3.41</v>
       </c>
       <c r="K5" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L5" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M5" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="N5" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="O5" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="P5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q5" t="n">
         <v>40</v>
       </c>
       <c r="R5" t="n">
-        <v>2.27</v>
+        <v>1.88</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
-        <v>3.07</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="W5" t="n">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="X5" t="n">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.91</v>
+        <v>2.37</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-10 19:45:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="G6" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="H6" t="n">
         <v>1.25</v>
       </c>
       <c r="I6" t="n">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="J6" t="n">
-        <v>2.51</v>
+        <v>3.02</v>
       </c>
       <c r="K6" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="L6" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="M6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="O6" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="P6" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q6" t="n">
         <v>48</v>
       </c>
-      <c r="Q6" t="n">
-        <v>52</v>
-      </c>
       <c r="R6" t="n">
-        <v>2.34</v>
+        <v>4.15</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="T6" t="n">
-        <v>3.13</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="W6" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="X6" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-12-10 19:45:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ferencváros</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L7" t="n">
+        <v>80</v>
+      </c>
+      <c r="M7" t="n">
         <v>20</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ipswich Town</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Stoke City</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
+        <v>20</v>
+      </c>
+      <c r="O7" t="n">
+        <v>80</v>
+      </c>
+      <c r="P7" t="n">
         <v>40</v>
       </c>
-      <c r="L7" t="n">
+      <c r="Q7" t="n">
         <v>60</v>
       </c>
-      <c r="M7" t="n">
-        <v>40</v>
-      </c>
-      <c r="N7" t="n">
-        <v>25</v>
-      </c>
-      <c r="O7" t="n">
-        <v>75</v>
-      </c>
-      <c r="P7" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>45</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="S7" t="n">
-        <v>3.78</v>
+        <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="X7" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.92</v>
+        <v>2.59</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.61</v>
+        <v>2.03</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-12-10 20:00:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.22</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>1.33</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="K8" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="M8" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="N8" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="P8" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="Q8" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="R8" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>2.92</v>
+        <v>1.82</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="W8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.86</v>
+        <v>2.37</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-12-10 20:00:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1451,108 +1451,108 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="G9" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="H9" t="n">
-        <v>2.01</v>
+        <v>1.69</v>
       </c>
       <c r="I9" t="n">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="K9" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L9" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="M9" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="O9" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="P9" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="Q9" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>2.6</v>
       </c>
       <c r="S9" t="n">
-        <v>5.9</v>
+        <v>3.35</v>
       </c>
       <c r="T9" t="n">
-        <v>17</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="W9" t="n">
-        <v>2.05</v>
+        <v>3.16</v>
       </c>
       <c r="X9" t="n">
-        <v>2.29</v>
+        <v>1.78</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>2.95</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-12-10 20:00:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa League</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1560,642 +1560,3149 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7</v>
+        <v>1.06</v>
       </c>
       <c r="I10" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="J10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K10" t="n">
+        <v>58</v>
+      </c>
+      <c r="L10" t="n">
+        <v>77</v>
+      </c>
+      <c r="M10" t="n">
+        <v>63</v>
+      </c>
+      <c r="N10" t="n">
+        <v>14</v>
+      </c>
+      <c r="O10" t="n">
+        <v>87</v>
+      </c>
+      <c r="P10" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>32</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S10" t="n">
         <v>3.45</v>
       </c>
-      <c r="K10" t="n">
-        <v>38</v>
-      </c>
-      <c r="L10" t="n">
-        <v>75</v>
-      </c>
-      <c r="M10" t="n">
-        <v>49</v>
-      </c>
-      <c r="N10" t="n">
-        <v>6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>95</v>
-      </c>
-      <c r="P10" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>26</v>
-      </c>
-      <c r="R10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5.1</v>
-      </c>
       <c r="T10" t="n">
-        <v>1.33</v>
+        <v>2.9</v>
       </c>
       <c r="U10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="X10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC10" t="n">
         <v>1.88</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-10 20:00:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.71</v>
-      </c>
       <c r="H11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.34</v>
       </c>
       <c r="J11" t="n">
-        <v>3.17</v>
+        <v>2.79</v>
       </c>
       <c r="K11" t="n">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="L11" t="n">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="M11" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="O11" t="n">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="P11" t="n">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>2.02</v>
       </c>
       <c r="S11" t="n">
-        <v>5.3</v>
+        <v>3.45</v>
       </c>
       <c r="T11" t="n">
-        <v>8.1</v>
+        <v>3.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="X11" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.68</v>
+        <v>2.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.41</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-10 20:00:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="G12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="K12" t="n">
+        <v>45</v>
+      </c>
+      <c r="L12" t="n">
+        <v>77</v>
+      </c>
+      <c r="M12" t="n">
+        <v>49</v>
+      </c>
+      <c r="N12" t="n">
+        <v>24</v>
+      </c>
+      <c r="O12" t="n">
+        <v>77</v>
+      </c>
+      <c r="P12" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>42</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>40</v>
-      </c>
-      <c r="L12" t="n">
-        <v>70</v>
-      </c>
-      <c r="M12" t="n">
-        <v>50</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20</v>
-      </c>
-      <c r="O12" t="n">
-        <v>80</v>
-      </c>
-      <c r="P12" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>50</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.41</v>
       </c>
-      <c r="Y12" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="AF12" t="n">
-        <v>3.7</v>
+        <v>2.94</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-10 20:00:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.8</v>
+        <v>2.33</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="H13" t="n">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="I13" t="n">
-        <v>2.32</v>
+        <v>1.94</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.03</v>
       </c>
       <c r="K13" t="n">
+        <v>40</v>
+      </c>
+      <c r="L13" t="n">
         <v>60</v>
       </c>
-      <c r="L13" t="n">
-        <v>80</v>
-      </c>
       <c r="M13" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="O13" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="P13" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="Q13" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="R13" t="n">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.8</v>
       </c>
-      <c r="W13" t="n">
-        <v>3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2</v>
-      </c>
       <c r="Z13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-10 20:00:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="G14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K14" t="n">
+        <v>75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>100</v>
+      </c>
+      <c r="M14" t="n">
+        <v>34</v>
+      </c>
+      <c r="N14" t="n">
+        <v>25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>75</v>
+      </c>
+      <c r="P14" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>42</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.4</v>
       </c>
-      <c r="H14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K14" t="n">
-        <v>26</v>
-      </c>
-      <c r="L14" t="n">
-        <v>54</v>
-      </c>
-      <c r="M14" t="n">
-        <v>21</v>
-      </c>
-      <c r="N14" t="n">
-        <v>32</v>
-      </c>
-      <c r="O14" t="n">
-        <v>68</v>
-      </c>
-      <c r="P14" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>69</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE14" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.59</v>
+        <v>3.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-10 20:00:00</t>
+          <t>2025-12-11 17:45:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Dynamo Kyiv</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>17</v>
+      </c>
+      <c r="L15" t="n">
+        <v>100</v>
+      </c>
+      <c r="M15" t="n">
+        <v>29</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>92</v>
+      </c>
+      <c r="P15" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>42</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-12-11 17:45:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Jagiellonia Białystok</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>54</v>
+      </c>
+      <c r="M16" t="n">
+        <v>40</v>
+      </c>
+      <c r="N16" t="n">
+        <v>24</v>
+      </c>
+      <c r="O16" t="n">
+        <v>77</v>
+      </c>
+      <c r="P16" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>47</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-12-11 17:45:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Shkendija</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="K17" t="n">
+        <v>50</v>
+      </c>
+      <c r="L17" t="n">
+        <v>75</v>
+      </c>
+      <c r="M17" t="n">
+        <v>38</v>
+      </c>
+      <c r="N17" t="n">
+        <v>38</v>
+      </c>
+      <c r="O17" t="n">
+        <v>63</v>
+      </c>
+      <c r="P17" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>63</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-12-11 17:45:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Samsunspor</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="K18" t="n">
+        <v>38</v>
+      </c>
+      <c r="L18" t="n">
+        <v>85</v>
+      </c>
+      <c r="M18" t="n">
+        <v>40</v>
+      </c>
+      <c r="N18" t="n">
+        <v>28</v>
+      </c>
+      <c r="O18" t="n">
+        <v>73</v>
+      </c>
+      <c r="P18" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>43</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-12-11 17:45:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CS U Craiova</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sparta Praha</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="K19" t="n">
+        <v>45</v>
+      </c>
+      <c r="L19" t="n">
+        <v>60</v>
+      </c>
+      <c r="M19" t="n">
+        <v>30</v>
+      </c>
+      <c r="N19" t="n">
+        <v>30</v>
+      </c>
+      <c r="O19" t="n">
+        <v>70</v>
+      </c>
+      <c r="P19" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>45</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>6</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Newcastle United</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K20" t="n">
+        <v>50</v>
+      </c>
+      <c r="L20" t="n">
+        <v>70</v>
+      </c>
+      <c r="M20" t="n">
+        <v>30</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20</v>
+      </c>
+      <c r="O20" t="n">
+        <v>80</v>
+      </c>
+      <c r="P20" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>60</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.6</v>
       </c>
-      <c r="G15" t="n">
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K21" t="n">
+        <v>47</v>
+      </c>
+      <c r="L21" t="n">
+        <v>64</v>
+      </c>
+      <c r="M21" t="n">
+        <v>26</v>
+      </c>
+      <c r="N21" t="n">
+        <v>37</v>
+      </c>
+      <c r="O21" t="n">
+        <v>64</v>
+      </c>
+      <c r="P21" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>58</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K22" t="n">
+        <v>50</v>
+      </c>
+      <c r="L22" t="n">
+        <v>90</v>
+      </c>
+      <c r="M22" t="n">
+        <v>30</v>
+      </c>
+      <c r="N22" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" t="n">
+        <v>90</v>
+      </c>
+      <c r="P22" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>50</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1.8</v>
       </c>
-      <c r="H15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="AB22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H23" t="n">
         <v>1.68</v>
       </c>
-      <c r="J15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="K23" t="n">
+        <v>70</v>
+      </c>
+      <c r="L23" t="n">
+        <v>80</v>
+      </c>
+      <c r="M23" t="n">
         <v>50</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N23" t="n">
+        <v>20</v>
+      </c>
+      <c r="O23" t="n">
+        <v>80</v>
+      </c>
+      <c r="P23" t="n">
         <v>70</v>
       </c>
-      <c r="M15" t="n">
+      <c r="Q23" t="n">
+        <v>30</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K24" t="n">
+        <v>70</v>
+      </c>
+      <c r="L24" t="n">
+        <v>80</v>
+      </c>
+      <c r="M24" t="n">
+        <v>40</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>90</v>
+      </c>
+      <c r="P24" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>40</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FCSB</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Feyenoord</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="K25" t="n">
+        <v>48</v>
+      </c>
+      <c r="L25" t="n">
+        <v>65</v>
+      </c>
+      <c r="M25" t="n">
+        <v>37</v>
+      </c>
+      <c r="N25" t="n">
+        <v>21</v>
+      </c>
+      <c r="O25" t="n">
+        <v>79</v>
+      </c>
+      <c r="P25" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>47</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Malmö FF</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K26" t="n">
+        <v>35</v>
+      </c>
+      <c r="L26" t="n">
+        <v>66</v>
+      </c>
+      <c r="M26" t="n">
+        <v>49</v>
+      </c>
+      <c r="N26" t="n">
+        <v>17</v>
+      </c>
+      <c r="O26" t="n">
+        <v>83</v>
+      </c>
+      <c r="P26" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>52</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>13</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Olympique Lyonnais</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K27" t="n">
         <v>20</v>
       </c>
-      <c r="N15" t="n">
-        <v>10</v>
-      </c>
-      <c r="O15" t="n">
+      <c r="L27" t="n">
+        <v>70</v>
+      </c>
+      <c r="M27" t="n">
+        <v>40</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20</v>
+      </c>
+      <c r="O27" t="n">
+        <v>80</v>
+      </c>
+      <c r="P27" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>60</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T27" t="n">
+        <v>14</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Viktoria Plzeň</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>48</v>
+      </c>
+      <c r="L28" t="n">
+        <v>47</v>
+      </c>
+      <c r="M28" t="n">
+        <v>37</v>
+      </c>
+      <c r="N28" t="n">
+        <v>42</v>
+      </c>
+      <c r="O28" t="n">
+        <v>58</v>
+      </c>
+      <c r="P28" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>52</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K29" t="n">
+        <v>67</v>
+      </c>
+      <c r="L29" t="n">
+        <v>71</v>
+      </c>
+      <c r="M29" t="n">
+        <v>42</v>
+      </c>
+      <c r="N29" t="n">
+        <v>21</v>
+      </c>
+      <c r="O29" t="n">
+        <v>79</v>
+      </c>
+      <c r="P29" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>42</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Hamrun Spartans</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="K30" t="n">
+        <v>58</v>
+      </c>
+      <c r="L30" t="n">
+        <v>67</v>
+      </c>
+      <c r="M30" t="n">
+        <v>17</v>
+      </c>
+      <c r="N30" t="n">
+        <v>25</v>
+      </c>
+      <c r="O30" t="n">
+        <v>75</v>
+      </c>
+      <c r="P30" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>42</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Celje</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K31" t="n">
+        <v>38</v>
+      </c>
+      <c r="L31" t="n">
+        <v>75</v>
+      </c>
+      <c r="M31" t="n">
+        <v>38</v>
+      </c>
+      <c r="N31" t="n">
+        <v>44</v>
+      </c>
+      <c r="O31" t="n">
+        <v>57</v>
+      </c>
+      <c r="P31" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>69</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Lech Poznań</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Mainz 05</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>63</v>
+      </c>
+      <c r="L32" t="n">
+        <v>71</v>
+      </c>
+      <c r="M32" t="n">
+        <v>42</v>
+      </c>
+      <c r="N32" t="n">
+        <v>25</v>
+      </c>
+      <c r="O32" t="n">
+        <v>75</v>
+      </c>
+      <c r="P32" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>38</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>45</v>
+      </c>
+      <c r="L33" t="n">
+        <v>53</v>
+      </c>
+      <c r="M33" t="n">
+        <v>33</v>
+      </c>
+      <c r="N33" t="n">
+        <v>35</v>
+      </c>
+      <c r="O33" t="n">
+        <v>65</v>
+      </c>
+      <c r="P33" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>68</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sigma Olomouc</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K34" t="n">
+        <v>75</v>
+      </c>
+      <c r="L34" t="n">
+        <v>75</v>
+      </c>
+      <c r="M34" t="n">
+        <v>38</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>100</v>
+      </c>
+      <c r="P34" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>38</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Raków Częstochowa</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Zrinjski</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>33</v>
+      </c>
+      <c r="L35" t="n">
+        <v>75</v>
+      </c>
+      <c r="M35" t="n">
+        <v>23</v>
+      </c>
+      <c r="N35" t="n">
+        <v>28</v>
+      </c>
+      <c r="O35" t="n">
+        <v>73</v>
+      </c>
+      <c r="P35" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>43</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K36" t="n">
+        <v>25</v>
+      </c>
+      <c r="L36" t="n">
+        <v>42</v>
+      </c>
+      <c r="M36" t="n">
+        <v>17</v>
+      </c>
+      <c r="N36" t="n">
+        <v>50</v>
+      </c>
+      <c r="O36" t="n">
+        <v>50</v>
+      </c>
+      <c r="P36" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>75</v>
+      </c>
+      <c r="R36" t="n">
+        <v>21</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Rapid Wien</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K37" t="n">
+        <v>45</v>
+      </c>
+      <c r="L37" t="n">
         <v>90</v>
       </c>
-      <c r="P15" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>40</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="M37" t="n">
+        <v>55</v>
+      </c>
+      <c r="N37" t="n">
+        <v>20</v>
+      </c>
+      <c r="O37" t="n">
+        <v>80</v>
+      </c>
+      <c r="P37" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>45</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB37" t="n">
         <v>1.43</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.51</v>
+      <c r="AC37" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-12-11 21:00:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mexico Liga MX</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="K38" t="n">
+        <v>55</v>
+      </c>
+      <c r="L38" t="n">
+        <v>69</v>
+      </c>
+      <c r="M38" t="n">
+        <v>41</v>
+      </c>
+      <c r="N38" t="n">
+        <v>22</v>
+      </c>
+      <c r="O38" t="n">
+        <v>79</v>
+      </c>
+      <c r="P38" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>48</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG27" headerRowCount="1">
-  <autoFilter ref="A1:AG27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG80" headerRowCount="1">
+  <autoFilter ref="A1:AG80"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG27"/>
+  <dimension ref="A1:AG80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="33.6" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="28.8" customWidth="1" min="5" max="5"/>
+    <col width="25.2" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,56 +675,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-12 17:00:00</t>
+          <t>2025-12-13 11:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>União de Leiria</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Felgueiras 1932</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K2" t="n">
+        <v>59</v>
+      </c>
+      <c r="L2" t="n">
+        <v>75</v>
+      </c>
+      <c r="M2" t="n">
+        <v>25</v>
+      </c>
+      <c r="N2" t="n">
         <v>17</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>HNK Vukovar 1991</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Varaždin</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="K2" t="n">
-        <v>69</v>
-      </c>
-      <c r="L2" t="n">
-        <v>63</v>
-      </c>
-      <c r="M2" t="n">
-        <v>44</v>
-      </c>
-      <c r="N2" t="n">
-        <v>32</v>
-      </c>
       <c r="O2" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="P2" t="n">
         <v>50</v>
@@ -733,49 +733,49 @@
         <v>50</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="W2" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="X2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.91</v>
+        <v>2.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.51</v>
+        <v>2.11</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.51</v>
+        <v>1.63</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="AG2" t="n">
         <v>1.36</v>
@@ -784,7 +784,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-12 17:00:00</t>
+          <t>2025-12-13 11:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -797,43 +797,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.43</v>
+        <v>0.88</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="H3" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="I3" t="n">
-        <v>0.88</v>
+        <v>1.26</v>
       </c>
       <c r="J3" t="n">
-        <v>2.31</v>
+        <v>2.67</v>
       </c>
       <c r="K3" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="L3" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="M3" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="O3" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="P3" t="n">
         <v>40</v>
@@ -842,58 +842,58 @@
         <v>61</v>
       </c>
       <c r="R3" t="n">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="W3" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AB3" t="n">
         <v>1.47</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-12 17:30:00</t>
+          <t>2025-12-13 12:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -906,103 +906,103 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.71</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="I4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="J4" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="K4" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="L4" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="P4" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="R4" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="S4" t="n">
-        <v>3.41</v>
+        <v>3.28</v>
       </c>
       <c r="T4" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="U4" t="n">
         <v>1.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="W4" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="X4" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-12 17:30:00</t>
+          <t>2025-12-13 12:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1015,1024 +1015,1024 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="I5" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="J5" t="n">
-        <v>2.45</v>
+        <v>2.96</v>
       </c>
       <c r="K5" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="L5" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="M5" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="N5" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="O5" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="P5" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="Q5" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="R5" t="n">
-        <v>3.69</v>
+        <v>3.51</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="T5" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="V5" t="n">
         <v>1.65</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="X5" t="n">
         <v>1.53</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-12 18:00:00</t>
+          <t>2025-12-13 12:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
         <v>1.71</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.28</v>
-      </c>
       <c r="I6" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="J6" t="n">
-        <v>2.71</v>
+        <v>2.94</v>
       </c>
       <c r="K6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L6" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P6" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="R6" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="S6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="W6" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="X6" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.77</v>
+        <v>2.42</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-12-12 18:00:00</t>
+          <t>2025-12-13 12:30:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="H7" t="n">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="K7" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="L7" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="M7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N7" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O7" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="P7" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q7" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R7" t="n">
-        <v>2.12</v>
+        <v>2.51</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="U7" t="n">
         <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="W7" t="n">
-        <v>3.73</v>
+        <v>3.79</v>
       </c>
       <c r="X7" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-12-12 18:30:00</t>
+          <t>2025-12-13 12:30:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="H8" t="n">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="J8" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="K8" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="L8" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="M8" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="O8" t="n">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="P8" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="Q8" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="S8" t="n">
-        <v>3.89</v>
+        <v>3.36</v>
       </c>
       <c r="T8" t="n">
-        <v>6.7</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="W8" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="X8" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.34</v>
+        <v>2.67</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.38</v>
+        <v>2.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-12-12 19:00:00</t>
+          <t>2025-12-13 12:30:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.89</v>
+        <v>0.44</v>
       </c>
       <c r="G9" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="H9" t="n">
-        <v>2.56</v>
+        <v>1.52</v>
       </c>
       <c r="I9" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9</v>
+        <v>3.04</v>
       </c>
       <c r="K9" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="L9" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="M9" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="N9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="O9" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="P9" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="Q9" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="R9" t="n">
-        <v>1.77</v>
+        <v>3.14</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="T9" t="n">
-        <v>3.75</v>
+        <v>2.09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.85</v>
+        <v>2.39</v>
       </c>
       <c r="X9" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="Y9" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-12-12 19:00:00</t>
+          <t>2025-12-13 13:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="G10" t="n">
-        <v>1.33</v>
+        <v>0.43</v>
       </c>
       <c r="H10" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="I10" t="n">
-        <v>1.43</v>
+        <v>0.84</v>
       </c>
       <c r="J10" t="n">
-        <v>3.32</v>
+        <v>2.77</v>
       </c>
       <c r="K10" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="L10" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M10" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="O10" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="P10" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="R10" t="n">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="T10" t="n">
-        <v>3.35</v>
+        <v>11.7</v>
       </c>
       <c r="U10" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="V10" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="W10" t="n">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="X10" t="n">
-        <v>1.44</v>
+        <v>2.21</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.68</v>
+        <v>2.63</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.63</v>
+        <v>2.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-12 19:00:00</t>
+          <t>2025-12-13 13:00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="G11" t="n">
-        <v>1.11</v>
+        <v>0.25</v>
       </c>
       <c r="H11" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="I11" t="n">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
       <c r="J11" t="n">
-        <v>3.23</v>
+        <v>2.98</v>
       </c>
       <c r="K11" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="L11" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N11" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="O11" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="P11" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>3.21</v>
       </c>
       <c r="T11" t="n">
-        <v>3.75</v>
+        <v>3.53</v>
       </c>
       <c r="U11" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="W11" t="n">
-        <v>2.49</v>
+        <v>3.54</v>
       </c>
       <c r="X11" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.42</v>
+        <v>2.31</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.47</v>
+        <v>1.84</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-12 19:00:00</t>
+          <t>2025-12-13 14:00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="G12" t="n">
-        <v>0.22</v>
+        <v>1.14</v>
       </c>
       <c r="H12" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="I12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K12" t="n">
+        <v>50</v>
+      </c>
+      <c r="L12" t="n">
+        <v>64</v>
+      </c>
+      <c r="M12" t="n">
+        <v>29</v>
+      </c>
+      <c r="N12" t="n">
+        <v>22</v>
+      </c>
+      <c r="O12" t="n">
+        <v>79</v>
+      </c>
+      <c r="P12" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>57</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.41</v>
       </c>
-      <c r="J12" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="K12" t="n">
-        <v>67</v>
-      </c>
-      <c r="L12" t="n">
-        <v>78</v>
-      </c>
-      <c r="M12" t="n">
-        <v>39</v>
-      </c>
-      <c r="N12" t="n">
-        <v>28</v>
-      </c>
-      <c r="O12" t="n">
-        <v>73</v>
-      </c>
-      <c r="P12" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>39</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE12" t="n">
-        <v>2.1</v>
+        <v>3.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-12 19:00:00</t>
+          <t>2025-12-13 14:00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.67</v>
+        <v>2.57</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.71</v>
       </c>
       <c r="H13" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="I13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K13" t="n">
+        <v>50</v>
+      </c>
+      <c r="L13" t="n">
+        <v>86</v>
+      </c>
+      <c r="M13" t="n">
+        <v>43</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>93</v>
+      </c>
+      <c r="P13" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>36</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.35</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="K13" t="n">
-        <v>61</v>
-      </c>
-      <c r="L13" t="n">
-        <v>84</v>
-      </c>
-      <c r="M13" t="n">
-        <v>33</v>
-      </c>
-      <c r="N13" t="n">
-        <v>17</v>
-      </c>
-      <c r="O13" t="n">
-        <v>84</v>
-      </c>
-      <c r="P13" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>45</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-12 19:00:00</t>
+          <t>2025-12-13 14:00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.67</v>
+        <v>1.86</v>
       </c>
       <c r="G14" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="I14" t="n">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="K14" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L14" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="M14" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="N14" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O14" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="P14" t="n">
         <v>56</v>
@@ -2041,1148 +2041,1148 @@
         <v>44</v>
       </c>
       <c r="R14" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="T14" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="U14" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="W14" t="n">
-        <v>2.25</v>
+        <v>4.25</v>
       </c>
       <c r="X14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.44</v>
       </c>
-      <c r="Y14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AE14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-12 19:00:00</t>
+          <t>2025-12-13 14:00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.89</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="H15" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="I15" t="n">
-        <v>1.61</v>
+        <v>0.92</v>
       </c>
       <c r="J15" t="n">
-        <v>3.28</v>
+        <v>2.66</v>
       </c>
       <c r="K15" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="L15" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="M15" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="N15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O15" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="P15" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="Q15" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="R15" t="n">
-        <v>2.76</v>
+        <v>2.12</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.07</v>
+        <v>3.45</v>
       </c>
       <c r="U15" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>2.13</v>
       </c>
       <c r="W15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.75</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.33</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-12 19:00:00</t>
+          <t>2025-12-13 14:00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="G16" t="n">
-        <v>2.44</v>
+        <v>1.38</v>
       </c>
       <c r="H16" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="I16" t="n">
-        <v>2.21</v>
+        <v>1.14</v>
       </c>
       <c r="J16" t="n">
-        <v>3.63</v>
+        <v>2.51</v>
       </c>
       <c r="K16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L16" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="M16" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="O16" t="n">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="P16" t="n">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="Q16" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="R16" t="n">
-        <v>6.57</v>
+        <v>2.34</v>
       </c>
       <c r="S16" t="n">
-        <v>4.96</v>
+        <v>3.13</v>
       </c>
       <c r="T16" t="n">
-        <v>1.35</v>
+        <v>3.09</v>
       </c>
       <c r="U16" t="n">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>2.2</v>
       </c>
       <c r="W16" t="n">
-        <v>2.05</v>
+        <v>4.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.26</v>
+        <v>1.77</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.92</v>
+        <v>2.14</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.57</v>
+        <v>2.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.09</v>
+        <v>3.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-12 19:00:00</t>
+          <t>2025-12-13 14:00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.67</v>
+        <v>0.75</v>
       </c>
       <c r="G17" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9</v>
+        <v>1.17</v>
       </c>
       <c r="I17" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="K17" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L17" t="n">
+        <v>73</v>
+      </c>
+      <c r="M17" t="n">
+        <v>26</v>
+      </c>
+      <c r="N17" t="n">
+        <v>34</v>
+      </c>
+      <c r="O17" t="n">
+        <v>66</v>
+      </c>
+      <c r="P17" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q17" t="n">
         <v>67</v>
       </c>
-      <c r="M17" t="n">
-        <v>39</v>
-      </c>
-      <c r="N17" t="n">
-        <v>33</v>
-      </c>
-      <c r="O17" t="n">
-        <v>67</v>
-      </c>
-      <c r="P17" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>62</v>
-      </c>
       <c r="R17" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6</v>
+        <v>3.07</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="U17" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="W17" t="n">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="X17" t="n">
-        <v>1.48</v>
+        <v>1.97</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.7</v>
+        <v>2.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.6</v>
+        <v>2.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-12 19:30:00</t>
+          <t>2025-12-13 14:00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="G18" t="n">
-        <v>0.29</v>
+        <v>1.71</v>
       </c>
       <c r="H18" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="I18" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="J18" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="K18" t="n">
+        <v>45</v>
+      </c>
+      <c r="L18" t="n">
+        <v>54</v>
+      </c>
+      <c r="M18" t="n">
+        <v>38</v>
+      </c>
+      <c r="N18" t="n">
+        <v>24</v>
+      </c>
+      <c r="O18" t="n">
+        <v>77</v>
+      </c>
+      <c r="P18" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>69</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.15</v>
       </c>
-      <c r="K18" t="n">
-        <v>48</v>
-      </c>
-      <c r="L18" t="n">
-        <v>60</v>
-      </c>
-      <c r="M18" t="n">
-        <v>35</v>
-      </c>
-      <c r="N18" t="n">
-        <v>27</v>
-      </c>
-      <c r="O18" t="n">
-        <v>73</v>
-      </c>
-      <c r="P18" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>54</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.56</v>
-      </c>
       <c r="T18" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="W18" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="X18" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-12 19:30:00</t>
+          <t>2025-12-13 14:00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.29</v>
+        <v>0.71</v>
       </c>
       <c r="G19" t="n">
-        <v>1.57</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="I19" t="n">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="J19" t="n">
-        <v>2.99</v>
+        <v>2.56</v>
       </c>
       <c r="K19" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="L19" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="M19" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="N19" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="P19" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="Q19" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="R19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S19" t="n">
         <v>3.4</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="U19" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V19" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="W19" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="X19" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-12 19:30:00</t>
+          <t>2025-12-13 14:00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>1.57</v>
       </c>
       <c r="H20" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="I20" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="J20" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="K20" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="L20" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="M20" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="O20" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="P20" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="Q20" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="R20" t="n">
-        <v>2.36</v>
+        <v>1.88</v>
       </c>
       <c r="S20" t="n">
-        <v>2.98</v>
+        <v>3.16</v>
       </c>
       <c r="T20" t="n">
-        <v>3.21</v>
+        <v>4.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="W20" t="n">
-        <v>5.5</v>
+        <v>3.76</v>
       </c>
       <c r="X20" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-12 19:45:00</t>
+          <t>2025-12-13 14:30:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.57</v>
+        <v>0.86</v>
       </c>
       <c r="G21" t="n">
-        <v>0.86</v>
+        <v>1.17</v>
       </c>
       <c r="H21" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="I21" t="n">
-        <v>0.88</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="K21" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L21" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M21" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="N21" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="O21" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="P21" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="Q21" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="R21" t="n">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="S21" t="n">
-        <v>3.18</v>
+        <v>3.73</v>
       </c>
       <c r="T21" t="n">
-        <v>3.08</v>
+        <v>3.41</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="V21" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="X21" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>2.54</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.23</v>
+        <v>2.97</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE21" t="n">
-        <v>3.24</v>
+        <v>2.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.53</v>
+        <v>3.48</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-12-12 19:45:00</t>
+          <t>2025-12-13 14:30:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="G22" t="n">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="H22" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="I22" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="J22" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="K22" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="L22" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="M22" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="N22" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="O22" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="P22" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="Q22" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="R22" t="n">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="S22" t="n">
-        <v>2.94</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.94</v>
+        <v>4.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="V22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W22" t="n">
         <v>2.25</v>
       </c>
-      <c r="W22" t="n">
-        <v>3.93</v>
-      </c>
       <c r="X22" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.46</v>
+        <v>2.09</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-12-12 19:45:00</t>
+          <t>2025-12-13 14:30:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="G23" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.14</v>
+        <v>1.54</v>
       </c>
       <c r="I23" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>2.11</v>
+        <v>2.54</v>
       </c>
       <c r="K23" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="L23" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M23" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="N23" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="O23" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="P23" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="Q23" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="R23" t="n">
-        <v>2.23</v>
+        <v>1.84</v>
       </c>
       <c r="S23" t="n">
-        <v>2.99</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="W23" t="n">
-        <v>5.25</v>
+        <v>3.36</v>
       </c>
       <c r="X23" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-12-12 20:00:00</t>
+          <t>2025-12-13 14:30:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G24" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="H24" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="J24" t="n">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="K24" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="L24" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M24" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N24" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="O24" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="P24" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Q24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="R24" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="S24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="V24" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="X24" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.76</v>
+        <v>2.26</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.93</v>
+        <v>3.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-12-12 20:00:00</t>
+          <t>2025-12-13 15:00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3195,315 +3195,6092 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="G25" t="n">
-        <v>1.2</v>
+        <v>0.67</v>
       </c>
       <c r="H25" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="I25" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="J25" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="K25" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="L25" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="M25" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="N25" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="O25" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="P25" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q25" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="R25" t="n">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="T25" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="W25" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="X25" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AB25" t="n">
         <v>1.36</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE25" t="n">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.69</v>
+        <v>2.96</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-12 20:15:00</t>
+          <t>2025-12-13 15:00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="G26" t="n">
-        <v>0.57</v>
+        <v>1.22</v>
       </c>
       <c r="H26" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="I26" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="J26" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="K26" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="L26" t="n">
         <v>69</v>
       </c>
       <c r="M26" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="N26" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="O26" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="P26" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="Q26" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="R26" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC26" t="n">
         <v>1.85</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AD26" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.53</v>
+        <v>3.03</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12-13 01:00:00</t>
+          <t>2025-12-13 15:00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Colombia Categoria Primera A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C27" t="n">
+        <v>21</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Birmingham City</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="K27" t="n">
+        <v>48</v>
+      </c>
+      <c r="L27" t="n">
+        <v>59</v>
+      </c>
+      <c r="M27" t="n">
+        <v>38</v>
+      </c>
+      <c r="N27" t="n">
+        <v>26</v>
+      </c>
+      <c r="O27" t="n">
+        <v>74</v>
+      </c>
+      <c r="P27" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>47</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K28" t="n">
+        <v>31</v>
+      </c>
+      <c r="L28" t="n">
+        <v>79</v>
+      </c>
+      <c r="M28" t="n">
+        <v>11</v>
+      </c>
+      <c r="N28" t="n">
+        <v>42</v>
+      </c>
+      <c r="O28" t="n">
+        <v>59</v>
+      </c>
+      <c r="P28" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>64</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W28" t="n">
+        <v>4</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>21</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K29" t="n">
+        <v>56</v>
+      </c>
+      <c r="L29" t="n">
+        <v>78</v>
+      </c>
+      <c r="M29" t="n">
+        <v>44</v>
+      </c>
+      <c r="N29" t="n">
+        <v>22</v>
+      </c>
+      <c r="O29" t="n">
+        <v>78</v>
+      </c>
+      <c r="P29" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>50</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="T29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>21</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Leicester City</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ipswich Town</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K30" t="n">
+        <v>73</v>
+      </c>
+      <c r="L30" t="n">
+        <v>78</v>
+      </c>
+      <c r="M30" t="n">
+        <v>17</v>
+      </c>
+      <c r="N30" t="n">
+        <v>11</v>
+      </c>
+      <c r="O30" t="n">
+        <v>89</v>
+      </c>
+      <c r="P30" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>62</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>21</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K31" t="n">
+        <v>64</v>
+      </c>
+      <c r="L31" t="n">
+        <v>74</v>
+      </c>
+      <c r="M31" t="n">
+        <v>31</v>
+      </c>
+      <c r="N31" t="n">
+        <v>37</v>
+      </c>
+      <c r="O31" t="n">
+        <v>64</v>
+      </c>
+      <c r="P31" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>47</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>20</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Argeș</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Botoşani</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K32" t="n">
+        <v>33</v>
+      </c>
+      <c r="L32" t="n">
+        <v>62</v>
+      </c>
+      <c r="M32" t="n">
+        <v>45</v>
+      </c>
+      <c r="N32" t="n">
+        <v>33</v>
+      </c>
+      <c r="O32" t="n">
+        <v>67</v>
+      </c>
+      <c r="P32" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>67</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Livingston</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Dundee</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K33" t="n">
+        <v>54</v>
+      </c>
+      <c r="L33" t="n">
+        <v>79</v>
+      </c>
+      <c r="M33" t="n">
+        <v>29</v>
+      </c>
+      <c r="N33" t="n">
+        <v>28</v>
+      </c>
+      <c r="O33" t="n">
+        <v>73</v>
+      </c>
+      <c r="P33" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>40</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K34" t="n">
+        <v>66</v>
+      </c>
+      <c r="L34" t="n">
+        <v>82</v>
+      </c>
+      <c r="M34" t="n">
+        <v>41</v>
+      </c>
+      <c r="N34" t="n">
+        <v>13</v>
+      </c>
+      <c r="O34" t="n">
+        <v>88</v>
+      </c>
+      <c r="P34" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>47</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>18</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="K35" t="n">
+        <v>76</v>
+      </c>
+      <c r="L35" t="n">
+        <v>88</v>
+      </c>
+      <c r="M35" t="n">
+        <v>53</v>
+      </c>
+      <c r="N35" t="n">
+        <v>13</v>
+      </c>
+      <c r="O35" t="n">
+        <v>88</v>
+      </c>
+      <c r="P35" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>48</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:00:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K36" t="n">
+        <v>50</v>
+      </c>
+      <c r="L36" t="n">
+        <v>57</v>
+      </c>
+      <c r="M36" t="n">
+        <v>22</v>
+      </c>
+      <c r="N36" t="n">
+        <v>29</v>
+      </c>
+      <c r="O36" t="n">
+        <v>72</v>
+      </c>
+      <c r="P36" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>57</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:00:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="K37" t="n">
+        <v>57</v>
+      </c>
+      <c r="L37" t="n">
+        <v>79</v>
+      </c>
+      <c r="M37" t="n">
+        <v>14</v>
+      </c>
+      <c r="N37" t="n">
+        <v>14</v>
+      </c>
+      <c r="O37" t="n">
+        <v>86</v>
+      </c>
+      <c r="P37" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>50</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:00:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>14</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Levadiakos</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K38" t="n">
+        <v>54</v>
+      </c>
+      <c r="L38" t="n">
+        <v>85</v>
+      </c>
+      <c r="M38" t="n">
+        <v>45</v>
+      </c>
+      <c r="N38" t="n">
+        <v>16</v>
+      </c>
+      <c r="O38" t="n">
+        <v>85</v>
+      </c>
+      <c r="P38" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>40</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:15:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RCD Mallorca</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Elche CF</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K39" t="n">
+        <v>64</v>
+      </c>
+      <c r="L39" t="n">
+        <v>64</v>
+      </c>
+      <c r="M39" t="n">
+        <v>22</v>
+      </c>
+      <c r="N39" t="n">
+        <v>29</v>
+      </c>
+      <c r="O39" t="n">
+        <v>71</v>
+      </c>
+      <c r="P39" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>64</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:15:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>18</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Real Valladolid</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>FC Andorra</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="K40" t="n">
+        <v>62</v>
+      </c>
+      <c r="L40" t="n">
+        <v>73</v>
+      </c>
+      <c r="M40" t="n">
+        <v>17</v>
+      </c>
+      <c r="N40" t="n">
+        <v>22</v>
+      </c>
+      <c r="O40" t="n">
+        <v>78</v>
+      </c>
+      <c r="P40" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>50</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:15:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>18</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sporting Gijón</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K41" t="n">
+        <v>59</v>
+      </c>
+      <c r="L41" t="n">
+        <v>71</v>
+      </c>
+      <c r="M41" t="n">
+        <v>29</v>
+      </c>
+      <c r="N41" t="n">
+        <v>36</v>
+      </c>
+      <c r="O41" t="n">
+        <v>65</v>
+      </c>
+      <c r="P41" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>53</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:30:00</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Telstar</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NEC</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K42" t="n">
+        <v>88</v>
+      </c>
+      <c r="L42" t="n">
+        <v>94</v>
+      </c>
+      <c r="M42" t="n">
+        <v>57</v>
+      </c>
+      <c r="N42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O42" t="n">
+        <v>94</v>
+      </c>
+      <c r="P42" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>25</v>
+      </c>
+      <c r="R42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:30:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>14</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K43" t="n">
+        <v>40</v>
+      </c>
+      <c r="L43" t="n">
+        <v>69</v>
+      </c>
+      <c r="M43" t="n">
+        <v>47</v>
+      </c>
+      <c r="N43" t="n">
+        <v>22</v>
+      </c>
+      <c r="O43" t="n">
+        <v>79</v>
+      </c>
+      <c r="P43" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>69</v>
+      </c>
+      <c r="R43" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:30:00</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>14</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CD Nacional</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CD Tondela</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K44" t="n">
+        <v>48</v>
+      </c>
+      <c r="L44" t="n">
+        <v>77</v>
+      </c>
+      <c r="M44" t="n">
+        <v>45</v>
+      </c>
+      <c r="N44" t="n">
+        <v>23</v>
+      </c>
+      <c r="O44" t="n">
+        <v>77</v>
+      </c>
+      <c r="P44" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>31</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W44" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025-12-13 16:00:00</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K45" t="n">
+        <v>57</v>
+      </c>
+      <c r="L45" t="n">
+        <v>71</v>
+      </c>
+      <c r="M45" t="n">
+        <v>43</v>
+      </c>
+      <c r="N45" t="n">
+        <v>22</v>
+      </c>
+      <c r="O45" t="n">
+        <v>79</v>
+      </c>
+      <c r="P45" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>36</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2025-12-13 16:00:00</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Austria Bundesliga</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>17</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ried</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Rheindorf Altach</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K46" t="n">
+        <v>32</v>
+      </c>
+      <c r="L46" t="n">
+        <v>63</v>
+      </c>
+      <c r="M46" t="n">
+        <v>38</v>
+      </c>
+      <c r="N46" t="n">
+        <v>38</v>
+      </c>
+      <c r="O46" t="n">
+        <v>63</v>
+      </c>
+      <c r="P46" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>63</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V46" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025-12-13 16:00:00</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Austria Bundesliga</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>17</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Hartberg</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Wattens</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K47" t="n">
+        <v>60</v>
+      </c>
+      <c r="L47" t="n">
+        <v>73</v>
+      </c>
+      <c r="M47" t="n">
+        <v>34</v>
+      </c>
+      <c r="N47" t="n">
+        <v>27</v>
+      </c>
+      <c r="O47" t="n">
+        <v>73</v>
+      </c>
+      <c r="P47" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>53</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W47" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025-12-13 16:00:00</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Austria Bundesliga</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>17</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Grazer AK</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K48" t="n">
+        <v>57</v>
+      </c>
+      <c r="L48" t="n">
+        <v>82</v>
+      </c>
+      <c r="M48" t="n">
+        <v>51</v>
+      </c>
+      <c r="N48" t="n">
+        <v>26</v>
+      </c>
+      <c r="O48" t="n">
+        <v>76</v>
+      </c>
+      <c r="P48" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>44</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U48" t="n">
         <v>0</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Deportes Tolima</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
+      <c r="V48" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025-12-13 16:00:00</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>14</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>OFI</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Panserraikos</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="K49" t="n">
+        <v>50</v>
+      </c>
+      <c r="L49" t="n">
+        <v>75</v>
+      </c>
+      <c r="M49" t="n">
+        <v>33</v>
+      </c>
+      <c r="N49" t="n">
+        <v>17</v>
+      </c>
+      <c r="O49" t="n">
+        <v>84</v>
+      </c>
+      <c r="P49" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>33</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W49" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-12-13 16:15:00</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Avellino</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K50" t="n">
+        <v>63</v>
+      </c>
+      <c r="L50" t="n">
+        <v>82</v>
+      </c>
+      <c r="M50" t="n">
+        <v>57</v>
+      </c>
+      <c r="N50" t="n">
+        <v>19</v>
+      </c>
+      <c r="O50" t="n">
+        <v>82</v>
+      </c>
+      <c r="P50" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>57</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-12-13 16:45:00</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Croatia Prva HNL</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>17</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K51" t="n">
+        <v>50</v>
+      </c>
+      <c r="L51" t="n">
+        <v>76</v>
+      </c>
+      <c r="M51" t="n">
+        <v>26</v>
+      </c>
+      <c r="N51" t="n">
+        <v>25</v>
+      </c>
+      <c r="O51" t="n">
+        <v>75</v>
+      </c>
+      <c r="P51" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>63</v>
+      </c>
+      <c r="R51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V51" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W51" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:00:00</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>17</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J52" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K52" t="n">
+        <v>57</v>
+      </c>
+      <c r="L52" t="n">
+        <v>100</v>
+      </c>
+      <c r="M52" t="n">
+        <v>63</v>
+      </c>
+      <c r="N52" t="n">
+        <v>7</v>
+      </c>
+      <c r="O52" t="n">
+        <v>94</v>
+      </c>
+      <c r="P52" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>7</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T52" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W52" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:00:00</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>17</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K53" t="n">
+        <v>38</v>
+      </c>
+      <c r="L53" t="n">
+        <v>69</v>
+      </c>
+      <c r="M53" t="n">
+        <v>38</v>
+      </c>
+      <c r="N53" t="n">
+        <v>32</v>
+      </c>
+      <c r="O53" t="n">
+        <v>69</v>
+      </c>
+      <c r="P53" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>57</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:00:00</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Turkey Süper Lig</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>16</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Antalyaspor</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K54" t="n">
+        <v>58</v>
+      </c>
+      <c r="L54" t="n">
+        <v>86</v>
+      </c>
+      <c r="M54" t="n">
+        <v>43</v>
+      </c>
+      <c r="N54" t="n">
+        <v>15</v>
+      </c>
+      <c r="O54" t="n">
+        <v>86</v>
+      </c>
+      <c r="P54" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>36</v>
+      </c>
+      <c r="R54" t="n">
+        <v>8</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:00:00</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>15</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="K55" t="n">
+        <v>29</v>
+      </c>
+      <c r="L55" t="n">
+        <v>50</v>
+      </c>
+      <c r="M55" t="n">
+        <v>22</v>
+      </c>
+      <c r="N55" t="n">
+        <v>43</v>
+      </c>
+      <c r="O55" t="n">
+        <v>57</v>
+      </c>
+      <c r="P55" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>72</v>
+      </c>
+      <c r="R55" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V55" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W55" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:15:00</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>18</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K56" t="n">
+        <v>57</v>
+      </c>
+      <c r="L56" t="n">
+        <v>57</v>
+      </c>
+      <c r="M56" t="n">
+        <v>32</v>
+      </c>
+      <c r="N56" t="n">
+        <v>26</v>
+      </c>
+      <c r="O56" t="n">
+        <v>76</v>
+      </c>
+      <c r="P56" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>63</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="W56" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:30:00</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>16</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CA Osasuna</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="K57" t="n">
+        <v>44</v>
+      </c>
+      <c r="L57" t="n">
+        <v>63</v>
+      </c>
+      <c r="M57" t="n">
+        <v>51</v>
+      </c>
+      <c r="N57" t="n">
+        <v>32</v>
+      </c>
+      <c r="O57" t="n">
+        <v>69</v>
+      </c>
+      <c r="P57" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>38</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S57" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T57" t="n">
+        <v>10</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X57" t="n">
         <v>1.62</v>
       </c>
-      <c r="G27" t="n">
+      <c r="Y57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:30:00</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="K58" t="n">
+        <v>43</v>
+      </c>
+      <c r="L58" t="n">
+        <v>71</v>
+      </c>
+      <c r="M58" t="n">
+        <v>29</v>
+      </c>
+      <c r="N58" t="n">
+        <v>15</v>
+      </c>
+      <c r="O58" t="n">
+        <v>86</v>
+      </c>
+      <c r="P58" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>72</v>
+      </c>
+      <c r="R58" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V58" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="W58" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:30:00</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>14</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Köln</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K59" t="n">
+        <v>57</v>
+      </c>
+      <c r="L59" t="n">
+        <v>79</v>
+      </c>
+      <c r="M59" t="n">
+        <v>36</v>
+      </c>
+      <c r="N59" t="n">
+        <v>22</v>
+      </c>
+      <c r="O59" t="n">
+        <v>79</v>
+      </c>
+      <c r="P59" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>50</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T59" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W59" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X59" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:30:00</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>18</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Leganés</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="K60" t="n">
+        <v>62</v>
+      </c>
+      <c r="L60" t="n">
+        <v>61</v>
+      </c>
+      <c r="M60" t="n">
+        <v>45</v>
+      </c>
+      <c r="N60" t="n">
+        <v>22</v>
+      </c>
+      <c r="O60" t="n">
+        <v>78</v>
+      </c>
+      <c r="P60" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>34</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W60" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X60" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:45:00</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>16</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Volendam</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K61" t="n">
+        <v>50</v>
+      </c>
+      <c r="L61" t="n">
+        <v>86</v>
+      </c>
+      <c r="M61" t="n">
+        <v>50</v>
+      </c>
+      <c r="N61" t="n">
+        <v>14</v>
+      </c>
+      <c r="O61" t="n">
+        <v>86</v>
+      </c>
+      <c r="P61" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>43</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S61" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T61" t="n">
+        <v>6</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W61" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-12-13 18:00:00</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>16</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K62" t="n">
+        <v>40</v>
+      </c>
+      <c r="L62" t="n">
+        <v>47</v>
+      </c>
+      <c r="M62" t="n">
+        <v>19</v>
+      </c>
+      <c r="N62" t="n">
+        <v>41</v>
+      </c>
+      <c r="O62" t="n">
+        <v>60</v>
+      </c>
+      <c r="P62" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>67</v>
+      </c>
+      <c r="R62" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="S62" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X62" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC62" t="n">
         <v>1.85</v>
       </c>
-      <c r="H27" t="n">
+      <c r="AD62" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-12-13 18:00:00</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>14</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Rio Ave FC</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Vitória Guimarães</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K63" t="n">
+        <v>25</v>
+      </c>
+      <c r="L63" t="n">
+        <v>84</v>
+      </c>
+      <c r="M63" t="n">
+        <v>50</v>
+      </c>
+      <c r="N63" t="n">
+        <v>9</v>
+      </c>
+      <c r="O63" t="n">
+        <v>92</v>
+      </c>
+      <c r="P63" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>58</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S63" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V63" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W63" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X63" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-12-13 18:00:00</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>14</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Asteras Tripolis</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H64" t="n">
         <v>1.29</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I64" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K64" t="n">
+        <v>48</v>
+      </c>
+      <c r="L64" t="n">
+        <v>77</v>
+      </c>
+      <c r="M64" t="n">
+        <v>25</v>
+      </c>
+      <c r="N64" t="n">
+        <v>30</v>
+      </c>
+      <c r="O64" t="n">
+        <v>70</v>
+      </c>
+      <c r="P64" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>52</v>
+      </c>
+      <c r="R64" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W64" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X64" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AG64" t="n">
         <v>1.33</v>
       </c>
-      <c r="J27" t="n">
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-12-13 18:30:00</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>16</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K65" t="n">
+        <v>41</v>
+      </c>
+      <c r="L65" t="n">
+        <v>63</v>
+      </c>
+      <c r="M65" t="n">
+        <v>24</v>
+      </c>
+      <c r="N65" t="n">
+        <v>44</v>
+      </c>
+      <c r="O65" t="n">
+        <v>56</v>
+      </c>
+      <c r="P65" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>61</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W65" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-12-13 18:30:00</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>20</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Rapid Bucureşti</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Oţelul Galaţi</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K66" t="n">
+        <v>56</v>
+      </c>
+      <c r="L66" t="n">
+        <v>67</v>
+      </c>
+      <c r="M66" t="n">
+        <v>33</v>
+      </c>
+      <c r="N66" t="n">
+        <v>22</v>
+      </c>
+      <c r="O66" t="n">
+        <v>78</v>
+      </c>
+      <c r="P66" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>50</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V66" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W66" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-12-13 19:00:00</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>16</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Heracles</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="K67" t="n">
+        <v>61</v>
+      </c>
+      <c r="L67" t="n">
+        <v>100</v>
+      </c>
+      <c r="M67" t="n">
+        <v>42</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>100</v>
+      </c>
+      <c r="P67" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>20</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="n">
+        <v>15</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X67" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-12-13 19:30:00</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>17</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="K68" t="n">
+        <v>81</v>
+      </c>
+      <c r="L68" t="n">
+        <v>66</v>
+      </c>
+      <c r="M68" t="n">
+        <v>53</v>
+      </c>
+      <c r="N68" t="n">
+        <v>14</v>
+      </c>
+      <c r="O68" t="n">
+        <v>87</v>
+      </c>
+      <c r="P68" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>20</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W68" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="X68" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z68" t="n">
         <v>2.62</v>
       </c>
-      <c r="K27" t="n">
-        <v>52</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="AA68" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-12-13 19:30:00</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>16</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Hannover 96</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="K69" t="n">
+        <v>53</v>
+      </c>
+      <c r="L69" t="n">
+        <v>54</v>
+      </c>
+      <c r="M69" t="n">
+        <v>41</v>
+      </c>
+      <c r="N69" t="n">
+        <v>14</v>
+      </c>
+      <c r="O69" t="n">
+        <v>87</v>
+      </c>
+      <c r="P69" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>26</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S69" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W69" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-12-13 19:45:00</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>18</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J70" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K70" t="n">
+        <v>54</v>
+      </c>
+      <c r="L70" t="n">
+        <v>66</v>
+      </c>
+      <c r="M70" t="n">
+        <v>30</v>
+      </c>
+      <c r="N70" t="n">
+        <v>28</v>
+      </c>
+      <c r="O70" t="n">
         <v>72</v>
       </c>
-      <c r="M27" t="n">
-        <v>31</v>
-      </c>
-      <c r="N27" t="n">
-        <v>32</v>
-      </c>
-      <c r="O27" t="n">
-        <v>68</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="P70" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>65</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S70" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W70" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-12-13 19:45:00</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>15</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K71" t="n">
+        <v>57</v>
+      </c>
+      <c r="L71" t="n">
+        <v>72</v>
+      </c>
+      <c r="M71" t="n">
+        <v>29</v>
+      </c>
+      <c r="N71" t="n">
+        <v>22</v>
+      </c>
+      <c r="O71" t="n">
+        <v>79</v>
+      </c>
+      <c r="P71" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>64</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T71" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W71" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X71" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-12-13 20:00:00</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>16</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PEC Zwolle</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J72" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K72" t="n">
+        <v>50</v>
+      </c>
+      <c r="L72" t="n">
+        <v>93</v>
+      </c>
+      <c r="M72" t="n">
         <v>43</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="N72" t="n">
+        <v>22</v>
+      </c>
+      <c r="O72" t="n">
+        <v>79</v>
+      </c>
+      <c r="P72" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>50</v>
+      </c>
+      <c r="R72" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S72" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W72" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X72" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-12-13 20:00:00</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>16</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RCD Espanyol</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K73" t="n">
+        <v>38</v>
+      </c>
+      <c r="L73" t="n">
+        <v>40</v>
+      </c>
+      <c r="M73" t="n">
+        <v>24</v>
+      </c>
+      <c r="N73" t="n">
+        <v>38</v>
+      </c>
+      <c r="O73" t="n">
+        <v>62</v>
+      </c>
+      <c r="P73" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>77</v>
+      </c>
+      <c r="R73" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S73" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V73" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W73" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="X73" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-12-13 20:00:00</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>20</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Falkirk</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Hearts</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J74" t="n">
+        <v>3</v>
+      </c>
+      <c r="K74" t="n">
+        <v>69</v>
+      </c>
+      <c r="L74" t="n">
+        <v>82</v>
+      </c>
+      <c r="M74" t="n">
+        <v>25</v>
+      </c>
+      <c r="N74" t="n">
+        <v>19</v>
+      </c>
+      <c r="O74" t="n">
+        <v>82</v>
+      </c>
+      <c r="P74" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>38</v>
+      </c>
+      <c r="R74" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W74" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X74" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-12-13 20:00:00</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>16</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K75" t="n">
+        <v>22</v>
+      </c>
+      <c r="L75" t="n">
+        <v>79</v>
+      </c>
+      <c r="M75" t="n">
+        <v>15</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29</v>
+      </c>
+      <c r="O75" t="n">
+        <v>72</v>
+      </c>
+      <c r="P75" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>64</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S75" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="T75" t="n">
+        <v>16</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V75" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025-12-13 20:00:00</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>18</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruña</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Real Sociedad II</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K76" t="n">
+        <v>50</v>
+      </c>
+      <c r="L76" t="n">
+        <v>69</v>
+      </c>
+      <c r="M76" t="n">
+        <v>25</v>
+      </c>
+      <c r="N76" t="n">
+        <v>38</v>
+      </c>
+      <c r="O76" t="n">
+        <v>63</v>
+      </c>
+      <c r="P76" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>50</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S76" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T76" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W76" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X76" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-12-13 20:00:00</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>18</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Real Zaragoza</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J77" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="K77" t="n">
+        <v>38</v>
+      </c>
+      <c r="L77" t="n">
+        <v>50</v>
+      </c>
+      <c r="M77" t="n">
+        <v>19</v>
+      </c>
+      <c r="N77" t="n">
+        <v>44</v>
+      </c>
+      <c r="O77" t="n">
         <v>57</v>
       </c>
-      <c r="R27" t="n">
+      <c r="P77" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>63</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V77" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W77" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X77" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-12-13 20:05:00</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>16</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K78" t="n">
+        <v>64</v>
+      </c>
+      <c r="L78" t="n">
+        <v>79</v>
+      </c>
+      <c r="M78" t="n">
+        <v>29</v>
+      </c>
+      <c r="N78" t="n">
+        <v>29</v>
+      </c>
+      <c r="O78" t="n">
+        <v>72</v>
+      </c>
+      <c r="P78" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>50</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S78" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W78" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X78" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-12-13 20:30:00</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>14</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AVS</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J79" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K79" t="n">
+        <v>42</v>
+      </c>
+      <c r="L79" t="n">
+        <v>67</v>
+      </c>
+      <c r="M79" t="n">
+        <v>50</v>
+      </c>
+      <c r="N79" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="n">
+      <c r="O79" t="n">
+        <v>100</v>
+      </c>
+      <c r="P79" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>25</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="S79" t="n">
+        <v>13</v>
+      </c>
+      <c r="T79" t="n">
+        <v>24</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X79" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-12-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Argentina Primera División</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
         <v>0</v>
       </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J80" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K80" t="n">
+        <v>40</v>
+      </c>
+      <c r="L80" t="n">
+        <v>61</v>
+      </c>
+      <c r="M80" t="n">
+        <v>18</v>
+      </c>
+      <c r="N80" t="n">
+        <v>42</v>
+      </c>
+      <c r="O80" t="n">
+        <v>59</v>
+      </c>
+      <c r="P80" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>67</v>
+      </c>
+      <c r="R80" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S80" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V80" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W80" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="X80" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -471,10 +471,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="31.2" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="20.4" customWidth="1" min="4" max="4"/>
-    <col width="14.4" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="15.6" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,116 +675,116 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-16 17:00:00</t>
+          <t>2025-12-17 19:30:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="I2" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="J2" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="L2" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="M2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N2" t="n">
+        <v>29</v>
+      </c>
+      <c r="O2" t="n">
+        <v>71</v>
+      </c>
+      <c r="P2" t="n">
         <v>54</v>
       </c>
-      <c r="N2" t="n">
-        <v>13</v>
-      </c>
-      <c r="O2" t="n">
-        <v>88</v>
-      </c>
-      <c r="P2" t="n">
-        <v>44</v>
-      </c>
       <c r="Q2" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="R2" t="n">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="V2" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="W2" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="X2" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AB2" t="n">
         <v>1.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-16 19:30:00</t>
+          <t>2025-12-17 19:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -797,103 +797,103 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.67</v>
+        <v>0.88</v>
       </c>
       <c r="G3" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="H3" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="I3" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="K3" t="n">
+        <v>78</v>
+      </c>
+      <c r="L3" t="n">
+        <v>76</v>
+      </c>
+      <c r="M3" t="n">
         <v>60</v>
       </c>
-      <c r="L3" t="n">
-        <v>82</v>
-      </c>
-      <c r="M3" t="n">
-        <v>53</v>
-      </c>
       <c r="N3" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="P3" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="Q3" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
-        <v>2.16</v>
+        <v>2.98</v>
       </c>
       <c r="S3" t="n">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-16 19:30:00</t>
+          <t>2025-12-17 19:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -906,206 +906,206 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.63</v>
+        <v>1.44</v>
       </c>
       <c r="G4" t="n">
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="H4" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="I4" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="L4" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M4" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="O4" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="P4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="R4" t="n">
-        <v>3.63</v>
+        <v>2.72</v>
       </c>
       <c r="S4" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="T4" t="n">
-        <v>1.73</v>
+        <v>2.21</v>
       </c>
       <c r="U4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W4" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="X4" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="AB4" t="n">
         <v>1.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-17 00:30:00</t>
+          <t>2025-12-17 20:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Colombia Categoria Primera A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.81</v>
+        <v>1.13</v>
       </c>
       <c r="G5" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="I5" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="J5" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="K5" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L5" t="n">
         <v>73</v>
       </c>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="N5" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="O5" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="P5" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q5" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.21</v>
+        <v>1.36</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="X5" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.95</v>
+        <v>2.87</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.56</v>
+        <v>1.61</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG5" headerRowCount="1">
-  <autoFilter ref="A1:AG5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG19" headerRowCount="1">
+  <autoFilter ref="A1:AG19"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG5"/>
+  <dimension ref="A1:AG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="31.2" customWidth="1" min="2" max="2"/>
+    <col width="45.6" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="15.6" customWidth="1" min="5" max="5"/>
+    <col width="22.8" customWidth="1" min="4" max="4"/>
+    <col width="27.6" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,437 +675,1963 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-17 19:30:00</t>
+          <t>2025-12-18 20:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="H2" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="I2" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="K2" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="L2" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="O2" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="P2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R2" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="W2" t="n">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="X2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.8</v>
+        <v>2.21</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.09</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.11</v>
+        <v>2.69</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.8</v>
+        <v>2.89</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-17 19:30:00</t>
+          <t>2025-12-18 20:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.88</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="K3" t="n">
+        <v>46</v>
+      </c>
+      <c r="L3" t="n">
+        <v>59</v>
+      </c>
+      <c r="M3" t="n">
+        <v>36</v>
+      </c>
+      <c r="N3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O3" t="n">
+        <v>78</v>
+      </c>
+      <c r="P3" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>46</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.56</v>
       </c>
-      <c r="H3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="K3" t="n">
-        <v>78</v>
-      </c>
-      <c r="L3" t="n">
-        <v>76</v>
-      </c>
-      <c r="M3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N3" t="n">
-        <v>11</v>
-      </c>
-      <c r="O3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P3" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>23</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AC3" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-17 19:30:00</t>
+          <t>2025-12-18 20:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>49</v>
+      </c>
+      <c r="L4" t="n">
+        <v>86</v>
+      </c>
+      <c r="M4" t="n">
+        <v>42</v>
+      </c>
+      <c r="N4" t="n">
+        <v>32</v>
+      </c>
+      <c r="O4" t="n">
+        <v>69</v>
+      </c>
+      <c r="P4" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>39</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.25</v>
       </c>
-      <c r="H4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>58</v>
-      </c>
-      <c r="L4" t="n">
-        <v>82</v>
-      </c>
-      <c r="M4" t="n">
-        <v>47</v>
-      </c>
-      <c r="N4" t="n">
-        <v>31</v>
-      </c>
-      <c r="O4" t="n">
-        <v>70</v>
-      </c>
-      <c r="P4" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>31</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-17 20:00:00</t>
+          <t>2025-12-18 20:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Europe UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K5" t="n">
+        <v>43</v>
+      </c>
+      <c r="L5" t="n">
+        <v>68</v>
+      </c>
+      <c r="M5" t="n">
+        <v>34</v>
+      </c>
+      <c r="N5" t="n">
+        <v>38</v>
+      </c>
+      <c r="O5" t="n">
+        <v>62</v>
+      </c>
+      <c r="P5" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>53</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>13</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.13</v>
       </c>
-      <c r="G5" t="n">
+      <c r="V5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AEK Larnaca</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Shkendija</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L6" t="n">
+        <v>40</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20</v>
+      </c>
+      <c r="N6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O6" t="n">
+        <v>50</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>90</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="K7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L7" t="n">
+        <v>87</v>
+      </c>
+      <c r="M7" t="n">
+        <v>33</v>
+      </c>
+      <c r="N7" t="n">
+        <v>21</v>
+      </c>
+      <c r="O7" t="n">
+        <v>80</v>
+      </c>
+      <c r="P7" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>47</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>1.86</v>
       </c>
-      <c r="H5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="G8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K8" t="n">
+        <v>35</v>
+      </c>
+      <c r="L8" t="n">
+        <v>39</v>
+      </c>
+      <c r="M8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N8" t="n">
+        <v>52</v>
+      </c>
+      <c r="O8" t="n">
+        <v>49</v>
+      </c>
+      <c r="P8" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>69</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dynamo Kyiv</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Artsakh</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K9" t="n">
+        <v>53</v>
+      </c>
+      <c r="L9" t="n">
+        <v>100</v>
+      </c>
+      <c r="M9" t="n">
+        <v>32</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>93</v>
+      </c>
+      <c r="P9" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>42</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Zrinjski</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Rapid Wien</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="K10" t="n">
+        <v>38</v>
+      </c>
+      <c r="L10" t="n">
+        <v>96</v>
+      </c>
+      <c r="M10" t="n">
+        <v>38</v>
+      </c>
+      <c r="N10" t="n">
+        <v>29</v>
+      </c>
+      <c r="O10" t="n">
+        <v>71</v>
+      </c>
+      <c r="P10" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>38</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Legia Warszawa</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K11" t="n">
+        <v>76</v>
+      </c>
+      <c r="L11" t="n">
+        <v>90</v>
+      </c>
+      <c r="M11" t="n">
+        <v>27</v>
+      </c>
+      <c r="N11" t="n">
+        <v>15</v>
+      </c>
+      <c r="O11" t="n">
+        <v>86</v>
+      </c>
+      <c r="P11" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>25</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Celje</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L12" t="n">
+        <v>66</v>
+      </c>
+      <c r="M12" t="n">
+        <v>48</v>
+      </c>
+      <c r="N12" t="n">
+        <v>27</v>
+      </c>
+      <c r="O12" t="n">
+        <v>73</v>
+      </c>
+      <c r="P12" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>52</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="T12" t="n">
+        <v>15</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Raków Częstochowa</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K13" t="n">
+        <v>32</v>
+      </c>
+      <c r="L13" t="n">
+        <v>73</v>
+      </c>
+      <c r="M13" t="n">
+        <v>32</v>
+      </c>
+      <c r="N13" t="n">
+        <v>36</v>
+      </c>
+      <c r="O13" t="n">
+        <v>64</v>
+      </c>
+      <c r="P13" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>64</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Drita</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>50</v>
+      </c>
+      <c r="L14" t="n">
+        <v>64</v>
+      </c>
+      <c r="M14" t="n">
+        <v>36</v>
+      </c>
+      <c r="N14" t="n">
+        <v>29</v>
+      </c>
+      <c r="O14" t="n">
+        <v>72</v>
+      </c>
+      <c r="P14" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>50</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>23</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K15" t="n">
+        <v>64</v>
+      </c>
+      <c r="L15" t="n">
+        <v>79</v>
+      </c>
+      <c r="M15" t="n">
+        <v>50</v>
+      </c>
+      <c r="N15" t="n">
+        <v>22</v>
+      </c>
+      <c r="O15" t="n">
+        <v>79</v>
+      </c>
+      <c r="P15" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>36</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>12</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.43</v>
       </c>
-      <c r="J5" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K5" t="n">
-        <v>47</v>
-      </c>
-      <c r="L5" t="n">
-        <v>73</v>
-      </c>
-      <c r="M5" t="n">
-        <v>47</v>
-      </c>
-      <c r="N5" t="n">
-        <v>21</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="AC15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="K16" t="n">
+        <v>46</v>
+      </c>
+      <c r="L16" t="n">
+        <v>56</v>
+      </c>
+      <c r="M16" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>30</v>
+      </c>
+      <c r="O16" t="n">
+        <v>70</v>
+      </c>
+      <c r="P16" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>62</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Hamrun Spartans</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="K17" t="n">
+        <v>37</v>
+      </c>
+      <c r="L17" t="n">
+        <v>58</v>
+      </c>
+      <c r="M17" t="n">
+        <v>25</v>
+      </c>
+      <c r="N17" t="n">
+        <v>35</v>
+      </c>
+      <c r="O17" t="n">
+        <v>65</v>
+      </c>
+      <c r="P17" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>51</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sigma Olomouc</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Lech Poznań</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K18" t="n">
         <v>80</v>
       </c>
-      <c r="P5" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>54</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="L18" t="n">
+        <v>80</v>
+      </c>
+      <c r="M18" t="n">
+        <v>60</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>100</v>
+      </c>
+      <c r="P18" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>40</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.78</v>
       </c>
-      <c r="Y5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AB18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-12-18 20:00:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Europe UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Häcken</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K19" t="n">
+        <v>66</v>
+      </c>
+      <c r="L19" t="n">
+        <v>79</v>
+      </c>
+      <c r="M19" t="n">
+        <v>45</v>
+      </c>
+      <c r="N19" t="n">
+        <v>25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>76</v>
+      </c>
+      <c r="P19" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>42</v>
+      </c>
+      <c r="R19" t="n">
         <v>2.25</v>
       </c>
-      <c r="AF5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.47</v>
+      <c r="S19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG19" headerRowCount="1">
-  <autoFilter ref="A1:AG19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG42" headerRowCount="1">
+  <autoFilter ref="A1:AG42"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG19"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="45.6" customWidth="1" min="2" max="2"/>
+    <col width="33.6" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="22.8" customWidth="1" min="4" max="4"/>
-    <col width="27.6" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="25.2" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,1249 +675,1249 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 15:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="I2" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="J2" t="n">
-        <v>3.04</v>
+        <v>2.72</v>
       </c>
       <c r="K2" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="L2" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="M2" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O2" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>2.09</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>3.31</v>
       </c>
       <c r="T2" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V2" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="W2" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="AD2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 17:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97</v>
+        <v>1.31</v>
       </c>
       <c r="I3" t="n">
-        <v>1.42</v>
+        <v>0.76</v>
       </c>
       <c r="J3" t="n">
-        <v>3.39</v>
+        <v>2.07</v>
       </c>
       <c r="K3" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="M3" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="O3" t="n">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="P3" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="Q3" t="n">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="R3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.38</v>
       </c>
-      <c r="S3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>6</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.19</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.48</v>
+        <v>3.54</v>
       </c>
       <c r="X3" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.44</v>
+        <v>2.04</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.85</v>
+        <v>2.52</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 17:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0.71</v>
       </c>
       <c r="H4" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="I4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="K4" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="M4" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="O4" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="P4" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="S4" t="n">
-        <v>4.33</v>
+        <v>3.02</v>
       </c>
       <c r="T4" t="n">
-        <v>5.2</v>
+        <v>3.83</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.6</v>
       </c>
-      <c r="W4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.65</v>
-      </c>
       <c r="Y4" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.78</v>
+        <v>2.28</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 17:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4</v>
+        <v>1.57</v>
       </c>
       <c r="H5" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="I5" t="n">
-        <v>0.99</v>
+        <v>1.42</v>
       </c>
       <c r="J5" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="K5" t="n">
+        <v>53</v>
+      </c>
+      <c r="L5" t="n">
+        <v>52</v>
+      </c>
+      <c r="M5" t="n">
+        <v>26</v>
+      </c>
+      <c r="N5" t="n">
+        <v>28</v>
+      </c>
+      <c r="O5" t="n">
+        <v>73</v>
+      </c>
+      <c r="P5" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>48</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W5" t="n">
         <v>2.57</v>
       </c>
-      <c r="K5" t="n">
-        <v>43</v>
-      </c>
-      <c r="L5" t="n">
-        <v>68</v>
-      </c>
-      <c r="M5" t="n">
-        <v>34</v>
-      </c>
-      <c r="N5" t="n">
-        <v>38</v>
-      </c>
-      <c r="O5" t="n">
-        <v>62</v>
-      </c>
-      <c r="P5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>53</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>13</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.23</v>
-      </c>
       <c r="X5" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 18:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="I6" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="J6" t="n">
-        <v>2.27</v>
+        <v>2.92</v>
       </c>
       <c r="K6" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="M6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="N6" t="n">
+        <v>15</v>
+      </c>
+      <c r="O6" t="n">
+        <v>85</v>
+      </c>
+      <c r="P6" t="n">
         <v>50</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>50</v>
       </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>90</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.62</v>
+        <v>2.64</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7</v>
+        <v>2.94</v>
       </c>
       <c r="T6" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="W6" t="n">
-        <v>3.79</v>
+        <v>3.34</v>
       </c>
       <c r="X6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y6" t="n">
         <v>2.05</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.7</v>
-      </c>
       <c r="Z6" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.78</v>
+        <v>1.86</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 19:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.14</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="I7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="K7" t="n">
+        <v>35</v>
+      </c>
+      <c r="L7" t="n">
+        <v>65</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="n">
+        <v>25</v>
+      </c>
+      <c r="O7" t="n">
+        <v>75</v>
+      </c>
+      <c r="P7" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>45</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.53</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="K7" t="n">
-        <v>40</v>
-      </c>
-      <c r="L7" t="n">
-        <v>87</v>
-      </c>
-      <c r="M7" t="n">
-        <v>33</v>
-      </c>
-      <c r="N7" t="n">
-        <v>21</v>
-      </c>
-      <c r="O7" t="n">
-        <v>80</v>
-      </c>
-      <c r="P7" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>47</v>
-      </c>
-      <c r="R7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.79</v>
-      </c>
       <c r="W7" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="X7" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.05</v>
+        <v>3.22</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.78</v>
+        <v>2.42</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.26</v>
+        <v>1.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 19:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.13</v>
+        <v>1.74</v>
       </c>
       <c r="J8" t="n">
-        <v>3.06</v>
+        <v>4.14</v>
       </c>
       <c r="K8" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="L8" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="M8" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="N8" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="Q8" t="n">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="R8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.26</v>
       </c>
-      <c r="S8" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="T8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AC8" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.42</v>
+        <v>5.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 19:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>50</v>
+      </c>
+      <c r="L9" t="n">
+        <v>75</v>
+      </c>
+      <c r="M9" t="n">
+        <v>50</v>
+      </c>
+      <c r="N9" t="n">
+        <v>30</v>
+      </c>
+      <c r="O9" t="n">
+        <v>70</v>
+      </c>
+      <c r="P9" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>40</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="K9" t="n">
-        <v>53</v>
-      </c>
-      <c r="L9" t="n">
-        <v>100</v>
-      </c>
-      <c r="M9" t="n">
-        <v>32</v>
-      </c>
-      <c r="N9" t="n">
-        <v>7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>93</v>
-      </c>
-      <c r="P9" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>42</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.35</v>
-      </c>
       <c r="X9" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.24</v>
+        <v>2.67</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.77</v>
+        <v>2.09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.77</v>
+        <v>4.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 19:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="H10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K10" t="n">
+        <v>60</v>
+      </c>
+      <c r="L10" t="n">
+        <v>75</v>
+      </c>
+      <c r="M10" t="n">
+        <v>60</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" t="n">
+        <v>70</v>
+      </c>
+      <c r="P10" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>35</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.44</v>
       </c>
-      <c r="I10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="K10" t="n">
-        <v>38</v>
-      </c>
-      <c r="L10" t="n">
-        <v>96</v>
-      </c>
-      <c r="M10" t="n">
-        <v>38</v>
-      </c>
-      <c r="N10" t="n">
-        <v>29</v>
-      </c>
-      <c r="O10" t="n">
-        <v>71</v>
-      </c>
-      <c r="P10" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>38</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="Y10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.37</v>
       </c>
-      <c r="V10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AC10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2.23</v>
       </c>
-      <c r="AD10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AF10" t="n">
-        <v>2.65</v>
+        <v>3.36</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 19:30:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="G11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K11" t="n">
+        <v>64</v>
+      </c>
+      <c r="L11" t="n">
+        <v>57</v>
+      </c>
+      <c r="M11" t="n">
+        <v>36</v>
+      </c>
+      <c r="N11" t="n">
+        <v>36</v>
+      </c>
+      <c r="O11" t="n">
+        <v>64</v>
+      </c>
+      <c r="P11" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>57</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.4</v>
       </c>
-      <c r="H11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K11" t="n">
-        <v>76</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
-      </c>
-      <c r="M11" t="n">
-        <v>27</v>
-      </c>
-      <c r="N11" t="n">
-        <v>15</v>
-      </c>
-      <c r="O11" t="n">
-        <v>86</v>
-      </c>
-      <c r="P11" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>25</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.15</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.46</v>
+        <v>2.1</v>
       </c>
       <c r="W11" t="n">
-        <v>2.15</v>
+        <v>3.84</v>
       </c>
       <c r="X11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Y11" t="n">
         <v>1.91</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.85</v>
+        <v>2.54</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>3.22</v>
       </c>
       <c r="AF11" t="n">
-        <v>3.58</v>
+        <v>2.39</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 19:30:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="H12" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="I12" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="J12" t="n">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M12" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="O12" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="P12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Q12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>6.85</v>
+        <v>4.6</v>
       </c>
       <c r="T12" t="n">
-        <v>15</v>
+        <v>5.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="V12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.62</v>
       </c>
-      <c r="W12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 19:30:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="G13" t="n">
-        <v>2.36</v>
+        <v>1.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.39</v>
+        <v>1.92</v>
       </c>
       <c r="I13" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="K13" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="L13" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="M13" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N13" t="n">
         <v>36</v>
@@ -1926,470 +1926,470 @@
         <v>64</v>
       </c>
       <c r="P13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R13" t="n">
-        <v>2.54</v>
+        <v>2.19</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>3.39</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="W13" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="X13" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.52</v>
+        <v>2.03</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 19:45:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K14" t="n">
+        <v>67</v>
+      </c>
+      <c r="L14" t="n">
+        <v>84</v>
+      </c>
+      <c r="M14" t="n">
+        <v>33</v>
+      </c>
+      <c r="N14" t="n">
+        <v>17</v>
+      </c>
+      <c r="O14" t="n">
+        <v>84</v>
+      </c>
+      <c r="P14" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>56</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K14" t="n">
-        <v>50</v>
-      </c>
-      <c r="L14" t="n">
-        <v>64</v>
-      </c>
-      <c r="M14" t="n">
-        <v>36</v>
-      </c>
-      <c r="N14" t="n">
-        <v>29</v>
-      </c>
-      <c r="O14" t="n">
-        <v>72</v>
-      </c>
-      <c r="P14" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>50</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="T14" t="n">
-        <v>23</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.57</v>
-      </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 20:00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.43</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.57</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I15" t="n">
         <v>1.28</v>
       </c>
-      <c r="I15" t="n">
-        <v>1.31</v>
-      </c>
       <c r="J15" t="n">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="K15" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="L15" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="M15" t="n">
+        <v>25</v>
+      </c>
+      <c r="N15" t="n">
+        <v>19</v>
+      </c>
+      <c r="O15" t="n">
+        <v>82</v>
+      </c>
+      <c r="P15" t="n">
         <v>50</v>
       </c>
-      <c r="N15" t="n">
-        <v>22</v>
-      </c>
-      <c r="O15" t="n">
-        <v>79</v>
-      </c>
-      <c r="P15" t="n">
-        <v>64</v>
-      </c>
       <c r="Q15" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.05</v>
+        <v>1.45</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.9</v>
+        <v>4.35</v>
       </c>
       <c r="X15" t="n">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
         <v>1.43</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.04</v>
+        <v>2.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.76</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 20:00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.29</v>
+        <v>1.36</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="H16" t="n">
-        <v>1.88</v>
+        <v>1.32</v>
       </c>
       <c r="I16" t="n">
-        <v>1.53</v>
+        <v>0.88</v>
       </c>
       <c r="J16" t="n">
-        <v>3.41</v>
+        <v>2.2</v>
       </c>
       <c r="K16" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="L16" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="N16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P16" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q16" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="S16" t="n">
-        <v>3.55</v>
+        <v>3.09</v>
       </c>
       <c r="T16" t="n">
-        <v>4.18</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="W16" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE16" t="n">
         <v>3.1</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.77</v>
-      </c>
       <c r="AF16" t="n">
-        <v>3.02</v>
+        <v>2.66</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-19 20:15:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="H17" t="n">
-        <v>0.93</v>
+        <v>1.39</v>
       </c>
       <c r="I17" t="n">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="J17" t="n">
-        <v>2.21</v>
+        <v>3.22</v>
       </c>
       <c r="K17" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="L17" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="M17" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="N17" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="O17" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="P17" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="Q17" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="R17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T17" t="n">
         <v>1.85</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4.48</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V17" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="W17" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="X17" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Z17" t="n">
         <v>2.05</v>
@@ -2398,240 +2398,2747 @@
         <v>1.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-20 11:30:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="I18" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="J18" t="n">
-        <v>3.13</v>
+        <v>2.89</v>
       </c>
       <c r="K18" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="L18" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M18" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O18" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="P18" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q18" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="R18" t="n">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
       <c r="S18" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.53</v>
+        <v>3.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="V18" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="W18" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.26</v>
+        <v>2.63</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>3.28</v>
+        <v>2.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.22</v>
+        <v>2.94</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-18 20:00:00</t>
+          <t>2025-12-20 12:00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Europe UEFA Europa Conference League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.6</v>
+        <v>1.71</v>
       </c>
       <c r="G19" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="H19" t="n">
-        <v>1.07</v>
+        <v>1.93</v>
       </c>
       <c r="I19" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="J19" t="n">
-        <v>2.53</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="L19" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="M19" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O19" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P19" t="n">
         <v>59</v>
       </c>
       <c r="Q19" t="n">
+        <v>41</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-12-20 12:00:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fortuna Düsseldorf</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Greuther Fürth</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K20" t="n">
+        <v>63</v>
+      </c>
+      <c r="L20" t="n">
+        <v>63</v>
+      </c>
+      <c r="M20" t="n">
+        <v>26</v>
+      </c>
+      <c r="N20" t="n">
+        <v>13</v>
+      </c>
+      <c r="O20" t="n">
+        <v>88</v>
+      </c>
+      <c r="P20" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>32</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-12-20 12:00:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="K21" t="n">
+        <v>57</v>
+      </c>
+      <c r="L21" t="n">
+        <v>63</v>
+      </c>
+      <c r="M21" t="n">
+        <v>32</v>
+      </c>
+      <c r="N21" t="n">
+        <v>25</v>
+      </c>
+      <c r="O21" t="n">
+        <v>75</v>
+      </c>
+      <c r="P21" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>51</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-12-20 12:30:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>22</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K22" t="n">
+        <v>75</v>
+      </c>
+      <c r="L22" t="n">
+        <v>65</v>
+      </c>
+      <c r="M22" t="n">
+        <v>30</v>
+      </c>
+      <c r="N22" t="n">
+        <v>15</v>
+      </c>
+      <c r="O22" t="n">
+        <v>85</v>
+      </c>
+      <c r="P22" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>50</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-12-20 12:30:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K23" t="n">
+        <v>73</v>
+      </c>
+      <c r="L23" t="n">
+        <v>78</v>
+      </c>
+      <c r="M23" t="n">
+        <v>32</v>
+      </c>
+      <c r="N23" t="n">
+        <v>18</v>
+      </c>
+      <c r="O23" t="n">
+        <v>82</v>
+      </c>
+      <c r="P23" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>55</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-12-20 12:30:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>22</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>58</v>
+      </c>
+      <c r="L24" t="n">
+        <v>67</v>
+      </c>
+      <c r="M24" t="n">
+        <v>38</v>
+      </c>
+      <c r="N24" t="n">
+        <v>19</v>
+      </c>
+      <c r="O24" t="n">
+        <v>81</v>
+      </c>
+      <c r="P24" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>34</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-12-20 12:30:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>21</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Metaloglobus</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Unirea Slobozia</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K25" t="n">
+        <v>60</v>
+      </c>
+      <c r="L25" t="n">
+        <v>85</v>
+      </c>
+      <c r="M25" t="n">
+        <v>40</v>
+      </c>
+      <c r="N25" t="n">
+        <v>15</v>
+      </c>
+      <c r="O25" t="n">
+        <v>85</v>
+      </c>
+      <c r="P25" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>45</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-12-20 12:30:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>17</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K26" t="n">
+        <v>63</v>
+      </c>
+      <c r="L26" t="n">
+        <v>69</v>
+      </c>
+      <c r="M26" t="n">
+        <v>26</v>
+      </c>
+      <c r="N26" t="n">
+        <v>19</v>
+      </c>
+      <c r="O26" t="n">
+        <v>82</v>
+      </c>
+      <c r="P26" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>32</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-12-20 13:00:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>17</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K27" t="n">
         <v>42</v>
       </c>
-      <c r="R19" t="n">
+      <c r="L27" t="n">
+        <v>54</v>
+      </c>
+      <c r="M27" t="n">
+        <v>15</v>
+      </c>
+      <c r="N27" t="n">
+        <v>32</v>
+      </c>
+      <c r="O27" t="n">
+        <v>68</v>
+      </c>
+      <c r="P27" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>66</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V27" t="n">
         <v>2.25</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="W27" t="n">
+        <v>4</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-12-20 13:00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>19</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FC Andorra</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruña</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="K28" t="n">
+        <v>71</v>
+      </c>
+      <c r="L28" t="n">
+        <v>64</v>
+      </c>
+      <c r="M28" t="n">
+        <v>35</v>
+      </c>
+      <c r="N28" t="n">
+        <v>13</v>
+      </c>
+      <c r="O28" t="n">
+        <v>88</v>
+      </c>
+      <c r="P28" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>36</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Croatia Prva HNL</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>18</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K29" t="n">
+        <v>57</v>
+      </c>
+      <c r="L29" t="n">
+        <v>69</v>
+      </c>
+      <c r="M29" t="n">
+        <v>32</v>
+      </c>
+      <c r="N29" t="n">
+        <v>13</v>
+      </c>
+      <c r="O29" t="n">
+        <v>88</v>
+      </c>
+      <c r="P29" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>57</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>17</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>57</v>
+      </c>
+      <c r="L30" t="n">
+        <v>63</v>
+      </c>
+      <c r="M30" t="n">
+        <v>32</v>
+      </c>
+      <c r="N30" t="n">
+        <v>32</v>
+      </c>
+      <c r="O30" t="n">
+        <v>69</v>
+      </c>
+      <c r="P30" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>57</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>17</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Juve Stabia</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>61</v>
+      </c>
+      <c r="L31" t="n">
+        <v>81</v>
+      </c>
+      <c r="M31" t="n">
+        <v>41</v>
+      </c>
+      <c r="N31" t="n">
+        <v>14</v>
+      </c>
+      <c r="O31" t="n">
+        <v>87</v>
+      </c>
+      <c r="P31" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>34</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>17</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="K32" t="n">
+        <v>57</v>
+      </c>
+      <c r="L32" t="n">
+        <v>63</v>
+      </c>
+      <c r="M32" t="n">
+        <v>19</v>
+      </c>
+      <c r="N32" t="n">
+        <v>19</v>
+      </c>
+      <c r="O32" t="n">
+        <v>82</v>
+      </c>
+      <c r="P32" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>51</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K33" t="n">
+        <v>43</v>
+      </c>
+      <c r="L33" t="n">
+        <v>72</v>
+      </c>
+      <c r="M33" t="n">
+        <v>22</v>
+      </c>
+      <c r="N33" t="n">
+        <v>22</v>
+      </c>
+      <c r="O33" t="n">
+        <v>79</v>
+      </c>
+      <c r="P33" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>50</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Calcio Padova</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K34" t="n">
+        <v>67</v>
+      </c>
+      <c r="L34" t="n">
+        <v>75</v>
+      </c>
+      <c r="M34" t="n">
+        <v>40</v>
+      </c>
+      <c r="N34" t="n">
+        <v>26</v>
+      </c>
+      <c r="O34" t="n">
+        <v>75</v>
+      </c>
+      <c r="P34" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>60</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>15</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>GD Chaves</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Portimonense</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K35" t="n">
+        <v>63</v>
+      </c>
+      <c r="L35" t="n">
+        <v>77</v>
+      </c>
+      <c r="M35" t="n">
+        <v>24</v>
+      </c>
+      <c r="N35" t="n">
+        <v>30</v>
+      </c>
+      <c r="O35" t="n">
+        <v>70</v>
+      </c>
+      <c r="P35" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>59</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W35" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:00:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Turkey Süper Lig</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Eyüpspor</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K36" t="n">
+        <v>57</v>
+      </c>
+      <c r="L36" t="n">
+        <v>51</v>
+      </c>
+      <c r="M36" t="n">
+        <v>32</v>
+      </c>
+      <c r="N36" t="n">
+        <v>25</v>
+      </c>
+      <c r="O36" t="n">
+        <v>75</v>
+      </c>
+      <c r="P36" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>63</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:00:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>15</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Asteras Tripolis</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="K37" t="n">
+        <v>70</v>
+      </c>
+      <c r="L37" t="n">
+        <v>79</v>
+      </c>
+      <c r="M37" t="n">
+        <v>31</v>
+      </c>
+      <c r="N37" t="n">
+        <v>15</v>
+      </c>
+      <c r="O37" t="n">
+        <v>86</v>
+      </c>
+      <c r="P37" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>38</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W37" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:30:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K38" t="n">
+        <v>57</v>
+      </c>
+      <c r="L38" t="n">
+        <v>86</v>
+      </c>
+      <c r="M38" t="n">
+        <v>36</v>
+      </c>
+      <c r="N38" t="n">
+        <v>22</v>
+      </c>
+      <c r="O38" t="n">
+        <v>79</v>
+      </c>
+      <c r="P38" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>36</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:30:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>15</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="K39" t="n">
+        <v>52</v>
+      </c>
+      <c r="L39" t="n">
+        <v>77</v>
+      </c>
+      <c r="M39" t="n">
+        <v>45</v>
+      </c>
+      <c r="N39" t="n">
+        <v>17</v>
+      </c>
+      <c r="O39" t="n">
+        <v>84</v>
+      </c>
+      <c r="P39" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>47</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:30:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>15</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Köln</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K40" t="n">
+        <v>67</v>
+      </c>
+      <c r="L40" t="n">
+        <v>75</v>
+      </c>
+      <c r="M40" t="n">
+        <v>33</v>
+      </c>
+      <c r="N40" t="n">
+        <v>17</v>
+      </c>
+      <c r="O40" t="n">
+        <v>84</v>
+      </c>
+      <c r="P40" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>42</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W40" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:30:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>15</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J41" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V19" t="n">
+      <c r="K41" t="n">
+        <v>72</v>
+      </c>
+      <c r="L41" t="n">
+        <v>93</v>
+      </c>
+      <c r="M41" t="n">
+        <v>50</v>
+      </c>
+      <c r="N41" t="n">
+        <v>7</v>
+      </c>
+      <c r="O41" t="n">
+        <v>93</v>
+      </c>
+      <c r="P41" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>29</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:30:00</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>15</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="K42" t="n">
+        <v>50</v>
+      </c>
+      <c r="L42" t="n">
+        <v>79</v>
+      </c>
+      <c r="M42" t="n">
+        <v>50</v>
+      </c>
+      <c r="N42" t="n">
+        <v>15</v>
+      </c>
+      <c r="O42" t="n">
+        <v>86</v>
+      </c>
+      <c r="P42" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>36</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC42" t="n">
         <v>1.77</v>
       </c>
-      <c r="W19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.48</v>
+      <c r="AD42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -471,10 +471,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="32.4" customWidth="1" min="2" max="2"/>
+    <col width="40.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="22.8" customWidth="1" min="4" max="4"/>
-    <col width="26.4" customWidth="1" min="5" max="5"/>
+    <col width="13.2" customWidth="1" min="4" max="4"/>
+    <col width="14.4" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,328 +675,328 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-23 16:00:00</t>
+          <t>2025-12-25 14:50:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Asia AFC Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.4</v>
+        <v>1.25</v>
       </c>
       <c r="G2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="K2" t="n">
+        <v>65</v>
+      </c>
+      <c r="L2" t="n">
+        <v>55</v>
+      </c>
+      <c r="M2" t="n">
+        <v>33</v>
+      </c>
+      <c r="N2" t="n">
+        <v>23</v>
+      </c>
+      <c r="O2" t="n">
+        <v>78</v>
+      </c>
+      <c r="P2" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>58</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>80</v>
-      </c>
-      <c r="L2" t="n">
-        <v>100</v>
-      </c>
-      <c r="M2" t="n">
-        <v>40</v>
-      </c>
-      <c r="N2" t="n">
-        <v>10</v>
-      </c>
-      <c r="O2" t="n">
-        <v>90</v>
-      </c>
-      <c r="P2" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>50</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.53</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.98</v>
+        <v>3.34</v>
       </c>
       <c r="X2" t="n">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.06</v>
+        <v>1.87</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.85</v>
+        <v>2.66</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-23 18:15:00</t>
+          <t>2025-12-25 17:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Asia AFC Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K3" t="n">
+        <v>78</v>
+      </c>
+      <c r="L3" t="n">
+        <v>78</v>
+      </c>
+      <c r="M3" t="n">
+        <v>55</v>
+      </c>
+      <c r="N3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O3" t="n">
+        <v>78</v>
+      </c>
+      <c r="P3" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>35</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>8</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.2</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="K3" t="n">
-        <v>70</v>
-      </c>
-      <c r="L3" t="n">
-        <v>100</v>
-      </c>
-      <c r="M3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20</v>
-      </c>
-      <c r="O3" t="n">
-        <v>80</v>
-      </c>
-      <c r="P3" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>20</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="X3" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-23 20:45:00</t>
+          <t>2025-12-25 17:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G4" t="n">
-        <v>2.71</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="I4" t="n">
-        <v>2.06</v>
+        <v>1.13</v>
       </c>
       <c r="J4" t="n">
-        <v>3.38</v>
+        <v>2.29</v>
       </c>
       <c r="K4" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="L4" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="N4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P4" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q4" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>2.95</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4</v>
+        <v>2.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="W4" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG4" headerRowCount="1">
-  <autoFilter ref="A1:AG4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG22" headerRowCount="1">
+  <autoFilter ref="A1:AG22"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AG22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="40.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="13.2" customWidth="1" min="4" max="4"/>
-    <col width="14.4" customWidth="1" min="5" max="5"/>
+    <col width="26.4" customWidth="1" min="4" max="4"/>
+    <col width="26.4" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,328 +675,2290 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-25 14:50:00</t>
+          <t>2025-12-26 12:30:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="I2" t="n">
-        <v>1.15</v>
+        <v>0.98</v>
       </c>
       <c r="J2" t="n">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="K2" t="n">
         <v>65</v>
       </c>
       <c r="L2" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="M2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P2" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="Q2" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="R2" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="T2" t="n">
-        <v>4.12</v>
+        <v>4.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="W2" t="n">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="X2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.82</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Z2" t="n">
-        <v>2.28</v>
+        <v>2.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-25 17:30:00</t>
+          <t>2025-12-26 12:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="J3" t="n">
-        <v>2.45</v>
+        <v>3.87</v>
       </c>
       <c r="K3" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="L3" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M3" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="O3" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="P3" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="Q3" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>2.71</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>3.32</v>
       </c>
       <c r="T3" t="n">
-        <v>8</v>
+        <v>2.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X3" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-25 17:30:00</t>
+          <t>2025-12-26 13:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ipswich Town</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K4" t="n">
+        <v>54</v>
+      </c>
+      <c r="L4" t="n">
+        <v>67</v>
+      </c>
+      <c r="M4" t="n">
+        <v>24</v>
+      </c>
+      <c r="N4" t="n">
+        <v>19</v>
+      </c>
+      <c r="O4" t="n">
+        <v>82</v>
+      </c>
+      <c r="P4" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>53</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-12-26 13:05:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Saudi Arabia Professional League</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>11</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Al Riyadh</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Al Ittifaq</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Al Fateh</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="K5" t="n">
+        <v>38</v>
+      </c>
+      <c r="L5" t="n">
+        <v>50</v>
+      </c>
+      <c r="M5" t="n">
+        <v>25</v>
+      </c>
+      <c r="N5" t="n">
+        <v>50</v>
+      </c>
+      <c r="O5" t="n">
+        <v>50</v>
+      </c>
+      <c r="P5" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>63</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-12-26 15:00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Al Taawon</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88</v>
+      </c>
+      <c r="L6" t="n">
+        <v>88</v>
+      </c>
+      <c r="M6" t="n">
+        <v>88</v>
+      </c>
+      <c r="N6" t="n">
+        <v>13</v>
+      </c>
+      <c r="O6" t="n">
+        <v>88</v>
+      </c>
+      <c r="P6" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>13</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-12-26 15:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>23</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Oxford United</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K7" t="n">
+        <v>80</v>
+      </c>
+      <c r="L7" t="n">
+        <v>82</v>
+      </c>
+      <c r="M7" t="n">
+        <v>38</v>
+      </c>
+      <c r="N7" t="n">
+        <v>15</v>
+      </c>
+      <c r="O7" t="n">
+        <v>85</v>
+      </c>
+      <c r="P7" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>29</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-12-26 15:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>23</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Leicester City</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K8" t="n">
+        <v>70</v>
+      </c>
+      <c r="L8" t="n">
+        <v>85</v>
+      </c>
+      <c r="M8" t="n">
+        <v>35</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20</v>
+      </c>
+      <c r="O8" t="n">
+        <v>80</v>
+      </c>
+      <c r="P8" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>55</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-12-26 15:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>23</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="K9" t="n">
+        <v>50</v>
+      </c>
+      <c r="L9" t="n">
+        <v>75</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20</v>
+      </c>
+      <c r="N9" t="n">
+        <v>30</v>
+      </c>
+      <c r="O9" t="n">
+        <v>70</v>
+      </c>
+      <c r="P9" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-12-26 15:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>23</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K10" t="n">
+        <v>58</v>
+      </c>
+      <c r="L10" t="n">
+        <v>48</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19</v>
+      </c>
+      <c r="N10" t="n">
+        <v>24</v>
+      </c>
+      <c r="O10" t="n">
+        <v>77</v>
+      </c>
+      <c r="P10" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>52</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-12-26 15:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>60</v>
+      </c>
+      <c r="M11" t="n">
+        <v>35</v>
+      </c>
+      <c r="N11" t="n">
+        <v>25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>75</v>
+      </c>
+      <c r="P11" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>45</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-12-26 15:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>23</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stoke City</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K12" t="n">
+        <v>60</v>
+      </c>
+      <c r="L12" t="n">
+        <v>90</v>
+      </c>
+      <c r="M12" t="n">
+        <v>30</v>
+      </c>
+      <c r="N12" t="n">
+        <v>30</v>
+      </c>
+      <c r="O12" t="n">
+        <v>70</v>
+      </c>
+      <c r="P12" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>55</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-12-26 15:00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>23</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>West Bromwich Albion</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="K13" t="n">
+        <v>50</v>
+      </c>
+      <c r="L13" t="n">
+        <v>65</v>
+      </c>
+      <c r="M13" t="n">
+        <v>25</v>
+      </c>
+      <c r="N13" t="n">
+        <v>35</v>
+      </c>
+      <c r="O13" t="n">
+        <v>65</v>
+      </c>
+      <c r="P13" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>70</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-12-26 15:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>23</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>82</v>
+      </c>
+      <c r="M14" t="n">
+        <v>27</v>
+      </c>
+      <c r="N14" t="n">
+        <v>41</v>
+      </c>
+      <c r="O14" t="n">
+        <v>60</v>
+      </c>
+      <c r="P14" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>50</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-12-26 15:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sheffield Wednesday</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K15" t="n">
+        <v>58</v>
+      </c>
+      <c r="L15" t="n">
+        <v>86</v>
+      </c>
+      <c r="M15" t="n">
+        <v>43</v>
+      </c>
+      <c r="N15" t="n">
+        <v>10</v>
+      </c>
+      <c r="O15" t="n">
+        <v>91</v>
+      </c>
+      <c r="P15" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>28</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-12-26 15:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="K16" t="n">
+        <v>75</v>
+      </c>
+      <c r="L16" t="n">
+        <v>80</v>
+      </c>
+      <c r="M16" t="n">
+        <v>40</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20</v>
+      </c>
+      <c r="O16" t="n">
+        <v>80</v>
+      </c>
+      <c r="P16" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>50</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-12-26 16:15:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="K17" t="n">
+        <v>53</v>
+      </c>
+      <c r="L17" t="n">
+        <v>71</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18</v>
+      </c>
+      <c r="N17" t="n">
+        <v>12</v>
+      </c>
+      <c r="O17" t="n">
+        <v>89</v>
+      </c>
+      <c r="P17" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>48</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-12-26 17:30:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K18" t="n">
+        <v>80</v>
+      </c>
+      <c r="L18" t="n">
+        <v>100</v>
+      </c>
+      <c r="M18" t="n">
+        <v>60</v>
+      </c>
+      <c r="N18" t="n">
+        <v>10</v>
+      </c>
+      <c r="O18" t="n">
+        <v>90</v>
+      </c>
+      <c r="P18" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>30</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>10</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-12-26 17:30:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>23</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K19" t="n">
+        <v>55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>73</v>
+      </c>
+      <c r="M19" t="n">
+        <v>27</v>
+      </c>
+      <c r="N19" t="n">
+        <v>27</v>
+      </c>
+      <c r="O19" t="n">
+        <v>73</v>
+      </c>
+      <c r="P19" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>50</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-12-26 17:30:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>62</v>
+      </c>
+      <c r="L20" t="n">
+        <v>62</v>
+      </c>
+      <c r="M20" t="n">
+        <v>33</v>
+      </c>
+      <c r="N20" t="n">
+        <v>17</v>
+      </c>
+      <c r="O20" t="n">
+        <v>84</v>
+      </c>
+      <c r="P20" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>56</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-12-26 19:45:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="K21" t="n">
+        <v>53</v>
+      </c>
+      <c r="L21" t="n">
+        <v>70</v>
+      </c>
+      <c r="M21" t="n">
+        <v>32</v>
+      </c>
+      <c r="N21" t="n">
+        <v>47</v>
+      </c>
+      <c r="O21" t="n">
+        <v>53</v>
+      </c>
+      <c r="P21" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>52</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.75</v>
       </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="AD21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-12-26 20:00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>18</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K22" t="n">
+        <v>57</v>
+      </c>
+      <c r="L22" t="n">
+        <v>69</v>
+      </c>
+      <c r="M22" t="n">
+        <v>38</v>
+      </c>
+      <c r="N22" t="n">
+        <v>38</v>
+      </c>
+      <c r="O22" t="n">
+        <v>63</v>
+      </c>
+      <c r="P22" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>50</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.16</v>
       </c>
-      <c r="I4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="V22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AA22" t="n">
         <v>2.29</v>
       </c>
-      <c r="K4" t="n">
-        <v>88</v>
-      </c>
-      <c r="L4" t="n">
-        <v>100</v>
-      </c>
-      <c r="M4" t="n">
-        <v>38</v>
-      </c>
-      <c r="N4" t="n">
-        <v>13</v>
-      </c>
-      <c r="O4" t="n">
-        <v>88</v>
-      </c>
-      <c r="P4" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>38</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
+      <c r="AB22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG22" headerRowCount="1">
-  <autoFilter ref="A1:AG22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG37" headerRowCount="1">
+  <autoFilter ref="A1:AG37"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG22"/>
+  <dimension ref="A1:AG37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="40.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="26.4" customWidth="1" min="4" max="4"/>
-    <col width="26.4" customWidth="1" min="5" max="5"/>
+    <col width="22.8" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,2078 +675,2078 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-26 12:30:00</t>
+          <t>2025-12-27 11:30:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.1</v>
+        <v>0.67</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7</v>
+        <v>0.43</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9</v>
+        <v>1.15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.98</v>
+        <v>1.04</v>
       </c>
       <c r="J2" t="n">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="K2" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="L2" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="P2" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="Q2" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>3.41</v>
+        <v>3.84</v>
       </c>
       <c r="T2" t="n">
         <v>4.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
-        <v>3.52</v>
+        <v>3.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-26 12:30:00</t>
+          <t>2025-12-27 11:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L3" t="n">
+        <v>51</v>
+      </c>
+      <c r="M3" t="n">
+        <v>25</v>
+      </c>
+      <c r="N3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O3" t="n">
+        <v>69</v>
+      </c>
+      <c r="P3" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>57</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.33</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="K3" t="n">
-        <v>64</v>
-      </c>
-      <c r="L3" t="n">
-        <v>80</v>
-      </c>
-      <c r="M3" t="n">
-        <v>37</v>
-      </c>
-      <c r="N3" t="n">
-        <v>36</v>
-      </c>
-      <c r="O3" t="n">
-        <v>64</v>
-      </c>
-      <c r="P3" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>58</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-26 13:00:00</t>
+          <t>2025-12-27 12:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2</v>
+        <v>2.22</v>
       </c>
       <c r="H4" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="I4" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.08</v>
+        <v>3.37</v>
       </c>
       <c r="K4" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="L4" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="M4" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P4" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="R4" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="T4" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="W4" t="n">
-        <v>3.82</v>
+        <v>3.18</v>
       </c>
       <c r="X4" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AD4" t="n">
         <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-26 13:05:00</t>
+          <t>2025-12-27 12:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="I5" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="J5" t="n">
-        <v>3.42</v>
+        <v>2.86</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="L5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="M5" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="N5" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="O5" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="P5" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="Q5" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="R5" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="T5" t="n">
-        <v>1.55</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="W5" t="n">
-        <v>2.17</v>
+        <v>3.16</v>
       </c>
       <c r="X5" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-26 15:00:00</t>
+          <t>2025-12-27 12:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="H6" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="I6" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="J6" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="K6" t="n">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="L6" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="M6" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O6" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="P6" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="S6" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="W6" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="X6" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Y6" t="n">
         <v>2.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-12-26 15:00:00</t>
+          <t>2025-12-27 13:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>1.09</v>
+        <v>0.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="I7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K7" t="n">
+        <v>75</v>
+      </c>
+      <c r="L7" t="n">
+        <v>88</v>
+      </c>
+      <c r="M7" t="n">
+        <v>50</v>
+      </c>
+      <c r="N7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O7" t="n">
+        <v>88</v>
+      </c>
+      <c r="P7" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>38</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.5</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="K7" t="n">
-        <v>80</v>
-      </c>
-      <c r="L7" t="n">
-        <v>82</v>
-      </c>
-      <c r="M7" t="n">
-        <v>38</v>
-      </c>
-      <c r="N7" t="n">
-        <v>15</v>
-      </c>
-      <c r="O7" t="n">
-        <v>85</v>
-      </c>
-      <c r="P7" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>29</v>
-      </c>
-      <c r="R7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.79</v>
-      </c>
       <c r="W7" t="n">
-        <v>2.68</v>
+        <v>2.25</v>
       </c>
       <c r="X7" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-12-26 15:00:00</t>
+          <t>2025-12-27 14:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="H8" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="I8" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="J8" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="K8" t="n">
+        <v>52</v>
+      </c>
+      <c r="L8" t="n">
+        <v>71</v>
+      </c>
+      <c r="M8" t="n">
+        <v>30</v>
+      </c>
+      <c r="N8" t="n">
+        <v>31</v>
+      </c>
+      <c r="O8" t="n">
         <v>70</v>
       </c>
-      <c r="L8" t="n">
-        <v>85</v>
-      </c>
-      <c r="M8" t="n">
-        <v>35</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20</v>
-      </c>
-      <c r="O8" t="n">
-        <v>80</v>
-      </c>
       <c r="P8" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="Q8" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="R8" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.31</v>
+        <v>3.12</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="W8" t="n">
-        <v>3.23</v>
+        <v>4.75</v>
       </c>
       <c r="X8" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.63</v>
+        <v>2.01</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.7</v>
+        <v>2.57</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-12-26 15:00:00</t>
+          <t>2025-12-27 14:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>0.25</v>
       </c>
       <c r="H9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K9" t="n">
+        <v>44</v>
+      </c>
+      <c r="L9" t="n">
+        <v>63</v>
+      </c>
+      <c r="M9" t="n">
+        <v>32</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>94</v>
+      </c>
+      <c r="P9" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>38</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.49</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="K9" t="n">
-        <v>50</v>
-      </c>
-      <c r="L9" t="n">
-        <v>75</v>
-      </c>
-      <c r="M9" t="n">
-        <v>20</v>
-      </c>
-      <c r="N9" t="n">
-        <v>30</v>
-      </c>
-      <c r="O9" t="n">
-        <v>70</v>
-      </c>
-      <c r="P9" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>50</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AC9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-12-26 15:00:00</t>
+          <t>2025-12-27 14:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.91</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="I10" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="J10" t="n">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="K10" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="L10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N10" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="O10" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="P10" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q10" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="R10" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="S10" t="n">
-        <v>3.31</v>
+        <v>3.01</v>
       </c>
       <c r="T10" t="n">
-        <v>3.34</v>
+        <v>3.62</v>
       </c>
       <c r="U10" t="n">
         <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="W10" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="X10" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Y10" t="n">
         <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.82</v>
+        <v>2.37</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AF10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-26 15:00:00</t>
+          <t>2025-12-27 14:00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>1.38</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="H11" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="J11" t="n">
-        <v>3.28</v>
+        <v>2.58</v>
       </c>
       <c r="K11" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M11" t="n">
         <v>35</v>
       </c>
       <c r="N11" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="O11" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="P11" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q11" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R11" t="n">
-        <v>1.51</v>
+        <v>1.93</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>3.33</v>
       </c>
       <c r="T11" t="n">
-        <v>5.8</v>
+        <v>3.96</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="W11" t="n">
-        <v>2.8</v>
+        <v>3.85</v>
       </c>
       <c r="X11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.7</v>
       </c>
-      <c r="Y11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE11" t="n">
         <v>3</v>
       </c>
-      <c r="AA11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AF11" t="n">
-        <v>3.11</v>
+        <v>2.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-26 15:00:00</t>
+          <t>2025-12-27 14:00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="H12" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="I12" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="J12" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="K12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="M12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O12" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="R12" t="n">
-        <v>2.05</v>
+        <v>2.68</v>
       </c>
       <c r="S12" t="n">
-        <v>3.23</v>
+        <v>2.86</v>
       </c>
       <c r="T12" t="n">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="W12" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="X12" t="n">
         <v>1.85</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.58</v>
+        <v>1.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.41</v>
+        <v>1.82</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-26 15:00:00</t>
+          <t>2025-12-27 14:00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="H13" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="L13" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="M13" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="N13" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="O13" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="P13" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Q13" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="R13" t="n">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
       <c r="S13" t="n">
-        <v>3.29</v>
+        <v>3.21</v>
       </c>
       <c r="T13" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="U13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V13" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="W13" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="X13" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.69</v>
+        <v>2.19</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-26 15:00:00</t>
+          <t>2025-12-27 14:00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="G14" t="n">
-        <v>1.27</v>
+        <v>0.75</v>
       </c>
       <c r="H14" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="I14" t="n">
-        <v>1.29</v>
+        <v>0.97</v>
       </c>
       <c r="J14" t="n">
-        <v>2.93</v>
+        <v>2.3</v>
       </c>
       <c r="K14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L14" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="M14" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="N14" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="P14" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="Q14" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="R14" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="S14" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>3.97</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="W14" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="X14" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.04</v>
+        <v>2.07</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.71</v>
+        <v>2.18</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-26 15:00:00</t>
+          <t>2025-12-27 14:00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.18</v>
+        <v>1.13</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="H15" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="J15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K15" t="n">
+        <v>38</v>
+      </c>
+      <c r="L15" t="n">
+        <v>44</v>
+      </c>
+      <c r="M15" t="n">
+        <v>32</v>
+      </c>
+      <c r="N15" t="n">
+        <v>50</v>
+      </c>
+      <c r="O15" t="n">
+        <v>50</v>
+      </c>
+      <c r="P15" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>63</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2.53</v>
       </c>
-      <c r="K15" t="n">
-        <v>58</v>
-      </c>
-      <c r="L15" t="n">
-        <v>86</v>
-      </c>
-      <c r="M15" t="n">
-        <v>43</v>
-      </c>
-      <c r="N15" t="n">
-        <v>10</v>
-      </c>
-      <c r="O15" t="n">
-        <v>91</v>
-      </c>
-      <c r="P15" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>28</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.99</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-26 15:00:00</t>
+          <t>2025-12-27 14:50:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6</v>
+        <v>0.25</v>
       </c>
       <c r="H16" t="n">
-        <v>1.69</v>
+        <v>2.55</v>
       </c>
       <c r="I16" t="n">
-        <v>1.57</v>
+        <v>0.61</v>
       </c>
       <c r="J16" t="n">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="K16" t="n">
+        <v>53</v>
+      </c>
+      <c r="L16" t="n">
+        <v>65</v>
+      </c>
+      <c r="M16" t="n">
+        <v>43</v>
+      </c>
+      <c r="N16" t="n">
+        <v>25</v>
+      </c>
+      <c r="O16" t="n">
         <v>75</v>
       </c>
-      <c r="L16" t="n">
-        <v>80</v>
-      </c>
-      <c r="M16" t="n">
-        <v>40</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20</v>
-      </c>
-      <c r="O16" t="n">
-        <v>80</v>
-      </c>
       <c r="P16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="R16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="T16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF16" t="n">
         <v>4.2</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.94</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-26 16:15:00</t>
+          <t>2025-12-27 15:00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.89</v>
+        <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="H17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K17" t="n">
+        <v>49</v>
+      </c>
+      <c r="L17" t="n">
+        <v>72</v>
+      </c>
+      <c r="M17" t="n">
+        <v>31</v>
+      </c>
+      <c r="N17" t="n">
+        <v>28</v>
+      </c>
+      <c r="O17" t="n">
+        <v>72</v>
+      </c>
+      <c r="P17" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>52</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.79</v>
       </c>
-      <c r="I17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="K17" t="n">
-        <v>53</v>
-      </c>
-      <c r="L17" t="n">
-        <v>71</v>
-      </c>
-      <c r="M17" t="n">
-        <v>18</v>
-      </c>
-      <c r="N17" t="n">
-        <v>12</v>
-      </c>
-      <c r="O17" t="n">
-        <v>89</v>
-      </c>
-      <c r="P17" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>48</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.99</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.09</v>
+        <v>2.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.49</v>
+        <v>1.51</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.34</v>
+        <v>2.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-26 17:30:00</t>
+          <t>2025-12-27 15:00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>1.25</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="H18" t="n">
-        <v>2.19</v>
+        <v>1.02</v>
       </c>
       <c r="I18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="J18" t="n">
-        <v>3.44</v>
+        <v>2.26</v>
       </c>
       <c r="K18" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="L18" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="M18" t="n">
         <v>60</v>
       </c>
       <c r="N18" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O18" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="P18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q18" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R18" t="n">
-        <v>1.17</v>
+        <v>2.83</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>2.99</v>
       </c>
       <c r="T18" t="n">
-        <v>10</v>
+        <v>2.32</v>
       </c>
       <c r="U18" t="n">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.93</v>
       </c>
       <c r="W18" t="n">
-        <v>1.72</v>
+        <v>3.24</v>
       </c>
       <c r="X18" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>4.33</v>
+        <v>2.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-26 17:30:00</t>
+          <t>2025-12-27 15:00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.55</v>
+        <v>0.71</v>
       </c>
       <c r="G19" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="H19" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="I19" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="J19" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="K19" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="L19" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M19" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="N19" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="O19" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="P19" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="Q19" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9</v>
+        <v>7.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.35</v>
+        <v>1.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="V19" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="W19" t="n">
-        <v>3.3</v>
+        <v>2.27</v>
       </c>
       <c r="X19" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.89</v>
+        <v>2.31</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.69</v>
+        <v>3.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-26 17:30:00</t>
+          <t>2025-12-27 15:00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G20" t="n">
         <v>1.33</v>
       </c>
-      <c r="G20" t="n">
-        <v>1.56</v>
-      </c>
       <c r="H20" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="I20" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="J20" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="K20" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L20" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M20" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="N20" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="O20" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="P20" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q20" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="R20" t="n">
-        <v>2.72</v>
+        <v>1.61</v>
       </c>
       <c r="S20" t="n">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.32</v>
+        <v>4.33</v>
       </c>
       <c r="U20" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V20" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="X20" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-26 19:45:00</t>
+          <t>2025-12-27 15:00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2759,103 +2759,103 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="G21" t="n">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="H21" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="I21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>33</v>
+      </c>
+      <c r="L21" t="n">
+        <v>56</v>
+      </c>
+      <c r="M21" t="n">
+        <v>22</v>
+      </c>
+      <c r="N21" t="n">
+        <v>45</v>
+      </c>
+      <c r="O21" t="n">
+        <v>56</v>
+      </c>
+      <c r="P21" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>67</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.28</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="K21" t="n">
-        <v>53</v>
-      </c>
-      <c r="L21" t="n">
-        <v>70</v>
-      </c>
-      <c r="M21" t="n">
-        <v>32</v>
-      </c>
-      <c r="N21" t="n">
-        <v>47</v>
-      </c>
-      <c r="O21" t="n">
-        <v>53</v>
-      </c>
-      <c r="P21" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>52</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-12-26 20:00:00</t>
+          <t>2025-12-27 15:00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2868,31 +2868,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.75</v>
+        <v>0.88</v>
       </c>
       <c r="G22" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="H22" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="I22" t="n">
-        <v>1.28</v>
+        <v>0.97</v>
       </c>
       <c r="J22" t="n">
-        <v>3.36</v>
+        <v>1.98</v>
       </c>
       <c r="K22" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="L22" t="n">
         <v>69</v>
@@ -2901,64 +2901,1699 @@
         <v>38</v>
       </c>
       <c r="N22" t="n">
+        <v>32</v>
+      </c>
+      <c r="O22" t="n">
+        <v>69</v>
+      </c>
+      <c r="P22" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>82</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-12-27 15:00:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>18</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K23" t="n">
         <v>38</v>
       </c>
-      <c r="O22" t="n">
+      <c r="L23" t="n">
         <v>63</v>
       </c>
-      <c r="P22" t="n">
+      <c r="M23" t="n">
+        <v>7</v>
+      </c>
+      <c r="N23" t="n">
+        <v>26</v>
+      </c>
+      <c r="O23" t="n">
+        <v>76</v>
+      </c>
+      <c r="P23" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>57</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="T23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-12-27 15:00:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>18</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K24" t="n">
+        <v>69</v>
+      </c>
+      <c r="L24" t="n">
+        <v>75</v>
+      </c>
+      <c r="M24" t="n">
+        <v>44</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>100</v>
+      </c>
+      <c r="P24" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>32</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-12-27 15:00:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>18</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K25" t="n">
+        <v>44</v>
+      </c>
+      <c r="L25" t="n">
+        <v>88</v>
+      </c>
+      <c r="M25" t="n">
+        <v>19</v>
+      </c>
+      <c r="N25" t="n">
+        <v>13</v>
+      </c>
+      <c r="O25" t="n">
+        <v>88</v>
+      </c>
+      <c r="P25" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>57</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-12-27 15:00:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>18</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K26" t="n">
+        <v>75</v>
+      </c>
+      <c r="L26" t="n">
+        <v>88</v>
+      </c>
+      <c r="M26" t="n">
         <v>50</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="N26" t="n">
+        <v>19</v>
+      </c>
+      <c r="O26" t="n">
+        <v>82</v>
+      </c>
+      <c r="P26" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>26</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-12-27 16:15:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>18</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Calcio Padova</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K27" t="n">
+        <v>33</v>
+      </c>
+      <c r="L27" t="n">
+        <v>56</v>
+      </c>
+      <c r="M27" t="n">
+        <v>11</v>
+      </c>
+      <c r="N27" t="n">
+        <v>45</v>
+      </c>
+      <c r="O27" t="n">
+        <v>56</v>
+      </c>
+      <c r="P27" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>62</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-12-27 17:00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>17</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K28" t="n">
+        <v>25</v>
+      </c>
+      <c r="L28" t="n">
+        <v>44</v>
+      </c>
+      <c r="M28" t="n">
+        <v>13</v>
+      </c>
+      <c r="N28" t="n">
+        <v>44</v>
+      </c>
+      <c r="O28" t="n">
+        <v>57</v>
+      </c>
+      <c r="P28" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>69</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-12-27 17:15:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FCV Dender EH</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>73</v>
+      </c>
+      <c r="L29" t="n">
+        <v>67</v>
+      </c>
+      <c r="M29" t="n">
+        <v>17</v>
+      </c>
+      <c r="N29" t="n">
+        <v>17</v>
+      </c>
+      <c r="O29" t="n">
+        <v>84</v>
+      </c>
+      <c r="P29" t="n">
         <v>50</v>
       </c>
-      <c r="R22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W22" t="n">
+      <c r="Q29" t="n">
+        <v>50</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-12-27 17:30:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>11</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Al Shabab</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K30" t="n">
+        <v>45</v>
+      </c>
+      <c r="L30" t="n">
+        <v>78</v>
+      </c>
+      <c r="M30" t="n">
+        <v>43</v>
+      </c>
+      <c r="N30" t="n">
+        <v>35</v>
+      </c>
+      <c r="O30" t="n">
+        <v>65</v>
+      </c>
+      <c r="P30" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>80</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T30" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-12-27 17:30:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>18</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>57</v>
+      </c>
+      <c r="L31" t="n">
+        <v>69</v>
+      </c>
+      <c r="M31" t="n">
+        <v>32</v>
+      </c>
+      <c r="N31" t="n">
+        <v>19</v>
+      </c>
+      <c r="O31" t="n">
+        <v>82</v>
+      </c>
+      <c r="P31" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>50</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-12-27 17:45:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>19</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K32" t="n">
+        <v>54</v>
+      </c>
+      <c r="L32" t="n">
+        <v>78</v>
+      </c>
+      <c r="M32" t="n">
+        <v>18</v>
+      </c>
+      <c r="N32" t="n">
+        <v>17</v>
+      </c>
+      <c r="O32" t="n">
+        <v>84</v>
+      </c>
+      <c r="P32" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>60</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-12-27 18:00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K33" t="n">
+        <v>34</v>
+      </c>
+      <c r="L33" t="n">
+        <v>73</v>
+      </c>
+      <c r="M33" t="n">
+        <v>47</v>
+      </c>
+      <c r="N33" t="n">
+        <v>34</v>
+      </c>
+      <c r="O33" t="n">
+        <v>67</v>
+      </c>
+      <c r="P33" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>54</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-12-27 18:30:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>18</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Bari 1908</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Avellino</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="K34" t="n">
+        <v>60</v>
+      </c>
+      <c r="L34" t="n">
+        <v>71</v>
+      </c>
+      <c r="M34" t="n">
+        <v>53</v>
+      </c>
+      <c r="N34" t="n">
+        <v>24</v>
+      </c>
+      <c r="O34" t="n">
+        <v>77</v>
+      </c>
+      <c r="P34" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>65</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W34" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-12-27 19:45:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>20</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="K35" t="n">
+        <v>56</v>
+      </c>
+      <c r="L35" t="n">
+        <v>78</v>
+      </c>
+      <c r="M35" t="n">
+        <v>28</v>
+      </c>
+      <c r="N35" t="n">
+        <v>11</v>
+      </c>
+      <c r="O35" t="n">
+        <v>89</v>
+      </c>
+      <c r="P35" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>44</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Y35" t="n">
         <v>2.5</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="Z35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-12-27 19:45:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K36" t="n">
+        <v>25</v>
+      </c>
+      <c r="L36" t="n">
+        <v>50</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7</v>
+      </c>
+      <c r="N36" t="n">
+        <v>63</v>
+      </c>
+      <c r="O36" t="n">
+        <v>38</v>
+      </c>
+      <c r="P36" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>88</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W36" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-12-27 20:30:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>GD Estoril Praia</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J37" t="n">
         <v>2.29</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="K37" t="n">
+        <v>60</v>
+      </c>
+      <c r="L37" t="n">
+        <v>73</v>
+      </c>
+      <c r="M37" t="n">
+        <v>48</v>
+      </c>
+      <c r="N37" t="n">
+        <v>26</v>
+      </c>
+      <c r="O37" t="n">
+        <v>75</v>
+      </c>
+      <c r="P37" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>53</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U37" t="n">
         <v>1.32</v>
       </c>
-      <c r="AC22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE22" t="n">
+      <c r="V37" t="n">
+        <v>2</v>
+      </c>
+      <c r="W37" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z37" t="n">
         <v>2.25</v>
       </c>
-      <c r="AF22" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.55</v>
+      <c r="AA37" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG11" headerRowCount="1">
-  <autoFilter ref="A1:AG11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG18" headerRowCount="1">
+  <autoFilter ref="A1:AG18"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AG18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="28.8" customWidth="1" min="2" max="2"/>
+    <col width="40.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="22.8" customWidth="1" min="4" max="4"/>
-    <col width="22.8" customWidth="1" min="5" max="5"/>
+    <col width="26.4" customWidth="1" min="4" max="4"/>
+    <col width="25.2" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,861 +675,861 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-28 14:00:00</t>
+          <t>2025-12-29 14:35:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="H2" t="n">
         <v>1.46</v>
       </c>
       <c r="I2" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98</v>
+        <v>2.77</v>
       </c>
       <c r="K2" t="n">
+        <v>65</v>
+      </c>
+      <c r="L2" t="n">
         <v>68</v>
       </c>
-      <c r="L2" t="n">
-        <v>75</v>
-      </c>
       <c r="M2" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="O2" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="P2" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="Q2" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="R2" t="n">
-        <v>4.05</v>
+        <v>2.15</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>2.81</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="V2" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>4</v>
+        <v>2.11</v>
       </c>
       <c r="X2" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.23</v>
+        <v>2.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.66</v>
+        <v>3.42</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-28 14:00:00</t>
+          <t>2025-12-29 17:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="I3" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="J3" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="K3" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="L3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O3" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="P3" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="Q3" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="R3" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>4.3</v>
+        <v>3.34</v>
       </c>
       <c r="X3" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.57</v>
+        <v>1.91</v>
       </c>
       <c r="AD3" t="n">
         <v>1.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-28 14:00:00</t>
+          <t>2025-12-29 17:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K4" t="n">
+        <v>72</v>
+      </c>
+      <c r="L4" t="n">
+        <v>64</v>
+      </c>
+      <c r="M4" t="n">
+        <v>35</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>92</v>
+      </c>
+      <c r="P4" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>29</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.29</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="K4" t="n">
-        <v>48</v>
-      </c>
-      <c r="L4" t="n">
-        <v>60</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20</v>
-      </c>
-      <c r="N4" t="n">
-        <v>32</v>
-      </c>
-      <c r="O4" t="n">
-        <v>68</v>
-      </c>
-      <c r="P4" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>66</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6</v>
-      </c>
       <c r="S4" t="n">
-        <v>3.95</v>
+        <v>4.65</v>
       </c>
       <c r="T4" t="n">
-        <v>1.57</v>
+        <v>6.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="W4" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="X4" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.16</v>
+        <v>2.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
         <v>2.12</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.68</v>
+        <v>3.08</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-28 15:30:00</t>
+          <t>2025-12-29 18:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="H5" t="n">
-        <v>1.27</v>
+        <v>2.06</v>
       </c>
       <c r="I5" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="J5" t="n">
-        <v>2.66</v>
+        <v>3.57</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="L5" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O5" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P5" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="Q5" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="R5" t="n">
-        <v>3.95</v>
+        <v>2.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="T5" t="n">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="V5" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="W5" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.78</v>
+        <v>2.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.12</v>
+        <v>2.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.69</v>
+        <v>2.16</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.08</v>
+        <v>1.61</v>
       </c>
       <c r="AD5" t="n">
         <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-28 15:30:00</t>
+          <t>2025-12-29 19:45:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.43</v>
+        <v>1.82</v>
       </c>
       <c r="G6" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.45</v>
       </c>
       <c r="I6" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="J6" t="n">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M6" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="N6" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="O6" t="n">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="Q6" t="n">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="T6" t="n">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="W6" t="n">
-        <v>4.55</v>
+        <v>3.38</v>
       </c>
       <c r="X6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y6" t="n">
         <v>2</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.73</v>
-      </c>
       <c r="Z6" t="n">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-12-28 16:30:00</t>
+          <t>2025-12-29 19:45:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="G7" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="H7" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="I7" t="n">
-        <v>1.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="K7" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="L7" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M7" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="N7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O7" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P7" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S7" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="W7" t="n">
-        <v>3.26</v>
+        <v>3.95</v>
       </c>
       <c r="X7" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.8</v>
+        <v>3.21</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.05</v>
+        <v>2.59</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-12-28 17:00:00</t>
+          <t>2025-12-29 19:45:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="G8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="H8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K8" t="n">
+        <v>73</v>
+      </c>
+      <c r="L8" t="n">
+        <v>73</v>
+      </c>
+      <c r="M8" t="n">
+        <v>41</v>
+      </c>
+      <c r="N8" t="n">
+        <v>23</v>
+      </c>
+      <c r="O8" t="n">
+        <v>78</v>
+      </c>
+      <c r="P8" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>32</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.72</v>
       </c>
-      <c r="I8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K8" t="n">
-        <v>40</v>
-      </c>
-      <c r="L8" t="n">
-        <v>46</v>
-      </c>
-      <c r="M8" t="n">
-        <v>27</v>
-      </c>
-      <c r="N8" t="n">
-        <v>34</v>
-      </c>
-      <c r="O8" t="n">
-        <v>66</v>
-      </c>
-      <c r="P8" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>48</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.3</v>
       </c>
-      <c r="V8" t="n">
-        <v>2</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AC8" t="n">
-        <v>2.39</v>
+        <v>1.57</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-12-28 18:00:00</t>
+          <t>2025-12-29 19:45:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>2.71</v>
+        <v>1.64</v>
       </c>
       <c r="H9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I9" t="n">
         <v>1.47</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.7</v>
-      </c>
       <c r="J9" t="n">
-        <v>3.17</v>
+        <v>3.04</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L9" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M9" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="N9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O9" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P9" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="R9" t="n">
-        <v>3.25</v>
+        <v>2.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="T9" t="n">
-        <v>2.25</v>
+        <v>3.07</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="W9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="X9" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.39</v>
+        <v>1.72</v>
       </c>
       <c r="AD9" t="n">
         <v>1.4</v>
@@ -1538,116 +1538,116 @@
         <v>2.95</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-12-28 19:45:00</t>
+          <t>2025-12-29 19:45:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K10" t="n">
+        <v>69</v>
+      </c>
+      <c r="L10" t="n">
+        <v>64</v>
+      </c>
+      <c r="M10" t="n">
+        <v>32</v>
+      </c>
+      <c r="N10" t="n">
+        <v>27</v>
+      </c>
+      <c r="O10" t="n">
+        <v>73</v>
+      </c>
+      <c r="P10" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>45</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC10" t="n">
         <v>1.63</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="K10" t="n">
-        <v>60</v>
-      </c>
-      <c r="L10" t="n">
-        <v>87</v>
-      </c>
-      <c r="M10" t="n">
-        <v>34</v>
-      </c>
-      <c r="N10" t="n">
-        <v>14</v>
-      </c>
-      <c r="O10" t="n">
-        <v>87</v>
-      </c>
-      <c r="P10" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>53</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AG10" t="n">
         <v>1.48</v>
@@ -1656,110 +1656,873 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-28 20:30:00</t>
+          <t>2025-12-29 19:45:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Oxford United</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>73</v>
+      </c>
+      <c r="M11" t="n">
+        <v>36</v>
+      </c>
+      <c r="N11" t="n">
+        <v>32</v>
+      </c>
+      <c r="O11" t="n">
+        <v>69</v>
+      </c>
+      <c r="P11" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>46</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-12-29 19:45:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K12" t="n">
+        <v>46</v>
+      </c>
+      <c r="L12" t="n">
+        <v>63</v>
+      </c>
+      <c r="M12" t="n">
+        <v>13</v>
+      </c>
+      <c r="N12" t="n">
+        <v>38</v>
+      </c>
+      <c r="O12" t="n">
+        <v>63</v>
+      </c>
+      <c r="P12" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>63</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-12-29 19:45:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sheffield Wednesday</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K13" t="n">
+        <v>35</v>
+      </c>
+      <c r="L13" t="n">
+        <v>83</v>
+      </c>
+      <c r="M13" t="n">
+        <v>26</v>
+      </c>
+      <c r="N13" t="n">
+        <v>22</v>
+      </c>
+      <c r="O13" t="n">
+        <v>78</v>
+      </c>
+      <c r="P13" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>49</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-12-29 19:45:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>West Bromwich Albion</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K14" t="n">
+        <v>66</v>
+      </c>
+      <c r="L14" t="n">
+        <v>74</v>
+      </c>
+      <c r="M14" t="n">
+        <v>30</v>
+      </c>
+      <c r="N14" t="n">
+        <v>30</v>
+      </c>
+      <c r="O14" t="n">
+        <v>70</v>
+      </c>
+      <c r="P14" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>57</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-12-29 19:45:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K15" t="n">
+        <v>70</v>
+      </c>
+      <c r="L15" t="n">
+        <v>87</v>
+      </c>
+      <c r="M15" t="n">
+        <v>39</v>
+      </c>
+      <c r="N15" t="n">
+        <v>22</v>
+      </c>
+      <c r="O15" t="n">
+        <v>78</v>
+      </c>
+      <c r="P15" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>57</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-12-29 19:45:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>17</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K16" t="n">
+        <v>57</v>
+      </c>
+      <c r="L16" t="n">
+        <v>68</v>
+      </c>
+      <c r="M16" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>32</v>
+      </c>
+      <c r="O16" t="n">
+        <v>69</v>
+      </c>
+      <c r="P16" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>51</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-12-29 20:15:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Birmingham City</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="K17" t="n">
+        <v>82</v>
+      </c>
+      <c r="L17" t="n">
+        <v>79</v>
+      </c>
+      <c r="M17" t="n">
+        <v>44</v>
+      </c>
+      <c r="N17" t="n">
+        <v>9</v>
+      </c>
+      <c r="O17" t="n">
+        <v>91</v>
+      </c>
+      <c r="P17" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>31</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-12-29 20:15:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Portugal Liga NOS</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C18" t="n">
         <v>16</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Sporting CP</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Rio Ave FC</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
-        <v>60</v>
-      </c>
-      <c r="M11" t="n">
-        <v>28</v>
-      </c>
-      <c r="N11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>94</v>
-      </c>
-      <c r="P11" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>34</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S11" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>19</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AVS</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K18" t="n">
+        <v>36</v>
+      </c>
+      <c r="L18" t="n">
+        <v>86</v>
+      </c>
+      <c r="M18" t="n">
+        <v>50</v>
+      </c>
+      <c r="N18" t="n">
+        <v>22</v>
+      </c>
+      <c r="O18" t="n">
+        <v>79</v>
+      </c>
+      <c r="P18" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>29</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.08</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="n">
+        <v>23</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X18" t="n">
         <v>2.55</v>
       </c>
-      <c r="AA11" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y18" t="n">
         <v>1.45</v>
       </c>
-      <c r="AC11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.73</v>
+      <c r="Z18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.69</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG18" headerRowCount="1">
-  <autoFilter ref="A1:AG18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG16" headerRowCount="1">
+  <autoFilter ref="A1:AG16"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG18"/>
+  <dimension ref="A1:AG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="40.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="26.4" customWidth="1" min="4" max="4"/>
-    <col width="25.2" customWidth="1" min="5" max="5"/>
+    <col width="22.8" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,7 +675,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-29 14:35:00</t>
+          <t>2025-12-30 15:30:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -688,103 +688,103 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="J2" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="K2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L2" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="P2" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="R2" t="n">
-        <v>2.15</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="T2" t="n">
-        <v>2.81</v>
+        <v>6.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-29 17:30:00</t>
+          <t>2025-12-30 17:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -797,103 +797,103 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>1.12</v>
+        <v>0.91</v>
       </c>
       <c r="J3" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="K3" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="S3" t="n">
-        <v>3.12</v>
+        <v>3.26</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="W3" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="X3" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-29 17:30:00</t>
+          <t>2025-12-30 17:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -906,152 +906,152 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.17</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.14</v>
+        <v>0.86</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>2.26</v>
       </c>
       <c r="J4" t="n">
-        <v>2.24</v>
+        <v>3.12</v>
       </c>
       <c r="K4" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="L4" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="M4" t="n">
+        <v>43</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" t="n">
+        <v>90</v>
+      </c>
+      <c r="P4" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q4" t="n">
         <v>35</v>
       </c>
-      <c r="N4" t="n">
+      <c r="R4" t="n">
         <v>9</v>
       </c>
-      <c r="O4" t="n">
-        <v>92</v>
-      </c>
-      <c r="P4" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>29</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S4" t="n">
-        <v>4.65</v>
+        <v>5.5</v>
       </c>
       <c r="T4" t="n">
-        <v>6.8</v>
+        <v>1.27</v>
       </c>
       <c r="U4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>2.95</v>
+        <v>1.86</v>
       </c>
       <c r="X4" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-29 18:00:00</t>
+          <t>2025-12-30 19:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.64</v>
+        <v>1.11</v>
       </c>
       <c r="G5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="H5" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="I5" t="n">
-        <v>1.51</v>
+        <v>1.05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.57</v>
+        <v>2.67</v>
       </c>
       <c r="K5" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="L5" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="O5" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P5" t="n">
         <v>50</v>
@@ -1060,864 +1060,864 @@
         <v>50</v>
       </c>
       <c r="R5" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="V5" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>3.84</v>
       </c>
       <c r="X5" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-29 19:45:00</t>
+          <t>2025-12-30 19:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.82</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="H6" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="I6" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="J6" t="n">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="K6" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="L6" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="M6" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N6" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="P6" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Q6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="R6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE6" t="n">
         <v>2.6</v>
       </c>
-      <c r="S6" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W6" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.94</v>
-      </c>
       <c r="AF6" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-12-29 19:45:00</t>
+          <t>2025-12-30 19:30:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.45</v>
+        <v>0.89</v>
       </c>
       <c r="G7" t="n">
-        <v>1.64</v>
+        <v>0.67</v>
       </c>
       <c r="H7" t="n">
-        <v>1.46</v>
+        <v>1.05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.35</v>
       </c>
       <c r="J7" t="n">
         <v>2.4</v>
       </c>
       <c r="K7" t="n">
+        <v>33</v>
+      </c>
+      <c r="L7" t="n">
+        <v>62</v>
+      </c>
+      <c r="M7" t="n">
+        <v>28</v>
+      </c>
+      <c r="N7" t="n">
+        <v>45</v>
+      </c>
+      <c r="O7" t="n">
+        <v>56</v>
+      </c>
+      <c r="P7" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q7" t="n">
         <v>73</v>
       </c>
-      <c r="L7" t="n">
-        <v>82</v>
-      </c>
-      <c r="M7" t="n">
-        <v>23</v>
-      </c>
-      <c r="N7" t="n">
-        <v>14</v>
-      </c>
-      <c r="O7" t="n">
-        <v>87</v>
-      </c>
-      <c r="P7" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>46</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>1.68</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2.17</v>
       </c>
-      <c r="W7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AB7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE7" t="n">
-        <v>3.21</v>
+        <v>2.67</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.59</v>
+        <v>3.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-12-29 19:45:00</t>
+          <t>2025-12-30 19:30:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.18</v>
+        <v>1.56</v>
       </c>
       <c r="G8" t="n">
-        <v>1.36</v>
+        <v>0.67</v>
       </c>
       <c r="H8" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="I8" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="J8" t="n">
-        <v>2.82</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
+        <v>67</v>
+      </c>
+      <c r="L8" t="n">
+        <v>84</v>
+      </c>
+      <c r="M8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11</v>
+      </c>
+      <c r="O8" t="n">
+        <v>89</v>
+      </c>
+      <c r="P8" t="n">
         <v>73</v>
       </c>
-      <c r="L8" t="n">
-        <v>73</v>
-      </c>
-      <c r="M8" t="n">
-        <v>41</v>
-      </c>
-      <c r="N8" t="n">
-        <v>23</v>
-      </c>
-      <c r="O8" t="n">
-        <v>78</v>
-      </c>
-      <c r="P8" t="n">
-        <v>69</v>
-      </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="V8" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Z8" t="n">
         <v>2.95</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.02</v>
-      </c>
       <c r="AA8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE8" t="n">
         <v>2.24</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AF8" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-12-29 19:45:00</t>
+          <t>2025-12-30 19:45:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="G9" t="n">
-        <v>1.64</v>
+        <v>0.78</v>
       </c>
       <c r="H9" t="n">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="J9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="K9" t="n">
+        <v>62</v>
+      </c>
+      <c r="L9" t="n">
+        <v>89</v>
+      </c>
+      <c r="M9" t="n">
+        <v>50</v>
+      </c>
+      <c r="N9" t="n">
+        <v>11</v>
+      </c>
+      <c r="O9" t="n">
+        <v>89</v>
+      </c>
+      <c r="P9" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>39</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE9" t="n">
         <v>3.04</v>
       </c>
-      <c r="K9" t="n">
-        <v>35</v>
-      </c>
-      <c r="L9" t="n">
-        <v>66</v>
-      </c>
-      <c r="M9" t="n">
-        <v>35</v>
-      </c>
-      <c r="N9" t="n">
-        <v>35</v>
-      </c>
-      <c r="O9" t="n">
-        <v>66</v>
-      </c>
-      <c r="P9" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>61</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AF9" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-12-29 19:45:00</t>
+          <t>2025-12-30 19:45:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.91</v>
+        <v>1.67</v>
       </c>
       <c r="G10" t="n">
-        <v>0.91</v>
+        <v>1.5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="I10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>41</v>
+      </c>
+      <c r="L10" t="n">
+        <v>76</v>
+      </c>
+      <c r="M10" t="n">
+        <v>35</v>
+      </c>
+      <c r="N10" t="n">
+        <v>25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>76</v>
+      </c>
+      <c r="P10" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>54</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.23</v>
       </c>
-      <c r="J10" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="K10" t="n">
-        <v>69</v>
-      </c>
-      <c r="L10" t="n">
-        <v>64</v>
-      </c>
-      <c r="M10" t="n">
-        <v>32</v>
-      </c>
-      <c r="N10" t="n">
-        <v>27</v>
-      </c>
-      <c r="O10" t="n">
-        <v>73</v>
-      </c>
-      <c r="P10" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>45</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AC10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-29 19:45:00</t>
+          <t>2025-12-30 19:45:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.18</v>
+        <v>0.63</v>
       </c>
       <c r="G11" t="n">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="I11" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="J11" t="n">
-        <v>2.83</v>
+        <v>2.52</v>
       </c>
       <c r="K11" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="L11" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="M11" t="n">
         <v>36</v>
       </c>
       <c r="N11" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="P11" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="Q11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="R11" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="S11" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="U11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.38</v>
       </c>
-      <c r="V11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE11" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-29 19:45:00</t>
+          <t>2025-12-30 19:45:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="G12" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="H12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>58</v>
+      </c>
+      <c r="L12" t="n">
+        <v>50</v>
+      </c>
+      <c r="M12" t="n">
+        <v>33</v>
+      </c>
+      <c r="N12" t="n">
+        <v>29</v>
+      </c>
+      <c r="O12" t="n">
+        <v>71</v>
+      </c>
+      <c r="P12" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>55</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.61</v>
       </c>
-      <c r="I12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K12" t="n">
-        <v>46</v>
-      </c>
-      <c r="L12" t="n">
-        <v>63</v>
-      </c>
-      <c r="M12" t="n">
-        <v>13</v>
-      </c>
-      <c r="N12" t="n">
-        <v>38</v>
-      </c>
-      <c r="O12" t="n">
-        <v>63</v>
-      </c>
-      <c r="P12" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>63</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W12" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.35</v>
+        <v>2.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-29 19:45:00</t>
+          <t>2025-12-30 20:00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="H13" t="n">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="J13" t="n">
-        <v>2.59</v>
+        <v>3.13</v>
       </c>
       <c r="K13" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L13" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="N13" t="n">
         <v>22</v>
@@ -1926,603 +1926,385 @@
         <v>78</v>
       </c>
       <c r="P13" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="Q13" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="R13" t="n">
-        <v>3.61</v>
+        <v>3.87</v>
       </c>
       <c r="S13" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF13" t="n">
         <v>3.28</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.81</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-29 19:45:00</t>
+          <t>2025-12-30 20:15:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="G14" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="H14" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="I14" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.02</v>
+        <v>2.84</v>
       </c>
       <c r="K14" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="L14" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="M14" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="N14" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="O14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="P14" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="Q14" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="R14" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="S14" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
         <v>1.95</v>
       </c>
       <c r="W14" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="X14" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="Y14" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.34</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29 19:45:00</t>
+          <t>2025-12-30 20:15:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.67</v>
+        <v>2.78</v>
       </c>
       <c r="G15" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="H15" t="n">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="I15" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="J15" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="L15" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M15" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="N15" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="O15" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="P15" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="Q15" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="R15" t="n">
-        <v>2.21</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>3.16</v>
+        <v>4.5</v>
       </c>
       <c r="T15" t="n">
-        <v>3.32</v>
+        <v>6.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="W15" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="X15" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29 19:45:00</t>
+          <t>2025-12-30 20:15:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>45</v>
+      </c>
+      <c r="L16" t="n">
+        <v>73</v>
+      </c>
+      <c r="M16" t="n">
+        <v>28</v>
+      </c>
+      <c r="N16" t="n">
+        <v>33</v>
+      </c>
+      <c r="O16" t="n">
+        <v>67</v>
+      </c>
+      <c r="P16" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>56</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.88</v>
       </c>
-      <c r="G16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K16" t="n">
-        <v>57</v>
-      </c>
-      <c r="L16" t="n">
-        <v>68</v>
-      </c>
-      <c r="M16" t="n">
-        <v>7</v>
-      </c>
-      <c r="N16" t="n">
-        <v>32</v>
-      </c>
-      <c r="O16" t="n">
-        <v>69</v>
-      </c>
-      <c r="P16" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>51</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="W16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.62</v>
-      </c>
       <c r="Z16" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.2</v>
+        <v>2.39</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.5</v>
+        <v>3.38</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2025-12-29 20:15:00</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>England Championship</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>24</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Birmingham City</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Southampton</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="K17" t="n">
-        <v>82</v>
-      </c>
-      <c r="L17" t="n">
-        <v>79</v>
-      </c>
-      <c r="M17" t="n">
-        <v>44</v>
-      </c>
-      <c r="N17" t="n">
-        <v>9</v>
-      </c>
-      <c r="O17" t="n">
-        <v>91</v>
-      </c>
-      <c r="P17" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>31</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025-12-29 20:15:00</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Portugal Liga NOS</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>16</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AVS</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="K18" t="n">
-        <v>36</v>
-      </c>
-      <c r="L18" t="n">
-        <v>86</v>
-      </c>
-      <c r="M18" t="n">
-        <v>50</v>
-      </c>
-      <c r="N18" t="n">
-        <v>22</v>
-      </c>
-      <c r="O18" t="n">
-        <v>79</v>
-      </c>
-      <c r="P18" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>29</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="n">
-        <v>23</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG4" headerRowCount="1">
-  <autoFilter ref="A1:AG4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG17" headerRowCount="1">
+  <autoFilter ref="A1:AG17"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AG17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="40.8" customWidth="1" min="2" max="2"/>
+    <col width="28.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="14.4" customWidth="1" min="4" max="4"/>
-    <col width="16.8" customWidth="1" min="5" max="5"/>
+    <col width="25.2" customWidth="1" min="4" max="4"/>
+    <col width="26.4" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,328 +675,1745 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-31 15:25:00</t>
+          <t>2026-01-01 12:30:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.4</v>
+        <v>0.82</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="I2" t="n">
-        <v>1.71</v>
+        <v>0.86</v>
       </c>
       <c r="J2" t="n">
-        <v>3.06</v>
+        <v>2.27</v>
       </c>
       <c r="K2" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="L2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M2" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="N2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P2" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="R2" t="n">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="S2" t="n">
-        <v>3.85</v>
+        <v>3.32</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>3.53</v>
       </c>
       <c r="U2" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="W2" t="n">
-        <v>2.22</v>
+        <v>3.3</v>
       </c>
       <c r="X2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.41</v>
       </c>
-      <c r="Y2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE2" t="n">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.7</v>
+        <v>2.69</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-31 17:30:00</t>
+          <t>2026-01-01 15:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.88</v>
+        <v>0.93</v>
       </c>
       <c r="J3" t="n">
-        <v>3.24</v>
+        <v>2.43</v>
       </c>
       <c r="K3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="M3" t="n">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="P3" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="R3" t="n">
-        <v>10.6</v>
+        <v>1.68</v>
       </c>
       <c r="S3" t="n">
-        <v>6.8</v>
+        <v>3.57</v>
       </c>
       <c r="T3" t="n">
-        <v>1.22</v>
+        <v>5.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81</v>
+        <v>2.99</v>
       </c>
       <c r="X3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AB3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.37</v>
       </c>
-      <c r="AC3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AE3" t="n">
-        <v>1.9</v>
+        <v>2.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>4.1</v>
+        <v>2.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-31 17:30:00</t>
+          <t>2026-01-01 15:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="K4" t="n">
+        <v>54</v>
+      </c>
+      <c r="L4" t="n">
+        <v>63</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32</v>
+      </c>
+      <c r="N4" t="n">
+        <v>29</v>
+      </c>
+      <c r="O4" t="n">
+        <v>72</v>
+      </c>
+      <c r="P4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>47</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Stoke City</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K5" t="n">
+        <v>42</v>
+      </c>
+      <c r="L5" t="n">
+        <v>67</v>
+      </c>
+      <c r="M5" t="n">
+        <v>38</v>
+      </c>
+      <c r="N5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O5" t="n">
+        <v>71</v>
+      </c>
+      <c r="P5" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ipswich Town</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Oxford United</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K6" t="n">
+        <v>54</v>
+      </c>
+      <c r="L6" t="n">
+        <v>75</v>
+      </c>
+      <c r="M6" t="n">
+        <v>38</v>
+      </c>
+      <c r="N6" t="n">
+        <v>29</v>
+      </c>
+      <c r="O6" t="n">
+        <v>71</v>
+      </c>
+      <c r="P6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>50</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sheffield Wednesday</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K7" t="n">
+        <v>69</v>
+      </c>
+      <c r="L7" t="n">
+        <v>74</v>
+      </c>
+      <c r="M7" t="n">
+        <v>29</v>
+      </c>
+      <c r="N7" t="n">
+        <v>23</v>
+      </c>
+      <c r="O7" t="n">
+        <v>78</v>
+      </c>
+      <c r="P7" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>49</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83</v>
+      </c>
+      <c r="L8" t="n">
+        <v>74</v>
+      </c>
+      <c r="M8" t="n">
+        <v>39</v>
+      </c>
+      <c r="N8" t="n">
+        <v>13</v>
+      </c>
+      <c r="O8" t="n">
+        <v>87</v>
+      </c>
+      <c r="P8" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>43</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.4</v>
       </c>
-      <c r="H4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="I4" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K9" t="n">
+        <v>64</v>
+      </c>
+      <c r="L9" t="n">
+        <v>69</v>
+      </c>
+      <c r="M9" t="n">
+        <v>41</v>
+      </c>
+      <c r="N9" t="n">
+        <v>18</v>
+      </c>
+      <c r="O9" t="n">
+        <v>82</v>
+      </c>
+      <c r="P9" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>25</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>West Bromwich Albion</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>83</v>
+      </c>
+      <c r="M10" t="n">
+        <v>33</v>
+      </c>
+      <c r="N10" t="n">
+        <v>34</v>
+      </c>
+      <c r="O10" t="n">
+        <v>67</v>
+      </c>
+      <c r="P10" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>46</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Derby County</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K11" t="n">
+        <v>67</v>
+      </c>
+      <c r="L11" t="n">
+        <v>83</v>
+      </c>
+      <c r="M11" t="n">
+        <v>33</v>
+      </c>
+      <c r="N11" t="n">
+        <v>21</v>
+      </c>
+      <c r="O11" t="n">
+        <v>79</v>
+      </c>
+      <c r="P11" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>59</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-01-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Birmingham City</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>63</v>
+      </c>
+      <c r="L12" t="n">
+        <v>88</v>
+      </c>
+      <c r="M12" t="n">
+        <v>42</v>
+      </c>
+      <c r="N12" t="n">
+        <v>21</v>
+      </c>
+      <c r="O12" t="n">
+        <v>79</v>
+      </c>
+      <c r="P12" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>46</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.41</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="K4" t="n">
-        <v>70</v>
-      </c>
-      <c r="L4" t="n">
-        <v>60</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20</v>
-      </c>
-      <c r="O4" t="n">
-        <v>80</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="AC12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-01-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>25</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Leicester City</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="K13" t="n">
+        <v>56</v>
+      </c>
+      <c r="L13" t="n">
+        <v>74</v>
+      </c>
+      <c r="M13" t="n">
+        <v>39</v>
+      </c>
+      <c r="N13" t="n">
+        <v>27</v>
+      </c>
+      <c r="O13" t="n">
+        <v>74</v>
+      </c>
+      <c r="P13" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>35</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K14" t="n">
+        <v>56</v>
+      </c>
+      <c r="L14" t="n">
+        <v>73</v>
+      </c>
+      <c r="M14" t="n">
+        <v>22</v>
+      </c>
+      <c r="N14" t="n">
+        <v>22</v>
+      </c>
+      <c r="O14" t="n">
+        <v>78</v>
+      </c>
+      <c r="P14" t="n">
         <v>50</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q14" t="n">
         <v>50</v>
       </c>
-      <c r="R4" t="n">
-        <v>5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.47</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="AE14" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-01-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>19</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H15" t="n">
         <v>1.83</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
+      <c r="I15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="K15" t="n">
+        <v>56</v>
+      </c>
+      <c r="L15" t="n">
+        <v>78</v>
+      </c>
+      <c r="M15" t="n">
+        <v>33</v>
+      </c>
+      <c r="N15" t="n">
+        <v>11</v>
+      </c>
+      <c r="O15" t="n">
+        <v>89</v>
+      </c>
+      <c r="P15" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>44</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-01 20:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K16" t="n">
+        <v>62</v>
+      </c>
+      <c r="L16" t="n">
+        <v>67</v>
+      </c>
+      <c r="M16" t="n">
+        <v>17</v>
+      </c>
+      <c r="N16" t="n">
+        <v>17</v>
+      </c>
+      <c r="O16" t="n">
+        <v>84</v>
+      </c>
+      <c r="P16" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>45</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-01-01 20:00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>61</v>
+      </c>
+      <c r="L17" t="n">
+        <v>78</v>
+      </c>
+      <c r="M17" t="n">
+        <v>45</v>
+      </c>
+      <c r="N17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O17" t="n">
+        <v>84</v>
+      </c>
+      <c r="P17" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>28</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG17" headerRowCount="1">
-  <autoFilter ref="A1:AG17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG10" headerRowCount="1">
+  <autoFilter ref="A1:AG10"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG17"/>
+  <dimension ref="A1:AG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="28.8" customWidth="1" min="2" max="2"/>
+    <col width="40.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="25.2" customWidth="1" min="4" max="4"/>
-    <col width="26.4" customWidth="1" min="5" max="5"/>
+    <col width="22.8" customWidth="1" min="4" max="4"/>
+    <col width="15.6" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,434 +675,434 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-01 12:30:00</t>
+          <t>2026-01-02 13:30:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="K2" t="n">
+        <v>75</v>
+      </c>
+      <c r="L2" t="n">
+        <v>75</v>
+      </c>
+      <c r="M2" t="n">
+        <v>46</v>
+      </c>
+      <c r="N2" t="n">
         <v>25</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Blackburn Rovers</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Wrexham</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="K2" t="n">
-        <v>64</v>
-      </c>
-      <c r="L2" t="n">
-        <v>69</v>
-      </c>
-      <c r="M2" t="n">
-        <v>14</v>
-      </c>
-      <c r="N2" t="n">
-        <v>18</v>
-      </c>
       <c r="O2" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="P2" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="Q2" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="R2" t="n">
-        <v>2.06</v>
+        <v>3.6</v>
       </c>
       <c r="S2" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>3.53</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="V2" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="W2" t="n">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="X2" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.84</v>
+        <v>2.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.69</v>
+        <v>3.12</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-01 15:00:00</t>
+          <t>2026-01-02 14:35:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="H3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K3" t="n">
+        <v>44</v>
+      </c>
+      <c r="L3" t="n">
+        <v>72</v>
+      </c>
+      <c r="M3" t="n">
+        <v>45</v>
+      </c>
+      <c r="N3" t="n">
+        <v>29</v>
+      </c>
+      <c r="O3" t="n">
+        <v>72</v>
+      </c>
+      <c r="P3" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>39</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="K3" t="n">
-        <v>50</v>
-      </c>
-      <c r="L3" t="n">
-        <v>82</v>
-      </c>
-      <c r="M3" t="n">
-        <v>36</v>
-      </c>
-      <c r="N3" t="n">
-        <v>32</v>
-      </c>
-      <c r="O3" t="n">
-        <v>69</v>
-      </c>
-      <c r="P3" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>55</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.68</v>
-      </c>
       <c r="S3" t="n">
-        <v>3.57</v>
+        <v>3.88</v>
       </c>
       <c r="T3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="W3" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-01 15:00:00</t>
+          <t>2026-01-02 17:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="I4" t="n">
-        <v>1.82</v>
+        <v>2.41</v>
       </c>
       <c r="J4" t="n">
-        <v>3.27</v>
+        <v>3.97</v>
       </c>
       <c r="K4" t="n">
         <v>54</v>
       </c>
       <c r="L4" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="O4" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="P4" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q4" t="n">
         <v>54</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>47</v>
       </c>
       <c r="R4" t="n">
         <v>4.2</v>
       </c>
       <c r="S4" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="U4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>3.15</v>
+        <v>1.94</v>
       </c>
       <c r="X4" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-01 15:00:00</t>
+          <t>2026-01-02 18:45:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="G5" t="n">
-        <v>1.17</v>
+        <v>2.75</v>
       </c>
       <c r="H5" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="I5" t="n">
-        <v>1.19</v>
+        <v>2.02</v>
       </c>
       <c r="J5" t="n">
-        <v>2.43</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L5" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="M5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N5" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="O5" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="P5" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="R5" t="n">
-        <v>2.32</v>
+        <v>6.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.23</v>
+        <v>3.95</v>
       </c>
       <c r="T5" t="n">
-        <v>3.03</v>
+        <v>1.52</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="W5" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="X5" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.63</v>
+        <v>2.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.71</v>
+        <v>2.45</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="AG5" t="n">
         <v>1.36</v>
@@ -1111,1309 +1111,546 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-01 15:00:00</t>
+          <t>2026-01-02 19:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="H6" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="I6" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="K6" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L6" t="n">
         <v>75</v>
       </c>
       <c r="M6" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N6" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="O6" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="P6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Q6" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>4.7</v>
+        <v>3.62</v>
       </c>
       <c r="T6" t="n">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="W6" t="n">
-        <v>3.05</v>
+        <v>3.92</v>
       </c>
       <c r="X6" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.86</v>
+        <v>2.46</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-01 15:00:00</t>
+          <t>2026-01-02 19:45:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="I7" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="J7" t="n">
-        <v>2.47</v>
+        <v>3.08</v>
       </c>
       <c r="K7" t="n">
+        <v>51</v>
+      </c>
+      <c r="L7" t="n">
         <v>69</v>
       </c>
-      <c r="L7" t="n">
-        <v>74</v>
-      </c>
       <c r="M7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O7" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P7" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="Q7" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="R7" t="n">
-        <v>1.54</v>
+        <v>2.76</v>
       </c>
       <c r="S7" t="n">
-        <v>3.83</v>
+        <v>3.33</v>
       </c>
       <c r="T7" t="n">
-        <v>6.3</v>
+        <v>2.46</v>
       </c>
       <c r="U7" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="W7" t="n">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="X7" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.36</v>
+        <v>2.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.64</v>
+        <v>2.31</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-01 15:00:00</t>
+          <t>2026-01-02 19:45:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.82</v>
+        <v>1.13</v>
       </c>
       <c r="G8" t="n">
-        <v>0.92</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>1.64</v>
+        <v>1.19</v>
       </c>
       <c r="I8" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="J8" t="n">
-        <v>2.87</v>
+        <v>2.52</v>
       </c>
       <c r="K8" t="n">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="L8" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="M8" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="N8" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="O8" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="P8" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="R8" t="n">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="S8" t="n">
-        <v>3.68</v>
+        <v>3.99</v>
       </c>
       <c r="T8" t="n">
-        <v>3.99</v>
+        <v>1.57</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="V8" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="W8" t="n">
         <v>3.25</v>
       </c>
       <c r="X8" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.99</v>
+        <v>2.07</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.28</v>
+        <v>1.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.57</v>
+        <v>2.53</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-01 15:00:00</t>
+          <t>2026-01-02 20:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.73</v>
+        <v>1.14</v>
       </c>
       <c r="G9" t="n">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="I9" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="J9" t="n">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="M9" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="N9" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="O9" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="P9" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="R9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.69</v>
       </c>
-      <c r="S9" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE9" t="n">
-        <v>2.56</v>
+        <v>4</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-01 15:00:00</t>
+          <t>2026-01-02 20:45:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="H10" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="I10" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="J10" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="K10" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L10" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M10" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="O10" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="P10" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="Q10" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2.9</v>
       </c>
-      <c r="U10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="W10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AF10" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-01-01 15:00:00</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>England Championship</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>25</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Derby County</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Middlesbrough</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K11" t="n">
-        <v>67</v>
-      </c>
-      <c r="L11" t="n">
-        <v>83</v>
-      </c>
-      <c r="M11" t="n">
-        <v>33</v>
-      </c>
-      <c r="N11" t="n">
-        <v>21</v>
-      </c>
-      <c r="O11" t="n">
-        <v>79</v>
-      </c>
-      <c r="P11" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>59</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AG11" t="n">
         <v>1.33</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-01-01 15:00:00</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>England Championship</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>25</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Watford</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Birmingham City</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K12" t="n">
-        <v>63</v>
-      </c>
-      <c r="L12" t="n">
-        <v>88</v>
-      </c>
-      <c r="M12" t="n">
-        <v>42</v>
-      </c>
-      <c r="N12" t="n">
-        <v>21</v>
-      </c>
-      <c r="O12" t="n">
-        <v>79</v>
-      </c>
-      <c r="P12" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>46</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-01-01 17:30:00</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>England Championship</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>25</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Sheffield United</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Leicester City</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="K13" t="n">
-        <v>56</v>
-      </c>
-      <c r="L13" t="n">
-        <v>74</v>
-      </c>
-      <c r="M13" t="n">
-        <v>39</v>
-      </c>
-      <c r="N13" t="n">
-        <v>27</v>
-      </c>
-      <c r="O13" t="n">
-        <v>74</v>
-      </c>
-      <c r="P13" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>35</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-01-01 17:30:00</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>England Premier League</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>19</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Crystal Palace</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Fulham</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K14" t="n">
-        <v>56</v>
-      </c>
-      <c r="L14" t="n">
-        <v>73</v>
-      </c>
-      <c r="M14" t="n">
-        <v>22</v>
-      </c>
-      <c r="N14" t="n">
-        <v>22</v>
-      </c>
-      <c r="O14" t="n">
-        <v>78</v>
-      </c>
-      <c r="P14" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>50</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-01-01 17:30:00</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>England Premier League</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>19</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Leeds United</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="K15" t="n">
-        <v>56</v>
-      </c>
-      <c r="L15" t="n">
-        <v>78</v>
-      </c>
-      <c r="M15" t="n">
-        <v>33</v>
-      </c>
-      <c r="N15" t="n">
-        <v>11</v>
-      </c>
-      <c r="O15" t="n">
-        <v>89</v>
-      </c>
-      <c r="P15" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>44</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-01-01 20:00:00</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>England Premier League</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>19</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Sunderland</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K16" t="n">
-        <v>62</v>
-      </c>
-      <c r="L16" t="n">
-        <v>67</v>
-      </c>
-      <c r="M16" t="n">
-        <v>17</v>
-      </c>
-      <c r="N16" t="n">
-        <v>17</v>
-      </c>
-      <c r="O16" t="n">
-        <v>84</v>
-      </c>
-      <c r="P16" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>45</v>
-      </c>
-      <c r="R16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-01-01 20:00:00</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>England Premier League</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>19</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Brentford</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Tottenham Hotspur</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>61</v>
-      </c>
-      <c r="L17" t="n">
-        <v>78</v>
-      </c>
-      <c r="M17" t="n">
-        <v>45</v>
-      </c>
-      <c r="N17" t="n">
-        <v>17</v>
-      </c>
-      <c r="O17" t="n">
-        <v>84</v>
-      </c>
-      <c r="P17" t="n">
-        <v>73</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>28</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG10" headerRowCount="1">
-  <autoFilter ref="A1:AG10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG38" headerRowCount="1">
+  <autoFilter ref="A1:AG38"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG10"/>
+  <dimension ref="A1:AG38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="40.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="22.8" customWidth="1" min="4" max="4"/>
-    <col width="15.6" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="26.4" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,982 +675,4034 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-02 13:30:00</t>
+          <t>2026-01-03 11:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="G2" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.76</v>
+        <v>1.89</v>
       </c>
       <c r="I2" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="J2" t="n">
-        <v>2.03</v>
+        <v>3.34</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="L2" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="M2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="P2" t="n">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="Q2" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="R2" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC2" t="n">
         <v>1.9</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.44</v>
+        <v>3.33</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.12</v>
+        <v>2.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-02 14:35:00</t>
+          <t>2026-01-03 11:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2</v>
+        <v>1.25</v>
       </c>
       <c r="H3" t="n">
-        <v>0.84</v>
+        <v>1.68</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6</v>
+        <v>1.18</v>
       </c>
       <c r="J3" t="n">
-        <v>1.44</v>
+        <v>2.86</v>
       </c>
       <c r="K3" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="L3" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="N3" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="P3" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>3.88</v>
+        <v>3.72</v>
       </c>
       <c r="T3" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X3" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Y3" t="n">
         <v>1.83</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-02 17:30:00</t>
+          <t>2026-01-03 12:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="H4" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="I4" t="n">
-        <v>2.41</v>
+        <v>1.67</v>
       </c>
       <c r="J4" t="n">
-        <v>3.97</v>
+        <v>4.11</v>
       </c>
       <c r="K4" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L4" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="O4" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="P4" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="Q4" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>4.2</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="T4" t="n">
-        <v>1.64</v>
+        <v>4.1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="W4" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="X4" t="n">
         <v>1.53</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-02 18:45:00</t>
+          <t>2026-01-03 12:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.86</v>
+        <v>2.44</v>
       </c>
       <c r="G5" t="n">
-        <v>2.75</v>
+        <v>0.89</v>
       </c>
       <c r="H5" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="I5" t="n">
-        <v>2.02</v>
+        <v>1.2</v>
       </c>
       <c r="J5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K5" t="n">
+        <v>33</v>
+      </c>
+      <c r="L5" t="n">
+        <v>78</v>
+      </c>
+      <c r="M5" t="n">
+        <v>33</v>
+      </c>
+      <c r="N5" t="n">
+        <v>28</v>
+      </c>
+      <c r="O5" t="n">
+        <v>73</v>
+      </c>
+      <c r="P5" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S5" t="n">
         <v>3.6</v>
       </c>
-      <c r="K5" t="n">
-        <v>39</v>
-      </c>
-      <c r="L5" t="n">
-        <v>93</v>
-      </c>
-      <c r="M5" t="n">
-        <v>40</v>
-      </c>
-      <c r="N5" t="n">
-        <v>21</v>
-      </c>
-      <c r="O5" t="n">
-        <v>80</v>
-      </c>
-      <c r="P5" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>62</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.95</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.52</v>
+        <v>4.4</v>
       </c>
       <c r="U5" t="n">
         <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="X5" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>2.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-02 19:30:00</t>
+          <t>2026-01-03 13:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.8</v>
+        <v>0.89</v>
       </c>
       <c r="G6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.9</v>
       </c>
-      <c r="H6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.06</v>
-      </c>
       <c r="J6" t="n">
-        <v>2.92</v>
+        <v>2.21</v>
       </c>
       <c r="K6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L6" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="M6" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O6" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P6" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="Q6" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>3.62</v>
+        <v>3.32</v>
       </c>
       <c r="T6" t="n">
-        <v>5.9</v>
+        <v>3.95</v>
       </c>
       <c r="U6" t="n">
         <v>1.34</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="W6" t="n">
-        <v>3.92</v>
+        <v>3.52</v>
       </c>
       <c r="X6" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.46</v>
+        <v>2.04</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-02 19:45:00</t>
+          <t>2026-01-03 13:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>0.89</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="H7" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="I7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="K7" t="n">
+        <v>33</v>
+      </c>
+      <c r="L7" t="n">
+        <v>62</v>
+      </c>
+      <c r="M7" t="n">
+        <v>22</v>
+      </c>
+      <c r="N7" t="n">
+        <v>56</v>
+      </c>
+      <c r="O7" t="n">
+        <v>45</v>
+      </c>
+      <c r="P7" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>61</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.45</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="K7" t="n">
-        <v>51</v>
-      </c>
-      <c r="L7" t="n">
-        <v>69</v>
-      </c>
-      <c r="M7" t="n">
-        <v>32</v>
-      </c>
-      <c r="N7" t="n">
-        <v>26</v>
-      </c>
-      <c r="O7" t="n">
-        <v>76</v>
-      </c>
-      <c r="P7" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>44</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AC7" t="n">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="AF7" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-02 19:45:00</t>
+          <t>2026-01-03 13:10:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.14</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.19</v>
+        <v>1.58</v>
       </c>
       <c r="I8" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="K8" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="L8" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M8" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N8" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q8" t="n">
         <v>60</v>
       </c>
       <c r="R8" t="n">
-        <v>5.5</v>
+        <v>2.31</v>
       </c>
       <c r="S8" t="n">
-        <v>3.99</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="V8" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="W8" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.82</v>
+        <v>2.34</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.07</v>
+        <v>2.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.53</v>
+        <v>1.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-02 20:00:00</t>
+          <t>2026-01-03 14:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="I9" t="n">
-        <v>1.07</v>
+        <v>1.37</v>
       </c>
       <c r="J9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K9" t="n">
+        <v>40</v>
+      </c>
+      <c r="L9" t="n">
+        <v>53</v>
+      </c>
+      <c r="M9" t="n">
+        <v>19</v>
+      </c>
+      <c r="N9" t="n">
+        <v>35</v>
+      </c>
+      <c r="O9" t="n">
+        <v>66</v>
+      </c>
+      <c r="P9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>75</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE9" t="n">
         <v>2.88</v>
       </c>
-      <c r="K9" t="n">
-        <v>33</v>
-      </c>
-      <c r="L9" t="n">
-        <v>54</v>
-      </c>
-      <c r="M9" t="n">
-        <v>17</v>
-      </c>
-      <c r="N9" t="n">
-        <v>40</v>
-      </c>
-      <c r="O9" t="n">
-        <v>61</v>
-      </c>
-      <c r="P9" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>72</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>4</v>
-      </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-02 20:45:00</t>
+          <t>2026-01-03 14:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="G10" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="H10" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="I10" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="J10" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="K10" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="M10" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="O10" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="P10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q10" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="R10" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="T10" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="U10" t="n">
         <v>1.35</v>
       </c>
       <c r="V10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="K11" t="n">
+        <v>54</v>
+      </c>
+      <c r="L11" t="n">
+        <v>72</v>
+      </c>
+      <c r="M11" t="n">
+        <v>41</v>
+      </c>
+      <c r="N11" t="n">
+        <v>29</v>
+      </c>
+      <c r="O11" t="n">
+        <v>72</v>
+      </c>
+      <c r="P11" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>41</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-01-03 14:55:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Al Feiha</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="K12" t="n">
+        <v>40</v>
+      </c>
+      <c r="L12" t="n">
+        <v>50</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20</v>
+      </c>
+      <c r="N12" t="n">
+        <v>30</v>
+      </c>
+      <c r="O12" t="n">
+        <v>70</v>
+      </c>
+      <c r="P12" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>60</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-01-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>21</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hearts</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Livingston</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K13" t="n">
+        <v>53</v>
+      </c>
+      <c r="L13" t="n">
+        <v>74</v>
+      </c>
+      <c r="M13" t="n">
+        <v>38</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16</v>
+      </c>
+      <c r="O13" t="n">
+        <v>85</v>
+      </c>
+      <c r="P13" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>42</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>21</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Falkirk</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K14" t="n">
+        <v>50</v>
+      </c>
+      <c r="L14" t="n">
+        <v>67</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17</v>
+      </c>
+      <c r="N14" t="n">
+        <v>22</v>
+      </c>
+      <c r="O14" t="n">
+        <v>78</v>
+      </c>
+      <c r="P14" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>61</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-01-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>21</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>St. Mirren</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K15" t="n">
+        <v>53</v>
+      </c>
+      <c r="L15" t="n">
+        <v>60</v>
+      </c>
+      <c r="M15" t="n">
+        <v>29</v>
+      </c>
+      <c r="N15" t="n">
+        <v>17</v>
+      </c>
+      <c r="O15" t="n">
+        <v>84</v>
+      </c>
+      <c r="P15" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>54</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Kilmarnock</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K16" t="n">
+        <v>45</v>
+      </c>
+      <c r="L16" t="n">
+        <v>75</v>
+      </c>
+      <c r="M16" t="n">
+        <v>40</v>
+      </c>
+      <c r="N16" t="n">
+        <v>30</v>
+      </c>
+      <c r="O16" t="n">
+        <v>70</v>
+      </c>
+      <c r="P16" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>50</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-01-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Dundee</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K17" t="n">
+        <v>45</v>
+      </c>
+      <c r="L17" t="n">
+        <v>80</v>
+      </c>
+      <c r="M17" t="n">
+        <v>40</v>
+      </c>
+      <c r="N17" t="n">
+        <v>25</v>
+      </c>
+      <c r="O17" t="n">
+        <v>75</v>
+      </c>
+      <c r="P17" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>55</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84</v>
+      </c>
+      <c r="L18" t="n">
+        <v>73</v>
+      </c>
+      <c r="M18" t="n">
+        <v>33</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>95</v>
+      </c>
+      <c r="P18" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>22</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-01-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="K19" t="n">
+        <v>56</v>
+      </c>
+      <c r="L19" t="n">
+        <v>62</v>
+      </c>
+      <c r="M19" t="n">
+        <v>45</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6</v>
+      </c>
+      <c r="O19" t="n">
+        <v>95</v>
+      </c>
+      <c r="P19" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>44</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-01-03 15:15:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CA Osasuna</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Athletic Club Bilbao</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K20" t="n">
+        <v>38</v>
+      </c>
+      <c r="L20" t="n">
+        <v>63</v>
+      </c>
+      <c r="M20" t="n">
+        <v>38</v>
+      </c>
+      <c r="N20" t="n">
+        <v>19</v>
+      </c>
+      <c r="O20" t="n">
+        <v>82</v>
+      </c>
+      <c r="P20" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>57</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-01-03 15:15:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CD Castellón</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SD Huesca</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K21" t="n">
+        <v>45</v>
+      </c>
+      <c r="L21" t="n">
+        <v>67</v>
+      </c>
+      <c r="M21" t="n">
+        <v>28</v>
+      </c>
+      <c r="N21" t="n">
+        <v>39</v>
+      </c>
+      <c r="O21" t="n">
+        <v>62</v>
+      </c>
+      <c r="P21" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>56</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-01-03 15:15:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="K22" t="n">
+        <v>56</v>
+      </c>
+      <c r="L22" t="n">
+        <v>67</v>
+      </c>
+      <c r="M22" t="n">
+        <v>33</v>
+      </c>
+      <c r="N22" t="n">
+        <v>33</v>
+      </c>
+      <c r="O22" t="n">
+        <v>67</v>
+      </c>
+      <c r="P22" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>39</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-01-03 15:30:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>17</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CD Tondela</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FC Arouca</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="K23" t="n">
+        <v>43</v>
+      </c>
+      <c r="L23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M23" t="n">
+        <v>36</v>
+      </c>
+      <c r="N23" t="n">
+        <v>29</v>
+      </c>
+      <c r="O23" t="n">
+        <v>72</v>
+      </c>
+      <c r="P23" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>43</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-01-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>17</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Olympique Lyonnais</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K24" t="n">
+        <v>51</v>
+      </c>
+      <c r="L24" t="n">
+        <v>75</v>
+      </c>
+      <c r="M24" t="n">
+        <v>26</v>
+      </c>
+      <c r="N24" t="n">
+        <v>51</v>
+      </c>
+      <c r="O24" t="n">
+        <v>51</v>
+      </c>
+      <c r="P24" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>51</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-01-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>18</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K25" t="n">
+        <v>46</v>
+      </c>
+      <c r="L25" t="n">
+        <v>67</v>
+      </c>
+      <c r="M25" t="n">
+        <v>26</v>
+      </c>
+      <c r="N25" t="n">
+        <v>34</v>
+      </c>
+      <c r="O25" t="n">
+        <v>66</v>
+      </c>
+      <c r="P25" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>61</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>10</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-01-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Al Taawon</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="K26" t="n">
+        <v>47</v>
+      </c>
+      <c r="L26" t="n">
+        <v>82</v>
+      </c>
+      <c r="M26" t="n">
+        <v>55</v>
+      </c>
+      <c r="N26" t="n">
+        <v>19</v>
+      </c>
+      <c r="O26" t="n">
+        <v>82</v>
+      </c>
+      <c r="P26" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>54</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-01-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>18</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Elche CF</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K27" t="n">
+        <v>51</v>
+      </c>
+      <c r="L27" t="n">
+        <v>64</v>
+      </c>
+      <c r="M27" t="n">
+        <v>6</v>
+      </c>
+      <c r="N27" t="n">
+        <v>11</v>
+      </c>
+      <c r="O27" t="n">
+        <v>89</v>
+      </c>
+      <c r="P27" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>57</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T27" t="n">
         <v>2.2</v>
       </c>
-      <c r="W10" t="n">
-        <v>4</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="U27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-01-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>20</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="K28" t="n">
+        <v>44</v>
+      </c>
+      <c r="L28" t="n">
+        <v>56</v>
+      </c>
+      <c r="M28" t="n">
+        <v>17</v>
+      </c>
+      <c r="N28" t="n">
+        <v>44</v>
+      </c>
+      <c r="O28" t="n">
+        <v>56</v>
+      </c>
+      <c r="P28" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>67</v>
+      </c>
+      <c r="R28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-01-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Real Valladolid</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="K29" t="n">
+        <v>70</v>
+      </c>
+      <c r="L29" t="n">
+        <v>79</v>
+      </c>
+      <c r="M29" t="n">
+        <v>32</v>
+      </c>
+      <c r="N29" t="n">
+        <v>20</v>
+      </c>
+      <c r="O29" t="n">
+        <v>80</v>
+      </c>
+      <c r="P29" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>41</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-01-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>17</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="K30" t="n">
+        <v>57</v>
+      </c>
+      <c r="L30" t="n">
+        <v>75</v>
+      </c>
+      <c r="M30" t="n">
+        <v>38</v>
+      </c>
+      <c r="N30" t="n">
+        <v>38</v>
+      </c>
+      <c r="O30" t="n">
+        <v>63</v>
+      </c>
+      <c r="P30" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>51</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-01-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>17</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sporting Braga</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="K31" t="n">
+        <v>57</v>
+      </c>
+      <c r="L31" t="n">
+        <v>88</v>
+      </c>
+      <c r="M31" t="n">
+        <v>51</v>
+      </c>
+      <c r="N31" t="n">
+        <v>19</v>
+      </c>
+      <c r="O31" t="n">
+        <v>82</v>
+      </c>
+      <c r="P31" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>44</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-01-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>17</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>GD Estoril Praia</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="K32" t="n">
+        <v>53</v>
+      </c>
+      <c r="L32" t="n">
+        <v>88</v>
+      </c>
+      <c r="M32" t="n">
+        <v>54</v>
+      </c>
+      <c r="N32" t="n">
+        <v>14</v>
+      </c>
+      <c r="O32" t="n">
+        <v>87</v>
+      </c>
+      <c r="P32" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>40</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T32" t="n">
+        <v>14</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-01-03 19:45:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>18</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>47</v>
+      </c>
+      <c r="L33" t="n">
+        <v>77</v>
+      </c>
+      <c r="M33" t="n">
+        <v>18</v>
+      </c>
+      <c r="N33" t="n">
+        <v>43</v>
+      </c>
+      <c r="O33" t="n">
+        <v>58</v>
+      </c>
+      <c r="P33" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>65</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-01-03 20:00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>18</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RCD Espanyol</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="K34" t="n">
+        <v>67</v>
+      </c>
+      <c r="L34" t="n">
+        <v>84</v>
+      </c>
+      <c r="M34" t="n">
+        <v>39</v>
+      </c>
+      <c r="N34" t="n">
+        <v>17</v>
+      </c>
+      <c r="O34" t="n">
+        <v>84</v>
+      </c>
+      <c r="P34" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>33</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-01-03 20:00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>20</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K35" t="n">
+        <v>67</v>
+      </c>
+      <c r="L35" t="n">
+        <v>67</v>
+      </c>
+      <c r="M35" t="n">
+        <v>33</v>
+      </c>
+      <c r="N35" t="n">
+        <v>22</v>
+      </c>
+      <c r="O35" t="n">
+        <v>78</v>
+      </c>
+      <c r="P35" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>39</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="W35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-01-03 20:05:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K36" t="n">
+        <v>50</v>
+      </c>
+      <c r="L36" t="n">
+        <v>69</v>
+      </c>
+      <c r="M36" t="n">
+        <v>32</v>
+      </c>
+      <c r="N36" t="n">
+        <v>38</v>
+      </c>
+      <c r="O36" t="n">
+        <v>63</v>
+      </c>
+      <c r="P36" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>51</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-01-03 20:30:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Farense</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Portimonense</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K37" t="n">
+        <v>43</v>
+      </c>
+      <c r="L37" t="n">
+        <v>64</v>
+      </c>
+      <c r="M37" t="n">
+        <v>22</v>
+      </c>
+      <c r="N37" t="n">
+        <v>29</v>
+      </c>
+      <c r="O37" t="n">
+        <v>71</v>
+      </c>
+      <c r="P37" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>50</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V37" t="n">
         <v>1.9</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="W37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X37" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Y37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-01-03 20:30:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>17</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AVS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Moreirense FC</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K38" t="n">
+        <v>51</v>
+      </c>
+      <c r="L38" t="n">
+        <v>76</v>
+      </c>
+      <c r="M38" t="n">
+        <v>38</v>
+      </c>
+      <c r="N38" t="n">
+        <v>19</v>
+      </c>
+      <c r="O38" t="n">
+        <v>82</v>
+      </c>
+      <c r="P38" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>44</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="W38" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC38" t="n">
         <v>2.46</v>
       </c>
-      <c r="AA10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.33</v>
+      <c r="AD38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG38" headerRowCount="1">
-  <autoFilter ref="A1:AG38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG45" headerRowCount="1">
+  <autoFilter ref="A1:AG45"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG38"/>
+  <dimension ref="A1:AG45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="40.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="26.4" customWidth="1" min="5" max="5"/>
+    <col width="25.2" customWidth="1" min="4" max="4"/>
+    <col width="25.2" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,7 +675,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-03 11:00:00</t>
+          <t>2026-01-04 11:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -688,1511 +688,1511 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.14</v>
+        <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="H2" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="I2" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="J2" t="n">
-        <v>3.34</v>
+        <v>3.41</v>
       </c>
       <c r="K2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="L2" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="M2" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="N2" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="O2" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="P2" t="n">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="Q2" t="n">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="W2" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="X2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="AF2" t="n">
         <v>2.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-03 11:30:00</t>
+          <t>2026-01-04 11:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.14</v>
+        <v>1.71</v>
       </c>
       <c r="G3" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="H3" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.18</v>
+        <v>0.95</v>
       </c>
       <c r="J3" t="n">
-        <v>2.86</v>
+        <v>2.35</v>
       </c>
       <c r="K3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L3" t="n">
+        <v>46</v>
+      </c>
+      <c r="M3" t="n">
+        <v>13</v>
+      </c>
+      <c r="N3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O3" t="n">
         <v>53</v>
       </c>
-      <c r="L3" t="n">
-        <v>86</v>
-      </c>
-      <c r="M3" t="n">
-        <v>32</v>
-      </c>
-      <c r="N3" t="n">
-        <v>14</v>
-      </c>
-      <c r="O3" t="n">
-        <v>87</v>
-      </c>
       <c r="P3" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="Q3" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="R3" t="n">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="S3" t="n">
-        <v>3.72</v>
+        <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V3" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="X3" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.09</v>
+        <v>2.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.48</v>
+        <v>1.92</v>
       </c>
       <c r="AD3" t="n">
         <v>1.44</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.89</v>
+        <v>2.56</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-03 12:30:00</t>
+          <t>2026-01-04 11:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.44</v>
+        <v>1.88</v>
       </c>
       <c r="G4" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="H4" t="n">
-        <v>2.44</v>
+        <v>1.45</v>
       </c>
       <c r="I4" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="J4" t="n">
-        <v>4.11</v>
+        <v>2.99</v>
       </c>
       <c r="K4" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="L4" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="M4" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="O4" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="P4" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="Q4" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="R4" t="n">
-        <v>1.64</v>
+        <v>3.26</v>
       </c>
       <c r="S4" t="n">
-        <v>3.72</v>
+        <v>2.98</v>
       </c>
       <c r="T4" t="n">
-        <v>4.1</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="V4" t="n">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="X4" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.2</v>
+        <v>1.92</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AF4" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>3.34</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-03 12:30:00</t>
+          <t>2026-01-04 12:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.44</v>
+        <v>1.92</v>
       </c>
       <c r="G5" t="n">
-        <v>0.89</v>
+        <v>1.77</v>
       </c>
       <c r="H5" t="n">
-        <v>1.39</v>
+        <v>1.98</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2</v>
+        <v>1.84</v>
       </c>
       <c r="J5" t="n">
-        <v>2.59</v>
+        <v>3.82</v>
       </c>
       <c r="K5" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="L5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M5" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N5" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="P5" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="Q5" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="R5" t="n">
-        <v>1.83</v>
+        <v>2.66</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>4.4</v>
+        <v>2.53</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="V5" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="W5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-03 13:00:00</t>
+          <t>2026-01-04 12:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.89</v>
+        <v>1.42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.38</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="J6" t="n">
-        <v>2.21</v>
+        <v>2.94</v>
       </c>
       <c r="K6" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="L6" t="n">
         <v>72</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="O6" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="P6" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="Q6" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="R6" t="n">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>3.32</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="V6" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="W6" t="n">
-        <v>3.52</v>
+        <v>2.64</v>
       </c>
       <c r="X6" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.19</v>
+        <v>3.28</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.74</v>
+        <v>2.52</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.04</v>
+        <v>1.64</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-03 13:00:00</t>
+          <t>2026-01-04 12:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.89</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
-        <v>0.33</v>
+        <v>0.64</v>
       </c>
       <c r="H7" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="I7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="J7" t="n">
-        <v>2.49</v>
+        <v>2.72</v>
       </c>
       <c r="K7" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="L7" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="M7" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="N7" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="O7" t="n">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="P7" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="Q7" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>3.39</v>
+        <v>4.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3.94</v>
+        <v>6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="V7" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="W7" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="X7" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.4</v>
+        <v>3.06</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.18</v>
+        <v>2.59</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-03 13:10:00</t>
+          <t>2026-01-04 12:30:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>1.33</v>
       </c>
       <c r="H8" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>1.59</v>
       </c>
       <c r="J8" t="n">
-        <v>2.58</v>
+        <v>3.23</v>
       </c>
       <c r="K8" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="L8" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M8" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="P8" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="Q8" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="R8" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="W8" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-03 14:00:00</t>
+          <t>2026-01-04 13:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="G9" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="H9" t="n">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="I9" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="J9" t="n">
-        <v>2.98</v>
+        <v>2.56</v>
       </c>
       <c r="K9" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="L9" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="N9" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="O9" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="Q9" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="R9" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="S9" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="T9" t="n">
-        <v>4.4</v>
+        <v>4.64</v>
       </c>
       <c r="U9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="W9" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="X9" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.02</v>
+        <v>2.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-03 14:00:00</t>
+          <t>2026-01-04 13:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="G10" t="n">
-        <v>1.14</v>
+        <v>0.78</v>
       </c>
       <c r="H10" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="I10" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="J10" t="n">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="K10" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="L10" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N10" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="O10" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="P10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="S10" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
         <v>1.35</v>
       </c>
       <c r="V10" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="W10" t="n">
-        <v>3.47</v>
+        <v>4.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-03 14:00:00</t>
+          <t>2026-01-04 14:00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.67</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="H11" t="n">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="I11" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
-        <v>2.27</v>
+        <v>2.73</v>
       </c>
       <c r="K11" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L11" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M11" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="N11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O11" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P11" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Q11" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R11" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>6.3</v>
       </c>
       <c r="T11" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.49</v>
+        <v>1.14</v>
       </c>
       <c r="V11" t="n">
-        <v>2.5</v>
+        <v>1.47</v>
       </c>
       <c r="W11" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="X11" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.46</v>
+        <v>3.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-03 14:55:00</t>
+          <t>2026-01-04 14:00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>0.63</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6</v>
+        <v>1.33</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="I12" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="J12" t="n">
-        <v>2.03</v>
+        <v>2.49</v>
       </c>
       <c r="K12" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="L12" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="N12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P12" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="Q12" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="W12" t="n">
-        <v>3.76</v>
+        <v>3.36</v>
       </c>
       <c r="X12" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AD12" t="n">
         <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-03 15:00:00</t>
+          <t>2026-01-04 15:00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.33</v>
+        <v>1.62</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4</v>
+        <v>1.42</v>
       </c>
       <c r="H13" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="I13" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="J13" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="K13" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L13" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="M13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O13" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="P13" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="Q13" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>2.03</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>3.37</v>
       </c>
       <c r="T13" t="n">
-        <v>6.4</v>
+        <v>3.56</v>
       </c>
       <c r="U13" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="W13" t="n">
-        <v>2.54</v>
+        <v>3.24</v>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-03 15:00:00</t>
+          <t>2026-01-04 15:00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="G14" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="H14" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="I14" t="n">
-        <v>1.26</v>
+        <v>0.86</v>
       </c>
       <c r="J14" t="n">
-        <v>2.59</v>
+        <v>2.12</v>
       </c>
       <c r="K14" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="L14" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="M14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O14" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="P14" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="Q14" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="R14" t="n">
-        <v>2.61</v>
+        <v>2.12</v>
       </c>
       <c r="S14" t="n">
-        <v>3.09</v>
+        <v>3.34</v>
       </c>
       <c r="T14" t="n">
-        <v>2.42</v>
+        <v>3.34</v>
       </c>
       <c r="U14" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="W14" t="n">
-        <v>2.99</v>
+        <v>4.33</v>
       </c>
       <c r="X14" t="n">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.82</v>
+        <v>2.69</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
         <v>1.38</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.77</v>
+        <v>2.44</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-03 15:00:00</t>
+          <t>2026-01-04 15:00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="G15" t="n">
-        <v>0.63</v>
+        <v>1.08</v>
       </c>
       <c r="H15" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="I15" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="J15" t="n">
-        <v>2.98</v>
+        <v>2.44</v>
       </c>
       <c r="K15" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N15" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="O15" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="P15" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q15" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="R15" t="n">
-        <v>1.92</v>
+        <v>2.63</v>
       </c>
       <c r="S15" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="U15" t="n">
         <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="W15" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="X15" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="Y15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.05</v>
+        <v>2.81</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AG15" t="n">
         <v>1.38</v>
@@ -2201,557 +2201,557 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-03 15:00:00</t>
+          <t>2026-01-04 15:00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.6</v>
+        <v>1.38</v>
       </c>
       <c r="G16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K16" t="n">
+        <v>61</v>
+      </c>
+      <c r="L16" t="n">
+        <v>68</v>
+      </c>
+      <c r="M16" t="n">
+        <v>13</v>
+      </c>
+      <c r="N16" t="n">
+        <v>28</v>
+      </c>
+      <c r="O16" t="n">
+        <v>73</v>
+      </c>
+      <c r="P16" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>56</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.3</v>
       </c>
-      <c r="H16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K16" t="n">
-        <v>45</v>
-      </c>
-      <c r="L16" t="n">
-        <v>75</v>
-      </c>
-      <c r="M16" t="n">
-        <v>40</v>
-      </c>
-      <c r="N16" t="n">
-        <v>30</v>
-      </c>
-      <c r="O16" t="n">
-        <v>70</v>
-      </c>
-      <c r="P16" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>50</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="W16" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="X16" t="n">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-03 15:00:00</t>
+          <t>2026-01-04 15:00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3</v>
+        <v>0.92</v>
       </c>
       <c r="H17" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="I17" t="n">
-        <v>0.83</v>
+        <v>1.2</v>
       </c>
       <c r="J17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K17" t="n">
+        <v>37</v>
+      </c>
+      <c r="L17" t="n">
+        <v>60</v>
+      </c>
+      <c r="M17" t="n">
+        <v>24</v>
+      </c>
+      <c r="N17" t="n">
+        <v>37</v>
+      </c>
+      <c r="O17" t="n">
+        <v>64</v>
+      </c>
+      <c r="P17" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>56</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2.38</v>
       </c>
-      <c r="K17" t="n">
-        <v>45</v>
-      </c>
-      <c r="L17" t="n">
-        <v>80</v>
-      </c>
-      <c r="M17" t="n">
-        <v>40</v>
-      </c>
-      <c r="N17" t="n">
-        <v>25</v>
-      </c>
-      <c r="O17" t="n">
-        <v>75</v>
-      </c>
-      <c r="P17" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>55</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AA17" t="n">
-        <v>2.21</v>
+        <v>1.86</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.88</v>
+        <v>2.47</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-03 15:00:00</t>
+          <t>2026-01-04 15:00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C18" t="n">
+        <v>26</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K18" t="n">
+        <v>57</v>
+      </c>
+      <c r="L18" t="n">
+        <v>53</v>
+      </c>
+      <c r="M18" t="n">
+        <v>24</v>
+      </c>
+      <c r="N18" t="n">
         <v>20</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Brighton &amp; Hove Albion</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K18" t="n">
-        <v>84</v>
-      </c>
-      <c r="L18" t="n">
-        <v>73</v>
-      </c>
-      <c r="M18" t="n">
-        <v>33</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6</v>
-      </c>
       <c r="O18" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="P18" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="S18" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T18" t="n">
         <v>4.2</v>
       </c>
-      <c r="T18" t="n">
-        <v>6.2</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="W18" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="X18" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.4</v>
+        <v>3.22</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.24</v>
+        <v>2.55</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-03 15:00:00</t>
+          <t>2026-01-04 15:00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.11</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="I19" t="n">
-        <v>1.14</v>
+        <v>1.54</v>
       </c>
       <c r="J19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K19" t="n">
+        <v>79</v>
+      </c>
+      <c r="L19" t="n">
+        <v>68</v>
+      </c>
+      <c r="M19" t="n">
+        <v>32</v>
+      </c>
+      <c r="N19" t="n">
+        <v>21</v>
+      </c>
+      <c r="O19" t="n">
+        <v>79</v>
+      </c>
+      <c r="P19" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>37</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2.29</v>
       </c>
-      <c r="K19" t="n">
-        <v>56</v>
-      </c>
-      <c r="L19" t="n">
-        <v>62</v>
-      </c>
-      <c r="M19" t="n">
-        <v>45</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>95</v>
-      </c>
-      <c r="P19" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>44</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W19" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-03 15:15:00</t>
+          <t>2026-01-04 15:00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>0.83</v>
       </c>
       <c r="G20" t="n">
-        <v>0.88</v>
+        <v>1.31</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I20" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="J20" t="n">
-        <v>2.87</v>
+        <v>2.72</v>
       </c>
       <c r="K20" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L20" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="M20" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="N20" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="O20" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="P20" t="n">
         <v>44</v>
       </c>
       <c r="Q20" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R20" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.95</v>
+        <v>3.41</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="U20" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="V20" t="n">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="W20" t="n">
-        <v>4.5</v>
+        <v>3.12</v>
       </c>
       <c r="X20" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.14</v>
+        <v>1.74</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-03 15:15:00</t>
+          <t>2026-01-04 15:00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2759,108 +2759,108 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="G21" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H21" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="I21" t="n">
-        <v>0.92</v>
+        <v>1.11</v>
       </c>
       <c r="J21" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="K21" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L21" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="M21" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N21" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="O21" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="P21" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q21" t="n">
         <v>56</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>3.94</v>
+        <v>3.15</v>
       </c>
       <c r="T21" t="n">
-        <v>5.7</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="W21" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="X21" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AA21" t="n">
         <v>2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="AF21" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-03 15:15:00</t>
+          <t>2026-01-04 15:00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2868,866 +2868,866 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1.89</v>
       </c>
       <c r="G22" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="H22" t="n">
-        <v>2.12</v>
+        <v>1.66</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="J22" t="n">
-        <v>3.22</v>
+        <v>2.84</v>
       </c>
       <c r="K22" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="L22" t="n">
+        <v>73</v>
+      </c>
+      <c r="M22" t="n">
+        <v>22</v>
+      </c>
+      <c r="N22" t="n">
+        <v>22</v>
+      </c>
+      <c r="O22" t="n">
+        <v>78</v>
+      </c>
+      <c r="P22" t="n">
         <v>67</v>
       </c>
-      <c r="M22" t="n">
+      <c r="Q22" t="n">
         <v>33</v>
       </c>
-      <c r="N22" t="n">
-        <v>33</v>
-      </c>
-      <c r="O22" t="n">
-        <v>67</v>
-      </c>
-      <c r="P22" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>39</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="S22" t="n">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="W22" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-03 15:30:00</t>
+          <t>2026-01-04 15:00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.29</v>
+        <v>0.89</v>
       </c>
       <c r="G23" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="I23" t="n">
-        <v>0.87</v>
+        <v>1.04</v>
       </c>
       <c r="J23" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="K23" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L23" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M23" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N23" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="O23" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="P23" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="Q23" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="R23" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="S23" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
         <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="X23" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.99</v>
+        <v>2.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.62</v>
+        <v>1.69</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AF23" t="n">
         <v>2.62</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-03 16:00:00</t>
+          <t>2026-01-04 15:00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="G24" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="H24" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="I24" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="J24" t="n">
-        <v>2.86</v>
+        <v>3.04</v>
       </c>
       <c r="K24" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L24" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="M24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N24" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="O24" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="P24" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="Q24" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="R24" t="n">
-        <v>1.92</v>
+        <v>3.55</v>
       </c>
       <c r="S24" t="n">
         <v>3.85</v>
       </c>
       <c r="T24" t="n">
-        <v>3.47</v>
+        <v>1.95</v>
       </c>
       <c r="U24" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="V24" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="W24" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="X24" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.38</v>
+        <v>2.97</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-03 17:00:00</t>
+          <t>2026-01-04 15:05:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.25</v>
+        <v>0.25</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>2.1</v>
+        <v>1.13</v>
       </c>
       <c r="I25" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="J25" t="n">
-        <v>3.15</v>
+        <v>2.44</v>
       </c>
       <c r="K25" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="L25" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M25" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="N25" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O25" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="P25" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q25" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>3.5</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="T25" t="n">
-        <v>10</v>
+        <v>2.03</v>
       </c>
       <c r="U25" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="V25" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="W25" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="X25" t="n">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.51</v>
+        <v>2.08</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AF25" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-01-03 17:30:00</t>
+          <t>2026-01-04 15:15:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>18</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="K26" t="n">
+        <v>57</v>
+      </c>
+      <c r="L26" t="n">
+        <v>63</v>
+      </c>
+      <c r="M26" t="n">
+        <v>26</v>
+      </c>
+      <c r="N26" t="n">
         <v>13</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Al Ittihad</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Al Taawon</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="K26" t="n">
-        <v>47</v>
-      </c>
-      <c r="L26" t="n">
-        <v>82</v>
-      </c>
-      <c r="M26" t="n">
-        <v>55</v>
-      </c>
-      <c r="N26" t="n">
-        <v>19</v>
-      </c>
       <c r="O26" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="P26" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Q26" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="R26" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="S26" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="T26" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="V26" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="W26" t="n">
-        <v>2.58</v>
+        <v>2.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="AF26" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-01-03 17:30:00</t>
+          <t>2026-01-04 15:15:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>2.11</v>
       </c>
       <c r="G27" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="I27" t="n">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="J27" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="K27" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L27" t="n">
         <v>64</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N27" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="O27" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="P27" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q27" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R27" t="n">
-        <v>3.1</v>
+        <v>1.99</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2</v>
+        <v>3.63</v>
       </c>
       <c r="U27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="W27" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-01-03 17:30:00</t>
+          <t>2026-01-04 15:30:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.78</v>
+        <v>0.86</v>
       </c>
       <c r="G28" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="I28" t="n">
-        <v>1.62</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>3.22</v>
+        <v>2.01</v>
       </c>
       <c r="K28" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L28" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="M28" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="N28" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="O28" t="n">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="P28" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="Q28" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="R28" t="n">
-        <v>5.2</v>
+        <v>2.35</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="T28" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="W28" t="n">
-        <v>2.56</v>
+        <v>4.92</v>
       </c>
       <c r="X28" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="Y28" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.44</v>
+        <v>1.92</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC28" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE28" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="AF28" t="n">
-        <v>3.3</v>
+        <v>2.34</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-01-03 17:30:00</t>
+          <t>2026-01-04 16:15:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G29" t="n">
-        <v>1.89</v>
+        <v>0.29</v>
       </c>
       <c r="H29" t="n">
-        <v>1.96</v>
+        <v>1.59</v>
       </c>
       <c r="I29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K29" t="n">
+        <v>47</v>
+      </c>
+      <c r="L29" t="n">
+        <v>73</v>
+      </c>
+      <c r="M29" t="n">
+        <v>53</v>
+      </c>
+      <c r="N29" t="n">
+        <v>26</v>
+      </c>
+      <c r="O29" t="n">
+        <v>75</v>
+      </c>
+      <c r="P29" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>48</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.41</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="K29" t="n">
-        <v>70</v>
-      </c>
-      <c r="L29" t="n">
-        <v>79</v>
-      </c>
-      <c r="M29" t="n">
-        <v>32</v>
-      </c>
-      <c r="N29" t="n">
-        <v>20</v>
-      </c>
-      <c r="O29" t="n">
-        <v>80</v>
-      </c>
-      <c r="P29" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>41</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-01-03 18:00:00</t>
+          <t>2026-01-04 16:15:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3740,94 +3740,94 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="G30" t="n">
-        <v>0.88</v>
+        <v>0.38</v>
       </c>
       <c r="H30" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="I30" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>2.51</v>
       </c>
       <c r="K30" t="n">
+        <v>69</v>
+      </c>
+      <c r="L30" t="n">
+        <v>82</v>
+      </c>
+      <c r="M30" t="n">
         <v>57</v>
       </c>
-      <c r="L30" t="n">
-        <v>75</v>
-      </c>
-      <c r="M30" t="n">
-        <v>38</v>
-      </c>
       <c r="N30" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="O30" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="P30" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="Q30" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="R30" t="n">
-        <v>2.78</v>
+        <v>1.74</v>
       </c>
       <c r="S30" t="n">
-        <v>3.41</v>
+        <v>3.72</v>
       </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="U30" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="V30" t="n">
         <v>1.79</v>
       </c>
       <c r="W30" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z30" t="n">
         <v>2.22</v>
       </c>
-      <c r="Z30" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AA30" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC30" t="n">
         <v>2.33</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="AF30" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AG30" t="n">
         <v>1.44</v>
@@ -3836,12 +3836,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-01-03 18:00:00</t>
+          <t>2026-01-04 16:15:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3849,588 +3849,588 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="G31" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="I31" t="n">
-        <v>1.81</v>
+        <v>0.85</v>
       </c>
       <c r="J31" t="n">
-        <v>3.32</v>
+        <v>2.41</v>
       </c>
       <c r="K31" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="L31" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="M31" t="n">
+        <v>13</v>
+      </c>
+      <c r="N31" t="n">
         <v>51</v>
       </c>
-      <c r="N31" t="n">
-        <v>19</v>
-      </c>
       <c r="O31" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="P31" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="Q31" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="R31" t="n">
-        <v>6.74</v>
+        <v>2.07</v>
       </c>
       <c r="S31" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>1.44</v>
+        <v>3.59</v>
       </c>
       <c r="U31" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="W31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.89</v>
       </c>
-      <c r="W31" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.98</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-01-03 18:00:00</t>
+          <t>2026-01-04 17:00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>0.86</v>
       </c>
       <c r="G32" t="n">
-        <v>0.71</v>
+        <v>1.13</v>
       </c>
       <c r="H32" t="n">
-        <v>1.94</v>
+        <v>1.49</v>
       </c>
       <c r="I32" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="J32" t="n">
-        <v>3.41</v>
+        <v>2.77</v>
       </c>
       <c r="K32" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L32" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="M32" t="n">
+        <v>41</v>
+      </c>
+      <c r="N32" t="n">
+        <v>40</v>
+      </c>
+      <c r="O32" t="n">
+        <v>61</v>
+      </c>
+      <c r="P32" t="n">
         <v>54</v>
       </c>
-      <c r="N32" t="n">
-        <v>14</v>
-      </c>
-      <c r="O32" t="n">
-        <v>87</v>
-      </c>
-      <c r="P32" t="n">
-        <v>61</v>
-      </c>
       <c r="Q32" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>2.62</v>
       </c>
       <c r="S32" t="n">
-        <v>5.8</v>
+        <v>2.97</v>
       </c>
       <c r="T32" t="n">
-        <v>14</v>
+        <v>2.84</v>
       </c>
       <c r="U32" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="V32" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="W32" t="n">
-        <v>2.15</v>
+        <v>4.45</v>
       </c>
       <c r="X32" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.63</v>
+        <v>2.06</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="AF32" t="n">
-        <v>3.34</v>
+        <v>2.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-01-03 19:45:00</t>
+          <t>2026-01-04 17:30:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
       <c r="G33" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="H33" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="J33" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="K33" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="L33" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="M33" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="N33" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="O33" t="n">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="P33" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="Q33" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="R33" t="n">
+        <v>11</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE33" t="n">
         <v>2.15</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V33" t="n">
-        <v>2</v>
-      </c>
-      <c r="W33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>3.04</v>
-      </c>
       <c r="AF33" t="n">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-01-03 20:00:00</t>
+          <t>2026-01-04 17:30:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="G34" t="n">
-        <v>2.11</v>
+        <v>0.2</v>
       </c>
       <c r="H34" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="I34" t="n">
-        <v>2.19</v>
+        <v>1.05</v>
       </c>
       <c r="J34" t="n">
-        <v>3.67</v>
+        <v>2.86</v>
       </c>
       <c r="K34" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L34" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="M34" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="N34" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O34" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="P34" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="Q34" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="R34" t="n">
-        <v>6</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="T34" t="n">
-        <v>1.46</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="U34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W34" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-01-03 20:00:00</t>
+          <t>2026-01-04 17:30:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="G35" t="n">
-        <v>1.78</v>
+        <v>0.5</v>
       </c>
       <c r="H35" t="n">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="I35" t="n">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="J35" t="n">
-        <v>2.78</v>
+        <v>2.22</v>
       </c>
       <c r="K35" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="L35" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="M35" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="N35" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O35" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="P35" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q35" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="R35" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="S35" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="T35" t="n">
-        <v>3.91</v>
+        <v>5.2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="V35" t="n">
-        <v>2.35</v>
+        <v>2.81</v>
       </c>
       <c r="W35" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="X35" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AE35" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-01-03 20:05:00</t>
+          <t>2026-01-04 17:30:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="G36" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="H36" t="n">
-        <v>1.69</v>
+        <v>1.23</v>
       </c>
       <c r="I36" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="J36" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="K36" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="L36" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="M36" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="N36" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="O36" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="P36" t="n">
         <v>51</v>
@@ -4439,270 +4439,1033 @@
         <v>51</v>
       </c>
       <c r="R36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="W36" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Y36" t="n">
         <v>1.85</v>
       </c>
-      <c r="S36" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="T36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z36" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.3</v>
+        <v>3.28</v>
       </c>
       <c r="AF36" t="n">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-01-03 20:30:00</t>
+          <t>2026-01-04 17:30:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>2.67</v>
       </c>
       <c r="G37" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="H37" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="I37" t="n">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="J37" t="n">
-        <v>2.85</v>
+        <v>3.49</v>
       </c>
       <c r="K37" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L37" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="M37" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="N37" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="O37" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="P37" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="Q37" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="R37" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="S37" t="n">
-        <v>3.55</v>
+        <v>4.15</v>
       </c>
       <c r="T37" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="U37" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="V37" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="W37" t="n">
-        <v>3.35</v>
+        <v>2.35</v>
       </c>
       <c r="X37" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.97</v>
+        <v>2.48</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.77</v>
+        <v>3.84</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-01-03 20:30:00</t>
+          <t>2026-01-04 17:30:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>20</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Real Zaragoza</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>UD Las Palmas</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K38" t="n">
+        <v>39</v>
+      </c>
+      <c r="L38" t="n">
+        <v>39</v>
+      </c>
+      <c r="M38" t="n">
+        <v>11</v>
+      </c>
+      <c r="N38" t="n">
+        <v>50</v>
+      </c>
+      <c r="O38" t="n">
+        <v>50</v>
+      </c>
+      <c r="P38" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>73</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W38" t="n">
+        <v>5</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-01-04 17:30:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>20</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Albacete Balompié</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Leganés</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K39" t="n">
+        <v>58</v>
+      </c>
+      <c r="L39" t="n">
+        <v>48</v>
+      </c>
+      <c r="M39" t="n">
+        <v>16</v>
+      </c>
+      <c r="N39" t="n">
+        <v>26</v>
+      </c>
+      <c r="O39" t="n">
+        <v>74</v>
+      </c>
+      <c r="P39" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>52</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W39" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-01-04 18:00:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Portugal Liga NOS</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C40" t="n">
         <v>17</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>AVS</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Moreirense FC</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K40" t="n">
+        <v>32</v>
+      </c>
+      <c r="L40" t="n">
+        <v>63</v>
+      </c>
+      <c r="M40" t="n">
+        <v>25</v>
+      </c>
+      <c r="N40" t="n">
+        <v>32</v>
+      </c>
+      <c r="O40" t="n">
+        <v>69</v>
+      </c>
+      <c r="P40" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>51</v>
+      </c>
+      <c r="R40" t="n">
+        <v>8</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W40" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-01-04 19:45:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>17</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="G41" t="n">
         <v>1</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H41" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K41" t="n">
+        <v>39</v>
+      </c>
+      <c r="L41" t="n">
+        <v>73</v>
+      </c>
+      <c r="M41" t="n">
+        <v>40</v>
+      </c>
+      <c r="N41" t="n">
+        <v>34</v>
+      </c>
+      <c r="O41" t="n">
+        <v>67</v>
+      </c>
+      <c r="P41" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>54</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S41" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>13</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-01-04 19:45:00</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>18</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Inter Milan</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="K42" t="n">
+        <v>44</v>
+      </c>
+      <c r="L42" t="n">
+        <v>69</v>
+      </c>
+      <c r="M42" t="n">
+        <v>38</v>
+      </c>
+      <c r="N42" t="n">
+        <v>19</v>
+      </c>
+      <c r="O42" t="n">
+        <v>82</v>
+      </c>
+      <c r="P42" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>38</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-01-04 20:00:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>18</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
         <v>1.25</v>
       </c>
-      <c r="I38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="K38" t="n">
-        <v>51</v>
-      </c>
-      <c r="L38" t="n">
-        <v>76</v>
-      </c>
-      <c r="M38" t="n">
-        <v>38</v>
-      </c>
-      <c r="N38" t="n">
+      <c r="G43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K43" t="n">
+        <v>66</v>
+      </c>
+      <c r="L43" t="n">
+        <v>71</v>
+      </c>
+      <c r="M43" t="n">
+        <v>47</v>
+      </c>
+      <c r="N43" t="n">
+        <v>24</v>
+      </c>
+      <c r="O43" t="n">
+        <v>77</v>
+      </c>
+      <c r="P43" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>46</v>
+      </c>
+      <c r="R43" t="n">
+        <v>4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V43" t="n">
+        <v>2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-01-04 20:00:00</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>20</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruña</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K44" t="n">
+        <v>44</v>
+      </c>
+      <c r="L44" t="n">
+        <v>61</v>
+      </c>
+      <c r="M44" t="n">
+        <v>17</v>
+      </c>
+      <c r="N44" t="n">
+        <v>33</v>
+      </c>
+      <c r="O44" t="n">
+        <v>67</v>
+      </c>
+      <c r="P44" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>50</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-01-04 20:30:00</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>17</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K45" t="n">
+        <v>34</v>
+      </c>
+      <c r="L45" t="n">
+        <v>66</v>
+      </c>
+      <c r="M45" t="n">
         <v>19</v>
       </c>
-      <c r="O38" t="n">
-        <v>82</v>
-      </c>
-      <c r="P38" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>44</v>
-      </c>
-      <c r="R38" t="n">
-        <v>3</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="W38" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.3</v>
+      <c r="N45" t="n">
+        <v>41</v>
+      </c>
+      <c r="O45" t="n">
+        <v>59</v>
+      </c>
+      <c r="P45" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>68</v>
+      </c>
+      <c r="R45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W45" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG4" headerRowCount="1">
-  <autoFilter ref="A1:AG4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG7" headerRowCount="1">
+  <autoFilter ref="A1:AG7"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AG7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="26.4" customWidth="1" min="2" max="2"/>
+    <col width="28.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="19.2" customWidth="1" min="4" max="4"/>
-    <col width="26.4" customWidth="1" min="5" max="5"/>
+    <col width="20.4" customWidth="1" min="4" max="4"/>
+    <col width="22.8" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,328 +675,655 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-05 18:00:00</t>
+          <t>2026-01-06 14:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="K2" t="n">
         <v>17</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Benfica II</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Porto II</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="K2" t="n">
-        <v>46</v>
-      </c>
       <c r="L2" t="n">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="M2" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="O2" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="P2" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="R2" t="n">
-        <v>1.73</v>
+        <v>4.9</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="X2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z2" t="n">
         <v>1.68</v>
       </c>
-      <c r="Y2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.68</v>
-      </c>
       <c r="AA2" t="n">
-        <v>2.61</v>
+        <v>1.51</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.19</v>
+        <v>1.91</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.44</v>
+        <v>2.87</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AE2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2.62</v>
       </c>
-      <c r="AF2" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AG2" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-05 20:00:00</t>
+          <t>2026-01-06 17:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.58</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.67</v>
       </c>
       <c r="H3" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="I3" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="J3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K3" t="n">
+        <v>33</v>
+      </c>
+      <c r="L3" t="n">
         <v>61</v>
       </c>
-      <c r="L3" t="n">
-        <v>85</v>
-      </c>
       <c r="M3" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="O3" t="n">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="P3" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q3" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="R3" t="n">
-        <v>2.32</v>
+        <v>5.2</v>
       </c>
       <c r="S3" t="n">
-        <v>3.34</v>
+        <v>3.47</v>
       </c>
       <c r="T3" t="n">
-        <v>2.94</v>
+        <v>1.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="V3" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="W3" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="X3" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.71</v>
+        <v>2.37</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-05 20:15:00</t>
+          <t>2026-01-06 19:45:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>1.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K4" t="n">
+        <v>78</v>
+      </c>
+      <c r="L4" t="n">
+        <v>73</v>
+      </c>
+      <c r="M4" t="n">
+        <v>39</v>
+      </c>
+      <c r="N4" t="n">
+        <v>11</v>
+      </c>
+      <c r="O4" t="n">
+        <v>89</v>
+      </c>
+      <c r="P4" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>28</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-06 19:45:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L5" t="n">
+        <v>73</v>
+      </c>
+      <c r="M5" t="n">
+        <v>28</v>
+      </c>
+      <c r="N5" t="n">
+        <v>33</v>
+      </c>
+      <c r="O5" t="n">
+        <v>67</v>
+      </c>
+      <c r="P5" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>67</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-06 20:00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="K6" t="n">
+        <v>45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>75</v>
+      </c>
+      <c r="M6" t="n">
+        <v>40</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15</v>
+      </c>
+      <c r="O6" t="n">
+        <v>85</v>
+      </c>
+      <c r="P6" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>45</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-06 20:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K7" t="n">
+        <v>35</v>
+      </c>
+      <c r="L7" t="n">
+        <v>55</v>
+      </c>
+      <c r="M7" t="n">
+        <v>15</v>
+      </c>
+      <c r="N7" t="n">
+        <v>40</v>
+      </c>
+      <c r="O7" t="n">
+        <v>60</v>
+      </c>
+      <c r="P7" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>70</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1.65</v>
       </c>
-      <c r="I4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K4" t="n">
-        <v>34</v>
-      </c>
-      <c r="L4" t="n">
-        <v>53</v>
-      </c>
-      <c r="M4" t="n">
-        <v>14</v>
-      </c>
-      <c r="N4" t="n">
-        <v>40</v>
-      </c>
-      <c r="O4" t="n">
-        <v>61</v>
-      </c>
-      <c r="P4" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>60</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.33</v>
+      <c r="AD7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG7" headerRowCount="1">
-  <autoFilter ref="A1:AG7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG14" headerRowCount="1">
+  <autoFilter ref="A1:AG14"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG7"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="28.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="20.4" customWidth="1" min="4" max="4"/>
-    <col width="22.8" customWidth="1" min="5" max="5"/>
+    <col width="21.6" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,7 +675,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-06 14:00:00</t>
+          <t>2026-01-07 17:30:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -688,103 +688,103 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.67</v>
+        <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>1.72</v>
       </c>
       <c r="I2" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="J2" t="n">
-        <v>2.51</v>
+        <v>3.09</v>
       </c>
       <c r="K2" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="L2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="N2" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="Q2" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="R2" t="n">
-        <v>4.9</v>
+        <v>2.69</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="T2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X2" t="n">
         <v>1.72</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Y2" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.68</v>
+        <v>2.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.87</v>
+        <v>2.41</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-06 17:00:00</t>
+          <t>2026-01-07 17:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -797,321 +797,321 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2.71</v>
       </c>
       <c r="G3" t="n">
-        <v>1.67</v>
+        <v>0.67</v>
       </c>
       <c r="H3" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="I3" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="J3" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="K3" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="L3" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="M3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N3" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="O3" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="P3" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="Q3" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="R3" t="n">
-        <v>5.2</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>3.47</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="U3" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="W3" t="n">
-        <v>4.3</v>
+        <v>3.67</v>
       </c>
       <c r="X3" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.44</v>
+        <v>2.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-06 19:45:00</t>
+          <t>2026-01-07 19:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="I4" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="J4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L4" t="n">
+        <v>75</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20</v>
+      </c>
+      <c r="N4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>75</v>
+      </c>
+      <c r="P4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.65</v>
       </c>
-      <c r="K4" t="n">
-        <v>78</v>
-      </c>
-      <c r="L4" t="n">
-        <v>73</v>
-      </c>
-      <c r="M4" t="n">
-        <v>39</v>
-      </c>
-      <c r="N4" t="n">
-        <v>11</v>
-      </c>
-      <c r="O4" t="n">
-        <v>89</v>
-      </c>
-      <c r="P4" t="n">
-        <v>73</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>28</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.47</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="W4" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="X4" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.69</v>
+        <v>3.06</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-06 19:45:00</t>
+          <t>2026-01-07 19:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.56</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="I5" t="n">
-        <v>1.46</v>
+        <v>0.97</v>
       </c>
       <c r="J5" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="K5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N5" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="O5" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="P5" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q5" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="R5" t="n">
-        <v>4.6</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.73</v>
+        <v>5.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="W5" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="X5" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AC5" t="n">
         <v>2.04</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.63</v>
+        <v>3.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.84</v>
+        <v>2.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-06 20:00:00</t>
+          <t>2026-01-07 19:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1124,206 +1124,969 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H6" t="n">
-        <v>1.22</v>
+        <v>1.92</v>
       </c>
       <c r="I6" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="J6" t="n">
-        <v>2.41</v>
+        <v>3.36</v>
       </c>
       <c r="K6" t="n">
+        <v>50</v>
+      </c>
+      <c r="L6" t="n">
+        <v>90</v>
+      </c>
+      <c r="M6" t="n">
         <v>45</v>
       </c>
-      <c r="L6" t="n">
-        <v>75</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>95</v>
+      </c>
+      <c r="P6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q6" t="n">
         <v>40</v>
       </c>
-      <c r="N6" t="n">
-        <v>15</v>
-      </c>
-      <c r="O6" t="n">
-        <v>85</v>
-      </c>
-      <c r="P6" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>45</v>
-      </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>3.55</v>
+        <v>5.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3</v>
+        <v>6.97</v>
       </c>
       <c r="U6" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="V6" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>3.35</v>
+        <v>2.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Y6" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-06 20:00:00</t>
+          <t>2026-01-07 19:30:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="I7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K7" t="n">
+        <v>45</v>
+      </c>
+      <c r="L7" t="n">
+        <v>60</v>
+      </c>
+      <c r="M7" t="n">
+        <v>40</v>
+      </c>
+      <c r="N7" t="n">
+        <v>30</v>
+      </c>
+      <c r="O7" t="n">
+        <v>70</v>
+      </c>
+      <c r="P7" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>45</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.21</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>35</v>
-      </c>
-      <c r="L7" t="n">
-        <v>55</v>
-      </c>
-      <c r="M7" t="n">
-        <v>15</v>
-      </c>
-      <c r="N7" t="n">
-        <v>40</v>
-      </c>
-      <c r="O7" t="n">
-        <v>60</v>
-      </c>
-      <c r="P7" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>70</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.18</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="W7" t="n">
-        <v>2.61</v>
+        <v>2.9</v>
       </c>
       <c r="X7" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.01</v>
+        <v>2.27</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.13</v>
+        <v>2.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AD7" t="n">
         <v>1.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-07 19:30:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>21</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>70</v>
+      </c>
+      <c r="M8" t="n">
+        <v>35</v>
+      </c>
+      <c r="N8" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" t="n">
+        <v>70</v>
+      </c>
+      <c r="P8" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>45</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-07 19:30:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>21</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="K9" t="n">
+        <v>50</v>
+      </c>
+      <c r="L9" t="n">
+        <v>60</v>
+      </c>
+      <c r="M9" t="n">
+        <v>30</v>
+      </c>
+      <c r="N9" t="n">
+        <v>35</v>
+      </c>
+      <c r="O9" t="n">
+        <v>65</v>
+      </c>
+      <c r="P9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>60</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-07 19:45:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>19</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K10" t="n">
+        <v>56</v>
+      </c>
+      <c r="L10" t="n">
+        <v>95</v>
+      </c>
+      <c r="M10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N10" t="n">
+        <v>28</v>
+      </c>
+      <c r="O10" t="n">
+        <v>73</v>
+      </c>
+      <c r="P10" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>45</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-07 19:45:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K11" t="n">
+        <v>33</v>
+      </c>
+      <c r="L11" t="n">
+        <v>56</v>
+      </c>
+      <c r="M11" t="n">
+        <v>33</v>
+      </c>
+      <c r="N11" t="n">
+        <v>33</v>
+      </c>
+      <c r="O11" t="n">
+        <v>67</v>
+      </c>
+      <c r="P11" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>67</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-01-07 19:45:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Inter Milan</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="K12" t="n">
+        <v>47</v>
+      </c>
+      <c r="L12" t="n">
+        <v>66</v>
+      </c>
+      <c r="M12" t="n">
+        <v>30</v>
+      </c>
+      <c r="N12" t="n">
+        <v>35</v>
+      </c>
+      <c r="O12" t="n">
+        <v>66</v>
+      </c>
+      <c r="P12" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>59</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-01-07 20:15:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>21</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K13" t="n">
+        <v>60</v>
+      </c>
+      <c r="L13" t="n">
+        <v>75</v>
+      </c>
+      <c r="M13" t="n">
+        <v>35</v>
+      </c>
+      <c r="N13" t="n">
+        <v>15</v>
+      </c>
+      <c r="O13" t="n">
+        <v>85</v>
+      </c>
+      <c r="P13" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>50</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-07 20:15:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>21</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K14" t="n">
+        <v>60</v>
+      </c>
+      <c r="L14" t="n">
+        <v>65</v>
+      </c>
+      <c r="M14" t="n">
+        <v>30</v>
+      </c>
+      <c r="N14" t="n">
+        <v>15</v>
+      </c>
+      <c r="O14" t="n">
+        <v>85</v>
+      </c>
+      <c r="P14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>40</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG14" headerRowCount="1">
-  <autoFilter ref="A1:AG14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG8" headerRowCount="1">
+  <autoFilter ref="A1:AG8"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG14"/>
+  <dimension ref="A1:AG8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
-    <col width="28.8" customWidth="1" min="2" max="2"/>
+    <col width="40.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="21.6" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22.8" customWidth="1" min="4" max="4"/>
+    <col width="16.8" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,552 +675,552 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-07 17:30:00</t>
+          <t>2026-01-08 14:55:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>2.67</v>
       </c>
       <c r="G2" t="n">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="H2" t="n">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
       <c r="I2" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="J2" t="n">
-        <v>3.09</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="L2" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="O2" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="P2" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q2" t="n">
         <v>38</v>
       </c>
-      <c r="Q2" t="n">
-        <v>63</v>
-      </c>
       <c r="R2" t="n">
-        <v>2.69</v>
+        <v>1.09</v>
       </c>
       <c r="S2" t="n">
-        <v>3.41</v>
+        <v>7.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.47</v>
+        <v>13.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-07 17:30:00</t>
+          <t>2026-01-08 17:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.67</v>
+        <v>1.67</v>
       </c>
       <c r="H3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="K3" t="n">
+        <v>67</v>
+      </c>
+      <c r="L3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P3" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.54</v>
       </c>
-      <c r="I3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K3" t="n">
-        <v>58</v>
-      </c>
-      <c r="L3" t="n">
-        <v>69</v>
-      </c>
-      <c r="M3" t="n">
-        <v>24</v>
-      </c>
-      <c r="N3" t="n">
-        <v>26</v>
-      </c>
-      <c r="O3" t="n">
-        <v>75</v>
-      </c>
-      <c r="P3" t="n">
-        <v>64</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>37</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.41</v>
-      </c>
       <c r="S3" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>7.4</v>
+        <v>4.55</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-07 19:30:00</t>
+          <t>2026-01-08 17:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.48</v>
+        <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="J4" t="n">
-        <v>2.76</v>
+        <v>2.33</v>
       </c>
       <c r="K4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L4" t="n">
         <v>60</v>
-      </c>
-      <c r="L4" t="n">
-        <v>75</v>
       </c>
       <c r="M4" t="n">
         <v>20</v>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="P4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="W4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-07 19:30:00</t>
+          <t>2026-01-08 17:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
         <v>0.97</v>
       </c>
       <c r="J5" t="n">
-        <v>2.44</v>
+        <v>2.01</v>
       </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="L5" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="M5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="O5" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="P5" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>2.21</v>
       </c>
       <c r="S5" t="n">
-        <v>3.75</v>
+        <v>3.17</v>
       </c>
       <c r="T5" t="n">
-        <v>5.4</v>
+        <v>3.31</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="W5" t="n">
-        <v>3.56</v>
+        <v>4.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.67</v>
+        <v>2.48</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-07 19:30:00</t>
+          <t>2026-01-08 19:45:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="I6" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="J6" t="n">
-        <v>3.36</v>
+        <v>2.85</v>
       </c>
       <c r="K6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="L6" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="O6" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="P6" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="Q6" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R6" t="n">
         <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="T6" t="n">
-        <v>6.97</v>
+        <v>7.6</v>
       </c>
       <c r="U6" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="W6" t="n">
-        <v>2.09</v>
+        <v>3.44</v>
       </c>
       <c r="X6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.57</v>
       </c>
-      <c r="Y6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AC6" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.06</v>
+        <v>2.93</v>
       </c>
       <c r="AF6" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.74</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-07 19:30:00</t>
+          <t>2026-01-08 20:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1233,860 +1233,206 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="K7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L7" t="n">
+        <v>70</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="n">
+        <v>90</v>
+      </c>
+      <c r="P7" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>30</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1.8</v>
       </c>
-      <c r="H7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="K7" t="n">
-        <v>45</v>
-      </c>
-      <c r="L7" t="n">
-        <v>60</v>
-      </c>
-      <c r="M7" t="n">
-        <v>40</v>
-      </c>
-      <c r="N7" t="n">
-        <v>30</v>
-      </c>
-      <c r="O7" t="n">
-        <v>70</v>
-      </c>
-      <c r="P7" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>45</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-07 19:30:00</t>
+          <t>2026-01-08 20:15:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="I8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K8" t="n">
+        <v>66</v>
+      </c>
+      <c r="L8" t="n">
+        <v>66</v>
+      </c>
+      <c r="M8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N8" t="n">
+        <v>13</v>
+      </c>
+      <c r="O8" t="n">
+        <v>88</v>
+      </c>
+      <c r="P8" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>60</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.48</v>
       </c>
-      <c r="J8" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="K8" t="n">
-        <v>55</v>
-      </c>
-      <c r="L8" t="n">
-        <v>70</v>
-      </c>
-      <c r="M8" t="n">
-        <v>35</v>
-      </c>
-      <c r="N8" t="n">
-        <v>30</v>
-      </c>
-      <c r="O8" t="n">
-        <v>70</v>
-      </c>
-      <c r="P8" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>45</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2.5</v>
       </c>
-      <c r="AF8" t="n">
-        <v>3.12</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-01-07 19:30:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>England Premier League</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>21</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Brentford</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Sunderland</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
         <v>1.31</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="K9" t="n">
-        <v>50</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-      <c r="M9" t="n">
-        <v>30</v>
-      </c>
-      <c r="N9" t="n">
-        <v>35</v>
-      </c>
-      <c r="O9" t="n">
-        <v>65</v>
-      </c>
-      <c r="P9" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>60</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-01-07 19:45:00</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Italy Serie A</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>19</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K10" t="n">
-        <v>56</v>
-      </c>
-      <c r="L10" t="n">
-        <v>95</v>
-      </c>
-      <c r="M10" t="n">
-        <v>50</v>
-      </c>
-      <c r="N10" t="n">
-        <v>28</v>
-      </c>
-      <c r="O10" t="n">
-        <v>73</v>
-      </c>
-      <c r="P10" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>45</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-01-07 19:45:00</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Italy Serie A</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>19</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="K11" t="n">
-        <v>33</v>
-      </c>
-      <c r="L11" t="n">
-        <v>56</v>
-      </c>
-      <c r="M11" t="n">
-        <v>33</v>
-      </c>
-      <c r="N11" t="n">
-        <v>33</v>
-      </c>
-      <c r="O11" t="n">
-        <v>67</v>
-      </c>
-      <c r="P11" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>67</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="W11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-01-07 19:45:00</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Italy Serie A</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>19</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Inter Milan</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="K12" t="n">
-        <v>47</v>
-      </c>
-      <c r="L12" t="n">
-        <v>66</v>
-      </c>
-      <c r="M12" t="n">
-        <v>30</v>
-      </c>
-      <c r="N12" t="n">
-        <v>35</v>
-      </c>
-      <c r="O12" t="n">
-        <v>66</v>
-      </c>
-      <c r="P12" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>59</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-01-07 20:15:00</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>England Premier League</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>21</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="K13" t="n">
-        <v>60</v>
-      </c>
-      <c r="L13" t="n">
-        <v>75</v>
-      </c>
-      <c r="M13" t="n">
-        <v>35</v>
-      </c>
-      <c r="N13" t="n">
-        <v>15</v>
-      </c>
-      <c r="O13" t="n">
-        <v>85</v>
-      </c>
-      <c r="P13" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-01-07 20:15:00</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>England Premier League</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>21</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Newcastle United</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Leeds United</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="K14" t="n">
-        <v>60</v>
-      </c>
-      <c r="L14" t="n">
-        <v>65</v>
-      </c>
-      <c r="M14" t="n">
-        <v>30</v>
-      </c>
-      <c r="N14" t="n">
-        <v>15</v>
-      </c>
-      <c r="O14" t="n">
-        <v>85</v>
-      </c>
-      <c r="P14" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>40</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T14" t="n">
-        <v>5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG8" headerRowCount="1">
-  <autoFilter ref="A1:AG8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG16" headerRowCount="1">
+  <autoFilter ref="A1:AG16"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG8"/>
+  <dimension ref="A1:AG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="40.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="22.8" customWidth="1" min="4" max="4"/>
-    <col width="16.8" customWidth="1" min="5" max="5"/>
+    <col width="25.2" customWidth="1" min="4" max="4"/>
+    <col width="22.8" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,7 +675,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-08 14:55:00</t>
+          <t>2026-01-09 13:10:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -688,103 +688,103 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.67</v>
+        <v>1.4</v>
       </c>
       <c r="G2" t="n">
-        <v>1.71</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.21</v>
+        <v>1.36</v>
       </c>
       <c r="I2" t="n">
-        <v>1.19</v>
+        <v>0.89</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="K2" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="L2" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="M2" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N2" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="O2" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="P2" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q2" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.09</v>
+        <v>1.85</v>
       </c>
       <c r="S2" t="n">
-        <v>7.25</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>13.5</v>
+        <v>3.8</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-08 17:30:00</t>
+          <t>2026-01-09 15:05:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -797,103 +797,103 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="G3" t="n">
-        <v>1.67</v>
+        <v>0.5</v>
       </c>
       <c r="H3" t="n">
-        <v>2.41</v>
+        <v>1.19</v>
       </c>
       <c r="I3" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="J3" t="n">
-        <v>3.84</v>
+        <v>2.21</v>
       </c>
       <c r="K3" t="n">
+        <v>42</v>
+      </c>
+      <c r="L3" t="n">
         <v>67</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N3" t="n">
+        <v>25</v>
+      </c>
+      <c r="O3" t="n">
         <v>75</v>
       </c>
-      <c r="M3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N3" t="n">
-        <v>9</v>
-      </c>
-      <c r="O3" t="n">
-        <v>92</v>
-      </c>
       <c r="P3" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q3" t="n">
         <v>75</v>
       </c>
-      <c r="Q3" t="n">
-        <v>25</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-08 17:30:00</t>
+          <t>2026-01-09 17:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -906,355 +906,355 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="H4" t="n">
-        <v>0.96</v>
+        <v>1.32</v>
       </c>
       <c r="I4" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="J4" t="n">
-        <v>2.33</v>
+        <v>2.96</v>
       </c>
       <c r="K4" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="L4" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="M4" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="N4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="P4" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-08 17:30:00</t>
+          <t>2026-01-09 19:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.13</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="I5" t="n">
-        <v>0.97</v>
+        <v>1.64</v>
       </c>
       <c r="J5" t="n">
-        <v>2.01</v>
+        <v>3.41</v>
       </c>
       <c r="K5" t="n">
         <v>65</v>
       </c>
       <c r="L5" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="M5" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O5" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P5" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="R5" t="n">
-        <v>2.21</v>
+        <v>2.87</v>
       </c>
       <c r="S5" t="n">
-        <v>3.17</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>3.31</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>2.17</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="X5" t="n">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.16</v>
+        <v>1.71</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.34</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.48</v>
+        <v>3.36</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-08 19:45:00</t>
+          <t>2026-01-09 19:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.22</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="I6" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="K6" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="L6" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="M6" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="O6" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="P6" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>4.2</v>
       </c>
       <c r="S6" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>7.6</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>3.44</v>
+        <v>2.35</v>
       </c>
       <c r="X6" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.93</v>
+        <v>2.19</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.8</v>
+        <v>3.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-08 20:00:00</t>
+          <t>2026-01-09 19:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="I7" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="J7" t="n">
-        <v>3.43</v>
+        <v>3.09</v>
       </c>
       <c r="K7" t="n">
         <v>60</v>
@@ -1263,176 +1263,1048 @@
         <v>70</v>
       </c>
       <c r="M7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="O7" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="P7" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V7" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="W7" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="X7" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-08 20:15:00</t>
+          <t>2026-01-09 19:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="K8" t="n">
+        <v>50</v>
+      </c>
+      <c r="L8" t="n">
+        <v>55</v>
+      </c>
+      <c r="M8" t="n">
+        <v>30</v>
+      </c>
+      <c r="N8" t="n">
+        <v>25</v>
+      </c>
+      <c r="O8" t="n">
+        <v>75</v>
+      </c>
+      <c r="P8" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>45</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-09 19:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>18</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NEC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="K9" t="n">
+        <v>69</v>
+      </c>
+      <c r="L9" t="n">
+        <v>88</v>
+      </c>
+      <c r="M9" t="n">
+        <v>44</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>94</v>
+      </c>
+      <c r="P9" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>32</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-09 19:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>22</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L10" t="n">
+        <v>80</v>
+      </c>
+      <c r="M10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20</v>
+      </c>
+      <c r="O10" t="n">
+        <v>80</v>
+      </c>
+      <c r="P10" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>35</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-09 19:30:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K11" t="n">
+        <v>53</v>
+      </c>
+      <c r="L11" t="n">
+        <v>73</v>
+      </c>
+      <c r="M11" t="n">
+        <v>34</v>
+      </c>
+      <c r="N11" t="n">
+        <v>21</v>
+      </c>
+      <c r="O11" t="n">
+        <v>80</v>
+      </c>
+      <c r="P11" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>60</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-01-09 19:30:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>21</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sporting Gijón</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K12" t="n">
+        <v>42</v>
+      </c>
+      <c r="L12" t="n">
+        <v>59</v>
+      </c>
+      <c r="M12" t="n">
+        <v>26</v>
+      </c>
+      <c r="N12" t="n">
+        <v>47</v>
+      </c>
+      <c r="O12" t="n">
+        <v>53</v>
+      </c>
+      <c r="P12" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>58</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-01-09 20:00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>19</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K13" t="n">
+        <v>58</v>
+      </c>
+      <c r="L13" t="n">
+        <v>52</v>
+      </c>
+      <c r="M13" t="n">
+        <v>18</v>
+      </c>
+      <c r="N13" t="n">
+        <v>36</v>
+      </c>
+      <c r="O13" t="n">
+        <v>64</v>
+      </c>
+      <c r="P13" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>78</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-10 03:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mexico Liga MX</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tijuana</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>América</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K14" t="n">
+        <v>54</v>
+      </c>
+      <c r="L14" t="n">
+        <v>75</v>
+      </c>
+      <c r="M14" t="n">
+        <v>31</v>
+      </c>
+      <c r="N14" t="n">
+        <v>13</v>
+      </c>
+      <c r="O14" t="n">
+        <v>87</v>
+      </c>
+      <c r="P14" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>44</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-01-10 03:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mexico Liga MX</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="K8" t="n">
-        <v>66</v>
-      </c>
-      <c r="L8" t="n">
-        <v>66</v>
-      </c>
-      <c r="M8" t="n">
-        <v>25</v>
-      </c>
-      <c r="N8" t="n">
-        <v>13</v>
-      </c>
-      <c r="O8" t="n">
-        <v>88</v>
-      </c>
-      <c r="P8" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>60</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>76</v>
+      </c>
+      <c r="M15" t="n">
+        <v>50</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15</v>
+      </c>
+      <c r="O15" t="n">
+        <v>85</v>
+      </c>
+      <c r="P15" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>35</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Y15" t="n">
         <v>2.01</v>
       </c>
-      <c r="AD8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG8" t="n">
+      <c r="Z15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-10 03:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mexico Liga MX</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mazatlán</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Juárez</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K16" t="n">
+        <v>74</v>
+      </c>
+      <c r="L16" t="n">
+        <v>79</v>
+      </c>
+      <c r="M16" t="n">
+        <v>40</v>
+      </c>
+      <c r="N16" t="n">
+        <v>19</v>
+      </c>
+      <c r="O16" t="n">
+        <v>81</v>
+      </c>
+      <c r="P16" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>40</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.31</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/data/todays_matches/todays_matches.xlsx
+++ b/data/todays_matches/todays_matches.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG16" headerRowCount="1">
-  <autoFilter ref="A1:AG16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:AG48" headerRowCount="1">
+  <autoFilter ref="A1:AG48"/>
   <tableColumns count="33">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="league"/>
@@ -467,14 +467,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG16"/>
+  <dimension ref="A1:AG48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.2" customWidth="1" min="1" max="1"/>
     <col width="40.8" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="25.2" customWidth="1" min="4" max="4"/>
-    <col width="22.8" customWidth="1" min="5" max="5"/>
+    <col width="21.6" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -675,1636 +675,5124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-09 13:10:00</t>
+          <t>2026-01-10 13:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.4</v>
+        <v>0.78</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="H2" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.89</v>
+        <v>1.46</v>
       </c>
       <c r="J2" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="K2" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="L2" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="M2" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="O2" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="P2" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="R2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="X2" t="n">
         <v>1.85</v>
       </c>
-      <c r="S2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.67</v>
-      </c>
       <c r="Y2" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-09 15:05:00</t>
+          <t>2026-01-10 13:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.17</v>
+        <v>0.78</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="I3" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="J3" t="n">
-        <v>2.21</v>
+        <v>2.77</v>
       </c>
       <c r="K3" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="L3" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O3" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="P3" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="Q3" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>3.37</v>
       </c>
       <c r="S3" t="n">
         <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>2.09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V3" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="W3" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="X3" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.39</v>
+        <v>2.11</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-09 17:30:00</t>
+          <t>2026-01-10 14:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="I4" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="J4" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="K4" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="L4" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M4" t="n">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="O4" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="P4" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="Q4" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="R4" t="n">
-        <v>6.7</v>
+        <v>2.39</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>2.79</v>
       </c>
       <c r="T4" t="n">
-        <v>1.39</v>
+        <v>3.41</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.41</v>
+        <v>4.2</v>
       </c>
       <c r="X4" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.29</v>
+        <v>3.34</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-09 19:00:00</t>
+          <t>2026-01-10 14:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="n">
         <v>1.77</v>
       </c>
       <c r="I5" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="J5" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="L5" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="M5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O5" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="P5" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="Q5" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="R5" t="n">
-        <v>2.87</v>
+        <v>2.04</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Y5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE5" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AF5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.43</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-09 19:00:00</t>
+          <t>2026-01-10 14:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Virtus Entella</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="K6" t="n">
+        <v>62</v>
+      </c>
+      <c r="L6" t="n">
+        <v>67</v>
+      </c>
+      <c r="M6" t="n">
+        <v>17</v>
+      </c>
+      <c r="N6" t="n">
         <v>22</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MVV</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Almere City</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="K6" t="n">
-        <v>65</v>
-      </c>
-      <c r="L6" t="n">
-        <v>75</v>
-      </c>
-      <c r="M6" t="n">
-        <v>45</v>
-      </c>
-      <c r="N6" t="n">
-        <v>25</v>
-      </c>
       <c r="O6" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P6" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="Q6" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="R6" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W6" t="n">
         <v>4.2</v>
       </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.35</v>
-      </c>
       <c r="X6" t="n">
-        <v>1.48</v>
+        <v>1.99</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.19</v>
+        <v>3.34</v>
       </c>
       <c r="AF6" t="n">
-        <v>3.52</v>
+        <v>2.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-09 19:00:00</t>
+          <t>2026-01-10 14:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.9</v>
+        <v>1.44</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="H7" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>1.35</v>
+        <v>0.99</v>
       </c>
       <c r="J7" t="n">
-        <v>3.09</v>
+        <v>2.54</v>
       </c>
       <c r="K7" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="L7" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="M7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N7" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="O7" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="P7" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="R7" t="n">
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="W7" t="n">
-        <v>2.65</v>
+        <v>3.62</v>
       </c>
       <c r="X7" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.49</v>
+        <v>2.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.16</v>
+        <v>2.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-09 19:00:00</t>
+          <t>2026-01-10 14:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>0.33</v>
       </c>
       <c r="H8" t="n">
-        <v>1.84</v>
+        <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2</v>
+        <v>1.31</v>
       </c>
       <c r="J8" t="n">
-        <v>4.04</v>
+        <v>2.48</v>
       </c>
       <c r="K8" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="L8" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="M8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O8" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Q8" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="R8" t="n">
-        <v>3.89</v>
+        <v>2.96</v>
       </c>
       <c r="S8" t="n">
-        <v>4.06</v>
+        <v>2.94</v>
       </c>
       <c r="T8" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="U8" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="W8" t="n">
-        <v>2.19</v>
+        <v>4.2</v>
       </c>
       <c r="X8" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.17</v>
+        <v>3.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.52</v>
+        <v>2.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-09 19:00:00</t>
+          <t>2026-01-10 14:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.75</v>
+        <v>1.22</v>
       </c>
       <c r="H9" t="n">
-        <v>1.76</v>
+        <v>1.38</v>
       </c>
       <c r="I9" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.29</v>
+        <v>3.18</v>
       </c>
       <c r="K9" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L9" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="M9" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P9" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="R9" t="n">
-        <v>2.02</v>
+        <v>5.2</v>
       </c>
       <c r="S9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="U9" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="W9" t="n">
-        <v>2.19</v>
+        <v>3.24</v>
       </c>
       <c r="X9" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.21</v>
+        <v>1.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>4</v>
+        <v>2.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-09 19:00:00</t>
+          <t>2026-01-10 14:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>0.83</v>
       </c>
       <c r="H10" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="I10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K10" t="n">
+        <v>75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>67</v>
+      </c>
+      <c r="M10" t="n">
+        <v>42</v>
+      </c>
+      <c r="N10" t="n">
+        <v>25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>75</v>
+      </c>
+      <c r="P10" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>42</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.53</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>50</v>
-      </c>
-      <c r="L10" t="n">
-        <v>80</v>
-      </c>
-      <c r="M10" t="n">
-        <v>50</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20</v>
-      </c>
-      <c r="O10" t="n">
-        <v>80</v>
-      </c>
-      <c r="P10" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>35</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.61</v>
-      </c>
       <c r="Y10" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.33</v>
+        <v>2.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-09 19:30:00</t>
+          <t>2026-01-10 14:00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="G11" t="n">
-        <v>1.88</v>
+        <v>0.67</v>
       </c>
       <c r="H11" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="I11" t="n">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="K11" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="L11" t="n">
         <v>73</v>
       </c>
       <c r="M11" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="N11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O11" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="P11" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="Q11" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R11" t="n">
-        <v>3.26</v>
+        <v>1.86</v>
       </c>
       <c r="S11" t="n">
-        <v>3.64</v>
+        <v>3.21</v>
       </c>
       <c r="T11" t="n">
-        <v>2.05</v>
+        <v>4.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="W11" t="n">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.53</v>
       </c>
-      <c r="Y11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AE11" t="n">
-        <v>2.39</v>
+        <v>3.34</v>
       </c>
       <c r="AF11" t="n">
-        <v>3.24</v>
+        <v>2.48</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-09 19:30:00</t>
+          <t>2026-01-10 14:00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="G12" t="n">
         <v>1.33</v>
       </c>
       <c r="H12" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="I12" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="J12" t="n">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
       <c r="K12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L12" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N12" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="O12" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="P12" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q12" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="R12" t="n">
-        <v>2.53</v>
+        <v>2.11</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>3.52</v>
       </c>
       <c r="U12" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="W12" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="X12" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-09 20:00:00</t>
+          <t>2026-01-10 14:30:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
         <v>1.38</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.78</v>
-      </c>
       <c r="H13" t="n">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="I13" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="J13" t="n">
-        <v>2.69</v>
+        <v>3.06</v>
       </c>
       <c r="K13" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="L13" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="M13" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="N13" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="O13" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="P13" t="n">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="Q13" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="U13" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="W13" t="n">
-        <v>6.1</v>
+        <v>2.84</v>
       </c>
       <c r="X13" t="n">
-        <v>2.39</v>
+        <v>1.65</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.47</v>
+        <v>1.97</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>4.2</v>
+        <v>2.63</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.19</v>
+        <v>3.12</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-10 03:00:00</t>
+          <t>2026-01-10 14:30:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mexico Liga MX</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>América</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="G14" t="n">
-        <v>1.95</v>
+        <v>0.29</v>
       </c>
       <c r="H14" t="n">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="I14" t="n">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="K14" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="L14" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M14" t="n">
-